--- a/clientes/files/TODITICO_CATÁLOGO.xlsx
+++ b/clientes/files/TODITICO_CATÁLOGO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\510 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\520 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6BE2AA4-59A2-4FA4-8676-1E393FD5C68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B448C6-95EB-4BCE-B7FE-09CA9B6946D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="16536" windowHeight="9432" tabRatio="671" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DAEWOO TICO" sheetId="1" r:id="rId1"/>
@@ -148,24 +148,12 @@
     <t>BOMBA AGUA PICANTO 2DA Y 3RA</t>
   </si>
   <si>
-    <t xml:space="preserve">CONDENSADOR  ATOS
-</t>
-  </si>
-  <si>
     <t>CONDENSADOR PICANTO 1RA [04-07]</t>
   </si>
   <si>
     <t>CONDENSADOR PICANTO 1RA[08-11]</t>
   </si>
   <si>
-    <t xml:space="preserve">CONDENSADOR PICANTO  2DA
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONDENSADOR PICANTO 3RA
-</t>
-  </si>
-  <si>
     <t>CORREA DE LOS AGREGADOS PICANTO 1RA [4PK0780]</t>
   </si>
   <si>
@@ -214,14 +202,6 @@
     <t>DEFENSA TRASERA PICANTO 3RA</t>
   </si>
   <si>
-    <t xml:space="preserve">ELECTROVENTILADOR PICANTO  2DA
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELECTROVENTILADOR PICANTO 3RA
-</t>
-  </si>
-  <si>
     <t>FILTRO DE AIRE PICANTO 1RA</t>
   </si>
   <si>
@@ -2049,10 +2029,6 @@
     <t>PARABRISAS ATOS (97-03)</t>
   </si>
   <si>
-    <t xml:space="preserve">RADIADOR MECANICO ATOS
-</t>
-  </si>
-  <si>
     <t>BATERIAS 110 Ah</t>
   </si>
   <si>
@@ -2357,6 +2333,24 @@
   </si>
   <si>
     <t>PUNTAS DE HOMOCINÉTICAS EXTERIORES ATOS 1.0 PAREJA</t>
+  </si>
+  <si>
+    <t>CONDENSADOR  ATOS</t>
+  </si>
+  <si>
+    <t>RADIADOR MECANICO ATOS</t>
+  </si>
+  <si>
+    <t>CONDENSADOR PICANTO  2DA</t>
+  </si>
+  <si>
+    <t>CONDENSADOR PICANTO 3RA</t>
+  </si>
+  <si>
+    <t>ELECTROVENTILADOR PICANTO  2DA</t>
+  </si>
+  <si>
+    <t>ELECTROVENTILADOR PICANTO 3RA</t>
   </si>
 </sst>
 </file>
@@ -2859,9 +2853,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B361"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="83.88671875" customWidth="1"/>
+    <col min="1" max="1" width="83.85546875" customWidth="1"/>
     <col min="2" max="2" width="11" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2870,1111 +2864,1111 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B2" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B3" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B4" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="B5" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="B6" s="1">
-        <v>3570</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="B7" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B8" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B9" s="1">
-        <v>45900</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B10" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B11" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B12" s="1">
-        <v>81600</v>
+        <v>83200</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B13" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B14" s="1">
-        <v>76500</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B15" s="1">
-        <v>56100</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="B16" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B17" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B18" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="B19" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="B20" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B21" s="1">
-        <v>1530</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B22" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B23" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="B24" s="1">
-        <v>25500</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B25" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B26" s="1">
-        <v>45900</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B27" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B28" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B29" s="1">
-        <v>76500</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B30" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B31" s="1">
-        <v>81600</v>
+        <v>83200</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B32" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B33" s="1">
-        <v>22950</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="B34" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="B35" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="B36" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B37" s="1">
-        <v>40800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B38" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="B39" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="B40" s="1">
-        <v>56100</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="B41" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B42" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B43" s="1">
-        <v>25500</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="B44" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="B45" s="1">
-        <v>22950</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="B46" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B47" s="1">
-        <v>40800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B48" s="1">
-        <v>22950</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B49" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B50" s="1">
-        <v>22950</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="B51" s="1">
-        <v>510</v>
+        <v>520</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B52" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B53" s="1">
-        <v>510</v>
+        <v>520</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="4" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B54" s="1">
-        <v>510</v>
+        <v>520</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="4" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="B55" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B56" s="1">
-        <v>45900</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B57" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B58" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="B59" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="B60" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B61" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B62" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B63" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B64" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B65" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B66" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B67" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B68" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B69" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B70" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B71" s="1">
-        <v>1020</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B72" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B73" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B74" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="B75" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B76" s="1">
-        <v>3570</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B77" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B78" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B79" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B80" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B81" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B82" s="1">
-        <v>22950</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B83" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B84" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="B85" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B86" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="B87" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B88" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B89" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B90" s="1">
-        <v>22950</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B91" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B92" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B93" s="1">
-        <v>178500</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B94" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B95" s="1">
-        <v>153000</v>
+        <v>156000</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B96" s="1">
-        <v>25500</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="B97" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="B98" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="4" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B99" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B100" s="1">
-        <v>22950</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B101" s="1">
-        <v>40800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B102" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B103" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B104" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B105" s="1">
-        <v>22950</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="B106" s="1">
-        <v>127500</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="B107" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B108" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B109" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B110" s="1">
-        <v>22950</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="B111" s="1">
-        <v>25500</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="B112" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="B113" s="1">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B114" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="B115" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B116" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="B117" s="1">
-        <v>1020</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B118" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B119" s="1">
-        <v>3570</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B120" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B121" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B122" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B123" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B124" s="1">
-        <v>76500</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B125" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="B126" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="B127" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B128" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B129" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="B130" s="1">
-        <v>219300</v>
+        <v>223600</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B131" s="1">
-        <v>91800</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="B132" s="1">
-        <v>3570</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B133" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="4" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="B134" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B135" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B136" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B137" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B138" s="1">
-        <v>40800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B139" s="1">
-        <v>127500</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -3982,1775 +3976,1775 @@
         <v>14</v>
       </c>
       <c r="B140" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="B141" s="1">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B142" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="B143" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B144" s="1">
-        <v>25500</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B145" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B146" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="B147" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B148" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B149" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B150" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B151" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B152" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B153" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B154" s="1">
-        <v>45900</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B155" s="1">
-        <v>25500</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B156" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B157" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="B158" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B159" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B160" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="B161" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="B162" s="1">
-        <v>1530</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="B163" s="1">
-        <v>1530</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="B164" s="1">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="B165" s="1">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B166" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B167" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="B168" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="B169" s="1">
-        <v>2040</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="B170" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B171" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B172" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B173" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B174" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B175" s="1">
-        <v>3570</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B176" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B177" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B178" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B179" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B180" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="B181" s="1">
-        <v>3570</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="B182" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="B183" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="B184" s="1">
-        <v>3570</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="B185" s="1">
-        <v>3570</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="B186" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B187" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B188" s="1">
-        <v>1020</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B189" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="B190" s="1">
-        <v>25500</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B191" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="B192" s="1">
-        <v>76500</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B193" s="1">
-        <v>45900</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="B194" s="1">
-        <v>1530</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B195" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B196" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B197" s="1">
-        <v>204000</v>
+        <v>208000</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B198" s="1">
-        <v>280500</v>
+        <v>286000</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="B199" s="1">
-        <v>285600</v>
+        <v>291200</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B200" s="1">
-        <v>3060</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="B201" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="B202" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B203" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B204" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B205" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="206" spans="1:2">
       <c r="A206" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B206" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B207" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B208" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B209" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="210" spans="1:2">
       <c r="A210" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B210" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B211" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B212" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="213" spans="1:2">
       <c r="A213" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B213" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="B214" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B215" s="1">
-        <v>25500</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="216" spans="1:2">
       <c r="A216" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="B216" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="B217" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B218" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="219" spans="1:2">
       <c r="A219" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B219" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B220" s="1">
-        <v>142800</v>
+        <v>145600</v>
       </c>
     </row>
     <row r="221" spans="1:2">
       <c r="A221" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B221" s="1">
-        <v>76500</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="B222" s="1">
-        <v>33150</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B223" s="1">
-        <v>40800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="224" spans="1:2">
       <c r="A224" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B224" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="B225" s="1">
-        <v>76500</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="226" spans="1:2">
       <c r="A226" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B226" s="1">
-        <v>76500</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="B227" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="B228" s="1">
-        <v>33150</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="B229" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="B230" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="B231" s="1">
-        <v>3570</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="232" spans="1:2">
       <c r="A232" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B232" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="B233" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="234" spans="1:2">
       <c r="A234" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B234" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B235" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="236" spans="1:2">
       <c r="A236" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B236" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="237" spans="1:2">
       <c r="A237" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B237" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B238" s="1">
-        <v>153000</v>
+        <v>156000</v>
       </c>
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B239" s="1">
-        <v>153000</v>
+        <v>156000</v>
       </c>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B240" s="1">
-        <v>81600</v>
+        <v>83200</v>
       </c>
     </row>
     <row r="241" spans="1:2">
       <c r="A241" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="B241" s="1">
-        <v>127500</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="242" spans="1:2">
       <c r="A242" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B242" s="1">
-        <v>56100</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="243" spans="1:2">
       <c r="A243" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B243" s="1">
-        <v>81600</v>
+        <v>83200</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B244" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="245" spans="1:2">
       <c r="A245" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="B245" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="246" spans="1:2">
       <c r="A246" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B246" s="1">
-        <v>86700</v>
+        <v>88400</v>
       </c>
     </row>
     <row r="247" spans="1:2">
       <c r="A247" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B247" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="248" spans="1:2">
       <c r="A248" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B248" s="1">
-        <v>102000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="249" spans="1:2">
       <c r="A249" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B249" s="1">
-        <v>45900</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="B250" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B251" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="252" spans="1:2">
       <c r="A252" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B252" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B253" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="254" spans="1:2">
       <c r="A254" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="B254" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="B255" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="B256" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="B257" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B258" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B259" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="260" spans="1:2">
       <c r="A260" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B260" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="261" spans="1:2">
       <c r="A261" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="B261" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="262" spans="1:2">
       <c r="A262" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B262" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="263" spans="1:2">
       <c r="A263" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B263" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="264" spans="1:2">
       <c r="A264" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="B264" s="1">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="265" spans="1:2">
       <c r="A265" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B265" s="1">
-        <v>76500</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="266" spans="1:2">
       <c r="A266" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B266" s="1">
-        <v>153000</v>
+        <v>156000</v>
       </c>
     </row>
     <row r="267" spans="1:2">
       <c r="A267" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="B267" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B268" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B269" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="270" spans="1:2">
       <c r="A270" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B270" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="271" spans="1:2">
       <c r="A271" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="B271" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B272" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B273" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="274" spans="1:2">
       <c r="A274" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B274" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B275" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="276" spans="1:2">
       <c r="A276" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B276" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="277" spans="1:2">
       <c r="A277" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B277" s="1">
-        <v>66300</v>
+        <v>67600</v>
       </c>
     </row>
     <row r="278" spans="1:2">
       <c r="A278" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B278" s="1">
-        <v>102000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="279" spans="1:2">
       <c r="A279" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B279" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="280" spans="1:2">
       <c r="A280" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B280" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="281" spans="1:2">
       <c r="A281" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="B281" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="282" spans="1:2">
       <c r="A282" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="B282" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="283" spans="1:2">
       <c r="A283" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="B283" s="1">
-        <v>48450</v>
+        <v>49400</v>
       </c>
     </row>
     <row r="284" spans="1:2">
       <c r="A284" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="B284" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="B285" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B286" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="287" spans="1:2">
       <c r="A287" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="B287" s="1">
-        <v>3570</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B288" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B289" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="290" spans="1:2">
       <c r="A290" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B290" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="291" spans="1:2">
       <c r="A291" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B291" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="292" spans="1:2">
       <c r="A292" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B292" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="293" spans="1:2">
       <c r="A293" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B293" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="294" spans="1:2">
       <c r="A294" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B294" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="295" spans="1:2">
       <c r="A295" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B295" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="296" spans="1:2">
       <c r="A296" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B296" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="297" spans="1:2">
       <c r="A297" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B297" s="1">
-        <v>3060</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="B298" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B299" s="1">
-        <v>76500</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="300" spans="1:2">
       <c r="A300" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B300" s="1">
-        <v>91800</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="301" spans="1:2">
       <c r="A301" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B301" s="1">
-        <v>45900</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="302" spans="1:2">
       <c r="A302" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B302" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="303" spans="1:2">
       <c r="A303" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B303" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="304" spans="1:2">
       <c r="A304" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B304" s="1">
-        <v>2040</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="305" spans="1:2">
       <c r="A305" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="B305" s="1">
-        <v>1020</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="306" spans="1:2">
       <c r="A306" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="B306" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="307" spans="1:2">
       <c r="A307" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B307" s="1">
-        <v>38250</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="308" spans="1:2">
       <c r="A308" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B308" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="309" spans="1:2">
       <c r="A309" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B309" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="310" spans="1:2">
       <c r="A310" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="B310" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="311" spans="1:2">
       <c r="A311" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B311" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B312" s="1">
-        <v>127500</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="313" spans="1:2">
       <c r="A313" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B313" s="1">
-        <v>280500</v>
+        <v>286000</v>
       </c>
     </row>
     <row r="314" spans="1:2">
       <c r="A314" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B314" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="315" spans="1:2">
       <c r="A315" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B315" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B316" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="317" spans="1:2">
       <c r="A317" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B317" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="318" spans="1:2">
       <c r="A318" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B318" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="B319" s="1">
-        <v>2040</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="320" spans="1:2">
       <c r="A320" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B320" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="B321" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B322" s="1">
-        <v>3570</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="323" spans="1:2">
       <c r="A323" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B323" s="1">
-        <v>22950</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B324" s="1">
-        <v>2040</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="325" spans="1:2">
       <c r="A325" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B325" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="326" spans="1:2">
       <c r="A326" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B326" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="327" spans="1:2">
       <c r="A327" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B327" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B328" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B329" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="330" spans="1:2">
       <c r="A330" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="B330" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B331" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="332" spans="1:2">
       <c r="A332" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="B332" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="B333" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B334" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B335" s="1">
-        <v>3570</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="336" spans="1:2">
       <c r="A336" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B336" s="1">
-        <v>3060</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="337" spans="1:2">
       <c r="A337" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B337" s="1">
-        <v>1020</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="338" spans="1:2">
       <c r="A338" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B338" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="339" spans="1:2">
       <c r="A339" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B339" s="1">
-        <v>1530</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="A340" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B340" s="1">
-        <v>2040</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="341" spans="1:2">
       <c r="A341" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B341" s="1">
-        <v>1530</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="342" spans="1:2">
       <c r="A342" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="B342" s="1">
-        <v>3570</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="A343" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="B343" s="1">
-        <v>1530</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="344" spans="1:2">
       <c r="A344" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B344" s="1">
-        <v>1020</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="345" spans="1:2">
       <c r="A345" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="B345" s="1">
-        <v>91800</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="346" spans="1:2">
       <c r="A346" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="B346" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="347" spans="1:2">
       <c r="A347" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="B347" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="348" spans="1:2">
       <c r="A348" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="B348" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="349" spans="1:2">
       <c r="A349" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="B349" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="350" spans="1:2">
       <c r="A350" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B350" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="351" spans="1:2">
       <c r="A351" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B351" s="1">
-        <v>22950</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="352" spans="1:2">
       <c r="A352" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="B352" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="353" spans="1:2">
       <c r="A353" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B353" s="1">
-        <v>1530</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="354" spans="1:2">
       <c r="A354" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B354" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="355" spans="1:2">
       <c r="A355" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="B355" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="356" spans="1:2">
       <c r="A356" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="B356" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="357" spans="1:2">
       <c r="A357" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="B357" s="1">
-        <v>102000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="358" spans="1:2">
       <c r="A358" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="B358" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="359" spans="1:2">
       <c r="A359" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="B359" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="360" spans="1:2">
       <c r="A360" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B360" s="1">
-        <v>2040</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="361" spans="1:2">
       <c r="A361" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B361" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
   </sheetData>
@@ -5761,9 +5755,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B129"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="64.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="64.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5772,55 +5766,55 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="B2" s="1">
-        <v>71400</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="6" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B3" s="1">
-        <v>102000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="7" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="B4" s="1">
-        <v>91800</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="7" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B5" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="7" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="B6" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="8" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="B7" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -5828,23 +5822,23 @@
         <v>5</v>
       </c>
       <c r="B8" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B9" s="1">
-        <v>40800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="10" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B10" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -5852,47 +5846,47 @@
         <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="10" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B12" s="1">
-        <v>40800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="10" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B13" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="9" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="B14" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="B15" s="1">
-        <v>56100</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="11" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="B16" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -5900,23 +5894,23 @@
         <v>6</v>
       </c>
       <c r="B17" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B18" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="5" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B19" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -5924,71 +5918,71 @@
         <v>36</v>
       </c>
       <c r="B20" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="B21" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="5" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="B22" s="1">
-        <v>40800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="5" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="B23" s="1">
-        <v>510</v>
+        <v>520</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="5" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B24" s="1">
-        <v>510</v>
+        <v>520</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="5" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B25" s="1">
-        <v>510</v>
+        <v>520</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="5" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="B26" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="5" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="B27" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="5" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="B28" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -5996,7 +5990,7 @@
         <v>12</v>
       </c>
       <c r="B29" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6004,7 +5998,7 @@
         <v>1</v>
       </c>
       <c r="B30" s="1">
-        <v>1275</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6012,15 +6006,15 @@
         <v>7</v>
       </c>
       <c r="B31" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="5" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="B32" s="1">
-        <v>3570</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6028,87 +6022,87 @@
         <v>2</v>
       </c>
       <c r="B33" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="5" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="B34" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="5" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="B35" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="5" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="B36" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="7" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B37" s="1">
-        <v>25500</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="13" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B38" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="11" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="B39" s="1">
-        <v>25500</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="5" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="B40" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="5" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="B41" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="9" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="B42" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="5" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="B43" s="1">
-        <v>25500</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6116,47 +6110,47 @@
         <v>29</v>
       </c>
       <c r="B44" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>39</v>
+        <v>768</v>
       </c>
       <c r="B45" s="1">
-        <v>71400</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="7" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="B46" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="14" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B47" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="7" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B48" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="13" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="B49" s="1">
-        <v>102000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -6164,15 +6158,15 @@
         <v>30</v>
       </c>
       <c r="B50" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B51" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -6180,15 +6174,15 @@
         <v>8</v>
       </c>
       <c r="B52" s="1">
-        <v>76500</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="5" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B53" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -6196,15 +6190,15 @@
         <v>13</v>
       </c>
       <c r="B54" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="16" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B55" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -6212,47 +6206,47 @@
         <v>14</v>
       </c>
       <c r="B56" s="1">
-        <v>66300</v>
+        <v>67600</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="16" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B57" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="17" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="B58" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="5" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="B59" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="5" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B60" s="1">
-        <v>28050</v>
+        <v>28600</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="10" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="B61" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -6260,7 +6254,7 @@
         <v>15</v>
       </c>
       <c r="B62" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -6268,39 +6262,39 @@
         <v>16</v>
       </c>
       <c r="B63" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="18" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="B64" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="10" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="B65" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="10" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B66" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="5" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="B67" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -6308,7 +6302,7 @@
         <v>3</v>
       </c>
       <c r="B68" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -6316,31 +6310,31 @@
         <v>17</v>
       </c>
       <c r="B69" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="5" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B70" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="5" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="B71" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="9" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B72" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -6348,15 +6342,15 @@
         <v>9</v>
       </c>
       <c r="B73" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="5" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="B74" s="1">
-        <v>285600</v>
+        <v>291200</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -6364,7 +6358,7 @@
         <v>18</v>
       </c>
       <c r="B75" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -6372,23 +6366,23 @@
         <v>19</v>
       </c>
       <c r="B76" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="10" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="B77" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="5" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="B78" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -6396,103 +6390,103 @@
         <v>25</v>
       </c>
       <c r="B79" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="13" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="B80" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="5" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="B81" s="1">
-        <v>22950</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="5" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="B82" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="5" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B83" s="1">
-        <v>102000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="10" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B84" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="B85" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="11" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="B86" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="17" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="B87" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="17" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="B88" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="17" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="B89" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="21" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B90" s="1">
-        <v>91800</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="5" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="B91" s="1">
-        <v>178500</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -6500,15 +6494,15 @@
         <v>24</v>
       </c>
       <c r="B92" s="1">
-        <v>91800</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="5" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="B93" s="1">
-        <v>127500</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -6516,63 +6510,63 @@
         <v>20</v>
       </c>
       <c r="B94" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="5" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B95" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="10" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="B96" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B97" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="5" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="B98" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="22" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="B99" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="B100" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="B101" s="1">
-        <v>38250</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -6580,111 +6574,111 @@
         <v>21</v>
       </c>
       <c r="B102" s="1">
-        <v>25500</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="5" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="B103" s="1">
-        <v>76500</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="5" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="B104" s="1">
-        <v>76500</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>671</v>
+        <v>769</v>
       </c>
       <c r="B105" s="1">
-        <v>66300</v>
+        <v>67600</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B106" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B107" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B108" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B109" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="B110" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="4" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="B111" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="B112" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="B113" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="B114" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="B115" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -6692,103 +6686,103 @@
         <v>4</v>
       </c>
       <c r="B116" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="B117" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="B118" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="B119" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="B120" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="B121" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B122" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="B123" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="B124" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="B125" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="B126" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="B127" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="B128" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -6796,7 +6790,7 @@
         <v>10</v>
       </c>
       <c r="B129" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
   </sheetData>
@@ -6807,9 +6801,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B259"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="83.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="83.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6818,7 +6812,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -6826,23 +6820,23 @@
         <v>28</v>
       </c>
       <c r="B2" s="1">
-        <v>71400</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="17" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="B3" s="1">
-        <v>3060</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="26" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="B4" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -6850,31 +6844,31 @@
         <v>35</v>
       </c>
       <c r="B5" s="1">
-        <v>71400</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="25" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="B6" s="1">
-        <v>102000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="25" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B7" s="1">
-        <v>102000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="17" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B8" s="1">
-        <v>127500</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -6882,127 +6876,127 @@
         <v>26</v>
       </c>
       <c r="B9" s="1">
-        <v>81600</v>
+        <v>83200</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="B10" s="1">
-        <v>91800</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="17" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B11" s="1">
-        <v>91800</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="17" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B12" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="17" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="B13" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="17" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="B14" s="1">
-        <v>40800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="17" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B15" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="17" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B16" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="17" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="B17" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="17" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="B18" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="27" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B19" s="1">
-        <v>40800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="17" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B20" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="17" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="B21" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="B22" s="1">
-        <v>56100</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="17" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="B23" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B24" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -7010,7 +7004,7 @@
         <v>31</v>
       </c>
       <c r="B25" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -7018,31 +7012,31 @@
         <v>22</v>
       </c>
       <c r="B26" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="17" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B27" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B28" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="17" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="B29" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -7050,15 +7044,15 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>40800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="17" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="B31" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -7066,15 +7060,15 @@
         <v>38</v>
       </c>
       <c r="B32" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="17" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B33" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -7082,367 +7076,367 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>22950</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="17" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="B35" s="1">
-        <v>510</v>
+        <v>520</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="17" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B36" s="1">
-        <v>510</v>
+        <v>520</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="17" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B37" s="1">
-        <v>510</v>
+        <v>520</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="28" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="B38" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="17" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="B39" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="17" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="B40" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="17" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="B41" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="26" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="B42" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="17" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B43" s="1">
-        <v>40800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="17" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B44" s="1">
-        <v>40800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="17" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B45" s="1">
-        <v>40800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="25" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B46" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="17" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B47" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="17" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B48" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="28" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="B49" s="1">
-        <v>3570</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="17" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="B50" s="1">
-        <v>3570</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="17" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B51" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="17" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="B52" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="17" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="B53" s="1">
-        <v>40800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="27" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="B54" s="1">
-        <v>45900</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="17" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B55" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="17" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="B56" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="17" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B57" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="17" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="B58" s="1">
-        <v>38250</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="17" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B59" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="17" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="B60" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="17" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B61" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="17" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B62" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="17" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B63" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="17" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="B64" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="17" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="B65" s="1">
-        <v>25500</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="17" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B66" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="17" t="s">
-        <v>42</v>
+        <v>770</v>
       </c>
       <c r="B67" s="1">
-        <v>81600</v>
+        <v>83200</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B68" s="1">
-        <v>81600</v>
+        <v>83200</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B69" s="1">
-        <v>81600</v>
+        <v>83200</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="17" t="s">
-        <v>43</v>
+        <v>771</v>
       </c>
       <c r="B70" s="1">
-        <v>81600</v>
+        <v>83200</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B71" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B72" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="17" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B73" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="17" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B74" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B75" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="17" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B76" s="1">
-        <v>76500</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="28" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B77" s="1">
-        <v>102000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="17" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="B78" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="29" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B79" s="1">
-        <v>25500</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -7450,7 +7444,7 @@
         <v>32</v>
       </c>
       <c r="B80" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -7458,7 +7452,7 @@
         <v>27</v>
       </c>
       <c r="B81" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -7466,743 +7460,743 @@
         <v>33</v>
       </c>
       <c r="B82" s="1">
-        <v>81600</v>
+        <v>83200</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="17" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B83" s="1">
-        <v>81600</v>
+        <v>83200</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="17" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B84" s="1">
-        <v>127500</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="17" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B85" s="1">
-        <v>127500</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="17" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B86" s="1">
-        <v>117300</v>
+        <v>119600</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="17" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B87" s="1">
-        <v>127500</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="26" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B88" s="1">
-        <v>127500</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="17" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="B89" s="1">
-        <v>127500</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="17" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B90" s="1">
-        <v>76500</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="17" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B91" s="1">
-        <v>102000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="17" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B92" s="1">
-        <v>112200</v>
+        <v>114400</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="17" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B93" s="1">
-        <v>112200</v>
+        <v>114400</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="17" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B94" s="1">
-        <v>112200</v>
+        <v>114400</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="17" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B95" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="17" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="B96" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="17" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="B97" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="17" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="B98" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="30" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B99" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="17" t="s">
-        <v>60</v>
+        <v>772</v>
       </c>
       <c r="B100" s="1">
-        <v>71400</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="17" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="B101" s="1">
-        <v>71400</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="31" t="s">
-        <v>61</v>
+        <v>773</v>
       </c>
       <c r="B102" s="1">
-        <v>91800</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="B103" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="17" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="B104" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="17" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B105" s="1">
-        <v>25500</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="17" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="B106" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="17" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="B107" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="17" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="B108" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="17" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B109" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="17" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B110" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="17" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B111" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="17" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B112" s="1">
-        <v>76500</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="B113" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="B114" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="17" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="B115" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B116" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="17" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B117" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="27" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B118" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="17" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="B119" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="17" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="B120" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="B121" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="17" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="B122" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="17" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="B123" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="17" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B124" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="17" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="B125" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="17" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B126" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="32" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B127" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="17" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B128" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="17" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B129" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="17" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="B130" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="17" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="B131" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="17" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="B132" s="1">
-        <v>71400</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="28" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="B133" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="17" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="B134" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="33" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="B135" s="1">
-        <v>285600</v>
+        <v>291200</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="17" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="B136" s="1">
-        <v>295800</v>
+        <v>301600</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="17" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="B137" s="1">
-        <v>306000</v>
+        <v>312000</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="17" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B138" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="17" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B139" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="B140" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="17" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B141" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="17" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B142" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="17" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B143" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="17" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="17" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="B145" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="17" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B146" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="17" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B147" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="17" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B148" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="17" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="B149" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="17" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="B150" s="1">
-        <v>22950</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="B151" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="17" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B152" s="1">
-        <v>127500</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B153" s="1">
-        <v>102000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="17" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="B154" s="1">
-        <v>38250</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="17" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="B155" s="1">
-        <v>38250</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="17" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B156" s="1">
-        <v>76500</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="17" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B157" s="1">
-        <v>76500</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="17" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B158" s="1">
-        <v>71400</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="17" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B159" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="17" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="B160" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="17" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="B161" s="1">
-        <v>40800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="17" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="B162" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="17" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="B163" s="1">
-        <v>40800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="17" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B164" s="1">
-        <v>765</v>
+        <v>780</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="30" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B165" s="1">
-        <v>102000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B166" s="1">
-        <v>117300</v>
+        <v>119600</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="17" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B167" s="1">
-        <v>178500</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="17" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="B168" s="1">
-        <v>178500</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="17" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="B169" s="1">
-        <v>183600</v>
+        <v>187200</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="17" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="B170" s="1">
-        <v>188700</v>
+        <v>192400</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="17" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="B171" s="1">
-        <v>178500</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="17" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="B172" s="1">
-        <v>178500</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="17" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="B173" s="1">
-        <v>178500</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="17" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="B174" s="1">
-        <v>127500</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -8210,679 +8204,679 @@
         <v>23</v>
       </c>
       <c r="B175" s="1">
-        <v>91800</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="17" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B176" s="1">
-        <v>91800</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="17" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="B177" s="1">
-        <v>102000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="17" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B178" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="17" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B179" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="34" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="B180" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="B181" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="B182" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="17" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="B183" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="17" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="B184" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="17" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B185" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="17" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="B186" s="1">
-        <v>45900</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="17" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B187" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="B188" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B189" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="B190" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="B191" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B192" s="1">
-        <v>22950</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B193" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="B194" s="1">
-        <v>38250</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B195" s="1">
-        <v>22950</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B196" s="1">
-        <v>76500</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="B197" s="1">
-        <v>86700</v>
+        <v>88400</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B198" s="1">
-        <v>81600</v>
+        <v>83200</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B199" s="1">
-        <v>76500</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B200" s="1">
-        <v>102000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" s="4" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="B201" s="1">
-        <v>71400</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="B202" s="1">
-        <v>91800</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B203" s="1">
-        <v>66300</v>
+        <v>67600</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B204" s="1">
-        <v>40800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B205" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="206" spans="1:2">
       <c r="A206" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B206" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B207" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B208" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B209" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="210" spans="1:2">
       <c r="A210" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="B210" s="1">
-        <v>91800</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B211" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B212" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="213" spans="1:2">
       <c r="A213" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B213" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B214" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B215" s="1">
-        <v>127500</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="216" spans="1:2">
       <c r="A216" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B216" s="1">
-        <v>102000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B217" s="1">
-        <v>102000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B218" s="1">
-        <v>76500</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="219" spans="1:2">
       <c r="A219" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B219" s="1">
-        <v>76500</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B220" s="1">
-        <v>91800</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="221" spans="1:2">
       <c r="A221" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B221" s="1">
-        <v>91800</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B222" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B223" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="224" spans="1:2">
       <c r="A224" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B224" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B225" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="226" spans="1:2">
       <c r="A226" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="B226" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B227" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="B228" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B229" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="B230" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B231" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="232" spans="1:2">
       <c r="A232" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B232" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="B233" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="234" spans="1:2">
       <c r="A234" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B234" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B235" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="236" spans="1:2">
       <c r="A236" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="B236" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="237" spans="1:2">
       <c r="A237" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="B237" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="B238" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="B239" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="B240" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="241" spans="1:2">
       <c r="A241" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="B241" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="242" spans="1:2">
       <c r="A242" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B242" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="243" spans="1:2">
       <c r="A243" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B243" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="B244" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="245" spans="1:2">
       <c r="A245" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="B245" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="246" spans="1:2">
       <c r="A246" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="B246" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="247" spans="1:2">
       <c r="A247" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="B247" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="248" spans="1:2">
       <c r="A248" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="B248" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="249" spans="1:2">
       <c r="A249" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="B249" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="B250" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="B251" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="252" spans="1:2">
       <c r="A252" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="B252" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="B253" s="1">
-        <v>117300</v>
+        <v>119600</v>
       </c>
     </row>
     <row r="254" spans="1:2">
       <c r="A254" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="B254" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B255" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="B256" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B257" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B258" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B259" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
   </sheetData>
@@ -8893,10 +8887,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.109375" customWidth="1"/>
-    <col min="2" max="2" width="21.109375" customWidth="1"/>
+    <col min="1" max="1" width="52.140625" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -8904,399 +8898,399 @@
         <v>0</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="35" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="B2" s="1">
-        <v>91800</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="36" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="B3" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="36" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="B4" s="1">
-        <v>56100</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="36" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="B5" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="36" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="B6" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="36" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="B7" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="36" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="B8" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="36" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="B9" s="1">
-        <v>45900</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="36" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="B10" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="36" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="B11" s="1">
-        <v>25500</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="36" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="B12" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="35" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="B13" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="36" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="B14" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="36" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="B15" s="1">
-        <v>25500</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="36" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="B16" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="36" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="B17" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="36" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="B18" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="35" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="B19" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="36" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="B20" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="36" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B21" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="36" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="B22" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="36" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="B23" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="36" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="B24" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="36" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="B25" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="36" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="B26" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="36" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="B27" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="B28">
-        <v>56100</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="B29">
-        <v>306000</v>
+        <v>312000</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="B30">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="B31">
-        <v>45900</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="B32">
-        <v>45900</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="B33">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="B34">
-        <v>183600</v>
+        <v>187200</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="B35">
-        <v>188700</v>
+        <v>192400</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="B36">
-        <v>127500</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="B37">
-        <v>45900</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="B38">
-        <v>25500</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="B39">
-        <v>22950</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="B40">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="B41">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="B42">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B43">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="B44">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="B45">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="B46">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="B47">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="B48">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="B49">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="B50">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
   </sheetData>
@@ -9307,9 +9301,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B79"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.109375" customWidth="1"/>
+    <col min="1" max="1" width="58.140625" customWidth="1"/>
     <col min="2" max="2" width="11" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9318,631 +9312,631 @@
         <v>0</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B2" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B3" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B4" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B5" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="B6" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B7" s="1">
-        <v>17850</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="B8" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="B9" s="1">
-        <v>4590</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="B10" s="1">
-        <v>20400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B11" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B12" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="B13" s="1">
-        <v>4590</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="B14" s="1">
-        <v>3570</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="B15" s="1">
-        <v>3060</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B16" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="B17" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="B18" s="1">
-        <v>94350</v>
+        <v>96200</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="B19" s="1">
-        <v>107100</v>
+        <v>109200</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="B20" s="1">
-        <v>124950</v>
+        <v>127400</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B21" s="1">
-        <v>40800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B22" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="B23" s="1">
-        <v>51000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="B24" s="1">
-        <v>56100</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="B25" s="1">
-        <v>61200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="B26" s="1">
-        <v>71400</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="B27" s="1">
-        <v>84150</v>
+        <v>85800</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="B28" s="1">
-        <v>89250</v>
+        <v>91000</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="B29" s="1">
-        <v>510</v>
+        <v>520</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B30" s="1">
-        <v>510</v>
+        <v>520</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B31" s="1">
-        <v>510</v>
+        <v>520</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="B32" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="B33" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B34" s="1">
-        <v>3570</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="B35" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B36" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B37" s="1">
-        <v>15300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B38" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B39" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="B40" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B41" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B42" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B43" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="B44" s="1">
-        <v>3570</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B45" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B46" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="B47" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="B48" s="1">
-        <v>3060</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="B49" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="B50" s="1">
-        <v>30600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="B51" s="1">
-        <v>33150</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="B52" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="B53" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="B54" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="B55" s="1">
-        <v>40800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="B56" s="1">
-        <v>35700</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="B57" s="1">
-        <v>40800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="B58" s="1">
-        <v>45900</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="B59" s="1">
-        <v>45900</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="B60" s="1">
-        <v>127500</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="B61" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="B62" s="1">
-        <v>9180</v>
+        <v>9360</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B63" s="1">
-        <v>10200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="B64" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="B65" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B66" s="1">
-        <v>3570</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B67" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="B68" s="1">
-        <v>4080</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B69" s="1">
-        <v>6120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="B70" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="B71" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="B72" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="B73" s="1">
-        <v>3570</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="B74" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B75" s="1">
-        <v>5100</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="B76" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="B77" s="1">
-        <v>12750</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="B78" s="1">
-        <v>7650</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="B79" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
     </row>
   </sheetData>

--- a/clientes/files/TODITICO_CATÁLOGO.xlsx
+++ b/clientes/files/TODITICO_CATÁLOGO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\520 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\510 Actual - Con lo nuevo de Mexico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B448C6-95EB-4BCE-B7FE-09CA9B6946D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C1262B-3D57-422E-99DE-8B8F31F69E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DAEWOO TICO" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="824">
   <si>
     <t>DESCRIPCION</t>
   </si>
@@ -1501,9 +1501,6 @@
     <t>AFORADOR ATOS</t>
   </si>
   <si>
-    <t>AROS STD, 0.50 ATOS, PICANTO 1RA, I10</t>
-  </si>
-  <si>
     <t>BOMBA DE COMBUSTIBLE ELECTRICA ATOS</t>
   </si>
   <si>
@@ -1555,9 +1552,6 @@
     <t>OBTURADORES JUEGO ATOS, PICANTO 1RA, I10</t>
   </si>
   <si>
-    <t>PISTONES STD, 0.50 ATOS, PICANTO 1RA, I10</t>
-  </si>
-  <si>
     <t>PORTACARBON DE MOTOR DE ARRANQUE ATOS, PICANTO 1RA, I10</t>
   </si>
   <si>
@@ -1579,9 +1573,6 @@
     <t>TENSOR DE CORREA DE DISTRIBUCION ATOS, PICANTO 1RA, I10.</t>
   </si>
   <si>
-    <t>AROS STD, 0.50 PICANTO 1RA, ATOS, I10</t>
-  </si>
-  <si>
     <t>BOTA DE CREMALLERA PICANTO 1RA Y 2DA</t>
   </si>
   <si>
@@ -1597,12 +1588,6 @@
     <t>ESFERICAS PICANTO 1RA (DE ROSCA)</t>
   </si>
   <si>
-    <t>METALES APOYO STD, 0.50, 0.25 PICANTO 1RA, ATOS, I10</t>
-  </si>
-  <si>
-    <t>PISTONES STD, 0.50 PICANTO 1RA, ATOS, I10</t>
-  </si>
-  <si>
     <t>PORTACARBON DE MOTOR DE ARRANQUE PICANTO 1RA, ATOS, I10</t>
   </si>
   <si>
@@ -1687,15 +1672,6 @@
     <t>REFRIGERANTE AL 30% 5LT</t>
   </si>
   <si>
-    <t>METALES APOYO STD, 0.50, 0.25 ATOS, PICANTO 1RA, I10</t>
-  </si>
-  <si>
-    <t>METALES BIELA STD, 0.50, 0.25 ATOS, PICANTO 1RA, I10</t>
-  </si>
-  <si>
-    <t>METALES BIELA STD, 0.50, 0.25 PICANTO 1RA, ATOS, I10</t>
-  </si>
-  <si>
     <t>ELECTROVENTILADOR PICANTO 1RA</t>
   </si>
   <si>
@@ -2335,12 +2311,132 @@
     <t>PUNTAS DE HOMOCINÉTICAS EXTERIORES ATOS 1.0 PAREJA</t>
   </si>
   <si>
+    <t>AMORTIGUADOR DE MALETERO ATOS</t>
+  </si>
+  <si>
+    <t>ÁRBOL DE LEVAS ATOS</t>
+  </si>
+  <si>
+    <t>AROS STD, 0,75, 0.50 ATOS, PICANTO 1RA, I10</t>
+  </si>
+  <si>
+    <t>BOTÓN DE ESTACIONAMIENTO ATOS</t>
+  </si>
+  <si>
+    <t>BRIDA DE AGUA ATOS</t>
+  </si>
+  <si>
+    <t>BUJE DE EJE TRASERO ATOS</t>
+  </si>
+  <si>
+    <t>CABLE DE CAPOT ATOS</t>
+  </si>
+  <si>
+    <t>CAPOT ATOS</t>
+  </si>
+  <si>
+    <t>CHUCHO DE ARRANQUE ATOS</t>
+  </si>
+  <si>
     <t>CONDENSADOR  ATOS</t>
   </si>
   <si>
+    <t>CREMALLERA DE PUERTA DELANTERA ATOS</t>
+  </si>
+  <si>
+    <t>DEFENSA DELANTERA COMPLETA ATOS</t>
+  </si>
+  <si>
+    <t>DEFENSA TRASERA COMPLETA ATOS</t>
+  </si>
+  <si>
+    <t>EMBLEMA HYUNDAI 10 CM</t>
+  </si>
+  <si>
+    <t>EMBLEMA HYUNDAI 8 CM</t>
+  </si>
+  <si>
+    <t>FARO TRASERO DERECHO ATOS</t>
+  </si>
+  <si>
+    <t>FARO TRASERO IZQUIERDO ATOS</t>
+  </si>
+  <si>
+    <t>GOMA DE PEDAL DE FRENO Y EMBRAGUE ATOS</t>
+  </si>
+  <si>
+    <t>GUARDAFANGO ATOS</t>
+  </si>
+  <si>
+    <t>LOGO DEL TEXTO ATOS</t>
+  </si>
+  <si>
+    <t>METALES APOYO STD, 0.75, 0.50, 0.25 ATOS, PICANTO 1RA, I10</t>
+  </si>
+  <si>
+    <t>METALES BIELA STD, 0.75, 0.50, 0.25 ATOS, PICANTO 1RA, I10</t>
+  </si>
+  <si>
+    <t>MOLDURA DE DEFENSA DELANTERA ATOS</t>
+  </si>
+  <si>
+    <t>MOLDURA DE PUERTA ATOS</t>
+  </si>
+  <si>
+    <t>NEBLINERO ATOS</t>
+  </si>
+  <si>
+    <t>PARRILLA DE DEFENSA ATOS</t>
+  </si>
+  <si>
+    <t>PISTONES STD, 0.75, 0.50 ATOS, PICANTO 1RA, I10</t>
+  </si>
+  <si>
+    <t>PULMÓN DE MARCHA ATRÁS ATOS</t>
+  </si>
+  <si>
+    <t>PULMÓN DEL STOP DE FRENO ATOS</t>
+  </si>
+  <si>
     <t>RADIADOR MECANICO ATOS</t>
   </si>
   <si>
+    <t>REFUERZO DE DEFENSA DELANTERA ATOS</t>
+  </si>
+  <si>
+    <t>REJILLA ATOS (FILO CROMADO)</t>
+  </si>
+  <si>
+    <t>REJILLA ATOS (LÍNEAS CROMADAS)</t>
+  </si>
+  <si>
+    <t>RETROVISOR ATOS</t>
+  </si>
+  <si>
+    <t>SEGURO DE PUERTA ATOS</t>
+  </si>
+  <si>
+    <t>TAPA DE ACEITE ATOS</t>
+  </si>
+  <si>
+    <t>TAPA DE GASOLINA ATOS</t>
+  </si>
+  <si>
+    <t>VÁLVULA PCV ATOS, PICANTO 1RA</t>
+  </si>
+  <si>
+    <t>VARILLA DE ACEITE ATOS</t>
+  </si>
+  <si>
+    <t>VÁSTAGO DE CREMALLERA DE PUERTA ATOS</t>
+  </si>
+  <si>
+    <t>ZAPATILLAS DE REPARACIÓN PARA UNA PINZA DE FRENO ATOS</t>
+  </si>
+  <si>
+    <t>AROS STD, 0,75, 0.50 PICANTO 1RA, ATOS, I10</t>
+  </si>
+  <si>
     <t>CONDENSADOR PICANTO  2DA</t>
   </si>
   <si>
@@ -2351,6 +2447,60 @@
   </si>
   <si>
     <t>ELECTROVENTILADOR PICANTO 3RA</t>
+  </si>
+  <si>
+    <t>METALES APOYO STD, 0,75, 0.50, 0.25 PICANTO 1RA, ATOS, I10</t>
+  </si>
+  <si>
+    <t>METALES BIELA STD, 0,75, 0.50, 0.25 PICANTO 1RA, ATOS, I10</t>
+  </si>
+  <si>
+    <t>PISTONES STD, 0.75, 0.50 PICANTO 1RA, ATOS, I10</t>
+  </si>
+  <si>
+    <t>AMORTIGUADOR DELANTERO SANDERO</t>
+  </si>
+  <si>
+    <t>AMORTIGUADOR TRASERO SANDERO</t>
+  </si>
+  <si>
+    <t>BANDAS DE FRENO SANDERO</t>
+  </si>
+  <si>
+    <t>BUJE DE PARRILLA DELANTERA SANDERO</t>
+  </si>
+  <si>
+    <t>DISCO DE FRENO SANDERO</t>
+  </si>
+  <si>
+    <t>RETÉN DE ÁRBOL DE LEVAS SANDERO</t>
+  </si>
+  <si>
+    <t>RETÉN DE CIGÜEÑAL DELANTERO SANDERO</t>
+  </si>
+  <si>
+    <t>RETÉN DE CIGÜEÑAL TRASERO SANDERO</t>
+  </si>
+  <si>
+    <t>RODAMIENTO TRASERO SANDERO</t>
+  </si>
+  <si>
+    <t>ROSCA DEL AFORADOR SANDERO</t>
+  </si>
+  <si>
+    <t>TANQUE AUXILIAR DEL RADIADOR SANDERO</t>
+  </si>
+  <si>
+    <t>TAPÓN CHICO DE ÁRBOL DE LEVAS SANDERO</t>
+  </si>
+  <si>
+    <t>TAPÓN DE TANQUE AUXILIAR DEL RADIADOR SANDERO</t>
+  </si>
+  <si>
+    <t>TAPÓN GRANDE DE ÁRBOL DE LEVAS SANDERO</t>
+  </si>
+  <si>
+    <t>FOCO H1 55W</t>
   </si>
 </sst>
 </file>
@@ -2909,7 +3059,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="B7" s="1">
         <v>4160</v>
@@ -2981,7 +3131,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="B16" s="1">
         <v>2600</v>
@@ -3005,7 +3155,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="B19" s="1">
         <v>4160</v>
@@ -3045,7 +3195,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="B24" s="1">
         <v>26000</v>
@@ -3125,7 +3275,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="B34" s="1">
         <v>36400</v>
@@ -3133,7 +3283,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="B35" s="1">
         <v>7800</v>
@@ -3141,7 +3291,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="B36" s="1">
         <v>15600</v>
@@ -3165,7 +3315,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="B39" s="1">
         <v>52000</v>
@@ -3173,7 +3323,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="B40" s="1">
         <v>57200</v>
@@ -3181,7 +3331,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="B41" s="1">
         <v>62400</v>
@@ -3213,7 +3363,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="B45" s="1">
         <v>23400</v>
@@ -3221,7 +3371,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="B46" s="1">
         <v>20800</v>
@@ -3261,7 +3411,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="B51" s="1">
         <v>520</v>
@@ -3325,7 +3475,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="B59" s="1">
         <v>5200</v>
@@ -3333,7 +3483,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="B60" s="1">
         <v>5200</v>
@@ -3533,7 +3683,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="B85" s="1">
         <v>7800</v>
@@ -3549,7 +3699,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="B87" s="1">
         <v>7800</v>
@@ -3629,7 +3779,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="B97" s="1">
         <v>7800</v>
@@ -3637,7 +3787,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="B98" s="1">
         <v>7800</v>
@@ -3693,7 +3843,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B105" s="1">
         <v>23400</v>
@@ -3709,7 +3859,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="B107" s="1">
         <v>13000</v>
@@ -3733,7 +3883,7 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="B110" s="1">
         <v>23400</v>
@@ -3741,7 +3891,7 @@
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="B111" s="1">
         <v>26000</v>
@@ -3749,7 +3899,7 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="B112" s="1">
         <v>15600</v>
@@ -3757,7 +3907,7 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="B113" s="1">
         <v>104</v>
@@ -3773,7 +3923,7 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="B115" s="1">
         <v>10400</v>
@@ -3789,7 +3939,7 @@
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="B117" s="1">
         <v>1040</v>
@@ -3861,7 +4011,7 @@
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="B126" s="1">
         <v>52000</v>
@@ -3869,7 +4019,7 @@
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="B127" s="1">
         <v>52000</v>
@@ -3893,7 +4043,7 @@
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="B130" s="1">
         <v>223600</v>
@@ -3981,7 +4131,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="B141" s="1">
         <v>104</v>
@@ -3997,7 +4147,7 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="B143" s="1">
         <v>5200</v>
@@ -4029,7 +4179,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="B147" s="1">
         <v>6240</v>
@@ -4141,7 +4291,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="B161" s="1">
         <v>18200</v>
@@ -4149,7 +4299,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="B162" s="1">
         <v>1560</v>
@@ -4157,7 +4307,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="B163" s="1">
         <v>1560</v>
@@ -4165,7 +4315,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="B164" s="1">
         <v>104</v>
@@ -4173,7 +4323,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="B165" s="1">
         <v>104</v>
@@ -4197,7 +4347,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="B168" s="1">
         <v>52000</v>
@@ -4205,7 +4355,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="B169" s="1">
         <v>2080</v>
@@ -4213,7 +4363,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="B170" s="1">
         <v>4160</v>
@@ -4301,7 +4451,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="B181" s="1">
         <v>3640</v>
@@ -4309,7 +4459,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="B182" s="1">
         <v>2600</v>
@@ -4317,7 +4467,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="B183" s="1">
         <v>7800</v>
@@ -4325,7 +4475,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="B184" s="1">
         <v>3640</v>
@@ -4333,7 +4483,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="B185" s="1">
         <v>3640</v>
@@ -4341,7 +4491,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="B186" s="1">
         <v>2600</v>
@@ -4373,7 +4523,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="B190" s="1">
         <v>26000</v>
@@ -4405,7 +4555,7 @@
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="B194" s="1">
         <v>1560</v>
@@ -4445,7 +4595,7 @@
     </row>
     <row r="199" spans="1:2">
       <c r="A199" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="B199" s="1">
         <v>291200</v>
@@ -4461,7 +4611,7 @@
     </row>
     <row r="201" spans="1:2">
       <c r="A201" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="B201" s="1">
         <v>6240</v>
@@ -4469,7 +4619,7 @@
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="B202" s="1">
         <v>4160</v>
@@ -4565,7 +4715,7 @@
     </row>
     <row r="214" spans="1:2">
       <c r="A214" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="B214" s="1">
         <v>6240</v>
@@ -4581,7 +4731,7 @@
     </row>
     <row r="216" spans="1:2">
       <c r="A216" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="B216" s="1">
         <v>2600</v>
@@ -4589,7 +4739,7 @@
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="B217" s="1">
         <v>2600</v>
@@ -4629,7 +4779,7 @@
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="B222" s="1">
         <v>33800</v>
@@ -4637,7 +4787,7 @@
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="B223" s="1">
         <v>41600</v>
@@ -4653,7 +4803,7 @@
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="B225" s="1">
         <v>78000</v>
@@ -4669,7 +4819,7 @@
     </row>
     <row r="227" spans="1:2">
       <c r="A227" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="B227" s="1">
         <v>31200</v>
@@ -4677,7 +4827,7 @@
     </row>
     <row r="228" spans="1:2">
       <c r="A228" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="B228" s="1">
         <v>33800</v>
@@ -4685,7 +4835,7 @@
     </row>
     <row r="229" spans="1:2">
       <c r="A229" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="B229" s="1">
         <v>36400</v>
@@ -4693,7 +4843,7 @@
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="B230" s="1">
         <v>36400</v>
@@ -4701,7 +4851,7 @@
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="B231" s="1">
         <v>3640</v>
@@ -4717,7 +4867,7 @@
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="B233" s="1">
         <v>31200</v>
@@ -4765,7 +4915,7 @@
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="B239" s="1">
         <v>156000</v>
@@ -4781,7 +4931,7 @@
     </row>
     <row r="241" spans="1:2">
       <c r="A241" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="B241" s="1">
         <v>130000</v>
@@ -4813,7 +4963,7 @@
     </row>
     <row r="245" spans="1:2">
       <c r="A245" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="B245" s="1">
         <v>15600</v>
@@ -4853,7 +5003,7 @@
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="B250" s="1">
         <v>10400</v>
@@ -4893,7 +5043,7 @@
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="B255" s="1">
         <v>6240</v>
@@ -4901,7 +5051,7 @@
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="B256" s="1">
         <v>6240</v>
@@ -4965,7 +5115,7 @@
     </row>
     <row r="264" spans="1:2">
       <c r="A264" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="B264" s="1">
         <v>104</v>
@@ -5101,7 +5251,7 @@
     </row>
     <row r="281" spans="1:2">
       <c r="A281" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="B281" s="1">
         <v>52000</v>
@@ -5109,7 +5259,7 @@
     </row>
     <row r="282" spans="1:2">
       <c r="A282" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="B282" s="1">
         <v>31200</v>
@@ -5117,7 +5267,7 @@
     </row>
     <row r="283" spans="1:2">
       <c r="A283" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="B283" s="1">
         <v>49400</v>
@@ -5125,7 +5275,7 @@
     </row>
     <row r="284" spans="1:2">
       <c r="A284" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="B284" s="1">
         <v>2600</v>
@@ -5133,7 +5283,7 @@
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="B285" s="1">
         <v>2600</v>
@@ -5149,7 +5299,7 @@
     </row>
     <row r="287" spans="1:2">
       <c r="A287" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="B287" s="1">
         <v>3640</v>
@@ -5237,7 +5387,7 @@
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="B298" s="1">
         <v>5200</v>
@@ -5293,7 +5443,7 @@
     </row>
     <row r="305" spans="1:2">
       <c r="A305" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="B305" s="1">
         <v>1040</v>
@@ -5301,7 +5451,7 @@
     </row>
     <row r="306" spans="1:2">
       <c r="A306" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="B306" s="1">
         <v>62400</v>
@@ -5333,7 +5483,7 @@
     </row>
     <row r="310" spans="1:2">
       <c r="A310" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="B310" s="1">
         <v>5200</v>
@@ -5381,7 +5531,7 @@
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="B316" s="1">
         <v>10400</v>
@@ -5405,7 +5555,7 @@
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="B319" s="1">
         <v>2080</v>
@@ -5413,7 +5563,7 @@
     </row>
     <row r="320" spans="1:2">
       <c r="A320" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="B320" s="1">
         <v>7800</v>
@@ -5421,7 +5571,7 @@
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="B321" s="1">
         <v>5200</v>
@@ -5493,7 +5643,7 @@
     </row>
     <row r="330" spans="1:2">
       <c r="A330" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="B330" s="1">
         <v>7800</v>
@@ -5509,7 +5659,7 @@
     </row>
     <row r="332" spans="1:2">
       <c r="A332" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="B332" s="1">
         <v>13000</v>
@@ -5517,7 +5667,7 @@
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="B333" s="1">
         <v>7800</v>
@@ -5597,7 +5747,7 @@
     </row>
     <row r="343" spans="1:2">
       <c r="A343" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="B343" s="1">
         <v>1560</v>
@@ -5637,7 +5787,7 @@
     </row>
     <row r="348" spans="1:2">
       <c r="A348" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="B348" s="1">
         <v>15600</v>
@@ -5645,7 +5795,7 @@
     </row>
     <row r="349" spans="1:2">
       <c r="A349" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="B349" s="1">
         <v>15600</v>
@@ -5677,7 +5827,7 @@
     </row>
     <row r="353" spans="1:2">
       <c r="A353" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="B353" s="1">
         <v>1560</v>
@@ -5709,7 +5859,7 @@
     </row>
     <row r="357" spans="1:2">
       <c r="A357" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="B357" s="1">
         <v>104000</v>
@@ -5754,7 +5904,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B129"/>
+  <dimension ref="A1:B164"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="64.5703125" bestFit="1" customWidth="1"/>
@@ -5787,23 +5937,23 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="7" t="s">
-        <v>589</v>
+        <v>760</v>
       </c>
       <c r="B4" s="1">
-        <v>93600</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="7" t="s">
-        <v>164</v>
+        <v>581</v>
       </c>
       <c r="B5" s="1">
-        <v>62400</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="7" t="s">
-        <v>590</v>
+        <v>164</v>
       </c>
       <c r="B6" s="1">
         <v>62400</v>
@@ -5811,31 +5961,31 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="8" t="s">
-        <v>600</v>
+        <v>582</v>
       </c>
       <c r="B7" s="1">
-        <v>4160</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="5" t="s">
-        <v>5</v>
+        <v>592</v>
       </c>
       <c r="B8" s="1">
-        <v>20800</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
-        <v>490</v>
+        <v>761</v>
       </c>
       <c r="B9" s="1">
-        <v>41600</v>
+        <v>67600</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="10" t="s">
-        <v>124</v>
+        <v>5</v>
       </c>
       <c r="B10" s="1">
         <v>20800</v>
@@ -5843,119 +5993,119 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="5" t="s">
-        <v>11</v>
+        <v>762</v>
       </c>
       <c r="B11" s="1">
-        <v>10400</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="10" t="s">
-        <v>433</v>
+        <v>124</v>
       </c>
       <c r="B12" s="1">
-        <v>41600</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="10" t="s">
-        <v>163</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1">
-        <v>52000</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="9" t="s">
-        <v>658</v>
+        <v>433</v>
       </c>
       <c r="B14" s="1">
-        <v>52000</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>592</v>
+        <v>163</v>
       </c>
       <c r="B15" s="1">
-        <v>57200</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="11" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="B16" s="1">
-        <v>62400</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
-        <v>6</v>
+        <v>584</v>
       </c>
       <c r="B17" s="1">
-        <v>13000</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="5" t="s">
-        <v>125</v>
+        <v>651</v>
       </c>
       <c r="B18" s="1">
-        <v>31200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="5" t="s">
-        <v>481</v>
+        <v>6</v>
       </c>
       <c r="B19" s="1">
-        <v>31200</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="5" t="s">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="B20" s="1">
-        <v>52000</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="B21" s="1">
-        <v>36400</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="5" t="s">
-        <v>492</v>
+        <v>36</v>
       </c>
       <c r="B22" s="1">
-        <v>41600</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="5" t="s">
-        <v>703</v>
+        <v>490</v>
       </c>
       <c r="B23" s="1">
-        <v>520</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="5" t="s">
-        <v>409</v>
+        <v>491</v>
       </c>
       <c r="B24" s="1">
-        <v>520</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="5" t="s">
-        <v>405</v>
+        <v>695</v>
       </c>
       <c r="B25" s="1">
         <v>520</v>
@@ -5963,71 +6113,71 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="5" t="s">
-        <v>442</v>
+        <v>409</v>
       </c>
       <c r="B26" s="1">
-        <v>7800</v>
+        <v>520</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="5" t="s">
-        <v>493</v>
+        <v>405</v>
       </c>
       <c r="B27" s="1">
-        <v>20800</v>
+        <v>520</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="5" t="s">
-        <v>494</v>
+        <v>442</v>
       </c>
       <c r="B28" s="1">
-        <v>20800</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="5" t="s">
-        <v>12</v>
+        <v>763</v>
       </c>
       <c r="B29" s="1">
-        <v>5200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="5" t="s">
-        <v>1</v>
+        <v>492</v>
       </c>
       <c r="B30" s="1">
-        <v>1300</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="12" t="s">
-        <v>7</v>
+        <v>493</v>
       </c>
       <c r="B31" s="1">
-        <v>5200</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="5" t="s">
-        <v>437</v>
+        <v>764</v>
       </c>
       <c r="B32" s="1">
-        <v>3640</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="5" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B33" s="1">
-        <v>13000</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="5" t="s">
-        <v>495</v>
+        <v>765</v>
       </c>
       <c r="B34" s="1">
         <v>7800</v>
@@ -6035,71 +6185,71 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="5" t="s">
-        <v>482</v>
+        <v>1</v>
       </c>
       <c r="B35" s="1">
-        <v>15600</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="5" t="s">
-        <v>441</v>
+        <v>7</v>
       </c>
       <c r="B36" s="1">
-        <v>13000</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="7" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="B37" s="1">
-        <v>26000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="13" t="s">
-        <v>496</v>
+        <v>2</v>
       </c>
       <c r="B38" s="1">
-        <v>31200</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="11" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B39" s="1">
-        <v>26000</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="5" t="s">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="B40" s="1">
-        <v>36400</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="5" t="s">
-        <v>562</v>
+        <v>766</v>
       </c>
       <c r="B41" s="1">
-        <v>7800</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="9" t="s">
-        <v>762</v>
+        <v>441</v>
       </c>
       <c r="B42" s="1">
-        <v>10400</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="5" t="s">
-        <v>733</v>
+        <v>443</v>
       </c>
       <c r="B43" s="1">
         <v>26000</v>
@@ -6107,23 +6257,23 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="7" t="s">
-        <v>29</v>
+        <v>495</v>
       </c>
       <c r="B44" s="1">
-        <v>18200</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>768</v>
+        <v>496</v>
       </c>
       <c r="B45" s="1">
-        <v>72800</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B46" s="1">
         <v>36400</v>
@@ -6131,247 +6281,247 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="14" t="s">
-        <v>439</v>
+        <v>767</v>
       </c>
       <c r="B47" s="1">
-        <v>7800</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="7" t="s">
-        <v>126</v>
+        <v>554</v>
       </c>
       <c r="B48" s="1">
-        <v>15600</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="13" t="s">
-        <v>500</v>
+        <v>768</v>
       </c>
       <c r="B49" s="1">
-        <v>104000</v>
+        <v>67600</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="15" t="s">
-        <v>30</v>
+        <v>754</v>
       </c>
       <c r="B50" s="1">
-        <v>52000</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>430</v>
+        <v>725</v>
       </c>
       <c r="B51" s="1">
-        <v>52000</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="5" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B52" s="1">
-        <v>78000</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="5" t="s">
-        <v>127</v>
+        <v>769</v>
       </c>
       <c r="B53" s="1">
-        <v>62400</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="6" t="s">
-        <v>13</v>
+        <v>498</v>
       </c>
       <c r="B54" s="1">
-        <v>31200</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="16" t="s">
-        <v>116</v>
+        <v>439</v>
       </c>
       <c r="B55" s="1">
-        <v>36400</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="10" t="s">
-        <v>14</v>
+        <v>126</v>
       </c>
       <c r="B56" s="1">
-        <v>67600</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="16" t="s">
-        <v>429</v>
+        <v>499</v>
       </c>
       <c r="B57" s="1">
-        <v>20800</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="17" t="s">
-        <v>563</v>
+        <v>770</v>
       </c>
       <c r="B58" s="1">
-        <v>5200</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="5" t="s">
-        <v>501</v>
+        <v>30</v>
       </c>
       <c r="B59" s="1">
-        <v>31200</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="5" t="s">
-        <v>502</v>
+        <v>430</v>
       </c>
       <c r="B60" s="1">
-        <v>28600</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="10" t="s">
-        <v>597</v>
+        <v>8</v>
       </c>
       <c r="B61" s="1">
-        <v>5200</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="10" t="s">
-        <v>15</v>
+        <v>771</v>
       </c>
       <c r="B62" s="1">
-        <v>5200</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="5" t="s">
-        <v>16</v>
+        <v>772</v>
       </c>
       <c r="B63" s="1">
-        <v>15600</v>
+        <v>114400</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="18" t="s">
-        <v>591</v>
+        <v>127</v>
       </c>
       <c r="B64" s="1">
-        <v>7800</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="10" t="s">
-        <v>699</v>
+        <v>13</v>
       </c>
       <c r="B65" s="1">
-        <v>18200</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="10" t="s">
-        <v>487</v>
+        <v>116</v>
       </c>
       <c r="B66" s="1">
-        <v>5200</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="5" t="s">
-        <v>746</v>
+        <v>14</v>
       </c>
       <c r="B67" s="1">
-        <v>4160</v>
+        <v>67600</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="5" t="s">
-        <v>3</v>
+        <v>773</v>
       </c>
       <c r="B68" s="1">
-        <v>62400</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="19" t="s">
-        <v>17</v>
+        <v>774</v>
       </c>
       <c r="B69" s="1">
-        <v>5200</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="5" t="s">
-        <v>128</v>
+        <v>429</v>
       </c>
       <c r="B70" s="1">
-        <v>10400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="5" t="s">
-        <v>726</v>
+        <v>555</v>
       </c>
       <c r="B71" s="1">
-        <v>15600</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="9" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B72" s="1">
-        <v>36400</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="5" t="s">
-        <v>9</v>
+        <v>501</v>
       </c>
       <c r="B73" s="1">
-        <v>31200</v>
+        <v>28600</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="5" t="s">
-        <v>634</v>
+        <v>775</v>
       </c>
       <c r="B74" s="1">
-        <v>291200</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="11" t="s">
-        <v>18</v>
+        <v>776</v>
       </c>
       <c r="B75" s="1">
-        <v>13000</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="20" t="s">
-        <v>19</v>
+        <v>589</v>
       </c>
       <c r="B76" s="1">
-        <v>7800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="10" t="s">
-        <v>504</v>
+        <v>15</v>
       </c>
       <c r="B77" s="1">
         <v>5200</v>
@@ -6379,367 +6529,367 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="5" t="s">
-        <v>505</v>
+        <v>16</v>
       </c>
       <c r="B78" s="1">
-        <v>7800</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="5" t="s">
-        <v>25</v>
+        <v>583</v>
       </c>
       <c r="B79" s="1">
-        <v>5200</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="13" t="s">
-        <v>564</v>
+        <v>691</v>
       </c>
       <c r="B80" s="1">
-        <v>6240</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="5" t="s">
-        <v>552</v>
+        <v>777</v>
       </c>
       <c r="B81" s="1">
-        <v>23400</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="5" t="s">
-        <v>553</v>
+        <v>487</v>
       </c>
       <c r="B82" s="1">
-        <v>18200</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="5" t="s">
-        <v>129</v>
+        <v>778</v>
       </c>
       <c r="B83" s="1">
-        <v>104000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="10" t="s">
-        <v>506</v>
+        <v>738</v>
       </c>
       <c r="B84" s="1">
-        <v>7800</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>763</v>
+        <v>3</v>
       </c>
       <c r="B85" s="1">
-        <v>36400</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="11" t="s">
-        <v>734</v>
+        <v>17</v>
       </c>
       <c r="B86" s="1">
-        <v>36400</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="17" t="s">
-        <v>731</v>
+        <v>128</v>
       </c>
       <c r="B87" s="1">
-        <v>36400</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="17" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
       <c r="B88" s="1">
-        <v>36400</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="17" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B89" s="1">
-        <v>6240</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="21" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="B90" s="1">
-        <v>93600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="5" t="s">
-        <v>665</v>
+        <v>626</v>
       </c>
       <c r="B91" s="1">
-        <v>182000</v>
+        <v>291200</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="5" t="s">
-        <v>24</v>
+        <v>779</v>
       </c>
       <c r="B92" s="1">
-        <v>93600</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="5" t="s">
-        <v>751</v>
+        <v>18</v>
       </c>
       <c r="B93" s="1">
-        <v>130000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B94" s="1">
-        <v>31200</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="5" t="s">
-        <v>436</v>
+        <v>503</v>
       </c>
       <c r="B95" s="1">
-        <v>20800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="10" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B96" s="1">
-        <v>62400</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="5" t="s">
-        <v>115</v>
+        <v>25</v>
       </c>
       <c r="B97" s="1">
-        <v>36400</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="5" t="s">
-        <v>509</v>
+        <v>556</v>
       </c>
       <c r="B98" s="1">
-        <v>10400</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="22" t="s">
-        <v>510</v>
+        <v>780</v>
       </c>
       <c r="B99" s="1">
-        <v>7800</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>727</v>
+        <v>781</v>
       </c>
       <c r="B100" s="1">
-        <v>7800</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>511</v>
+        <v>782</v>
       </c>
       <c r="B101" s="1">
-        <v>39000</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="5" t="s">
-        <v>21</v>
+        <v>783</v>
       </c>
       <c r="B102" s="1">
-        <v>26000</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="5" t="s">
-        <v>767</v>
+        <v>129</v>
       </c>
       <c r="B103" s="1">
-        <v>78000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="5" t="s">
-        <v>483</v>
+        <v>505</v>
       </c>
       <c r="B104" s="1">
-        <v>78000</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>769</v>
+        <v>784</v>
       </c>
       <c r="B105" s="1">
-        <v>67600</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>73</v>
+        <v>755</v>
       </c>
       <c r="B106" s="1">
-        <v>2600</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>74</v>
+        <v>726</v>
       </c>
       <c r="B107" s="1">
-        <v>5200</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>162</v>
+        <v>723</v>
       </c>
       <c r="B108" s="1">
-        <v>2600</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>130</v>
+        <v>724</v>
       </c>
       <c r="B109" s="1">
-        <v>18200</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>720</v>
+        <v>506</v>
       </c>
       <c r="B110" s="1">
-        <v>7800</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="4" t="s">
-        <v>435</v>
+        <v>100</v>
       </c>
       <c r="B111" s="1">
-        <v>20800</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>512</v>
+        <v>657</v>
       </c>
       <c r="B112" s="1">
-        <v>20800</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>513</v>
+        <v>24</v>
       </c>
       <c r="B113" s="1">
-        <v>36400</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>440</v>
+        <v>785</v>
       </c>
       <c r="B114" s="1">
-        <v>10400</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>514</v>
+        <v>743</v>
       </c>
       <c r="B115" s="1">
-        <v>20800</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B116" s="1">
-        <v>7800</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>661</v>
+        <v>436</v>
       </c>
       <c r="B117" s="1">
-        <v>5200</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>662</v>
+        <v>786</v>
       </c>
       <c r="B118" s="1">
-        <v>2600</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>599</v>
+        <v>115</v>
       </c>
       <c r="B119" s="1">
-        <v>5200</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>565</v>
+        <v>507</v>
       </c>
       <c r="B120" s="1">
-        <v>5200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="B121" s="1">
-        <v>15600</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>406</v>
+        <v>787</v>
       </c>
       <c r="B122" s="1">
-        <v>5200</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>557</v>
+        <v>719</v>
       </c>
       <c r="B123" s="1">
         <v>7800</v>
@@ -6747,7 +6897,7 @@
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>444</v>
+        <v>788</v>
       </c>
       <c r="B124" s="1">
         <v>7800</v>
@@ -6755,42 +6905,322 @@
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>567</v>
+        <v>509</v>
       </c>
       <c r="B125" s="1">
-        <v>13000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>568</v>
+        <v>21</v>
       </c>
       <c r="B126" s="1">
-        <v>7800</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>438</v>
+        <v>759</v>
       </c>
       <c r="B127" s="1">
-        <v>5200</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>635</v>
+        <v>483</v>
       </c>
       <c r="B128" s="1">
-        <v>52000</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
+        <v>789</v>
+      </c>
+      <c r="B129" s="1">
+        <v>67600</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" t="s">
+        <v>790</v>
+      </c>
+      <c r="B130" s="1">
+        <v>93600</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" t="s">
+        <v>791</v>
+      </c>
+      <c r="B131" s="1">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" t="s">
+        <v>792</v>
+      </c>
+      <c r="B132" s="1">
+        <v>46800</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" t="s">
+        <v>73</v>
+      </c>
+      <c r="B133" s="1">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" t="s">
+        <v>74</v>
+      </c>
+      <c r="B134" s="1">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" t="s">
+        <v>162</v>
+      </c>
+      <c r="B135" s="1">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" t="s">
+        <v>793</v>
+      </c>
+      <c r="B136" s="1">
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" t="s">
+        <v>130</v>
+      </c>
+      <c r="B137" s="1">
+        <v>18200</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" t="s">
+        <v>794</v>
+      </c>
+      <c r="B138" s="1">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" t="s">
+        <v>712</v>
+      </c>
+      <c r="B139" s="1">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" t="s">
+        <v>435</v>
+      </c>
+      <c r="B140" s="1">
+        <v>20800</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" t="s">
+        <v>510</v>
+      </c>
+      <c r="B141" s="1">
+        <v>20800</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" t="s">
+        <v>511</v>
+      </c>
+      <c r="B142" s="1">
+        <v>36400</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" t="s">
+        <v>440</v>
+      </c>
+      <c r="B143" s="1">
+        <v>10400</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" t="s">
+        <v>512</v>
+      </c>
+      <c r="B144" s="1">
+        <v>20800</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" t="s">
+        <v>795</v>
+      </c>
+      <c r="B145" s="1">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" t="s">
+        <v>4</v>
+      </c>
+      <c r="B146" s="1">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" t="s">
+        <v>796</v>
+      </c>
+      <c r="B147" s="1">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" t="s">
+        <v>653</v>
+      </c>
+      <c r="B148" s="1">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" t="s">
+        <v>654</v>
+      </c>
+      <c r="B149" s="1">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" t="s">
+        <v>591</v>
+      </c>
+      <c r="B150" s="1">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" t="s">
+        <v>557</v>
+      </c>
+      <c r="B151" s="1">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" t="s">
+        <v>513</v>
+      </c>
+      <c r="B152" s="1">
+        <v>15600</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" t="s">
+        <v>406</v>
+      </c>
+      <c r="B153" s="1">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" t="s">
+        <v>549</v>
+      </c>
+      <c r="B154" s="1">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" t="s">
+        <v>444</v>
+      </c>
+      <c r="B155" s="1">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" t="s">
+        <v>559</v>
+      </c>
+      <c r="B156" s="1">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" t="s">
+        <v>560</v>
+      </c>
+      <c r="B157" s="1">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" t="s">
+        <v>797</v>
+      </c>
+      <c r="B158" s="1">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" t="s">
+        <v>438</v>
+      </c>
+      <c r="B159" s="1">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" t="s">
+        <v>798</v>
+      </c>
+      <c r="B160" s="1">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" t="s">
+        <v>799</v>
+      </c>
+      <c r="B161" s="1">
+        <v>6240</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" t="s">
+        <v>627</v>
+      </c>
+      <c r="B162" s="1">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" t="s">
         <v>10</v>
       </c>
-      <c r="B129" s="1">
+      <c r="B163" s="1">
         <v>18200</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" t="s">
+        <v>800</v>
+      </c>
+      <c r="B164" s="1">
+        <v>5200</v>
       </c>
     </row>
   </sheetData>
@@ -6800,7 +7230,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B259"/>
+  <dimension ref="A1:B260"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="83.85546875" bestFit="1" customWidth="1"/>
@@ -6825,7 +7255,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="17" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B3" s="1">
         <v>3120</v>
@@ -6833,7 +7263,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="26" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="B4" s="1">
         <v>13000</v>
@@ -6849,7 +7279,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="25" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="B6" s="1">
         <v>104000</v>
@@ -6881,7 +7311,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="B10" s="1">
         <v>93600</v>
@@ -6905,7 +7335,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="17" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="B13" s="1">
         <v>4160</v>
@@ -6913,7 +7343,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="17" t="s">
-        <v>516</v>
+        <v>801</v>
       </c>
       <c r="B14" s="1">
         <v>41600</v>
@@ -6937,7 +7367,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="17" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="B17" s="1">
         <v>20800</v>
@@ -6945,7 +7375,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="17" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="B18" s="1">
         <v>5200</v>
@@ -6969,7 +7399,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="17" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="B21" s="1">
         <v>52000</v>
@@ -6977,7 +7407,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="B22" s="1">
         <v>57200</v>
@@ -6985,7 +7415,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="17" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="B23" s="1">
         <v>62400</v>
@@ -7033,7 +7463,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="17" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="B29" s="1">
         <v>15600</v>
@@ -7081,7 +7511,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="17" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="B35" s="1">
         <v>520</v>
@@ -7105,7 +7535,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="28" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="B38" s="1">
         <v>62400</v>
@@ -7113,7 +7543,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="17" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="B39" s="1">
         <v>62400</v>
@@ -7121,7 +7551,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="17" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="B40" s="1">
         <v>52000</v>
@@ -7129,7 +7559,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="17" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="B41" s="1">
         <v>52000</v>
@@ -7137,7 +7567,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="26" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B42" s="1">
         <v>5200</v>
@@ -7201,7 +7631,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="17" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B50" s="1">
         <v>3640</v>
@@ -7217,7 +7647,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="17" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B52" s="1">
         <v>20800</v>
@@ -7249,7 +7679,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="17" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="B56" s="1">
         <v>15600</v>
@@ -7257,7 +7687,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="17" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="B57" s="1">
         <v>52000</v>
@@ -7265,7 +7695,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="17" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="B58" s="1">
         <v>39000</v>
@@ -7281,7 +7711,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="17" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="B60" s="1">
         <v>7800</v>
@@ -7313,7 +7743,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="17" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="B64" s="1">
         <v>15600</v>
@@ -7321,7 +7751,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="17" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="B65" s="1">
         <v>26000</v>
@@ -7337,7 +7767,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="17" t="s">
-        <v>770</v>
+        <v>802</v>
       </c>
       <c r="B67" s="1">
         <v>83200</v>
@@ -7361,7 +7791,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="17" t="s">
-        <v>771</v>
+        <v>803</v>
       </c>
       <c r="B70" s="1">
         <v>83200</v>
@@ -7425,7 +7855,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="17" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="B78" s="1">
         <v>52000</v>
@@ -7569,7 +7999,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="17" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B96" s="1">
         <v>36400</v>
@@ -7577,7 +8007,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="17" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="B97" s="1">
         <v>31200</v>
@@ -7585,7 +8015,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="17" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="B98" s="1">
         <v>36400</v>
@@ -7601,7 +8031,7 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="17" t="s">
-        <v>772</v>
+        <v>804</v>
       </c>
       <c r="B100" s="1">
         <v>72800</v>
@@ -7609,7 +8039,7 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="17" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="B101" s="1">
         <v>72800</v>
@@ -7617,7 +8047,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="31" t="s">
-        <v>773</v>
+        <v>805</v>
       </c>
       <c r="B102" s="1">
         <v>93600</v>
@@ -7625,7 +8055,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="B103" s="1">
         <v>4160</v>
@@ -7633,7 +8063,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="17" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B104" s="1">
         <v>13000</v>
@@ -7649,7 +8079,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="17" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="B106" s="1">
         <v>13000</v>
@@ -7657,7 +8087,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="17" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="B107" s="1">
         <v>5200</v>
@@ -7665,7 +8095,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="17" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="B108" s="1">
         <v>31200</v>
@@ -7705,7 +8135,7 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="B113" s="1">
         <v>5200</v>
@@ -7713,7 +8143,7 @@
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="B114" s="1">
         <v>7800</v>
@@ -7721,7 +8151,7 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="17" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="B115" s="1">
         <v>7800</v>
@@ -7753,7 +8183,7 @@
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="17" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="B119" s="1">
         <v>7800</v>
@@ -7761,7 +8191,7 @@
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="17" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="B120" s="1">
         <v>10400</v>
@@ -7769,7 +8199,7 @@
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="B121" s="1">
         <v>6240</v>
@@ -7777,7 +8207,7 @@
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="17" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="B122" s="1">
         <v>18200</v>
@@ -7785,7 +8215,7 @@
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="17" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B123" s="1">
         <v>18200</v>
@@ -7801,7 +8231,7 @@
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="17" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="B125" s="1">
         <v>4160</v>
@@ -7841,7 +8271,7 @@
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="17" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="B130" s="1">
         <v>5200</v>
@@ -7849,7 +8279,7 @@
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="17" t="s">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="B131" s="1">
         <v>5200</v>
@@ -7857,7 +8287,7 @@
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="17" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="B132" s="1">
         <v>72800</v>
@@ -7865,7 +8295,7 @@
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="28" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="B133" s="1">
         <v>31200</v>
@@ -7881,7 +8311,7 @@
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="33" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="B135" s="1">
         <v>291200</v>
@@ -7889,7 +8319,7 @@
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="17" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="B136" s="1">
         <v>301600</v>
@@ -7897,7 +8327,7 @@
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="17" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="B137" s="1">
         <v>312000</v>
@@ -7961,7 +8391,7 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="17" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="B145" s="1">
         <v>5200</v>
@@ -7993,7 +8423,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="17" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="B149" s="1">
         <v>6240</v>
@@ -8001,7 +8431,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="17" t="s">
-        <v>522</v>
+        <v>806</v>
       </c>
       <c r="B150" s="1">
         <v>23400</v>
@@ -8009,7 +8439,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>554</v>
+        <v>807</v>
       </c>
       <c r="B151" s="1">
         <v>18200</v>
@@ -8033,7 +8463,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="17" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="B154" s="1">
         <v>39000</v>
@@ -8041,7 +8471,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="17" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="B155" s="1">
         <v>39000</v>
@@ -8081,7 +8511,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="17" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="B160" s="1">
         <v>36400</v>
@@ -8089,7 +8519,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="17" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="B161" s="1">
         <v>41600</v>
@@ -8097,7 +8527,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="17" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="B162" s="1">
         <v>36400</v>
@@ -8105,7 +8535,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="17" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="B163" s="1">
         <v>41600</v>
@@ -8113,7 +8543,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="17" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="B164" s="1">
         <v>780</v>
@@ -8145,7 +8575,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="17" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="B168" s="1">
         <v>182000</v>
@@ -8153,7 +8583,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="17" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B169" s="1">
         <v>187200</v>
@@ -8161,7 +8591,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="17" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="B170" s="1">
         <v>192400</v>
@@ -8169,7 +8599,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="17" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="B171" s="1">
         <v>182000</v>
@@ -8177,7 +8607,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="17" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="B172" s="1">
         <v>182000</v>
@@ -8185,7 +8615,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="17" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="B173" s="1">
         <v>182000</v>
@@ -8193,7 +8623,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="17" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="B174" s="1">
         <v>130000</v>
@@ -8217,7 +8647,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="17" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="B177" s="1">
         <v>104000</v>
@@ -8241,7 +8671,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="34" t="s">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="B180" s="1">
         <v>20800</v>
@@ -8249,7 +8679,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="B181" s="1">
         <v>20800</v>
@@ -8257,7 +8687,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="B182" s="1">
         <v>36400</v>
@@ -8265,7 +8695,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="17" t="s">
-        <v>523</v>
+        <v>808</v>
       </c>
       <c r="B183" s="1">
         <v>62400</v>
@@ -8273,7 +8703,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="17" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="B184" s="1">
         <v>31200</v>
@@ -8289,7 +8719,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="17" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="B186" s="1">
         <v>46800</v>
@@ -8297,7 +8727,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="17" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="B187" s="1">
         <v>10400</v>
@@ -8305,7 +8735,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="B188" s="1">
         <v>15600</v>
@@ -8321,7 +8751,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="B190" s="1">
         <v>18200</v>
@@ -8329,7 +8759,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="B191" s="1">
         <v>7800</v>
@@ -8353,7 +8783,7 @@
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="B194" s="1">
         <v>39000</v>
@@ -8377,7 +8807,7 @@
     </row>
     <row r="197" spans="1:2">
       <c r="A197" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="B197" s="1">
         <v>88400</v>
@@ -8409,7 +8839,7 @@
     </row>
     <row r="201" spans="1:2">
       <c r="A201" s="4" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="B201" s="1">
         <v>72800</v>
@@ -8417,7 +8847,7 @@
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="B202" s="1">
         <v>93600</v>
@@ -8609,7 +9039,7 @@
     </row>
     <row r="226" spans="1:2">
       <c r="A226" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="B226" s="1">
         <v>15600</v>
@@ -8641,7 +9071,7 @@
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="B230" s="1">
         <v>20800</v>
@@ -8665,7 +9095,7 @@
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="B233" s="1">
         <v>18200</v>
@@ -8697,7 +9127,7 @@
     </row>
     <row r="237" spans="1:2">
       <c r="A237" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="B237" s="1">
         <v>36400</v>
@@ -8705,7 +9135,7 @@
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="B238" s="1">
         <v>7800</v>
@@ -8713,7 +9143,7 @@
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="B239" s="1">
         <v>5200</v>
@@ -8721,7 +9151,7 @@
     </row>
     <row r="240" spans="1:2">
       <c r="A240" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="B240" s="1">
         <v>5200</v>
@@ -8729,7 +9159,7 @@
     </row>
     <row r="241" spans="1:2">
       <c r="A241" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="B241" s="1">
         <v>5200</v>
@@ -8753,7 +9183,7 @@
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="B244" s="1">
         <v>7800</v>
@@ -8761,7 +9191,7 @@
     </row>
     <row r="245" spans="1:2">
       <c r="A245" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B245" s="1">
         <v>10400</v>
@@ -8769,7 +9199,7 @@
     </row>
     <row r="246" spans="1:2">
       <c r="A246" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="B246" s="1">
         <v>15600</v>
@@ -8777,7 +9207,7 @@
     </row>
     <row r="247" spans="1:2">
       <c r="A247" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="B247" s="1">
         <v>13000</v>
@@ -8785,7 +9215,7 @@
     </row>
     <row r="248" spans="1:2">
       <c r="A248" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="B248" s="1">
         <v>7800</v>
@@ -8793,7 +9223,7 @@
     </row>
     <row r="249" spans="1:2">
       <c r="A249" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="B249" s="1">
         <v>7800</v>
@@ -8801,7 +9231,7 @@
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="B250" s="1">
         <v>7800</v>
@@ -8809,7 +9239,7 @@
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="B251" s="1">
         <v>10400</v>
@@ -8817,7 +9247,7 @@
     </row>
     <row r="252" spans="1:2">
       <c r="A252" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="B252" s="1">
         <v>2600</v>
@@ -8825,7 +9255,7 @@
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="B253" s="1">
         <v>119600</v>
@@ -8833,7 +9263,7 @@
     </row>
     <row r="254" spans="1:2">
       <c r="A254" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="B254" s="1">
         <v>10400</v>
@@ -8841,41 +9271,49 @@
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>448</v>
+        <v>797</v>
       </c>
       <c r="B255" s="1">
-        <v>5200</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>693</v>
+        <v>448</v>
       </c>
       <c r="B256" s="1">
-        <v>52000</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>112</v>
+        <v>685</v>
       </c>
       <c r="B257" s="1">
-        <v>31200</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
-        <v>155</v>
+        <v>112</v>
       </c>
       <c r="B258" s="1">
-        <v>18200</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
+        <v>155</v>
+      </c>
+      <c r="B259" s="1">
+        <v>18200</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" t="s">
         <v>156</v>
       </c>
-      <c r="B259" s="1">
+      <c r="B260" s="1">
         <v>20800</v>
       </c>
     </row>
@@ -8886,7 +9324,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52.140625" customWidth="1"/>
@@ -8903,7 +9341,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="35" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="B2" s="1">
         <v>93600</v>
@@ -8911,103 +9349,103 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="36" t="s">
-        <v>600</v>
+        <v>809</v>
       </c>
       <c r="B3" s="1">
-        <v>4160</v>
+        <v>70200</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="36" t="s">
-        <v>592</v>
+        <v>810</v>
       </c>
       <c r="B4" s="1">
-        <v>57200</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="36" t="s">
-        <v>659</v>
+        <v>592</v>
       </c>
       <c r="B5" s="1">
-        <v>62400</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="36" t="s">
-        <v>528</v>
+        <v>811</v>
       </c>
       <c r="B6" s="1">
-        <v>13000</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="36" t="s">
-        <v>529</v>
+        <v>584</v>
       </c>
       <c r="B7" s="1">
-        <v>18200</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="36" t="s">
-        <v>530</v>
+        <v>651</v>
       </c>
       <c r="B8" s="1">
-        <v>52000</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="36" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="B9" s="1">
-        <v>46800</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="36" t="s">
-        <v>562</v>
+        <v>524</v>
       </c>
       <c r="B10" s="1">
-        <v>7800</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="36" t="s">
-        <v>733</v>
+        <v>525</v>
       </c>
       <c r="B11" s="1">
-        <v>26000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="36" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="B12" s="1">
-        <v>20800</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="35" t="s">
-        <v>533</v>
+        <v>812</v>
       </c>
       <c r="B13" s="1">
-        <v>18200</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="36" t="s">
-        <v>702</v>
+        <v>554</v>
       </c>
       <c r="B14" s="1">
-        <v>52000</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="36" t="s">
-        <v>534</v>
+        <v>725</v>
       </c>
       <c r="B15" s="1">
         <v>26000</v>
@@ -9015,87 +9453,87 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="36" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="B16" s="1">
-        <v>13000</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="36" t="s">
-        <v>563</v>
+        <v>528</v>
       </c>
       <c r="B17" s="1">
-        <v>5200</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="36" t="s">
-        <v>536</v>
+        <v>694</v>
       </c>
       <c r="B18" s="1">
-        <v>5200</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="35" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="B19" s="1">
-        <v>5200</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="36" t="s">
-        <v>695</v>
+        <v>813</v>
       </c>
       <c r="B20" s="1">
-        <v>18200</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="36" t="s">
-        <v>487</v>
+        <v>530</v>
       </c>
       <c r="B21" s="1">
-        <v>5200</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="36" t="s">
-        <v>746</v>
+        <v>555</v>
       </c>
       <c r="B22" s="1">
-        <v>4160</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="36" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="B23" s="1">
-        <v>7800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="36" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="B24" s="1">
-        <v>13000</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="36" t="s">
-        <v>540</v>
+        <v>687</v>
       </c>
       <c r="B25" s="1">
-        <v>10400</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="36" t="s">
-        <v>541</v>
+        <v>487</v>
       </c>
       <c r="B26" s="1">
         <v>5200</v>
@@ -9103,87 +9541,87 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="36" t="s">
-        <v>542</v>
+        <v>738</v>
       </c>
       <c r="B27" s="1">
-        <v>62400</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B28">
-        <v>57200</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>642</v>
+        <v>534</v>
       </c>
       <c r="B29">
-        <v>312000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>564</v>
+        <v>535</v>
       </c>
       <c r="B30">
-        <v>6240</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>737</v>
+        <v>536</v>
       </c>
       <c r="B31">
-        <v>46800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>738</v>
+        <v>537</v>
       </c>
       <c r="B32">
-        <v>46800</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="B33">
-        <v>15600</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>694</v>
+        <v>634</v>
       </c>
       <c r="B34">
-        <v>187200</v>
+        <v>312000</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>647</v>
+        <v>556</v>
       </c>
       <c r="B35">
-        <v>192400</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>751</v>
+        <v>729</v>
       </c>
       <c r="B36">
-        <v>130000</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>545</v>
+        <v>730</v>
       </c>
       <c r="B37">
         <v>46800</v>
@@ -9191,71 +9629,71 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B38">
-        <v>26000</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>547</v>
+        <v>686</v>
       </c>
       <c r="B39">
-        <v>23400</v>
+        <v>187200</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>599</v>
+        <v>639</v>
       </c>
       <c r="B40">
-        <v>5200</v>
+        <v>192400</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>559</v>
+        <v>743</v>
       </c>
       <c r="B41">
-        <v>36400</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="B42">
-        <v>15600</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>406</v>
+        <v>541</v>
       </c>
       <c r="B43">
-        <v>5200</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>557</v>
+        <v>814</v>
       </c>
       <c r="B44">
-        <v>7800</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>567</v>
+        <v>815</v>
       </c>
       <c r="B45">
-        <v>13000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>568</v>
+        <v>816</v>
       </c>
       <c r="B46">
         <v>7800</v>
@@ -9263,33 +9701,145 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="B47">
-        <v>5200</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>549</v>
+        <v>817</v>
       </c>
       <c r="B48">
-        <v>5200</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>648</v>
+        <v>818</v>
       </c>
       <c r="B49">
-        <v>52000</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>550</v>
+        <v>819</v>
       </c>
       <c r="B50">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>591</v>
+      </c>
+      <c r="B51">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>820</v>
+      </c>
+      <c r="B52">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>821</v>
+      </c>
+      <c r="B53">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>822</v>
+      </c>
+      <c r="B54">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>551</v>
+      </c>
+      <c r="B55">
+        <v>36400</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>552</v>
+      </c>
+      <c r="B56">
+        <v>15600</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>406</v>
+      </c>
+      <c r="B57">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>549</v>
+      </c>
+      <c r="B58">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>559</v>
+      </c>
+      <c r="B59">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>560</v>
+      </c>
+      <c r="B60">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>543</v>
+      </c>
+      <c r="B61">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>544</v>
+      </c>
+      <c r="B62">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>640</v>
+      </c>
+      <c r="B63">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>545</v>
+      </c>
+      <c r="B64">
         <v>15600</v>
       </c>
     </row>
@@ -9300,7 +9850,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="58.140625" customWidth="1"/>
@@ -9349,7 +9899,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="B6" s="1">
         <v>20800</v>
@@ -9365,7 +9915,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="B8" s="1">
         <v>20800</v>
@@ -9373,7 +9923,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="B9" s="1">
         <v>4680</v>
@@ -9381,7 +9931,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="B10" s="1">
         <v>20800</v>
@@ -9405,7 +9955,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="B13" s="1">
         <v>4680</v>
@@ -9413,7 +9963,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="B14" s="1">
         <v>3640</v>
@@ -9421,7 +9971,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B15" s="1">
         <v>3120</v>
@@ -9437,7 +9987,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="B17" s="1">
         <v>4160</v>
@@ -9445,7 +9995,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="B18" s="1">
         <v>96200</v>
@@ -9453,7 +10003,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="B19" s="1">
         <v>109200</v>
@@ -9461,7 +10011,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="B20" s="1">
         <v>127400</v>
@@ -9485,7 +10035,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="B23" s="1">
         <v>52000</v>
@@ -9493,7 +10043,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="B24" s="1">
         <v>57200</v>
@@ -9501,7 +10051,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="B25" s="1">
         <v>62400</v>
@@ -9509,7 +10059,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="B26" s="1">
         <v>72800</v>
@@ -9517,7 +10067,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="B27" s="1">
         <v>85800</v>
@@ -9525,7 +10075,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="B28" s="1">
         <v>91000</v>
@@ -9533,7 +10083,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="B29" s="1">
         <v>520</v>
@@ -9565,7 +10115,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="B33" s="1">
         <v>7800</v>
@@ -9581,7 +10131,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="B35" s="1">
         <v>5200</v>
@@ -9589,39 +10139,39 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>407</v>
+        <v>823</v>
       </c>
       <c r="B36" s="1">
-        <v>4160</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>260</v>
+        <v>407</v>
       </c>
       <c r="B37" s="1">
-        <v>15600</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>428</v>
+        <v>260</v>
       </c>
       <c r="B38" s="1">
-        <v>2600</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>487</v>
+        <v>428</v>
       </c>
       <c r="B39" s="1">
-        <v>4160</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>746</v>
+        <v>487</v>
       </c>
       <c r="B40" s="1">
         <v>4160</v>
@@ -9629,47 +10179,47 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>394</v>
+        <v>738</v>
       </c>
       <c r="B41" s="1">
-        <v>6240</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B42" s="1">
-        <v>5200</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B43" s="1">
-        <v>7800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>649</v>
+        <v>396</v>
       </c>
       <c r="B44" s="1">
-        <v>3640</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>397</v>
+        <v>641</v>
       </c>
       <c r="B45" s="1">
-        <v>6240</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B46" s="1">
         <v>6240</v>
@@ -9677,55 +10227,55 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B47" s="1">
-        <v>4160</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>739</v>
+        <v>399</v>
       </c>
       <c r="B48" s="1">
-        <v>3120</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>564</v>
+        <v>731</v>
       </c>
       <c r="B49" s="1">
-        <v>6240</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>729</v>
+        <v>556</v>
       </c>
       <c r="B50" s="1">
-        <v>31200</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="B51" s="1">
-        <v>33800</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>763</v>
+        <v>722</v>
       </c>
       <c r="B52" s="1">
-        <v>36400</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>734</v>
+        <v>755</v>
       </c>
       <c r="B53" s="1">
         <v>36400</v>
@@ -9733,7 +10283,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="B54" s="1">
         <v>36400</v>
@@ -9741,39 +10291,39 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>735</v>
+        <v>723</v>
       </c>
       <c r="B55" s="1">
-        <v>41600</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="B56" s="1">
-        <v>36400</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>736</v>
+        <v>724</v>
       </c>
       <c r="B57" s="1">
-        <v>41600</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="B58" s="1">
-        <v>46800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
       <c r="B59" s="1">
         <v>46800</v>
@@ -9781,95 +10331,95 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>751</v>
+        <v>730</v>
       </c>
       <c r="B60" s="1">
-        <v>130000</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>650</v>
+        <v>743</v>
       </c>
       <c r="B61" s="1">
-        <v>6240</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>551</v>
+        <v>642</v>
       </c>
       <c r="B62" s="1">
-        <v>9360</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>400</v>
+        <v>546</v>
       </c>
       <c r="B63" s="1">
-        <v>10400</v>
+        <v>9360</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>664</v>
+        <v>400</v>
       </c>
       <c r="B64" s="1">
-        <v>7800</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>401</v>
+        <v>656</v>
       </c>
       <c r="B65" s="1">
-        <v>6240</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B66" s="1">
-        <v>3640</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B67" s="1">
-        <v>6240</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>593</v>
+        <v>403</v>
       </c>
       <c r="B68" s="1">
-        <v>4160</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>404</v>
+        <v>585</v>
       </c>
       <c r="B69" s="1">
-        <v>6240</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>599</v>
+        <v>404</v>
       </c>
       <c r="B70" s="1">
-        <v>5200</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>565</v>
+        <v>591</v>
       </c>
       <c r="B71" s="1">
         <v>5200</v>
@@ -9877,7 +10427,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="B72" s="1">
         <v>5200</v>
@@ -9885,57 +10435,65 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>655</v>
+        <v>558</v>
       </c>
       <c r="B73" s="1">
-        <v>3640</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="B74" s="1">
-        <v>2600</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>406</v>
+        <v>648</v>
       </c>
       <c r="B75" s="1">
-        <v>5200</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>557</v>
+        <v>406</v>
       </c>
       <c r="B76" s="1">
-        <v>7800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>567</v>
+        <v>549</v>
       </c>
       <c r="B77" s="1">
-        <v>13000</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="B78" s="1">
-        <v>7800</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="B79" s="1">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>561</v>
+      </c>
+      <c r="B80" s="1">
         <v>2600</v>
       </c>
     </row>

--- a/clientes/files/TODITICO_CATÁLOGO.xlsx
+++ b/clientes/files/TODITICO_CATÁLOGO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\510 Actual - Con lo nuevo de Mexico\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\520 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C1262B-3D57-422E-99DE-8B8F31F69E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5A1C31-4F2B-47D6-BF18-13D1D76041A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DAEWOO TICO" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="777">
   <si>
     <t>DESCRIPCION</t>
   </si>
@@ -1501,6 +1501,9 @@
     <t>AFORADOR ATOS</t>
   </si>
   <si>
+    <t>AROS STD, 0.50 ATOS, PICANTO 1RA, I10</t>
+  </si>
+  <si>
     <t>BOMBA DE COMBUSTIBLE ELECTRICA ATOS</t>
   </si>
   <si>
@@ -1552,6 +1555,9 @@
     <t>OBTURADORES JUEGO ATOS, PICANTO 1RA, I10</t>
   </si>
   <si>
+    <t>PISTONES STD, 0.50 ATOS, PICANTO 1RA, I10</t>
+  </si>
+  <si>
     <t>PORTACARBON DE MOTOR DE ARRANQUE ATOS, PICANTO 1RA, I10</t>
   </si>
   <si>
@@ -1573,6 +1579,9 @@
     <t>TENSOR DE CORREA DE DISTRIBUCION ATOS, PICANTO 1RA, I10.</t>
   </si>
   <si>
+    <t>AROS STD, 0.50 PICANTO 1RA, ATOS, I10</t>
+  </si>
+  <si>
     <t>BOTA DE CREMALLERA PICANTO 1RA Y 2DA</t>
   </si>
   <si>
@@ -1588,6 +1597,12 @@
     <t>ESFERICAS PICANTO 1RA (DE ROSCA)</t>
   </si>
   <si>
+    <t>METALES APOYO STD, 0.50, 0.25 PICANTO 1RA, ATOS, I10</t>
+  </si>
+  <si>
+    <t>PISTONES STD, 0.50 PICANTO 1RA, ATOS, I10</t>
+  </si>
+  <si>
     <t>PORTACARBON DE MOTOR DE ARRANQUE PICANTO 1RA, ATOS, I10</t>
   </si>
   <si>
@@ -1672,6 +1687,15 @@
     <t>REFRIGERANTE AL 30% 5LT</t>
   </si>
   <si>
+    <t>METALES APOYO STD, 0.50, 0.25 ATOS, PICANTO 1RA, I10</t>
+  </si>
+  <si>
+    <t>METALES BIELA STD, 0.50, 0.25 ATOS, PICANTO 1RA, I10</t>
+  </si>
+  <si>
+    <t>METALES BIELA STD, 0.50, 0.25 PICANTO 1RA, ATOS, I10</t>
+  </si>
+  <si>
     <t>ELECTROVENTILADOR PICANTO 1RA</t>
   </si>
   <si>
@@ -2311,132 +2335,12 @@
     <t>PUNTAS DE HOMOCINÉTICAS EXTERIORES ATOS 1.0 PAREJA</t>
   </si>
   <si>
-    <t>AMORTIGUADOR DE MALETERO ATOS</t>
-  </si>
-  <si>
-    <t>ÁRBOL DE LEVAS ATOS</t>
-  </si>
-  <si>
-    <t>AROS STD, 0,75, 0.50 ATOS, PICANTO 1RA, I10</t>
-  </si>
-  <si>
-    <t>BOTÓN DE ESTACIONAMIENTO ATOS</t>
-  </si>
-  <si>
-    <t>BRIDA DE AGUA ATOS</t>
-  </si>
-  <si>
-    <t>BUJE DE EJE TRASERO ATOS</t>
-  </si>
-  <si>
-    <t>CABLE DE CAPOT ATOS</t>
-  </si>
-  <si>
-    <t>CAPOT ATOS</t>
-  </si>
-  <si>
-    <t>CHUCHO DE ARRANQUE ATOS</t>
-  </si>
-  <si>
     <t>CONDENSADOR  ATOS</t>
   </si>
   <si>
-    <t>CREMALLERA DE PUERTA DELANTERA ATOS</t>
-  </si>
-  <si>
-    <t>DEFENSA DELANTERA COMPLETA ATOS</t>
-  </si>
-  <si>
-    <t>DEFENSA TRASERA COMPLETA ATOS</t>
-  </si>
-  <si>
-    <t>EMBLEMA HYUNDAI 10 CM</t>
-  </si>
-  <si>
-    <t>EMBLEMA HYUNDAI 8 CM</t>
-  </si>
-  <si>
-    <t>FARO TRASERO DERECHO ATOS</t>
-  </si>
-  <si>
-    <t>FARO TRASERO IZQUIERDO ATOS</t>
-  </si>
-  <si>
-    <t>GOMA DE PEDAL DE FRENO Y EMBRAGUE ATOS</t>
-  </si>
-  <si>
-    <t>GUARDAFANGO ATOS</t>
-  </si>
-  <si>
-    <t>LOGO DEL TEXTO ATOS</t>
-  </si>
-  <si>
-    <t>METALES APOYO STD, 0.75, 0.50, 0.25 ATOS, PICANTO 1RA, I10</t>
-  </si>
-  <si>
-    <t>METALES BIELA STD, 0.75, 0.50, 0.25 ATOS, PICANTO 1RA, I10</t>
-  </si>
-  <si>
-    <t>MOLDURA DE DEFENSA DELANTERA ATOS</t>
-  </si>
-  <si>
-    <t>MOLDURA DE PUERTA ATOS</t>
-  </si>
-  <si>
-    <t>NEBLINERO ATOS</t>
-  </si>
-  <si>
-    <t>PARRILLA DE DEFENSA ATOS</t>
-  </si>
-  <si>
-    <t>PISTONES STD, 0.75, 0.50 ATOS, PICANTO 1RA, I10</t>
-  </si>
-  <si>
-    <t>PULMÓN DE MARCHA ATRÁS ATOS</t>
-  </si>
-  <si>
-    <t>PULMÓN DEL STOP DE FRENO ATOS</t>
-  </si>
-  <si>
     <t>RADIADOR MECANICO ATOS</t>
   </si>
   <si>
-    <t>REFUERZO DE DEFENSA DELANTERA ATOS</t>
-  </si>
-  <si>
-    <t>REJILLA ATOS (FILO CROMADO)</t>
-  </si>
-  <si>
-    <t>REJILLA ATOS (LÍNEAS CROMADAS)</t>
-  </si>
-  <si>
-    <t>RETROVISOR ATOS</t>
-  </si>
-  <si>
-    <t>SEGURO DE PUERTA ATOS</t>
-  </si>
-  <si>
-    <t>TAPA DE ACEITE ATOS</t>
-  </si>
-  <si>
-    <t>TAPA DE GASOLINA ATOS</t>
-  </si>
-  <si>
-    <t>VÁLVULA PCV ATOS, PICANTO 1RA</t>
-  </si>
-  <si>
-    <t>VARILLA DE ACEITE ATOS</t>
-  </si>
-  <si>
-    <t>VÁSTAGO DE CREMALLERA DE PUERTA ATOS</t>
-  </si>
-  <si>
-    <t>ZAPATILLAS DE REPARACIÓN PARA UNA PINZA DE FRENO ATOS</t>
-  </si>
-  <si>
-    <t>AROS STD, 0,75, 0.50 PICANTO 1RA, ATOS, I10</t>
-  </si>
-  <si>
     <t>CONDENSADOR PICANTO  2DA</t>
   </si>
   <si>
@@ -2449,58 +2353,13 @@
     <t>ELECTROVENTILADOR PICANTO 3RA</t>
   </si>
   <si>
-    <t>METALES APOYO STD, 0,75, 0.50, 0.25 PICANTO 1RA, ATOS, I10</t>
-  </si>
-  <si>
-    <t>METALES BIELA STD, 0,75, 0.50, 0.25 PICANTO 1RA, ATOS, I10</t>
-  </si>
-  <si>
-    <t>PISTONES STD, 0.75, 0.50 PICANTO 1RA, ATOS, I10</t>
-  </si>
-  <si>
-    <t>AMORTIGUADOR DELANTERO SANDERO</t>
-  </si>
-  <si>
-    <t>AMORTIGUADOR TRASERO SANDERO</t>
+    <t>TERMOSTATO</t>
   </si>
   <si>
     <t>BANDAS DE FRENO SANDERO</t>
   </si>
   <si>
-    <t>BUJE DE PARRILLA DELANTERA SANDERO</t>
-  </si>
-  <si>
-    <t>DISCO DE FRENO SANDERO</t>
-  </si>
-  <si>
-    <t>RETÉN DE ÁRBOL DE LEVAS SANDERO</t>
-  </si>
-  <si>
-    <t>RETÉN DE CIGÜEÑAL DELANTERO SANDERO</t>
-  </si>
-  <si>
-    <t>RETÉN DE CIGÜEÑAL TRASERO SANDERO</t>
-  </si>
-  <si>
-    <t>RODAMIENTO TRASERO SANDERO</t>
-  </si>
-  <si>
-    <t>ROSCA DEL AFORADOR SANDERO</t>
-  </si>
-  <si>
-    <t>TANQUE AUXILIAR DEL RADIADOR SANDERO</t>
-  </si>
-  <si>
-    <t>TAPÓN CHICO DE ÁRBOL DE LEVAS SANDERO</t>
-  </si>
-  <si>
-    <t>TAPÓN DE TANQUE AUXILIAR DEL RADIADOR SANDERO</t>
-  </si>
-  <si>
-    <t>TAPÓN GRANDE DE ÁRBOL DE LEVAS SANDERO</t>
-  </si>
-  <si>
-    <t>FOCO H1 55W</t>
+    <t>FILTRO DE AIRE ACONDICIONADO SANDERO</t>
   </si>
 </sst>
 </file>
@@ -3002,7 +2861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B361"/>
+  <dimension ref="A1:B362"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="83.85546875" customWidth="1"/>
@@ -3059,7 +2918,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="B7" s="1">
         <v>4160</v>
@@ -3131,7 +2990,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="B16" s="1">
         <v>2600</v>
@@ -3155,7 +3014,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="B19" s="1">
         <v>4160</v>
@@ -3195,7 +3054,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="B24" s="1">
         <v>26000</v>
@@ -3275,7 +3134,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="B34" s="1">
         <v>36400</v>
@@ -3283,7 +3142,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="B35" s="1">
         <v>7800</v>
@@ -3291,7 +3150,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="B36" s="1">
         <v>15600</v>
@@ -3315,7 +3174,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="B39" s="1">
         <v>52000</v>
@@ -3323,7 +3182,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="B40" s="1">
         <v>57200</v>
@@ -3331,7 +3190,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="B41" s="1">
         <v>62400</v>
@@ -3363,7 +3222,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="B45" s="1">
         <v>23400</v>
@@ -3371,7 +3230,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="B46" s="1">
         <v>20800</v>
@@ -3411,7 +3270,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="B51" s="1">
         <v>520</v>
@@ -3475,7 +3334,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="B59" s="1">
         <v>5200</v>
@@ -3483,7 +3342,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="B60" s="1">
         <v>5200</v>
@@ -3683,7 +3542,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="B85" s="1">
         <v>7800</v>
@@ -3699,7 +3558,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="B87" s="1">
         <v>7800</v>
@@ -3779,7 +3638,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="B97" s="1">
         <v>7800</v>
@@ -3787,7 +3646,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="B98" s="1">
         <v>7800</v>
@@ -3843,7 +3702,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="B105" s="1">
         <v>23400</v>
@@ -3859,7 +3718,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="B107" s="1">
         <v>13000</v>
@@ -3883,7 +3742,7 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="B110" s="1">
         <v>23400</v>
@@ -3891,7 +3750,7 @@
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="B111" s="1">
         <v>26000</v>
@@ -3899,7 +3758,7 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="B112" s="1">
         <v>15600</v>
@@ -3907,7 +3766,7 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="B113" s="1">
         <v>104</v>
@@ -3923,7 +3782,7 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="B115" s="1">
         <v>10400</v>
@@ -3939,7 +3798,7 @@
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="B117" s="1">
         <v>1040</v>
@@ -4011,7 +3870,7 @@
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="B126" s="1">
         <v>52000</v>
@@ -4019,7 +3878,7 @@
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="B127" s="1">
         <v>52000</v>
@@ -4043,7 +3902,7 @@
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="B130" s="1">
         <v>223600</v>
@@ -4131,7 +3990,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="B141" s="1">
         <v>104</v>
@@ -4147,7 +4006,7 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="B143" s="1">
         <v>5200</v>
@@ -4179,7 +4038,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="B147" s="1">
         <v>6240</v>
@@ -4291,7 +4150,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="B161" s="1">
         <v>18200</v>
@@ -4299,7 +4158,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="B162" s="1">
         <v>1560</v>
@@ -4307,7 +4166,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="B163" s="1">
         <v>1560</v>
@@ -4315,7 +4174,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="B164" s="1">
         <v>104</v>
@@ -4323,7 +4182,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="B165" s="1">
         <v>104</v>
@@ -4347,7 +4206,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="B168" s="1">
         <v>52000</v>
@@ -4355,7 +4214,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="B169" s="1">
         <v>2080</v>
@@ -4363,7 +4222,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="B170" s="1">
         <v>4160</v>
@@ -4451,7 +4310,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="B181" s="1">
         <v>3640</v>
@@ -4459,7 +4318,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="B182" s="1">
         <v>2600</v>
@@ -4467,7 +4326,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="B183" s="1">
         <v>7800</v>
@@ -4475,7 +4334,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="B184" s="1">
         <v>3640</v>
@@ -4483,7 +4342,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="B185" s="1">
         <v>3640</v>
@@ -4491,7 +4350,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="B186" s="1">
         <v>2600</v>
@@ -4523,7 +4382,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="B190" s="1">
         <v>26000</v>
@@ -4555,7 +4414,7 @@
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="B194" s="1">
         <v>1560</v>
@@ -4595,7 +4454,7 @@
     </row>
     <row r="199" spans="1:2">
       <c r="A199" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="B199" s="1">
         <v>291200</v>
@@ -4611,7 +4470,7 @@
     </row>
     <row r="201" spans="1:2">
       <c r="A201" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="B201" s="1">
         <v>6240</v>
@@ -4619,7 +4478,7 @@
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="B202" s="1">
         <v>4160</v>
@@ -4715,7 +4574,7 @@
     </row>
     <row r="214" spans="1:2">
       <c r="A214" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="B214" s="1">
         <v>6240</v>
@@ -4731,7 +4590,7 @@
     </row>
     <row r="216" spans="1:2">
       <c r="A216" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="B216" s="1">
         <v>2600</v>
@@ -4739,7 +4598,7 @@
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="B217" s="1">
         <v>2600</v>
@@ -4779,7 +4638,7 @@
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="B222" s="1">
         <v>33800</v>
@@ -4787,7 +4646,7 @@
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="B223" s="1">
         <v>41600</v>
@@ -4803,7 +4662,7 @@
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="B225" s="1">
         <v>78000</v>
@@ -4819,7 +4678,7 @@
     </row>
     <row r="227" spans="1:2">
       <c r="A227" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="B227" s="1">
         <v>31200</v>
@@ -4827,7 +4686,7 @@
     </row>
     <row r="228" spans="1:2">
       <c r="A228" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="B228" s="1">
         <v>33800</v>
@@ -4835,7 +4694,7 @@
     </row>
     <row r="229" spans="1:2">
       <c r="A229" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="B229" s="1">
         <v>36400</v>
@@ -4843,7 +4702,7 @@
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="B230" s="1">
         <v>36400</v>
@@ -4851,7 +4710,7 @@
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="B231" s="1">
         <v>3640</v>
@@ -4867,7 +4726,7 @@
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="B233" s="1">
         <v>31200</v>
@@ -4915,7 +4774,7 @@
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="B239" s="1">
         <v>156000</v>
@@ -4931,7 +4790,7 @@
     </row>
     <row r="241" spans="1:2">
       <c r="A241" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="B241" s="1">
         <v>130000</v>
@@ -4963,7 +4822,7 @@
     </row>
     <row r="245" spans="1:2">
       <c r="A245" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="B245" s="1">
         <v>15600</v>
@@ -5003,7 +4862,7 @@
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="B250" s="1">
         <v>10400</v>
@@ -5043,7 +4902,7 @@
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="B255" s="1">
         <v>6240</v>
@@ -5051,7 +4910,7 @@
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="B256" s="1">
         <v>6240</v>
@@ -5115,7 +4974,7 @@
     </row>
     <row r="264" spans="1:2">
       <c r="A264" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="B264" s="1">
         <v>104</v>
@@ -5251,7 +5110,7 @@
     </row>
     <row r="281" spans="1:2">
       <c r="A281" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="B281" s="1">
         <v>52000</v>
@@ -5259,7 +5118,7 @@
     </row>
     <row r="282" spans="1:2">
       <c r="A282" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="B282" s="1">
         <v>31200</v>
@@ -5267,7 +5126,7 @@
     </row>
     <row r="283" spans="1:2">
       <c r="A283" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="B283" s="1">
         <v>49400</v>
@@ -5275,7 +5134,7 @@
     </row>
     <row r="284" spans="1:2">
       <c r="A284" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="B284" s="1">
         <v>2600</v>
@@ -5283,7 +5142,7 @@
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="B285" s="1">
         <v>2600</v>
@@ -5299,7 +5158,7 @@
     </row>
     <row r="287" spans="1:2">
       <c r="A287" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="B287" s="1">
         <v>3640</v>
@@ -5387,7 +5246,7 @@
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="B298" s="1">
         <v>5200</v>
@@ -5443,7 +5302,7 @@
     </row>
     <row r="305" spans="1:2">
       <c r="A305" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="B305" s="1">
         <v>1040</v>
@@ -5451,7 +5310,7 @@
     </row>
     <row r="306" spans="1:2">
       <c r="A306" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="B306" s="1">
         <v>62400</v>
@@ -5483,7 +5342,7 @@
     </row>
     <row r="310" spans="1:2">
       <c r="A310" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="B310" s="1">
         <v>5200</v>
@@ -5531,7 +5390,7 @@
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="B316" s="1">
         <v>10400</v>
@@ -5555,7 +5414,7 @@
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="B319" s="1">
         <v>2080</v>
@@ -5563,7 +5422,7 @@
     </row>
     <row r="320" spans="1:2">
       <c r="A320" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="B320" s="1">
         <v>7800</v>
@@ -5571,7 +5430,7 @@
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="B321" s="1">
         <v>5200</v>
@@ -5643,7 +5502,7 @@
     </row>
     <row r="330" spans="1:2">
       <c r="A330" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="B330" s="1">
         <v>7800</v>
@@ -5651,151 +5510,151 @@
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
-        <v>369</v>
+        <v>774</v>
       </c>
       <c r="B331" s="1">
-        <v>7800</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="332" spans="1:2">
       <c r="A332" t="s">
-        <v>559</v>
+        <v>369</v>
       </c>
       <c r="B332" s="1">
-        <v>13000</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="B333" s="1">
-        <v>7800</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
-        <v>370</v>
+        <v>568</v>
       </c>
       <c r="B334" s="1">
-        <v>2600</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B335" s="1">
-        <v>3640</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="336" spans="1:2">
       <c r="A336" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B336" s="1">
-        <v>3120</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="337" spans="1:2">
       <c r="A337" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B337" s="1">
-        <v>1040</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="338" spans="1:2">
       <c r="A338" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B338" s="1">
-        <v>2600</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="339" spans="1:2">
       <c r="A339" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B339" s="1">
-        <v>1560</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="A340" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B340" s="1">
-        <v>2080</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="341" spans="1:2">
       <c r="A341" t="s">
-        <v>416</v>
+        <v>376</v>
       </c>
       <c r="B341" s="1">
-        <v>1560</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="342" spans="1:2">
       <c r="A342" t="s">
-        <v>468</v>
+        <v>416</v>
       </c>
       <c r="B342" s="1">
-        <v>3640</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="A343" t="s">
-        <v>624</v>
+        <v>468</v>
       </c>
       <c r="B343" s="1">
-        <v>1560</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="344" spans="1:2">
       <c r="A344" t="s">
-        <v>377</v>
+        <v>632</v>
       </c>
       <c r="B344" s="1">
-        <v>1040</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="345" spans="1:2">
       <c r="A345" t="s">
-        <v>488</v>
+        <v>377</v>
       </c>
       <c r="B345" s="1">
-        <v>93600</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="346" spans="1:2">
       <c r="A346" t="s">
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="B346" s="1">
-        <v>5200</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="347" spans="1:2">
       <c r="A347" t="s">
-        <v>378</v>
+        <v>472</v>
       </c>
       <c r="B347" s="1">
-        <v>10400</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="348" spans="1:2">
       <c r="A348" t="s">
-        <v>677</v>
+        <v>378</v>
       </c>
       <c r="B348" s="1">
-        <v>15600</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="349" spans="1:2">
       <c r="A349" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="B349" s="1">
         <v>15600</v>
@@ -5803,55 +5662,55 @@
     </row>
     <row r="350" spans="1:2">
       <c r="A350" t="s">
-        <v>379</v>
+        <v>686</v>
       </c>
       <c r="B350" s="1">
-        <v>10400</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="351" spans="1:2">
       <c r="A351" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B351" s="1">
-        <v>23400</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="352" spans="1:2">
       <c r="A352" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B352" s="1">
-        <v>7800</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="353" spans="1:2">
       <c r="A353" t="s">
-        <v>625</v>
+        <v>381</v>
       </c>
       <c r="B353" s="1">
-        <v>1560</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="354" spans="1:2">
       <c r="A354" t="s">
-        <v>382</v>
+        <v>633</v>
       </c>
       <c r="B354" s="1">
-        <v>31200</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="355" spans="1:2">
       <c r="A355" t="s">
-        <v>473</v>
+        <v>382</v>
       </c>
       <c r="B355" s="1">
-        <v>7800</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="356" spans="1:2">
       <c r="A356" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B356" s="1">
         <v>7800</v>
@@ -5859,41 +5718,49 @@
     </row>
     <row r="357" spans="1:2">
       <c r="A357" t="s">
-        <v>679</v>
+        <v>474</v>
       </c>
       <c r="B357" s="1">
-        <v>104000</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="358" spans="1:2">
       <c r="A358" t="s">
-        <v>383</v>
+        <v>687</v>
       </c>
       <c r="B358" s="1">
-        <v>18200</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="359" spans="1:2">
       <c r="A359" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B359" s="1">
-        <v>5200</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="360" spans="1:2">
       <c r="A360" t="s">
-        <v>457</v>
+        <v>384</v>
       </c>
       <c r="B360" s="1">
-        <v>2080</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="361" spans="1:2">
       <c r="A361" t="s">
+        <v>457</v>
+      </c>
+      <c r="B361" s="1">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" t="s">
         <v>385</v>
       </c>
-      <c r="B361" s="1">
+      <c r="B362" s="1">
         <v>6240</v>
       </c>
     </row>
@@ -5904,7 +5771,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B164"/>
+  <dimension ref="A1:B129"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="64.5703125" bestFit="1" customWidth="1"/>
@@ -5937,23 +5804,23 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="7" t="s">
-        <v>760</v>
+        <v>589</v>
       </c>
       <c r="B4" s="1">
-        <v>18200</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="7" t="s">
-        <v>581</v>
+        <v>164</v>
       </c>
       <c r="B5" s="1">
-        <v>93600</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="7" t="s">
-        <v>164</v>
+        <v>590</v>
       </c>
       <c r="B6" s="1">
         <v>62400</v>
@@ -5961,31 +5828,31 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="8" t="s">
-        <v>582</v>
+        <v>600</v>
       </c>
       <c r="B7" s="1">
-        <v>62400</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="5" t="s">
-        <v>592</v>
+        <v>5</v>
       </c>
       <c r="B8" s="1">
-        <v>4160</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
-        <v>761</v>
+        <v>490</v>
       </c>
       <c r="B9" s="1">
-        <v>67600</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="10" t="s">
-        <v>5</v>
+        <v>124</v>
       </c>
       <c r="B10" s="1">
         <v>20800</v>
@@ -5993,119 +5860,119 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="5" t="s">
-        <v>762</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>41600</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="10" t="s">
-        <v>124</v>
+        <v>433</v>
       </c>
       <c r="B12" s="1">
-        <v>20800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="10" t="s">
-        <v>11</v>
+        <v>163</v>
       </c>
       <c r="B13" s="1">
-        <v>10400</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="9" t="s">
-        <v>433</v>
+        <v>658</v>
       </c>
       <c r="B14" s="1">
-        <v>41600</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>163</v>
+        <v>592</v>
       </c>
       <c r="B15" s="1">
-        <v>52000</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="11" t="s">
-        <v>650</v>
+        <v>659</v>
       </c>
       <c r="B16" s="1">
-        <v>52000</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
-        <v>584</v>
+        <v>6</v>
       </c>
       <c r="B17" s="1">
-        <v>57200</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="5" t="s">
-        <v>651</v>
+        <v>125</v>
       </c>
       <c r="B18" s="1">
-        <v>62400</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="5" t="s">
-        <v>6</v>
+        <v>481</v>
       </c>
       <c r="B19" s="1">
-        <v>13000</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="5" t="s">
-        <v>125</v>
+        <v>36</v>
       </c>
       <c r="B20" s="1">
-        <v>31200</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="B21" s="1">
-        <v>31200</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="5" t="s">
-        <v>36</v>
+        <v>492</v>
       </c>
       <c r="B22" s="1">
-        <v>52000</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="5" t="s">
-        <v>490</v>
+        <v>703</v>
       </c>
       <c r="B23" s="1">
-        <v>36400</v>
+        <v>520</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="5" t="s">
-        <v>491</v>
+        <v>409</v>
       </c>
       <c r="B24" s="1">
-        <v>41600</v>
+        <v>520</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="5" t="s">
-        <v>695</v>
+        <v>405</v>
       </c>
       <c r="B25" s="1">
         <v>520</v>
@@ -6113,71 +5980,71 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="5" t="s">
-        <v>409</v>
+        <v>442</v>
       </c>
       <c r="B26" s="1">
-        <v>520</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="5" t="s">
-        <v>405</v>
+        <v>493</v>
       </c>
       <c r="B27" s="1">
-        <v>520</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="5" t="s">
-        <v>442</v>
+        <v>494</v>
       </c>
       <c r="B28" s="1">
-        <v>7800</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="5" t="s">
-        <v>763</v>
+        <v>12</v>
       </c>
       <c r="B29" s="1">
-        <v>10400</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="5" t="s">
-        <v>492</v>
+        <v>1</v>
       </c>
       <c r="B30" s="1">
-        <v>20800</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="12" t="s">
-        <v>493</v>
+        <v>7</v>
       </c>
       <c r="B31" s="1">
-        <v>20800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="5" t="s">
-        <v>764</v>
+        <v>437</v>
       </c>
       <c r="B32" s="1">
-        <v>7800</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="5" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B33" s="1">
-        <v>5200</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="5" t="s">
-        <v>765</v>
+        <v>495</v>
       </c>
       <c r="B34" s="1">
         <v>7800</v>
@@ -6185,71 +6052,71 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="5" t="s">
-        <v>1</v>
+        <v>482</v>
       </c>
       <c r="B35" s="1">
-        <v>1300</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="5" t="s">
-        <v>7</v>
+        <v>441</v>
       </c>
       <c r="B36" s="1">
-        <v>5200</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="7" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="B37" s="1">
-        <v>3640</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="13" t="s">
-        <v>2</v>
+        <v>496</v>
       </c>
       <c r="B38" s="1">
-        <v>13000</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="11" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B39" s="1">
-        <v>7800</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="5" t="s">
-        <v>482</v>
+        <v>498</v>
       </c>
       <c r="B40" s="1">
-        <v>15600</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="5" t="s">
-        <v>766</v>
+        <v>562</v>
       </c>
       <c r="B41" s="1">
-        <v>10400</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="9" t="s">
-        <v>441</v>
+        <v>762</v>
       </c>
       <c r="B42" s="1">
-        <v>13000</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="5" t="s">
-        <v>443</v>
+        <v>733</v>
       </c>
       <c r="B43" s="1">
         <v>26000</v>
@@ -6257,23 +6124,23 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="7" t="s">
-        <v>495</v>
+        <v>29</v>
       </c>
       <c r="B44" s="1">
-        <v>31200</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>496</v>
+        <v>768</v>
       </c>
       <c r="B45" s="1">
-        <v>26000</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="7" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B46" s="1">
         <v>36400</v>
@@ -6281,247 +6148,247 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="14" t="s">
-        <v>767</v>
+        <v>439</v>
       </c>
       <c r="B47" s="1">
-        <v>182000</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="7" t="s">
-        <v>554</v>
+        <v>126</v>
       </c>
       <c r="B48" s="1">
-        <v>7800</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="13" t="s">
-        <v>768</v>
+        <v>500</v>
       </c>
       <c r="B49" s="1">
-        <v>67600</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="15" t="s">
-        <v>754</v>
+        <v>30</v>
       </c>
       <c r="B50" s="1">
-        <v>10400</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>725</v>
+        <v>430</v>
       </c>
       <c r="B51" s="1">
-        <v>26000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="5" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="B52" s="1">
-        <v>18200</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="5" t="s">
-        <v>769</v>
+        <v>127</v>
       </c>
       <c r="B53" s="1">
-        <v>72800</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="6" t="s">
-        <v>498</v>
+        <v>13</v>
       </c>
       <c r="B54" s="1">
-        <v>36400</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="16" t="s">
-        <v>439</v>
+        <v>116</v>
       </c>
       <c r="B55" s="1">
-        <v>7800</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="10" t="s">
-        <v>126</v>
+        <v>14</v>
       </c>
       <c r="B56" s="1">
-        <v>15600</v>
+        <v>67600</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="16" t="s">
-        <v>499</v>
+        <v>429</v>
       </c>
       <c r="B57" s="1">
-        <v>104000</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="17" t="s">
-        <v>770</v>
+        <v>563</v>
       </c>
       <c r="B58" s="1">
-        <v>41600</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="5" t="s">
-        <v>30</v>
+        <v>501</v>
       </c>
       <c r="B59" s="1">
-        <v>52000</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="5" t="s">
-        <v>430</v>
+        <v>502</v>
       </c>
       <c r="B60" s="1">
-        <v>52000</v>
+        <v>28600</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="10" t="s">
-        <v>8</v>
+        <v>597</v>
       </c>
       <c r="B61" s="1">
-        <v>78000</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="10" t="s">
-        <v>771</v>
+        <v>15</v>
       </c>
       <c r="B62" s="1">
-        <v>130000</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="5" t="s">
-        <v>772</v>
+        <v>16</v>
       </c>
       <c r="B63" s="1">
-        <v>114400</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="18" t="s">
-        <v>127</v>
+        <v>591</v>
       </c>
       <c r="B64" s="1">
-        <v>62400</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="10" t="s">
-        <v>13</v>
+        <v>699</v>
       </c>
       <c r="B65" s="1">
-        <v>31200</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="10" t="s">
-        <v>116</v>
+        <v>487</v>
       </c>
       <c r="B66" s="1">
-        <v>36400</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="5" t="s">
-        <v>14</v>
+        <v>746</v>
       </c>
       <c r="B67" s="1">
-        <v>67600</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="5" t="s">
-        <v>773</v>
+        <v>3</v>
       </c>
       <c r="B68" s="1">
-        <v>10400</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="19" t="s">
-        <v>774</v>
+        <v>17</v>
       </c>
       <c r="B69" s="1">
-        <v>7800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="5" t="s">
-        <v>429</v>
+        <v>128</v>
       </c>
       <c r="B70" s="1">
-        <v>20800</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="5" t="s">
-        <v>555</v>
+        <v>726</v>
       </c>
       <c r="B71" s="1">
-        <v>5200</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="9" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B72" s="1">
-        <v>31200</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="5" t="s">
-        <v>501</v>
+        <v>9</v>
       </c>
       <c r="B73" s="1">
-        <v>28600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="5" t="s">
-        <v>775</v>
+        <v>634</v>
       </c>
       <c r="B74" s="1">
-        <v>36400</v>
+        <v>291200</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="11" t="s">
-        <v>776</v>
+        <v>18</v>
       </c>
       <c r="B75" s="1">
-        <v>36400</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="20" t="s">
-        <v>589</v>
+        <v>19</v>
       </c>
       <c r="B76" s="1">
-        <v>5200</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="10" t="s">
-        <v>15</v>
+        <v>504</v>
       </c>
       <c r="B77" s="1">
         <v>5200</v>
@@ -6529,367 +6396,367 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="5" t="s">
-        <v>16</v>
+        <v>505</v>
       </c>
       <c r="B78" s="1">
-        <v>15600</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="5" t="s">
-        <v>583</v>
+        <v>25</v>
       </c>
       <c r="B79" s="1">
-        <v>7800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="13" t="s">
-        <v>691</v>
+        <v>564</v>
       </c>
       <c r="B80" s="1">
-        <v>18200</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="5" t="s">
-        <v>777</v>
+        <v>552</v>
       </c>
       <c r="B81" s="1">
-        <v>2080</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="5" t="s">
-        <v>487</v>
+        <v>553</v>
       </c>
       <c r="B82" s="1">
-        <v>5200</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="5" t="s">
-        <v>778</v>
+        <v>129</v>
       </c>
       <c r="B83" s="1">
-        <v>52000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="10" t="s">
-        <v>738</v>
+        <v>506</v>
       </c>
       <c r="B84" s="1">
-        <v>4160</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>3</v>
+        <v>763</v>
       </c>
       <c r="B85" s="1">
-        <v>62400</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="11" t="s">
-        <v>17</v>
+        <v>734</v>
       </c>
       <c r="B86" s="1">
-        <v>5200</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="17" t="s">
-        <v>128</v>
+        <v>731</v>
       </c>
       <c r="B87" s="1">
-        <v>10400</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="17" t="s">
-        <v>718</v>
+        <v>732</v>
       </c>
       <c r="B88" s="1">
-        <v>15600</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="17" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="B89" s="1">
-        <v>36400</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="21" t="s">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="B90" s="1">
-        <v>31200</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="5" t="s">
-        <v>626</v>
+        <v>665</v>
       </c>
       <c r="B91" s="1">
-        <v>291200</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="5" t="s">
-        <v>779</v>
+        <v>24</v>
       </c>
       <c r="B92" s="1">
-        <v>10400</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="5" t="s">
-        <v>18</v>
+        <v>751</v>
       </c>
       <c r="B93" s="1">
-        <v>13000</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B94" s="1">
-        <v>7800</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="5" t="s">
-        <v>503</v>
+        <v>436</v>
       </c>
       <c r="B95" s="1">
-        <v>5200</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="10" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B96" s="1">
-        <v>7800</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="5" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="B97" s="1">
-        <v>5200</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="5" t="s">
-        <v>556</v>
+        <v>509</v>
       </c>
       <c r="B98" s="1">
-        <v>6240</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="22" t="s">
-        <v>780</v>
+        <v>510</v>
       </c>
       <c r="B99" s="1">
-        <v>23400</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>781</v>
+        <v>727</v>
       </c>
       <c r="B100" s="1">
-        <v>18200</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>782</v>
+        <v>511</v>
       </c>
       <c r="B101" s="1">
-        <v>20800</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="5" t="s">
-        <v>783</v>
+        <v>21</v>
       </c>
       <c r="B102" s="1">
-        <v>18200</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="5" t="s">
-        <v>129</v>
+        <v>767</v>
       </c>
       <c r="B103" s="1">
-        <v>104000</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="5" t="s">
-        <v>505</v>
+        <v>483</v>
       </c>
       <c r="B104" s="1">
-        <v>7800</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>784</v>
+        <v>769</v>
       </c>
       <c r="B105" s="1">
-        <v>23400</v>
+        <v>67600</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>755</v>
+        <v>73</v>
       </c>
       <c r="B106" s="1">
-        <v>36400</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>726</v>
+        <v>74</v>
       </c>
       <c r="B107" s="1">
-        <v>36400</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>723</v>
+        <v>162</v>
       </c>
       <c r="B108" s="1">
-        <v>36400</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>724</v>
+        <v>130</v>
       </c>
       <c r="B109" s="1">
-        <v>36400</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>506</v>
+        <v>720</v>
       </c>
       <c r="B110" s="1">
-        <v>6240</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="4" t="s">
-        <v>100</v>
+        <v>435</v>
       </c>
       <c r="B111" s="1">
-        <v>93600</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>657</v>
+        <v>512</v>
       </c>
       <c r="B112" s="1">
-        <v>182000</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>24</v>
+        <v>513</v>
       </c>
       <c r="B113" s="1">
-        <v>93600</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>785</v>
+        <v>440</v>
       </c>
       <c r="B114" s="1">
-        <v>26000</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>743</v>
+        <v>514</v>
       </c>
       <c r="B115" s="1">
-        <v>130000</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B116" s="1">
-        <v>31200</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>436</v>
+        <v>661</v>
       </c>
       <c r="B117" s="1">
-        <v>20800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>786</v>
+        <v>662</v>
       </c>
       <c r="B118" s="1">
-        <v>62400</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>115</v>
+        <v>599</v>
       </c>
       <c r="B119" s="1">
-        <v>36400</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="B120" s="1">
-        <v>10400</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="B121" s="1">
-        <v>7800</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>787</v>
+        <v>406</v>
       </c>
       <c r="B122" s="1">
-        <v>7800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>719</v>
+        <v>557</v>
       </c>
       <c r="B123" s="1">
         <v>7800</v>
@@ -6897,7 +6764,7 @@
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>788</v>
+        <v>444</v>
       </c>
       <c r="B124" s="1">
         <v>7800</v>
@@ -6905,322 +6772,42 @@
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>509</v>
+        <v>567</v>
       </c>
       <c r="B125" s="1">
-        <v>39000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>21</v>
+        <v>568</v>
       </c>
       <c r="B126" s="1">
-        <v>26000</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>759</v>
+        <v>438</v>
       </c>
       <c r="B127" s="1">
-        <v>78000</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>483</v>
+        <v>635</v>
       </c>
       <c r="B128" s="1">
-        <v>78000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>789</v>
+        <v>10</v>
       </c>
       <c r="B129" s="1">
-        <v>67600</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2">
-      <c r="A130" t="s">
-        <v>790</v>
-      </c>
-      <c r="B130" s="1">
-        <v>93600</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2">
-      <c r="A131" t="s">
-        <v>791</v>
-      </c>
-      <c r="B131" s="1">
-        <v>52000</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2">
-      <c r="A132" t="s">
-        <v>792</v>
-      </c>
-      <c r="B132" s="1">
-        <v>46800</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" t="s">
-        <v>73</v>
-      </c>
-      <c r="B133" s="1">
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2">
-      <c r="A134" t="s">
-        <v>74</v>
-      </c>
-      <c r="B134" s="1">
-        <v>5200</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2">
-      <c r="A135" t="s">
-        <v>162</v>
-      </c>
-      <c r="B135" s="1">
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2">
-      <c r="A136" t="s">
-        <v>793</v>
-      </c>
-      <c r="B136" s="1">
-        <v>39000</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2">
-      <c r="A137" t="s">
-        <v>130</v>
-      </c>
-      <c r="B137" s="1">
         <v>18200</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2">
-      <c r="A138" t="s">
-        <v>794</v>
-      </c>
-      <c r="B138" s="1">
-        <v>1560</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2">
-      <c r="A139" t="s">
-        <v>712</v>
-      </c>
-      <c r="B139" s="1">
-        <v>7800</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2">
-      <c r="A140" t="s">
-        <v>435</v>
-      </c>
-      <c r="B140" s="1">
-        <v>20800</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2">
-      <c r="A141" t="s">
-        <v>510</v>
-      </c>
-      <c r="B141" s="1">
-        <v>20800</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2">
-      <c r="A142" t="s">
-        <v>511</v>
-      </c>
-      <c r="B142" s="1">
-        <v>36400</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2">
-      <c r="A143" t="s">
-        <v>440</v>
-      </c>
-      <c r="B143" s="1">
-        <v>10400</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2">
-      <c r="A144" t="s">
-        <v>512</v>
-      </c>
-      <c r="B144" s="1">
-        <v>20800</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" t="s">
-        <v>795</v>
-      </c>
-      <c r="B145" s="1">
-        <v>5200</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2">
-      <c r="A146" t="s">
-        <v>4</v>
-      </c>
-      <c r="B146" s="1">
-        <v>7800</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2">
-      <c r="A147" t="s">
-        <v>796</v>
-      </c>
-      <c r="B147" s="1">
-        <v>5200</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2">
-      <c r="A148" t="s">
-        <v>653</v>
-      </c>
-      <c r="B148" s="1">
-        <v>5200</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="A149" t="s">
-        <v>654</v>
-      </c>
-      <c r="B149" s="1">
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2">
-      <c r="A150" t="s">
-        <v>591</v>
-      </c>
-      <c r="B150" s="1">
-        <v>5200</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2">
-      <c r="A151" t="s">
-        <v>557</v>
-      </c>
-      <c r="B151" s="1">
-        <v>5200</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2">
-      <c r="A152" t="s">
-        <v>513</v>
-      </c>
-      <c r="B152" s="1">
-        <v>15600</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2">
-      <c r="A153" t="s">
-        <v>406</v>
-      </c>
-      <c r="B153" s="1">
-        <v>5200</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2">
-      <c r="A154" t="s">
-        <v>549</v>
-      </c>
-      <c r="B154" s="1">
-        <v>7800</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2">
-      <c r="A155" t="s">
-        <v>444</v>
-      </c>
-      <c r="B155" s="1">
-        <v>7800</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
-      <c r="A156" t="s">
-        <v>559</v>
-      </c>
-      <c r="B156" s="1">
-        <v>13000</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2">
-      <c r="A157" t="s">
-        <v>560</v>
-      </c>
-      <c r="B157" s="1">
-        <v>7800</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2">
-      <c r="A158" t="s">
-        <v>797</v>
-      </c>
-      <c r="B158" s="1">
-        <v>7800</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2">
-      <c r="A159" t="s">
-        <v>438</v>
-      </c>
-      <c r="B159" s="1">
-        <v>5200</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2">
-      <c r="A160" t="s">
-        <v>798</v>
-      </c>
-      <c r="B160" s="1">
-        <v>5200</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2">
-      <c r="A161" t="s">
-        <v>799</v>
-      </c>
-      <c r="B161" s="1">
-        <v>6240</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="A162" t="s">
-        <v>627</v>
-      </c>
-      <c r="B162" s="1">
-        <v>52000</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2">
-      <c r="A163" t="s">
-        <v>10</v>
-      </c>
-      <c r="B163" s="1">
-        <v>18200</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2">
-      <c r="A164" t="s">
-        <v>800</v>
-      </c>
-      <c r="B164" s="1">
-        <v>5200</v>
       </c>
     </row>
   </sheetData>
@@ -7230,7 +6817,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B260"/>
+  <dimension ref="A1:B259"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="83.85546875" bestFit="1" customWidth="1"/>
@@ -7255,7 +6842,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="17" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="B3" s="1">
         <v>3120</v>
@@ -7263,7 +6850,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="26" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="B4" s="1">
         <v>13000</v>
@@ -7279,7 +6866,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="25" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="B6" s="1">
         <v>104000</v>
@@ -7311,7 +6898,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="B10" s="1">
         <v>93600</v>
@@ -7335,7 +6922,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="17" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="B13" s="1">
         <v>4160</v>
@@ -7343,7 +6930,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="17" t="s">
-        <v>801</v>
+        <v>516</v>
       </c>
       <c r="B14" s="1">
         <v>41600</v>
@@ -7367,7 +6954,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="17" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="B17" s="1">
         <v>20800</v>
@@ -7375,7 +6962,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="17" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="B18" s="1">
         <v>5200</v>
@@ -7399,7 +6986,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="17" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="B21" s="1">
         <v>52000</v>
@@ -7407,7 +6994,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="B22" s="1">
         <v>57200</v>
@@ -7415,7 +7002,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="17" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="B23" s="1">
         <v>62400</v>
@@ -7463,7 +7050,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="17" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B29" s="1">
         <v>15600</v>
@@ -7511,7 +7098,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="17" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="B35" s="1">
         <v>520</v>
@@ -7535,7 +7122,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="28" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="B38" s="1">
         <v>62400</v>
@@ -7543,7 +7130,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="17" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="B39" s="1">
         <v>62400</v>
@@ -7551,7 +7138,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="17" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="B40" s="1">
         <v>52000</v>
@@ -7559,7 +7146,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="17" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="B41" s="1">
         <v>52000</v>
@@ -7567,7 +7154,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="26" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B42" s="1">
         <v>5200</v>
@@ -7631,7 +7218,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="17" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B50" s="1">
         <v>3640</v>
@@ -7647,7 +7234,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="17" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B52" s="1">
         <v>20800</v>
@@ -7679,7 +7266,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="17" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="B56" s="1">
         <v>15600</v>
@@ -7687,7 +7274,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="17" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="B57" s="1">
         <v>52000</v>
@@ -7695,7 +7282,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="17" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="B58" s="1">
         <v>39000</v>
@@ -7711,7 +7298,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="17" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="B60" s="1">
         <v>7800</v>
@@ -7743,7 +7330,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="17" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="B64" s="1">
         <v>15600</v>
@@ -7751,7 +7338,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="17" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="B65" s="1">
         <v>26000</v>
@@ -7767,7 +7354,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="17" t="s">
-        <v>802</v>
+        <v>770</v>
       </c>
       <c r="B67" s="1">
         <v>83200</v>
@@ -7791,7 +7378,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="17" t="s">
-        <v>803</v>
+        <v>771</v>
       </c>
       <c r="B70" s="1">
         <v>83200</v>
@@ -7855,7 +7442,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="17" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="B78" s="1">
         <v>52000</v>
@@ -7999,7 +7586,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="17" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B96" s="1">
         <v>36400</v>
@@ -8007,7 +7594,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="17" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="B97" s="1">
         <v>31200</v>
@@ -8015,7 +7602,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="17" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="B98" s="1">
         <v>36400</v>
@@ -8031,7 +7618,7 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="17" t="s">
-        <v>804</v>
+        <v>772</v>
       </c>
       <c r="B100" s="1">
         <v>72800</v>
@@ -8039,7 +7626,7 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="17" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="B101" s="1">
         <v>72800</v>
@@ -8047,7 +7634,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="31" t="s">
-        <v>805</v>
+        <v>773</v>
       </c>
       <c r="B102" s="1">
         <v>93600</v>
@@ -8055,7 +7642,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="B103" s="1">
         <v>4160</v>
@@ -8063,7 +7650,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="17" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B104" s="1">
         <v>13000</v>
@@ -8079,7 +7666,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="17" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="B106" s="1">
         <v>13000</v>
@@ -8087,7 +7674,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="17" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="B107" s="1">
         <v>5200</v>
@@ -8095,7 +7682,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="17" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="B108" s="1">
         <v>31200</v>
@@ -8135,7 +7722,7 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="B113" s="1">
         <v>5200</v>
@@ -8143,7 +7730,7 @@
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="B114" s="1">
         <v>7800</v>
@@ -8151,7 +7738,7 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="17" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="B115" s="1">
         <v>7800</v>
@@ -8183,7 +7770,7 @@
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="17" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="B119" s="1">
         <v>7800</v>
@@ -8191,7 +7778,7 @@
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="17" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="B120" s="1">
         <v>10400</v>
@@ -8199,7 +7786,7 @@
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="B121" s="1">
         <v>6240</v>
@@ -8207,7 +7794,7 @@
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="17" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="B122" s="1">
         <v>18200</v>
@@ -8215,7 +7802,7 @@
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="17" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="B123" s="1">
         <v>18200</v>
@@ -8231,7 +7818,7 @@
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="17" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="B125" s="1">
         <v>4160</v>
@@ -8271,7 +7858,7 @@
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="17" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="B130" s="1">
         <v>5200</v>
@@ -8279,7 +7866,7 @@
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="17" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="B131" s="1">
         <v>5200</v>
@@ -8287,7 +7874,7 @@
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="17" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="B132" s="1">
         <v>72800</v>
@@ -8295,7 +7882,7 @@
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="28" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="B133" s="1">
         <v>31200</v>
@@ -8311,7 +7898,7 @@
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="33" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="B135" s="1">
         <v>291200</v>
@@ -8319,7 +7906,7 @@
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="17" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="B136" s="1">
         <v>301600</v>
@@ -8327,7 +7914,7 @@
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="17" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="B137" s="1">
         <v>312000</v>
@@ -8391,7 +7978,7 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="17" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="B145" s="1">
         <v>5200</v>
@@ -8423,7 +8010,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="17" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="B149" s="1">
         <v>6240</v>
@@ -8431,7 +8018,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="17" t="s">
-        <v>806</v>
+        <v>522</v>
       </c>
       <c r="B150" s="1">
         <v>23400</v>
@@ -8439,7 +8026,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>807</v>
+        <v>554</v>
       </c>
       <c r="B151" s="1">
         <v>18200</v>
@@ -8463,7 +8050,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="17" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="B154" s="1">
         <v>39000</v>
@@ -8471,7 +8058,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="17" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="B155" s="1">
         <v>39000</v>
@@ -8511,7 +8098,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="17" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="B160" s="1">
         <v>36400</v>
@@ -8519,7 +8106,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="17" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="B161" s="1">
         <v>41600</v>
@@ -8527,7 +8114,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="17" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="B162" s="1">
         <v>36400</v>
@@ -8535,7 +8122,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="17" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="B163" s="1">
         <v>41600</v>
@@ -8543,7 +8130,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="17" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="B164" s="1">
         <v>780</v>
@@ -8575,7 +8162,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="17" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="B168" s="1">
         <v>182000</v>
@@ -8583,7 +8170,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="17" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="B169" s="1">
         <v>187200</v>
@@ -8591,7 +8178,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="17" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="B170" s="1">
         <v>192400</v>
@@ -8599,7 +8186,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="17" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="B171" s="1">
         <v>182000</v>
@@ -8607,7 +8194,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="17" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="B172" s="1">
         <v>182000</v>
@@ -8615,7 +8202,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="17" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="B173" s="1">
         <v>182000</v>
@@ -8623,7 +8210,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="17" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="B174" s="1">
         <v>130000</v>
@@ -8647,7 +8234,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="17" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="B177" s="1">
         <v>104000</v>
@@ -8671,7 +8258,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="34" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="B180" s="1">
         <v>20800</v>
@@ -8679,7 +8266,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="B181" s="1">
         <v>20800</v>
@@ -8687,7 +8274,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="B182" s="1">
         <v>36400</v>
@@ -8695,7 +8282,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="17" t="s">
-        <v>808</v>
+        <v>523</v>
       </c>
       <c r="B183" s="1">
         <v>62400</v>
@@ -8703,7 +8290,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="17" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="B184" s="1">
         <v>31200</v>
@@ -8719,7 +8306,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="17" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="B186" s="1">
         <v>46800</v>
@@ -8727,7 +8314,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="17" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="B187" s="1">
         <v>10400</v>
@@ -8735,7 +8322,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="B188" s="1">
         <v>15600</v>
@@ -8751,7 +8338,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="B190" s="1">
         <v>18200</v>
@@ -8759,7 +8346,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="B191" s="1">
         <v>7800</v>
@@ -8783,7 +8370,7 @@
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B194" s="1">
         <v>39000</v>
@@ -8807,7 +8394,7 @@
     </row>
     <row r="197" spans="1:2">
       <c r="A197" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="B197" s="1">
         <v>88400</v>
@@ -8839,7 +8426,7 @@
     </row>
     <row r="201" spans="1:2">
       <c r="A201" s="4" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="B201" s="1">
         <v>72800</v>
@@ -8847,7 +8434,7 @@
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="B202" s="1">
         <v>93600</v>
@@ -9039,7 +8626,7 @@
     </row>
     <row r="226" spans="1:2">
       <c r="A226" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="B226" s="1">
         <v>15600</v>
@@ -9071,7 +8658,7 @@
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="B230" s="1">
         <v>20800</v>
@@ -9095,7 +8682,7 @@
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="B233" s="1">
         <v>18200</v>
@@ -9127,7 +8714,7 @@
     </row>
     <row r="237" spans="1:2">
       <c r="A237" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="B237" s="1">
         <v>36400</v>
@@ -9135,7 +8722,7 @@
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="B238" s="1">
         <v>7800</v>
@@ -9143,7 +8730,7 @@
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="B239" s="1">
         <v>5200</v>
@@ -9151,7 +8738,7 @@
     </row>
     <row r="240" spans="1:2">
       <c r="A240" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="B240" s="1">
         <v>5200</v>
@@ -9159,7 +8746,7 @@
     </row>
     <row r="241" spans="1:2">
       <c r="A241" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="B241" s="1">
         <v>5200</v>
@@ -9183,7 +8770,7 @@
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="B244" s="1">
         <v>7800</v>
@@ -9191,7 +8778,7 @@
     </row>
     <row r="245" spans="1:2">
       <c r="A245" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="B245" s="1">
         <v>10400</v>
@@ -9199,7 +8786,7 @@
     </row>
     <row r="246" spans="1:2">
       <c r="A246" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="B246" s="1">
         <v>15600</v>
@@ -9207,7 +8794,7 @@
     </row>
     <row r="247" spans="1:2">
       <c r="A247" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="B247" s="1">
         <v>13000</v>
@@ -9215,7 +8802,7 @@
     </row>
     <row r="248" spans="1:2">
       <c r="A248" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="B248" s="1">
         <v>7800</v>
@@ -9223,7 +8810,7 @@
     </row>
     <row r="249" spans="1:2">
       <c r="A249" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="B249" s="1">
         <v>7800</v>
@@ -9231,7 +8818,7 @@
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="B250" s="1">
         <v>7800</v>
@@ -9239,7 +8826,7 @@
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="B251" s="1">
         <v>10400</v>
@@ -9247,7 +8834,7 @@
     </row>
     <row r="252" spans="1:2">
       <c r="A252" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="B252" s="1">
         <v>2600</v>
@@ -9255,7 +8842,7 @@
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="B253" s="1">
         <v>119600</v>
@@ -9263,7 +8850,7 @@
     </row>
     <row r="254" spans="1:2">
       <c r="A254" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="B254" s="1">
         <v>10400</v>
@@ -9271,49 +8858,41 @@
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>797</v>
+        <v>448</v>
       </c>
       <c r="B255" s="1">
-        <v>7800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>448</v>
+        <v>693</v>
       </c>
       <c r="B256" s="1">
-        <v>5200</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>685</v>
+        <v>112</v>
       </c>
       <c r="B257" s="1">
-        <v>52000</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
-        <v>112</v>
+        <v>155</v>
       </c>
       <c r="B258" s="1">
-        <v>31200</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B259" s="1">
-        <v>18200</v>
-      </c>
-    </row>
-    <row r="260" spans="1:2">
-      <c r="A260" t="s">
-        <v>156</v>
-      </c>
-      <c r="B260" s="1">
         <v>20800</v>
       </c>
     </row>
@@ -9324,7 +8903,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52.140625" customWidth="1"/>
@@ -9341,7 +8920,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="35" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="B2" s="1">
         <v>93600</v>
@@ -9349,18 +8928,18 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="36" t="s">
-        <v>809</v>
+        <v>600</v>
       </c>
       <c r="B3" s="1">
-        <v>70200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="36" t="s">
-        <v>810</v>
+        <v>775</v>
       </c>
       <c r="B4" s="1">
-        <v>46800</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9368,148 +8947,148 @@
         <v>592</v>
       </c>
       <c r="B5" s="1">
-        <v>4160</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="36" t="s">
-        <v>811</v>
+        <v>659</v>
       </c>
       <c r="B6" s="1">
-        <v>31200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="36" t="s">
-        <v>584</v>
+        <v>528</v>
       </c>
       <c r="B7" s="1">
-        <v>57200</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="36" t="s">
-        <v>651</v>
+        <v>529</v>
       </c>
       <c r="B8" s="1">
-        <v>62400</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="36" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="B9" s="1">
-        <v>13000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="36" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="B10" s="1">
-        <v>18200</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="36" t="s">
-        <v>525</v>
+        <v>562</v>
       </c>
       <c r="B11" s="1">
-        <v>52000</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="36" t="s">
-        <v>526</v>
+        <v>733</v>
       </c>
       <c r="B12" s="1">
-        <v>46800</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="35" t="s">
-        <v>812</v>
+        <v>532</v>
       </c>
       <c r="B13" s="1">
-        <v>6240</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="36" t="s">
-        <v>554</v>
+        <v>533</v>
       </c>
       <c r="B14" s="1">
-        <v>7800</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="36" t="s">
-        <v>725</v>
+        <v>702</v>
       </c>
       <c r="B15" s="1">
-        <v>26000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="36" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="B16" s="1">
-        <v>20800</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="36" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="B17" s="1">
-        <v>18200</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="36" t="s">
-        <v>694</v>
+        <v>563</v>
       </c>
       <c r="B18" s="1">
-        <v>52000</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="35" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="B19" s="1">
-        <v>26000</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="36" t="s">
-        <v>813</v>
+        <v>776</v>
       </c>
       <c r="B20" s="1">
-        <v>31200</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="36" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="B21" s="1">
-        <v>13000</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="36" t="s">
-        <v>555</v>
+        <v>695</v>
       </c>
       <c r="B22" s="1">
-        <v>5200</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="36" t="s">
-        <v>531</v>
+        <v>487</v>
       </c>
       <c r="B23" s="1">
         <v>5200</v>
@@ -9517,183 +9096,183 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="36" t="s">
-        <v>532</v>
+        <v>746</v>
       </c>
       <c r="B24" s="1">
-        <v>5200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="36" t="s">
-        <v>687</v>
+        <v>538</v>
       </c>
       <c r="B25" s="1">
-        <v>18200</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="36" t="s">
-        <v>487</v>
+        <v>539</v>
       </c>
       <c r="B26" s="1">
-        <v>5200</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="36" t="s">
-        <v>738</v>
+        <v>540</v>
       </c>
       <c r="B27" s="1">
-        <v>4160</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="B28">
-        <v>7800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="B29">
-        <v>13000</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="B30">
-        <v>10400</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>536</v>
+        <v>642</v>
       </c>
       <c r="B31">
-        <v>5200</v>
+        <v>312000</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>537</v>
+        <v>564</v>
       </c>
       <c r="B32">
-        <v>62400</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>538</v>
+        <v>737</v>
       </c>
       <c r="B33">
-        <v>57200</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>634</v>
+        <v>738</v>
       </c>
       <c r="B34">
-        <v>312000</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="B35">
-        <v>6240</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>729</v>
+        <v>694</v>
       </c>
       <c r="B36">
-        <v>46800</v>
+        <v>187200</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>730</v>
+        <v>647</v>
       </c>
       <c r="B37">
-        <v>46800</v>
+        <v>192400</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>539</v>
+        <v>751</v>
       </c>
       <c r="B38">
-        <v>15600</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>686</v>
+        <v>545</v>
       </c>
       <c r="B39">
-        <v>187200</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>639</v>
+        <v>546</v>
       </c>
       <c r="B40">
-        <v>192400</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>743</v>
+        <v>547</v>
       </c>
       <c r="B41">
-        <v>130000</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>540</v>
+        <v>599</v>
       </c>
       <c r="B42">
-        <v>46800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="B43">
-        <v>26000</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>814</v>
+        <v>560</v>
       </c>
       <c r="B44">
-        <v>2600</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>815</v>
+        <v>406</v>
       </c>
       <c r="B45">
-        <v>2600</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>816</v>
+        <v>557</v>
       </c>
       <c r="B46">
         <v>7800</v>
@@ -9701,145 +9280,49 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>542</v>
+        <v>567</v>
       </c>
       <c r="B47">
-        <v>23400</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>817</v>
+        <v>568</v>
       </c>
       <c r="B48">
-        <v>20800</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>818</v>
+        <v>548</v>
       </c>
       <c r="B49">
-        <v>10400</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>819</v>
+        <v>549</v>
       </c>
       <c r="B50">
-        <v>13000</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>591</v>
+        <v>648</v>
       </c>
       <c r="B51">
-        <v>5200</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>820</v>
+        <v>550</v>
       </c>
       <c r="B52">
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" t="s">
-        <v>821</v>
-      </c>
-      <c r="B53">
-        <v>5200</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" t="s">
-        <v>822</v>
-      </c>
-      <c r="B54">
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" t="s">
-        <v>551</v>
-      </c>
-      <c r="B55">
-        <v>36400</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" t="s">
-        <v>552</v>
-      </c>
-      <c r="B56">
-        <v>15600</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" t="s">
-        <v>406</v>
-      </c>
-      <c r="B57">
-        <v>5200</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" t="s">
-        <v>549</v>
-      </c>
-      <c r="B58">
-        <v>7800</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" t="s">
-        <v>559</v>
-      </c>
-      <c r="B59">
-        <v>13000</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" t="s">
-        <v>560</v>
-      </c>
-      <c r="B60">
-        <v>7800</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" t="s">
-        <v>543</v>
-      </c>
-      <c r="B61">
-        <v>5200</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" t="s">
-        <v>544</v>
-      </c>
-      <c r="B62">
-        <v>5200</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" t="s">
-        <v>640</v>
-      </c>
-      <c r="B63">
-        <v>52000</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" t="s">
-        <v>545</v>
-      </c>
-      <c r="B64">
         <v>15600</v>
       </c>
     </row>
@@ -9850,7 +9333,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="58.140625" customWidth="1"/>
@@ -9899,7 +9382,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="B6" s="1">
         <v>20800</v>
@@ -9915,7 +9398,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="B8" s="1">
         <v>20800</v>
@@ -9923,7 +9406,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="B9" s="1">
         <v>4680</v>
@@ -9931,7 +9414,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="B10" s="1">
         <v>20800</v>
@@ -9955,7 +9438,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="B13" s="1">
         <v>4680</v>
@@ -9963,7 +9446,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="B14" s="1">
         <v>3640</v>
@@ -9971,7 +9454,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="B15" s="1">
         <v>3120</v>
@@ -9987,7 +9470,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="B17" s="1">
         <v>4160</v>
@@ -9995,7 +9478,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="B18" s="1">
         <v>96200</v>
@@ -10003,7 +9486,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="B19" s="1">
         <v>109200</v>
@@ -10011,7 +9494,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="B20" s="1">
         <v>127400</v>
@@ -10035,7 +9518,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="B23" s="1">
         <v>52000</v>
@@ -10043,7 +9526,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="B24" s="1">
         <v>57200</v>
@@ -10051,7 +9534,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="B25" s="1">
         <v>62400</v>
@@ -10059,7 +9542,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="B26" s="1">
         <v>72800</v>
@@ -10067,7 +9550,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="B27" s="1">
         <v>85800</v>
@@ -10075,7 +9558,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="B28" s="1">
         <v>91000</v>
@@ -10083,7 +9566,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="B29" s="1">
         <v>520</v>
@@ -10115,7 +9598,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="B33" s="1">
         <v>7800</v>
@@ -10131,7 +9614,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="B35" s="1">
         <v>5200</v>
@@ -10139,39 +9622,39 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>823</v>
+        <v>407</v>
       </c>
       <c r="B36" s="1">
-        <v>2600</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>407</v>
+        <v>260</v>
       </c>
       <c r="B37" s="1">
-        <v>4160</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>260</v>
+        <v>428</v>
       </c>
       <c r="B38" s="1">
-        <v>15600</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>428</v>
+        <v>487</v>
       </c>
       <c r="B39" s="1">
-        <v>2600</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>487</v>
+        <v>746</v>
       </c>
       <c r="B40" s="1">
         <v>4160</v>
@@ -10179,47 +9662,47 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>738</v>
+        <v>394</v>
       </c>
       <c r="B41" s="1">
-        <v>4160</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B42" s="1">
-        <v>6240</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B43" s="1">
-        <v>5200</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>396</v>
+        <v>649</v>
       </c>
       <c r="B44" s="1">
-        <v>7800</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>641</v>
+        <v>397</v>
       </c>
       <c r="B45" s="1">
-        <v>3640</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B46" s="1">
         <v>6240</v>
@@ -10227,55 +9710,55 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B47" s="1">
-        <v>6240</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>399</v>
+        <v>739</v>
       </c>
       <c r="B48" s="1">
-        <v>4160</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>731</v>
+        <v>564</v>
       </c>
       <c r="B49" s="1">
-        <v>3120</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>556</v>
+        <v>729</v>
       </c>
       <c r="B50" s="1">
-        <v>6240</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="B51" s="1">
-        <v>31200</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>722</v>
+        <v>763</v>
       </c>
       <c r="B52" s="1">
-        <v>33800</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>755</v>
+        <v>734</v>
       </c>
       <c r="B53" s="1">
         <v>36400</v>
@@ -10283,7 +9766,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="B54" s="1">
         <v>36400</v>
@@ -10291,39 +9774,39 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="B55" s="1">
-        <v>36400</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="B56" s="1">
-        <v>41600</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
       <c r="B57" s="1">
-        <v>36400</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>728</v>
+        <v>737</v>
       </c>
       <c r="B58" s="1">
-        <v>41600</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>729</v>
+        <v>738</v>
       </c>
       <c r="B59" s="1">
         <v>46800</v>
@@ -10331,95 +9814,95 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>730</v>
+        <v>751</v>
       </c>
       <c r="B60" s="1">
-        <v>46800</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>743</v>
+        <v>650</v>
       </c>
       <c r="B61" s="1">
-        <v>130000</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>642</v>
+        <v>551</v>
       </c>
       <c r="B62" s="1">
-        <v>6240</v>
+        <v>9360</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>546</v>
+        <v>400</v>
       </c>
       <c r="B63" s="1">
-        <v>9360</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>400</v>
+        <v>664</v>
       </c>
       <c r="B64" s="1">
-        <v>10400</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>656</v>
+        <v>401</v>
       </c>
       <c r="B65" s="1">
-        <v>7800</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B66" s="1">
-        <v>6240</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B67" s="1">
-        <v>3640</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>403</v>
+        <v>593</v>
       </c>
       <c r="B68" s="1">
-        <v>6240</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>585</v>
+        <v>404</v>
       </c>
       <c r="B69" s="1">
-        <v>4160</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>404</v>
+        <v>599</v>
       </c>
       <c r="B70" s="1">
-        <v>6240</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="B71" s="1">
         <v>5200</v>
@@ -10427,7 +9910,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>557</v>
+        <v>566</v>
       </c>
       <c r="B72" s="1">
         <v>5200</v>
@@ -10435,65 +9918,57 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>558</v>
+        <v>655</v>
       </c>
       <c r="B73" s="1">
-        <v>5200</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="B74" s="1">
-        <v>3640</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>648</v>
+        <v>406</v>
       </c>
       <c r="B75" s="1">
-        <v>2600</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>406</v>
+        <v>557</v>
       </c>
       <c r="B76" s="1">
-        <v>5200</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="B77" s="1">
-        <v>7800</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="B78" s="1">
-        <v>13000</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="B79" s="1">
-        <v>7800</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80" t="s">
-        <v>561</v>
-      </c>
-      <c r="B80" s="1">
         <v>2600</v>
       </c>
     </row>

--- a/clientes/files/TODITICO_CATÁLOGO.xlsx
+++ b/clientes/files/TODITICO_CATÁLOGO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\520 Actual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\510 Con lo nuevo de Mexico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5A1C31-4F2B-47D6-BF18-13D1D76041A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D94514-2E7D-4928-BAC6-44C6F5237A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DAEWOO TICO" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="826">
   <si>
     <t>DESCRIPCION</t>
   </si>
@@ -1501,9 +1501,6 @@
     <t>AFORADOR ATOS</t>
   </si>
   <si>
-    <t>AROS STD, 0.50 ATOS, PICANTO 1RA, I10</t>
-  </si>
-  <si>
     <t>BOMBA DE COMBUSTIBLE ELECTRICA ATOS</t>
   </si>
   <si>
@@ -1555,9 +1552,6 @@
     <t>OBTURADORES JUEGO ATOS, PICANTO 1RA, I10</t>
   </si>
   <si>
-    <t>PISTONES STD, 0.50 ATOS, PICANTO 1RA, I10</t>
-  </si>
-  <si>
     <t>PORTACARBON DE MOTOR DE ARRANQUE ATOS, PICANTO 1RA, I10</t>
   </si>
   <si>
@@ -1579,9 +1573,6 @@
     <t>TENSOR DE CORREA DE DISTRIBUCION ATOS, PICANTO 1RA, I10.</t>
   </si>
   <si>
-    <t>AROS STD, 0.50 PICANTO 1RA, ATOS, I10</t>
-  </si>
-  <si>
     <t>BOTA DE CREMALLERA PICANTO 1RA Y 2DA</t>
   </si>
   <si>
@@ -1597,12 +1588,6 @@
     <t>ESFERICAS PICANTO 1RA (DE ROSCA)</t>
   </si>
   <si>
-    <t>METALES APOYO STD, 0.50, 0.25 PICANTO 1RA, ATOS, I10</t>
-  </si>
-  <si>
-    <t>PISTONES STD, 0.50 PICANTO 1RA, ATOS, I10</t>
-  </si>
-  <si>
     <t>PORTACARBON DE MOTOR DE ARRANQUE PICANTO 1RA, ATOS, I10</t>
   </si>
   <si>
@@ -1687,15 +1672,6 @@
     <t>REFRIGERANTE AL 30% 5LT</t>
   </si>
   <si>
-    <t>METALES APOYO STD, 0.50, 0.25 ATOS, PICANTO 1RA, I10</t>
-  </si>
-  <si>
-    <t>METALES BIELA STD, 0.50, 0.25 ATOS, PICANTO 1RA, I10</t>
-  </si>
-  <si>
-    <t>METALES BIELA STD, 0.50, 0.25 PICANTO 1RA, ATOS, I10</t>
-  </si>
-  <si>
     <t>ELECTROVENTILADOR PICANTO 1RA</t>
   </si>
   <si>
@@ -2335,12 +2311,132 @@
     <t>PUNTAS DE HOMOCINÉTICAS EXTERIORES ATOS 1.0 PAREJA</t>
   </si>
   <si>
+    <t>AMORTIGUADOR DE MALETERO ATOS</t>
+  </si>
+  <si>
+    <t>ÁRBOL DE LEVAS ATOS</t>
+  </si>
+  <si>
+    <t>AROS STD, 0,75, 0.50 ATOS, PICANTO 1RA, I10</t>
+  </si>
+  <si>
+    <t>BOTÓN DE ESTACIONAMIENTO ATOS</t>
+  </si>
+  <si>
+    <t>BRIDA DE AGUA ATOS</t>
+  </si>
+  <si>
+    <t>BUJE DE EJE TRASERO ATOS</t>
+  </si>
+  <si>
+    <t>CABLE DE CAPOT ATOS</t>
+  </si>
+  <si>
+    <t>CAPOT ATOS</t>
+  </si>
+  <si>
+    <t>CHUCHO DE ARRANQUE ATOS</t>
+  </si>
+  <si>
     <t>CONDENSADOR  ATOS</t>
   </si>
   <si>
+    <t>CREMALLERA DE PUERTA DELANTERA ATOS</t>
+  </si>
+  <si>
+    <t>DEFENSA DELANTERA COMPLETA ATOS</t>
+  </si>
+  <si>
+    <t>DEFENSA TRASERA COMPLETA ATOS</t>
+  </si>
+  <si>
+    <t>EMBLEMA HYUNDAI 10 CM</t>
+  </si>
+  <si>
+    <t>EMBLEMA HYUNDAI 8 CM</t>
+  </si>
+  <si>
+    <t>FARO TRASERO DERECHO ATOS</t>
+  </si>
+  <si>
+    <t>FARO TRASERO IZQUIERDO ATOS</t>
+  </si>
+  <si>
+    <t>GOMA DE PEDAL DE FRENO Y EMBRAGUE ATOS</t>
+  </si>
+  <si>
+    <t>GUARDAFANGO ATOS</t>
+  </si>
+  <si>
+    <t>LOGO DEL TEXTO ATOS</t>
+  </si>
+  <si>
+    <t>METALES APOYO STD, 0.75, 0.50, 0.25 ATOS, PICANTO 1RA, I10</t>
+  </si>
+  <si>
+    <t>METALES BIELA STD, 0.75, 0.50, 0.25 ATOS, PICANTO 1RA, I10</t>
+  </si>
+  <si>
+    <t>MOLDURA DE DEFENSA DELANTERA ATOS</t>
+  </si>
+  <si>
+    <t>MOLDURA DE PUERTA ATOS</t>
+  </si>
+  <si>
+    <t>NEBLINERO ATOS</t>
+  </si>
+  <si>
+    <t>PARRILLA DE DEFENSA ATOS</t>
+  </si>
+  <si>
+    <t>PISTONES STD, 0.75, 0.50 ATOS, PICANTO 1RA, I10</t>
+  </si>
+  <si>
+    <t>PULMÓN DE MARCHA ATRÁS ATOS</t>
+  </si>
+  <si>
+    <t>PULMÓN DEL STOP DE FRENO ATOS</t>
+  </si>
+  <si>
     <t>RADIADOR MECANICO ATOS</t>
   </si>
   <si>
+    <t>REFUERZO DE DEFENSA DELANTERA ATOS</t>
+  </si>
+  <si>
+    <t>REJILLA ATOS (FILO CROMADO)</t>
+  </si>
+  <si>
+    <t>REJILLA ATOS (LÍNEAS CROMADAS)</t>
+  </si>
+  <si>
+    <t>RETROVISOR ATOS</t>
+  </si>
+  <si>
+    <t>SEGURO DE PUERTA ATOS</t>
+  </si>
+  <si>
+    <t>TAPA DE ACEITE ATOS</t>
+  </si>
+  <si>
+    <t>TAPA DE GASOLINA ATOS</t>
+  </si>
+  <si>
+    <t>VÁLVULA PCV ATOS, PICANTO 1RA</t>
+  </si>
+  <si>
+    <t>VARILLA DE ACEITE ATOS</t>
+  </si>
+  <si>
+    <t>VÁSTAGO DE CREMALLERA DE PUERTA ATOS</t>
+  </si>
+  <si>
+    <t>ZAPATILLAS DE REPARACIÓN PARA UNA PINZA DE FRENO ATOS</t>
+  </si>
+  <si>
+    <t>AROS STD, 0,75, 0.50 PICANTO 1RA, ATOS, I10</t>
+  </si>
+  <si>
     <t>CONDENSADOR PICANTO  2DA</t>
   </si>
   <si>
@@ -2353,13 +2449,64 @@
     <t>ELECTROVENTILADOR PICANTO 3RA</t>
   </si>
   <si>
+    <t>METALES APOYO STD, 0,75, 0.50, 0.25 PICANTO 1RA, ATOS, I10</t>
+  </si>
+  <si>
+    <t>METALES BIELA STD, 0,75, 0.50, 0.25 PICANTO 1RA, ATOS, I10</t>
+  </si>
+  <si>
+    <t>PISTONES STD, 0.75, 0.50 PICANTO 1RA, ATOS, I10</t>
+  </si>
+  <si>
+    <t>AMORTIGUADOR DELANTERO SANDERO</t>
+  </si>
+  <si>
+    <t>AMORTIGUADOR TRASERO SANDERO</t>
+  </si>
+  <si>
+    <t>BANDAS DE FRENO SANDERO</t>
+  </si>
+  <si>
+    <t>BUJE DE PARRILLA DELANTERA SANDERO</t>
+  </si>
+  <si>
+    <t>DISCO DE FRENO SANDERO</t>
+  </si>
+  <si>
+    <t>RETÉN DE ÁRBOL DE LEVAS SANDERO</t>
+  </si>
+  <si>
+    <t>RETÉN DE CIGÜEÑAL DELANTERO SANDERO</t>
+  </si>
+  <si>
+    <t>RETÉN DE CIGÜEÑAL TRASERO SANDERO</t>
+  </si>
+  <si>
+    <t>RODAMIENTO TRASERO SANDERO</t>
+  </si>
+  <si>
+    <t>ROSCA DEL AFORADOR SANDERO</t>
+  </si>
+  <si>
+    <t>TANQUE AUXILIAR DEL RADIADOR SANDERO</t>
+  </si>
+  <si>
+    <t>TAPÓN CHICO DE ÁRBOL DE LEVAS SANDERO</t>
+  </si>
+  <si>
+    <t>TAPÓN DE TANQUE AUXILIAR DEL RADIADOR SANDERO</t>
+  </si>
+  <si>
+    <t>TAPÓN GRANDE DE ÁRBOL DE LEVAS SANDERO</t>
+  </si>
+  <si>
+    <t>FOCO H1 55W</t>
+  </si>
+  <si>
+    <t>FILTRO DE AIRE ACONDICIONADO SANDERO</t>
+  </si>
+  <si>
     <t>TERMOSTATO</t>
-  </si>
-  <si>
-    <t>BANDAS DE FRENO SANDERO</t>
-  </si>
-  <si>
-    <t>FILTRO DE AIRE ACONDICIONADO SANDERO</t>
   </si>
 </sst>
 </file>
@@ -2918,7 +3065,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="B7" s="1">
         <v>4160</v>
@@ -2990,7 +3137,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="B16" s="1">
         <v>2600</v>
@@ -3014,7 +3161,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="B19" s="1">
         <v>4160</v>
@@ -3054,7 +3201,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="B24" s="1">
         <v>26000</v>
@@ -3134,7 +3281,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="B34" s="1">
         <v>36400</v>
@@ -3142,7 +3289,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="B35" s="1">
         <v>7800</v>
@@ -3150,7 +3297,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="B36" s="1">
         <v>15600</v>
@@ -3174,7 +3321,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="B39" s="1">
         <v>52000</v>
@@ -3182,7 +3329,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="B40" s="1">
         <v>57200</v>
@@ -3190,7 +3337,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="B41" s="1">
         <v>62400</v>
@@ -3222,7 +3369,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="B45" s="1">
         <v>23400</v>
@@ -3230,7 +3377,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="B46" s="1">
         <v>20800</v>
@@ -3270,7 +3417,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="B51" s="1">
         <v>520</v>
@@ -3334,7 +3481,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="B59" s="1">
         <v>5200</v>
@@ -3342,7 +3489,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="B60" s="1">
         <v>5200</v>
@@ -3542,7 +3689,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="B85" s="1">
         <v>7800</v>
@@ -3558,7 +3705,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="B87" s="1">
         <v>7800</v>
@@ -3638,7 +3785,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="B97" s="1">
         <v>7800</v>
@@ -3646,7 +3793,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="B98" s="1">
         <v>7800</v>
@@ -3702,7 +3849,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B105" s="1">
         <v>23400</v>
@@ -3718,7 +3865,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="B107" s="1">
         <v>13000</v>
@@ -3742,7 +3889,7 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="B110" s="1">
         <v>23400</v>
@@ -3750,7 +3897,7 @@
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="B111" s="1">
         <v>26000</v>
@@ -3758,7 +3905,7 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="B112" s="1">
         <v>15600</v>
@@ -3766,7 +3913,7 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="B113" s="1">
         <v>104</v>
@@ -3782,7 +3929,7 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="B115" s="1">
         <v>10400</v>
@@ -3798,7 +3945,7 @@
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="B117" s="1">
         <v>1040</v>
@@ -3870,7 +4017,7 @@
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="B126" s="1">
         <v>52000</v>
@@ -3878,7 +4025,7 @@
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="B127" s="1">
         <v>52000</v>
@@ -3902,7 +4049,7 @@
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="B130" s="1">
         <v>223600</v>
@@ -3990,7 +4137,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="B141" s="1">
         <v>104</v>
@@ -4006,7 +4153,7 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="B143" s="1">
         <v>5200</v>
@@ -4038,7 +4185,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="B147" s="1">
         <v>6240</v>
@@ -4150,7 +4297,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="B161" s="1">
         <v>18200</v>
@@ -4158,7 +4305,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="B162" s="1">
         <v>1560</v>
@@ -4166,7 +4313,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="B163" s="1">
         <v>1560</v>
@@ -4174,7 +4321,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="B164" s="1">
         <v>104</v>
@@ -4182,7 +4329,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="B165" s="1">
         <v>104</v>
@@ -4206,7 +4353,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="B168" s="1">
         <v>52000</v>
@@ -4214,7 +4361,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="B169" s="1">
         <v>2080</v>
@@ -4222,7 +4369,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="B170" s="1">
         <v>4160</v>
@@ -4310,7 +4457,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="B181" s="1">
         <v>3640</v>
@@ -4318,7 +4465,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="B182" s="1">
         <v>2600</v>
@@ -4326,7 +4473,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="B183" s="1">
         <v>7800</v>
@@ -4334,7 +4481,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="B184" s="1">
         <v>3640</v>
@@ -4342,7 +4489,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="B185" s="1">
         <v>3640</v>
@@ -4350,7 +4497,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="B186" s="1">
         <v>2600</v>
@@ -4382,7 +4529,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="B190" s="1">
         <v>26000</v>
@@ -4414,7 +4561,7 @@
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="B194" s="1">
         <v>1560</v>
@@ -4454,7 +4601,7 @@
     </row>
     <row r="199" spans="1:2">
       <c r="A199" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="B199" s="1">
         <v>291200</v>
@@ -4470,7 +4617,7 @@
     </row>
     <row r="201" spans="1:2">
       <c r="A201" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="B201" s="1">
         <v>6240</v>
@@ -4478,7 +4625,7 @@
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="B202" s="1">
         <v>4160</v>
@@ -4574,7 +4721,7 @@
     </row>
     <row r="214" spans="1:2">
       <c r="A214" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="B214" s="1">
         <v>6240</v>
@@ -4590,7 +4737,7 @@
     </row>
     <row r="216" spans="1:2">
       <c r="A216" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="B216" s="1">
         <v>2600</v>
@@ -4598,7 +4745,7 @@
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="B217" s="1">
         <v>2600</v>
@@ -4638,7 +4785,7 @@
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="B222" s="1">
         <v>33800</v>
@@ -4646,7 +4793,7 @@
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="B223" s="1">
         <v>41600</v>
@@ -4662,7 +4809,7 @@
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="B225" s="1">
         <v>78000</v>
@@ -4678,7 +4825,7 @@
     </row>
     <row r="227" spans="1:2">
       <c r="A227" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="B227" s="1">
         <v>31200</v>
@@ -4686,7 +4833,7 @@
     </row>
     <row r="228" spans="1:2">
       <c r="A228" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="B228" s="1">
         <v>33800</v>
@@ -4694,7 +4841,7 @@
     </row>
     <row r="229" spans="1:2">
       <c r="A229" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="B229" s="1">
         <v>36400</v>
@@ -4702,7 +4849,7 @@
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="B230" s="1">
         <v>36400</v>
@@ -4710,7 +4857,7 @@
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="B231" s="1">
         <v>3640</v>
@@ -4726,7 +4873,7 @@
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="B233" s="1">
         <v>31200</v>
@@ -4774,7 +4921,7 @@
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="B239" s="1">
         <v>156000</v>
@@ -4790,7 +4937,7 @@
     </row>
     <row r="241" spans="1:2">
       <c r="A241" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="B241" s="1">
         <v>130000</v>
@@ -4822,7 +4969,7 @@
     </row>
     <row r="245" spans="1:2">
       <c r="A245" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="B245" s="1">
         <v>15600</v>
@@ -4862,7 +5009,7 @@
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="B250" s="1">
         <v>10400</v>
@@ -4902,7 +5049,7 @@
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="B255" s="1">
         <v>6240</v>
@@ -4910,7 +5057,7 @@
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="B256" s="1">
         <v>6240</v>
@@ -4974,7 +5121,7 @@
     </row>
     <row r="264" spans="1:2">
       <c r="A264" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="B264" s="1">
         <v>104</v>
@@ -5110,7 +5257,7 @@
     </row>
     <row r="281" spans="1:2">
       <c r="A281" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="B281" s="1">
         <v>52000</v>
@@ -5118,7 +5265,7 @@
     </row>
     <row r="282" spans="1:2">
       <c r="A282" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="B282" s="1">
         <v>31200</v>
@@ -5126,7 +5273,7 @@
     </row>
     <row r="283" spans="1:2">
       <c r="A283" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="B283" s="1">
         <v>49400</v>
@@ -5134,7 +5281,7 @@
     </row>
     <row r="284" spans="1:2">
       <c r="A284" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="B284" s="1">
         <v>2600</v>
@@ -5142,7 +5289,7 @@
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="B285" s="1">
         <v>2600</v>
@@ -5158,7 +5305,7 @@
     </row>
     <row r="287" spans="1:2">
       <c r="A287" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="B287" s="1">
         <v>3640</v>
@@ -5246,7 +5393,7 @@
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="B298" s="1">
         <v>5200</v>
@@ -5302,7 +5449,7 @@
     </row>
     <row r="305" spans="1:2">
       <c r="A305" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="B305" s="1">
         <v>1040</v>
@@ -5310,7 +5457,7 @@
     </row>
     <row r="306" spans="1:2">
       <c r="A306" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="B306" s="1">
         <v>62400</v>
@@ -5342,7 +5489,7 @@
     </row>
     <row r="310" spans="1:2">
       <c r="A310" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="B310" s="1">
         <v>5200</v>
@@ -5390,7 +5537,7 @@
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="B316" s="1">
         <v>10400</v>
@@ -5414,7 +5561,7 @@
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="B319" s="1">
         <v>2080</v>
@@ -5422,7 +5569,7 @@
     </row>
     <row r="320" spans="1:2">
       <c r="A320" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="B320" s="1">
         <v>7800</v>
@@ -5430,7 +5577,7 @@
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="B321" s="1">
         <v>5200</v>
@@ -5502,7 +5649,7 @@
     </row>
     <row r="330" spans="1:2">
       <c r="A330" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="B330" s="1">
         <v>7800</v>
@@ -5510,7 +5657,7 @@
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
-        <v>774</v>
+        <v>825</v>
       </c>
       <c r="B331" s="1">
         <v>6240</v>
@@ -5526,7 +5673,7 @@
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="B333" s="1">
         <v>13000</v>
@@ -5534,7 +5681,7 @@
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="B334" s="1">
         <v>7800</v>
@@ -5614,7 +5761,7 @@
     </row>
     <row r="344" spans="1:2">
       <c r="A344" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="B344" s="1">
         <v>1560</v>
@@ -5654,7 +5801,7 @@
     </row>
     <row r="349" spans="1:2">
       <c r="A349" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="B349" s="1">
         <v>15600</v>
@@ -5662,7 +5809,7 @@
     </row>
     <row r="350" spans="1:2">
       <c r="A350" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="B350" s="1">
         <v>15600</v>
@@ -5694,7 +5841,7 @@
     </row>
     <row r="354" spans="1:2">
       <c r="A354" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="B354" s="1">
         <v>1560</v>
@@ -5726,7 +5873,7 @@
     </row>
     <row r="358" spans="1:2">
       <c r="A358" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="B358" s="1">
         <v>104000</v>
@@ -5771,7 +5918,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B129"/>
+  <dimension ref="A1:B164"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="64.5703125" bestFit="1" customWidth="1"/>
@@ -5804,23 +5951,23 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="7" t="s">
-        <v>589</v>
+        <v>760</v>
       </c>
       <c r="B4" s="1">
-        <v>93600</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="7" t="s">
-        <v>164</v>
+        <v>581</v>
       </c>
       <c r="B5" s="1">
-        <v>62400</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="7" t="s">
-        <v>590</v>
+        <v>164</v>
       </c>
       <c r="B6" s="1">
         <v>62400</v>
@@ -5828,31 +5975,31 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="8" t="s">
-        <v>600</v>
+        <v>582</v>
       </c>
       <c r="B7" s="1">
-        <v>4160</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="5" t="s">
-        <v>5</v>
+        <v>592</v>
       </c>
       <c r="B8" s="1">
-        <v>20800</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
-        <v>490</v>
+        <v>761</v>
       </c>
       <c r="B9" s="1">
-        <v>41600</v>
+        <v>67600</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="10" t="s">
-        <v>124</v>
+        <v>5</v>
       </c>
       <c r="B10" s="1">
         <v>20800</v>
@@ -5860,119 +6007,119 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="5" t="s">
-        <v>11</v>
+        <v>762</v>
       </c>
       <c r="B11" s="1">
-        <v>10400</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="10" t="s">
-        <v>433</v>
+        <v>124</v>
       </c>
       <c r="B12" s="1">
-        <v>41600</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="10" t="s">
-        <v>163</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1">
-        <v>52000</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="9" t="s">
-        <v>658</v>
+        <v>433</v>
       </c>
       <c r="B14" s="1">
-        <v>52000</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>592</v>
+        <v>163</v>
       </c>
       <c r="B15" s="1">
-        <v>57200</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="11" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="B16" s="1">
-        <v>62400</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
-        <v>6</v>
+        <v>584</v>
       </c>
       <c r="B17" s="1">
-        <v>13000</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="5" t="s">
-        <v>125</v>
+        <v>651</v>
       </c>
       <c r="B18" s="1">
-        <v>31200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="5" t="s">
-        <v>481</v>
+        <v>6</v>
       </c>
       <c r="B19" s="1">
-        <v>31200</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="5" t="s">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="B20" s="1">
-        <v>52000</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="B21" s="1">
-        <v>36400</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="5" t="s">
-        <v>492</v>
+        <v>36</v>
       </c>
       <c r="B22" s="1">
-        <v>41600</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="5" t="s">
-        <v>703</v>
+        <v>490</v>
       </c>
       <c r="B23" s="1">
-        <v>520</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="5" t="s">
-        <v>409</v>
+        <v>491</v>
       </c>
       <c r="B24" s="1">
-        <v>520</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="5" t="s">
-        <v>405</v>
+        <v>695</v>
       </c>
       <c r="B25" s="1">
         <v>520</v>
@@ -5980,71 +6127,71 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="5" t="s">
-        <v>442</v>
+        <v>409</v>
       </c>
       <c r="B26" s="1">
-        <v>7800</v>
+        <v>520</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="5" t="s">
-        <v>493</v>
+        <v>405</v>
       </c>
       <c r="B27" s="1">
-        <v>20800</v>
+        <v>520</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="5" t="s">
-        <v>494</v>
+        <v>442</v>
       </c>
       <c r="B28" s="1">
-        <v>20800</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="5" t="s">
-        <v>12</v>
+        <v>763</v>
       </c>
       <c r="B29" s="1">
-        <v>5200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="5" t="s">
-        <v>1</v>
+        <v>492</v>
       </c>
       <c r="B30" s="1">
-        <v>1300</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="12" t="s">
-        <v>7</v>
+        <v>493</v>
       </c>
       <c r="B31" s="1">
-        <v>5200</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="5" t="s">
-        <v>437</v>
+        <v>764</v>
       </c>
       <c r="B32" s="1">
-        <v>3640</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="5" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B33" s="1">
-        <v>13000</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="5" t="s">
-        <v>495</v>
+        <v>765</v>
       </c>
       <c r="B34" s="1">
         <v>7800</v>
@@ -6052,71 +6199,71 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="5" t="s">
-        <v>482</v>
+        <v>1</v>
       </c>
       <c r="B35" s="1">
-        <v>15600</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="5" t="s">
-        <v>441</v>
+        <v>7</v>
       </c>
       <c r="B36" s="1">
-        <v>13000</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="7" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="B37" s="1">
-        <v>26000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="13" t="s">
-        <v>496</v>
+        <v>2</v>
       </c>
       <c r="B38" s="1">
-        <v>31200</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="11" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B39" s="1">
-        <v>26000</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="5" t="s">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="B40" s="1">
-        <v>36400</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="5" t="s">
-        <v>562</v>
+        <v>766</v>
       </c>
       <c r="B41" s="1">
-        <v>7800</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="9" t="s">
-        <v>762</v>
+        <v>441</v>
       </c>
       <c r="B42" s="1">
-        <v>10400</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="5" t="s">
-        <v>733</v>
+        <v>443</v>
       </c>
       <c r="B43" s="1">
         <v>26000</v>
@@ -6124,23 +6271,23 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="7" t="s">
-        <v>29</v>
+        <v>495</v>
       </c>
       <c r="B44" s="1">
-        <v>18200</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>768</v>
+        <v>496</v>
       </c>
       <c r="B45" s="1">
-        <v>72800</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B46" s="1">
         <v>36400</v>
@@ -6148,247 +6295,247 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="14" t="s">
-        <v>439</v>
+        <v>767</v>
       </c>
       <c r="B47" s="1">
-        <v>7800</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="7" t="s">
-        <v>126</v>
+        <v>554</v>
       </c>
       <c r="B48" s="1">
-        <v>15600</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="13" t="s">
-        <v>500</v>
+        <v>768</v>
       </c>
       <c r="B49" s="1">
-        <v>104000</v>
+        <v>67600</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="15" t="s">
-        <v>30</v>
+        <v>754</v>
       </c>
       <c r="B50" s="1">
-        <v>52000</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>430</v>
+        <v>725</v>
       </c>
       <c r="B51" s="1">
-        <v>52000</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="5" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B52" s="1">
-        <v>78000</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="5" t="s">
-        <v>127</v>
+        <v>769</v>
       </c>
       <c r="B53" s="1">
-        <v>62400</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="6" t="s">
-        <v>13</v>
+        <v>498</v>
       </c>
       <c r="B54" s="1">
-        <v>31200</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="16" t="s">
-        <v>116</v>
+        <v>439</v>
       </c>
       <c r="B55" s="1">
-        <v>36400</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="10" t="s">
-        <v>14</v>
+        <v>126</v>
       </c>
       <c r="B56" s="1">
-        <v>67600</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="16" t="s">
-        <v>429</v>
+        <v>499</v>
       </c>
       <c r="B57" s="1">
-        <v>20800</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="17" t="s">
-        <v>563</v>
+        <v>770</v>
       </c>
       <c r="B58" s="1">
-        <v>5200</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="5" t="s">
-        <v>501</v>
+        <v>30</v>
       </c>
       <c r="B59" s="1">
-        <v>31200</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="5" t="s">
-        <v>502</v>
+        <v>430</v>
       </c>
       <c r="B60" s="1">
-        <v>28600</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="10" t="s">
-        <v>597</v>
+        <v>8</v>
       </c>
       <c r="B61" s="1">
-        <v>5200</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="10" t="s">
-        <v>15</v>
+        <v>771</v>
       </c>
       <c r="B62" s="1">
-        <v>5200</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="5" t="s">
-        <v>16</v>
+        <v>772</v>
       </c>
       <c r="B63" s="1">
-        <v>15600</v>
+        <v>114400</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="18" t="s">
-        <v>591</v>
+        <v>127</v>
       </c>
       <c r="B64" s="1">
-        <v>7800</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="10" t="s">
-        <v>699</v>
+        <v>13</v>
       </c>
       <c r="B65" s="1">
-        <v>18200</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="10" t="s">
-        <v>487</v>
+        <v>116</v>
       </c>
       <c r="B66" s="1">
-        <v>5200</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="5" t="s">
-        <v>746</v>
+        <v>14</v>
       </c>
       <c r="B67" s="1">
-        <v>4160</v>
+        <v>67600</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="5" t="s">
-        <v>3</v>
+        <v>773</v>
       </c>
       <c r="B68" s="1">
-        <v>62400</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="19" t="s">
-        <v>17</v>
+        <v>774</v>
       </c>
       <c r="B69" s="1">
-        <v>5200</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="5" t="s">
-        <v>128</v>
+        <v>429</v>
       </c>
       <c r="B70" s="1">
-        <v>10400</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="5" t="s">
-        <v>726</v>
+        <v>555</v>
       </c>
       <c r="B71" s="1">
-        <v>15600</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="9" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B72" s="1">
-        <v>36400</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="5" t="s">
-        <v>9</v>
+        <v>501</v>
       </c>
       <c r="B73" s="1">
-        <v>31200</v>
+        <v>28600</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="5" t="s">
-        <v>634</v>
+        <v>775</v>
       </c>
       <c r="B74" s="1">
-        <v>291200</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="11" t="s">
-        <v>18</v>
+        <v>776</v>
       </c>
       <c r="B75" s="1">
-        <v>13000</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="20" t="s">
-        <v>19</v>
+        <v>589</v>
       </c>
       <c r="B76" s="1">
-        <v>7800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="10" t="s">
-        <v>504</v>
+        <v>15</v>
       </c>
       <c r="B77" s="1">
         <v>5200</v>
@@ -6396,367 +6543,367 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="5" t="s">
-        <v>505</v>
+        <v>16</v>
       </c>
       <c r="B78" s="1">
-        <v>7800</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="5" t="s">
-        <v>25</v>
+        <v>583</v>
       </c>
       <c r="B79" s="1">
-        <v>5200</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="13" t="s">
-        <v>564</v>
+        <v>691</v>
       </c>
       <c r="B80" s="1">
-        <v>6240</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="5" t="s">
-        <v>552</v>
+        <v>777</v>
       </c>
       <c r="B81" s="1">
-        <v>23400</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="5" t="s">
-        <v>553</v>
+        <v>487</v>
       </c>
       <c r="B82" s="1">
-        <v>18200</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="5" t="s">
-        <v>129</v>
+        <v>778</v>
       </c>
       <c r="B83" s="1">
-        <v>104000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="10" t="s">
-        <v>506</v>
+        <v>738</v>
       </c>
       <c r="B84" s="1">
-        <v>7800</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>763</v>
+        <v>3</v>
       </c>
       <c r="B85" s="1">
-        <v>36400</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="11" t="s">
-        <v>734</v>
+        <v>17</v>
       </c>
       <c r="B86" s="1">
-        <v>36400</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="17" t="s">
-        <v>731</v>
+        <v>128</v>
       </c>
       <c r="B87" s="1">
-        <v>36400</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="17" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
       <c r="B88" s="1">
-        <v>36400</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="17" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B89" s="1">
-        <v>6240</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="21" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="B90" s="1">
-        <v>93600</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="5" t="s">
-        <v>665</v>
+        <v>626</v>
       </c>
       <c r="B91" s="1">
-        <v>182000</v>
+        <v>291200</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="5" t="s">
-        <v>24</v>
+        <v>779</v>
       </c>
       <c r="B92" s="1">
-        <v>93600</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="5" t="s">
-        <v>751</v>
+        <v>18</v>
       </c>
       <c r="B93" s="1">
-        <v>130000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B94" s="1">
-        <v>31200</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="5" t="s">
-        <v>436</v>
+        <v>503</v>
       </c>
       <c r="B95" s="1">
-        <v>20800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="10" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B96" s="1">
-        <v>62400</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="5" t="s">
-        <v>115</v>
+        <v>25</v>
       </c>
       <c r="B97" s="1">
-        <v>36400</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="5" t="s">
-        <v>509</v>
+        <v>556</v>
       </c>
       <c r="B98" s="1">
-        <v>10400</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="22" t="s">
-        <v>510</v>
+        <v>780</v>
       </c>
       <c r="B99" s="1">
-        <v>7800</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>727</v>
+        <v>781</v>
       </c>
       <c r="B100" s="1">
-        <v>7800</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>511</v>
+        <v>782</v>
       </c>
       <c r="B101" s="1">
-        <v>39000</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="5" t="s">
-        <v>21</v>
+        <v>783</v>
       </c>
       <c r="B102" s="1">
-        <v>26000</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="5" t="s">
-        <v>767</v>
+        <v>129</v>
       </c>
       <c r="B103" s="1">
-        <v>78000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="5" t="s">
-        <v>483</v>
+        <v>505</v>
       </c>
       <c r="B104" s="1">
-        <v>78000</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>769</v>
+        <v>784</v>
       </c>
       <c r="B105" s="1">
-        <v>67600</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>73</v>
+        <v>755</v>
       </c>
       <c r="B106" s="1">
-        <v>2600</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>74</v>
+        <v>726</v>
       </c>
       <c r="B107" s="1">
-        <v>5200</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>162</v>
+        <v>723</v>
       </c>
       <c r="B108" s="1">
-        <v>2600</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>130</v>
+        <v>724</v>
       </c>
       <c r="B109" s="1">
-        <v>18200</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>720</v>
+        <v>506</v>
       </c>
       <c r="B110" s="1">
-        <v>7800</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="4" t="s">
-        <v>435</v>
+        <v>100</v>
       </c>
       <c r="B111" s="1">
-        <v>20800</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>512</v>
+        <v>657</v>
       </c>
       <c r="B112" s="1">
-        <v>20800</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>513</v>
+        <v>24</v>
       </c>
       <c r="B113" s="1">
-        <v>36400</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>440</v>
+        <v>785</v>
       </c>
       <c r="B114" s="1">
-        <v>10400</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>514</v>
+        <v>743</v>
       </c>
       <c r="B115" s="1">
-        <v>20800</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B116" s="1">
-        <v>7800</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>661</v>
+        <v>436</v>
       </c>
       <c r="B117" s="1">
-        <v>5200</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>662</v>
+        <v>786</v>
       </c>
       <c r="B118" s="1">
-        <v>2600</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>599</v>
+        <v>115</v>
       </c>
       <c r="B119" s="1">
-        <v>5200</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>565</v>
+        <v>507</v>
       </c>
       <c r="B120" s="1">
-        <v>5200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="B121" s="1">
-        <v>15600</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>406</v>
+        <v>787</v>
       </c>
       <c r="B122" s="1">
-        <v>5200</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>557</v>
+        <v>719</v>
       </c>
       <c r="B123" s="1">
         <v>7800</v>
@@ -6764,7 +6911,7 @@
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>444</v>
+        <v>788</v>
       </c>
       <c r="B124" s="1">
         <v>7800</v>
@@ -6772,42 +6919,322 @@
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>567</v>
+        <v>509</v>
       </c>
       <c r="B125" s="1">
-        <v>13000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>568</v>
+        <v>21</v>
       </c>
       <c r="B126" s="1">
-        <v>7800</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>438</v>
+        <v>759</v>
       </c>
       <c r="B127" s="1">
-        <v>5200</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>635</v>
+        <v>483</v>
       </c>
       <c r="B128" s="1">
-        <v>52000</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
+        <v>789</v>
+      </c>
+      <c r="B129" s="1">
+        <v>67600</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" t="s">
+        <v>790</v>
+      </c>
+      <c r="B130" s="1">
+        <v>93600</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" t="s">
+        <v>791</v>
+      </c>
+      <c r="B131" s="1">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" t="s">
+        <v>792</v>
+      </c>
+      <c r="B132" s="1">
+        <v>46800</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" t="s">
+        <v>73</v>
+      </c>
+      <c r="B133" s="1">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" t="s">
+        <v>74</v>
+      </c>
+      <c r="B134" s="1">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" t="s">
+        <v>162</v>
+      </c>
+      <c r="B135" s="1">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" t="s">
+        <v>793</v>
+      </c>
+      <c r="B136" s="1">
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" t="s">
+        <v>130</v>
+      </c>
+      <c r="B137" s="1">
+        <v>18200</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" t="s">
+        <v>794</v>
+      </c>
+      <c r="B138" s="1">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" t="s">
+        <v>712</v>
+      </c>
+      <c r="B139" s="1">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" t="s">
+        <v>435</v>
+      </c>
+      <c r="B140" s="1">
+        <v>20800</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" t="s">
+        <v>510</v>
+      </c>
+      <c r="B141" s="1">
+        <v>20800</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" t="s">
+        <v>511</v>
+      </c>
+      <c r="B142" s="1">
+        <v>36400</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" t="s">
+        <v>440</v>
+      </c>
+      <c r="B143" s="1">
+        <v>10400</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" t="s">
+        <v>512</v>
+      </c>
+      <c r="B144" s="1">
+        <v>20800</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" t="s">
+        <v>795</v>
+      </c>
+      <c r="B145" s="1">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" t="s">
+        <v>4</v>
+      </c>
+      <c r="B146" s="1">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" t="s">
+        <v>796</v>
+      </c>
+      <c r="B147" s="1">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" t="s">
+        <v>653</v>
+      </c>
+      <c r="B148" s="1">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" t="s">
+        <v>654</v>
+      </c>
+      <c r="B149" s="1">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" t="s">
+        <v>591</v>
+      </c>
+      <c r="B150" s="1">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" t="s">
+        <v>557</v>
+      </c>
+      <c r="B151" s="1">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" t="s">
+        <v>513</v>
+      </c>
+      <c r="B152" s="1">
+        <v>15600</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" t="s">
+        <v>406</v>
+      </c>
+      <c r="B153" s="1">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" t="s">
+        <v>549</v>
+      </c>
+      <c r="B154" s="1">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" t="s">
+        <v>444</v>
+      </c>
+      <c r="B155" s="1">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" t="s">
+        <v>559</v>
+      </c>
+      <c r="B156" s="1">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" t="s">
+        <v>560</v>
+      </c>
+      <c r="B157" s="1">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" t="s">
+        <v>797</v>
+      </c>
+      <c r="B158" s="1">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" t="s">
+        <v>438</v>
+      </c>
+      <c r="B159" s="1">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" t="s">
+        <v>798</v>
+      </c>
+      <c r="B160" s="1">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" t="s">
+        <v>799</v>
+      </c>
+      <c r="B161" s="1">
+        <v>6240</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" t="s">
+        <v>627</v>
+      </c>
+      <c r="B162" s="1">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" t="s">
         <v>10</v>
       </c>
-      <c r="B129" s="1">
+      <c r="B163" s="1">
         <v>18200</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" t="s">
+        <v>800</v>
+      </c>
+      <c r="B164" s="1">
+        <v>5200</v>
       </c>
     </row>
   </sheetData>
@@ -6817,7 +7244,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B259"/>
+  <dimension ref="A1:B260"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="83.85546875" bestFit="1" customWidth="1"/>
@@ -6842,7 +7269,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="17" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B3" s="1">
         <v>3120</v>
@@ -6850,7 +7277,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="26" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="B4" s="1">
         <v>13000</v>
@@ -6866,7 +7293,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="25" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="B6" s="1">
         <v>104000</v>
@@ -6898,7 +7325,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="B10" s="1">
         <v>93600</v>
@@ -6922,7 +7349,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="17" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="B13" s="1">
         <v>4160</v>
@@ -6930,7 +7357,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="17" t="s">
-        <v>516</v>
+        <v>801</v>
       </c>
       <c r="B14" s="1">
         <v>41600</v>
@@ -6954,7 +7381,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="17" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="B17" s="1">
         <v>20800</v>
@@ -6962,7 +7389,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="17" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="B18" s="1">
         <v>5200</v>
@@ -6986,7 +7413,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="17" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="B21" s="1">
         <v>52000</v>
@@ -6994,7 +7421,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="B22" s="1">
         <v>57200</v>
@@ -7002,7 +7429,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="17" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="B23" s="1">
         <v>62400</v>
@@ -7050,7 +7477,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="17" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="B29" s="1">
         <v>15600</v>
@@ -7098,7 +7525,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="17" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="B35" s="1">
         <v>520</v>
@@ -7122,7 +7549,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="28" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="B38" s="1">
         <v>62400</v>
@@ -7130,7 +7557,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="17" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="B39" s="1">
         <v>62400</v>
@@ -7138,7 +7565,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="17" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="B40" s="1">
         <v>52000</v>
@@ -7146,7 +7573,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="17" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="B41" s="1">
         <v>52000</v>
@@ -7154,7 +7581,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="26" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B42" s="1">
         <v>5200</v>
@@ -7218,7 +7645,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="17" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B50" s="1">
         <v>3640</v>
@@ -7234,7 +7661,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="17" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B52" s="1">
         <v>20800</v>
@@ -7266,7 +7693,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="17" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="B56" s="1">
         <v>15600</v>
@@ -7274,7 +7701,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="17" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="B57" s="1">
         <v>52000</v>
@@ -7282,7 +7709,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="17" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="B58" s="1">
         <v>39000</v>
@@ -7298,7 +7725,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="17" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="B60" s="1">
         <v>7800</v>
@@ -7330,7 +7757,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="17" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="B64" s="1">
         <v>15600</v>
@@ -7338,7 +7765,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="17" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="B65" s="1">
         <v>26000</v>
@@ -7354,7 +7781,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="17" t="s">
-        <v>770</v>
+        <v>802</v>
       </c>
       <c r="B67" s="1">
         <v>83200</v>
@@ -7378,7 +7805,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="17" t="s">
-        <v>771</v>
+        <v>803</v>
       </c>
       <c r="B70" s="1">
         <v>83200</v>
@@ -7442,7 +7869,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="17" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="B78" s="1">
         <v>52000</v>
@@ -7586,7 +8013,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="17" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B96" s="1">
         <v>36400</v>
@@ -7594,7 +8021,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="17" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="B97" s="1">
         <v>31200</v>
@@ -7602,7 +8029,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="17" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="B98" s="1">
         <v>36400</v>
@@ -7618,7 +8045,7 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="17" t="s">
-        <v>772</v>
+        <v>804</v>
       </c>
       <c r="B100" s="1">
         <v>72800</v>
@@ -7626,7 +8053,7 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="17" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="B101" s="1">
         <v>72800</v>
@@ -7634,7 +8061,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="31" t="s">
-        <v>773</v>
+        <v>805</v>
       </c>
       <c r="B102" s="1">
         <v>93600</v>
@@ -7642,7 +8069,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="B103" s="1">
         <v>4160</v>
@@ -7650,7 +8077,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="17" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B104" s="1">
         <v>13000</v>
@@ -7666,7 +8093,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="17" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="B106" s="1">
         <v>13000</v>
@@ -7674,7 +8101,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="17" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="B107" s="1">
         <v>5200</v>
@@ -7682,7 +8109,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="17" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="B108" s="1">
         <v>31200</v>
@@ -7722,7 +8149,7 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="B113" s="1">
         <v>5200</v>
@@ -7730,7 +8157,7 @@
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="B114" s="1">
         <v>7800</v>
@@ -7738,7 +8165,7 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="17" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="B115" s="1">
         <v>7800</v>
@@ -7770,7 +8197,7 @@
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="17" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="B119" s="1">
         <v>7800</v>
@@ -7778,7 +8205,7 @@
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="17" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="B120" s="1">
         <v>10400</v>
@@ -7786,7 +8213,7 @@
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="B121" s="1">
         <v>6240</v>
@@ -7794,7 +8221,7 @@
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="17" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="B122" s="1">
         <v>18200</v>
@@ -7802,7 +8229,7 @@
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="17" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B123" s="1">
         <v>18200</v>
@@ -7818,7 +8245,7 @@
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="17" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="B125" s="1">
         <v>4160</v>
@@ -7858,7 +8285,7 @@
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="17" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="B130" s="1">
         <v>5200</v>
@@ -7866,7 +8293,7 @@
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="17" t="s">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="B131" s="1">
         <v>5200</v>
@@ -7874,7 +8301,7 @@
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="17" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="B132" s="1">
         <v>72800</v>
@@ -7882,7 +8309,7 @@
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="28" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="B133" s="1">
         <v>31200</v>
@@ -7898,7 +8325,7 @@
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="33" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="B135" s="1">
         <v>291200</v>
@@ -7906,7 +8333,7 @@
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="17" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="B136" s="1">
         <v>301600</v>
@@ -7914,7 +8341,7 @@
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="17" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="B137" s="1">
         <v>312000</v>
@@ -7978,7 +8405,7 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="17" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="B145" s="1">
         <v>5200</v>
@@ -8010,7 +8437,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="17" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="B149" s="1">
         <v>6240</v>
@@ -8018,7 +8445,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="17" t="s">
-        <v>522</v>
+        <v>806</v>
       </c>
       <c r="B150" s="1">
         <v>23400</v>
@@ -8026,7 +8453,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>554</v>
+        <v>807</v>
       </c>
       <c r="B151" s="1">
         <v>18200</v>
@@ -8050,7 +8477,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="17" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="B154" s="1">
         <v>39000</v>
@@ -8058,7 +8485,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="17" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="B155" s="1">
         <v>39000</v>
@@ -8098,7 +8525,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="17" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="B160" s="1">
         <v>36400</v>
@@ -8106,7 +8533,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="17" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="B161" s="1">
         <v>41600</v>
@@ -8114,7 +8541,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="17" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="B162" s="1">
         <v>36400</v>
@@ -8122,7 +8549,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="17" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="B163" s="1">
         <v>41600</v>
@@ -8130,7 +8557,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="17" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="B164" s="1">
         <v>780</v>
@@ -8162,7 +8589,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="17" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="B168" s="1">
         <v>182000</v>
@@ -8170,7 +8597,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="17" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B169" s="1">
         <v>187200</v>
@@ -8178,7 +8605,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="17" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="B170" s="1">
         <v>192400</v>
@@ -8186,7 +8613,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="17" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="B171" s="1">
         <v>182000</v>
@@ -8194,7 +8621,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="17" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="B172" s="1">
         <v>182000</v>
@@ -8202,7 +8629,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="17" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="B173" s="1">
         <v>182000</v>
@@ -8210,7 +8637,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="17" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="B174" s="1">
         <v>130000</v>
@@ -8234,7 +8661,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="17" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="B177" s="1">
         <v>104000</v>
@@ -8258,7 +8685,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="34" t="s">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="B180" s="1">
         <v>20800</v>
@@ -8266,7 +8693,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="B181" s="1">
         <v>20800</v>
@@ -8274,7 +8701,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="B182" s="1">
         <v>36400</v>
@@ -8282,7 +8709,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="17" t="s">
-        <v>523</v>
+        <v>808</v>
       </c>
       <c r="B183" s="1">
         <v>62400</v>
@@ -8290,7 +8717,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="17" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="B184" s="1">
         <v>31200</v>
@@ -8306,7 +8733,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="17" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="B186" s="1">
         <v>46800</v>
@@ -8314,7 +8741,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="17" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="B187" s="1">
         <v>10400</v>
@@ -8322,7 +8749,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="B188" s="1">
         <v>15600</v>
@@ -8338,7 +8765,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="B190" s="1">
         <v>18200</v>
@@ -8346,7 +8773,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="B191" s="1">
         <v>7800</v>
@@ -8370,7 +8797,7 @@
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="B194" s="1">
         <v>39000</v>
@@ -8394,7 +8821,7 @@
     </row>
     <row r="197" spans="1:2">
       <c r="A197" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="B197" s="1">
         <v>88400</v>
@@ -8426,7 +8853,7 @@
     </row>
     <row r="201" spans="1:2">
       <c r="A201" s="4" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="B201" s="1">
         <v>72800</v>
@@ -8434,7 +8861,7 @@
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="B202" s="1">
         <v>93600</v>
@@ -8626,7 +9053,7 @@
     </row>
     <row r="226" spans="1:2">
       <c r="A226" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="B226" s="1">
         <v>15600</v>
@@ -8658,7 +9085,7 @@
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="B230" s="1">
         <v>20800</v>
@@ -8682,7 +9109,7 @@
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="B233" s="1">
         <v>18200</v>
@@ -8714,7 +9141,7 @@
     </row>
     <row r="237" spans="1:2">
       <c r="A237" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="B237" s="1">
         <v>36400</v>
@@ -8722,7 +9149,7 @@
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="B238" s="1">
         <v>7800</v>
@@ -8730,7 +9157,7 @@
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="B239" s="1">
         <v>5200</v>
@@ -8738,7 +9165,7 @@
     </row>
     <row r="240" spans="1:2">
       <c r="A240" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="B240" s="1">
         <v>5200</v>
@@ -8746,7 +9173,7 @@
     </row>
     <row r="241" spans="1:2">
       <c r="A241" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="B241" s="1">
         <v>5200</v>
@@ -8770,7 +9197,7 @@
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="B244" s="1">
         <v>7800</v>
@@ -8778,7 +9205,7 @@
     </row>
     <row r="245" spans="1:2">
       <c r="A245" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B245" s="1">
         <v>10400</v>
@@ -8786,7 +9213,7 @@
     </row>
     <row r="246" spans="1:2">
       <c r="A246" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="B246" s="1">
         <v>15600</v>
@@ -8794,7 +9221,7 @@
     </row>
     <row r="247" spans="1:2">
       <c r="A247" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="B247" s="1">
         <v>13000</v>
@@ -8802,7 +9229,7 @@
     </row>
     <row r="248" spans="1:2">
       <c r="A248" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="B248" s="1">
         <v>7800</v>
@@ -8810,7 +9237,7 @@
     </row>
     <row r="249" spans="1:2">
       <c r="A249" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="B249" s="1">
         <v>7800</v>
@@ -8818,7 +9245,7 @@
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="B250" s="1">
         <v>7800</v>
@@ -8826,7 +9253,7 @@
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="B251" s="1">
         <v>10400</v>
@@ -8834,7 +9261,7 @@
     </row>
     <row r="252" spans="1:2">
       <c r="A252" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="B252" s="1">
         <v>2600</v>
@@ -8842,7 +9269,7 @@
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="B253" s="1">
         <v>119600</v>
@@ -8850,7 +9277,7 @@
     </row>
     <row r="254" spans="1:2">
       <c r="A254" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="B254" s="1">
         <v>10400</v>
@@ -8858,41 +9285,49 @@
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>448</v>
+        <v>797</v>
       </c>
       <c r="B255" s="1">
-        <v>5200</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>693</v>
+        <v>448</v>
       </c>
       <c r="B256" s="1">
-        <v>52000</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>112</v>
+        <v>685</v>
       </c>
       <c r="B257" s="1">
-        <v>31200</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
-        <v>155</v>
+        <v>112</v>
       </c>
       <c r="B258" s="1">
-        <v>18200</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
+        <v>155</v>
+      </c>
+      <c r="B259" s="1">
+        <v>18200</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" t="s">
         <v>156</v>
       </c>
-      <c r="B259" s="1">
+      <c r="B260" s="1">
         <v>20800</v>
       </c>
     </row>
@@ -8903,7 +9338,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52.140625" customWidth="1"/>
@@ -8920,7 +9355,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="35" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="B2" s="1">
         <v>93600</v>
@@ -8928,18 +9363,18 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="36" t="s">
-        <v>600</v>
+        <v>809</v>
       </c>
       <c r="B3" s="1">
-        <v>4160</v>
+        <v>70200</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="36" t="s">
-        <v>775</v>
+        <v>810</v>
       </c>
       <c r="B4" s="1">
-        <v>31200</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -8947,148 +9382,148 @@
         <v>592</v>
       </c>
       <c r="B5" s="1">
-        <v>57200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="36" t="s">
-        <v>659</v>
+        <v>811</v>
       </c>
       <c r="B6" s="1">
-        <v>62400</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="36" t="s">
-        <v>528</v>
+        <v>584</v>
       </c>
       <c r="B7" s="1">
-        <v>13000</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="36" t="s">
-        <v>529</v>
+        <v>651</v>
       </c>
       <c r="B8" s="1">
-        <v>18200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="36" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="B9" s="1">
-        <v>52000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="36" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="B10" s="1">
-        <v>46800</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="36" t="s">
-        <v>562</v>
+        <v>525</v>
       </c>
       <c r="B11" s="1">
-        <v>7800</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="36" t="s">
-        <v>733</v>
+        <v>526</v>
       </c>
       <c r="B12" s="1">
-        <v>26000</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="35" t="s">
-        <v>532</v>
+        <v>812</v>
       </c>
       <c r="B13" s="1">
-        <v>20800</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="36" t="s">
-        <v>533</v>
+        <v>554</v>
       </c>
       <c r="B14" s="1">
-        <v>18200</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="36" t="s">
-        <v>702</v>
+        <v>725</v>
       </c>
       <c r="B15" s="1">
-        <v>52000</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="36" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="B16" s="1">
-        <v>26000</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="36" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="B17" s="1">
-        <v>13000</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="36" t="s">
-        <v>563</v>
+        <v>694</v>
       </c>
       <c r="B18" s="1">
-        <v>5200</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="35" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="B19" s="1">
-        <v>5200</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="36" t="s">
-        <v>776</v>
+        <v>813</v>
       </c>
       <c r="B20" s="1">
-        <v>7800</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="36" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="B21" s="1">
-        <v>5200</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="36" t="s">
-        <v>695</v>
+        <v>555</v>
       </c>
       <c r="B22" s="1">
-        <v>18200</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="36" t="s">
-        <v>487</v>
+        <v>531</v>
       </c>
       <c r="B23" s="1">
         <v>5200</v>
@@ -9096,233 +9531,337 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="36" t="s">
-        <v>746</v>
+        <v>824</v>
       </c>
       <c r="B24" s="1">
-        <v>4160</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="36" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="B25" s="1">
-        <v>7800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="36" t="s">
-        <v>539</v>
+        <v>687</v>
       </c>
       <c r="B26" s="1">
-        <v>13000</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="36" t="s">
-        <v>540</v>
+        <v>487</v>
       </c>
       <c r="B27" s="1">
-        <v>10400</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>541</v>
+        <v>738</v>
       </c>
       <c r="B28">
-        <v>5200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="B29">
-        <v>62400</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="B30">
-        <v>57200</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>642</v>
+        <v>535</v>
       </c>
       <c r="B31">
-        <v>312000</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>564</v>
+        <v>536</v>
       </c>
       <c r="B32">
-        <v>6240</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>737</v>
+        <v>537</v>
       </c>
       <c r="B33">
-        <v>46800</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>738</v>
+        <v>538</v>
       </c>
       <c r="B34">
-        <v>46800</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>544</v>
+        <v>634</v>
       </c>
       <c r="B35">
-        <v>15600</v>
+        <v>312000</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>694</v>
+        <v>556</v>
       </c>
       <c r="B36">
-        <v>187200</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>647</v>
+        <v>729</v>
       </c>
       <c r="B37">
-        <v>192400</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>751</v>
+        <v>730</v>
       </c>
       <c r="B38">
-        <v>130000</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="B39">
-        <v>46800</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>546</v>
+        <v>686</v>
       </c>
       <c r="B40">
-        <v>26000</v>
+        <v>187200</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>547</v>
+        <v>639</v>
       </c>
       <c r="B41">
-        <v>23400</v>
+        <v>192400</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>599</v>
+        <v>743</v>
       </c>
       <c r="B42">
-        <v>5200</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>559</v>
+        <v>540</v>
       </c>
       <c r="B43">
-        <v>36400</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>560</v>
+        <v>541</v>
       </c>
       <c r="B44">
-        <v>15600</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>406</v>
+        <v>814</v>
       </c>
       <c r="B45">
-        <v>5200</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>557</v>
+        <v>815</v>
       </c>
       <c r="B46">
-        <v>7800</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>567</v>
+        <v>816</v>
       </c>
       <c r="B47">
-        <v>13000</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>568</v>
+        <v>542</v>
       </c>
       <c r="B48">
-        <v>7800</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>548</v>
+        <v>817</v>
       </c>
       <c r="B49">
-        <v>5200</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>549</v>
+        <v>818</v>
       </c>
       <c r="B50">
-        <v>5200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>648</v>
+        <v>819</v>
       </c>
       <c r="B51">
-        <v>52000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>550</v>
+        <v>591</v>
       </c>
       <c r="B52">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>820</v>
+      </c>
+      <c r="B53">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>821</v>
+      </c>
+      <c r="B54">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>822</v>
+      </c>
+      <c r="B55">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>551</v>
+      </c>
+      <c r="B56">
+        <v>36400</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>552</v>
+      </c>
+      <c r="B57">
+        <v>15600</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>406</v>
+      </c>
+      <c r="B58">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>549</v>
+      </c>
+      <c r="B59">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>559</v>
+      </c>
+      <c r="B60">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>560</v>
+      </c>
+      <c r="B61">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>543</v>
+      </c>
+      <c r="B62">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>544</v>
+      </c>
+      <c r="B63">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>640</v>
+      </c>
+      <c r="B64">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>545</v>
+      </c>
+      <c r="B65">
         <v>15600</v>
       </c>
     </row>
@@ -9333,7 +9872,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="58.140625" customWidth="1"/>
@@ -9382,7 +9921,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="B6" s="1">
         <v>20800</v>
@@ -9398,7 +9937,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="B8" s="1">
         <v>20800</v>
@@ -9406,7 +9945,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="B9" s="1">
         <v>4680</v>
@@ -9414,7 +9953,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="B10" s="1">
         <v>20800</v>
@@ -9438,7 +9977,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="B13" s="1">
         <v>4680</v>
@@ -9446,7 +9985,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="B14" s="1">
         <v>3640</v>
@@ -9454,7 +9993,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B15" s="1">
         <v>3120</v>
@@ -9470,7 +10009,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="B17" s="1">
         <v>4160</v>
@@ -9478,7 +10017,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="B18" s="1">
         <v>96200</v>
@@ -9486,7 +10025,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="B19" s="1">
         <v>109200</v>
@@ -9494,7 +10033,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="B20" s="1">
         <v>127400</v>
@@ -9518,7 +10057,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="B23" s="1">
         <v>52000</v>
@@ -9526,7 +10065,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="B24" s="1">
         <v>57200</v>
@@ -9534,7 +10073,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="B25" s="1">
         <v>62400</v>
@@ -9542,7 +10081,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="B26" s="1">
         <v>72800</v>
@@ -9550,7 +10089,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="B27" s="1">
         <v>85800</v>
@@ -9558,7 +10097,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="B28" s="1">
         <v>91000</v>
@@ -9566,7 +10105,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="B29" s="1">
         <v>520</v>
@@ -9598,7 +10137,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="B33" s="1">
         <v>7800</v>
@@ -9614,7 +10153,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="B35" s="1">
         <v>5200</v>
@@ -9622,39 +10161,39 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>407</v>
+        <v>823</v>
       </c>
       <c r="B36" s="1">
-        <v>4160</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>260</v>
+        <v>407</v>
       </c>
       <c r="B37" s="1">
-        <v>15600</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>428</v>
+        <v>260</v>
       </c>
       <c r="B38" s="1">
-        <v>2600</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>487</v>
+        <v>428</v>
       </c>
       <c r="B39" s="1">
-        <v>4160</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>746</v>
+        <v>487</v>
       </c>
       <c r="B40" s="1">
         <v>4160</v>
@@ -9662,47 +10201,47 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>394</v>
+        <v>738</v>
       </c>
       <c r="B41" s="1">
-        <v>6240</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B42" s="1">
-        <v>5200</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B43" s="1">
-        <v>7800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>649</v>
+        <v>396</v>
       </c>
       <c r="B44" s="1">
-        <v>3640</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>397</v>
+        <v>641</v>
       </c>
       <c r="B45" s="1">
-        <v>6240</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B46" s="1">
         <v>6240</v>
@@ -9710,55 +10249,55 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B47" s="1">
-        <v>4160</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>739</v>
+        <v>399</v>
       </c>
       <c r="B48" s="1">
-        <v>3120</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>564</v>
+        <v>731</v>
       </c>
       <c r="B49" s="1">
-        <v>6240</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>729</v>
+        <v>556</v>
       </c>
       <c r="B50" s="1">
-        <v>31200</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="B51" s="1">
-        <v>33800</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>763</v>
+        <v>722</v>
       </c>
       <c r="B52" s="1">
-        <v>36400</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>734</v>
+        <v>755</v>
       </c>
       <c r="B53" s="1">
         <v>36400</v>
@@ -9766,7 +10305,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="B54" s="1">
         <v>36400</v>
@@ -9774,39 +10313,39 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>735</v>
+        <v>723</v>
       </c>
       <c r="B55" s="1">
-        <v>41600</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="B56" s="1">
-        <v>36400</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>736</v>
+        <v>724</v>
       </c>
       <c r="B57" s="1">
-        <v>41600</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="B58" s="1">
-        <v>46800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
       <c r="B59" s="1">
         <v>46800</v>
@@ -9814,95 +10353,95 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>751</v>
+        <v>730</v>
       </c>
       <c r="B60" s="1">
-        <v>130000</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>650</v>
+        <v>743</v>
       </c>
       <c r="B61" s="1">
-        <v>6240</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>551</v>
+        <v>642</v>
       </c>
       <c r="B62" s="1">
-        <v>9360</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>400</v>
+        <v>546</v>
       </c>
       <c r="B63" s="1">
-        <v>10400</v>
+        <v>9360</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>664</v>
+        <v>400</v>
       </c>
       <c r="B64" s="1">
-        <v>7800</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>401</v>
+        <v>656</v>
       </c>
       <c r="B65" s="1">
-        <v>6240</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B66" s="1">
-        <v>3640</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B67" s="1">
-        <v>6240</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>593</v>
+        <v>403</v>
       </c>
       <c r="B68" s="1">
-        <v>4160</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>404</v>
+        <v>585</v>
       </c>
       <c r="B69" s="1">
-        <v>6240</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>599</v>
+        <v>404</v>
       </c>
       <c r="B70" s="1">
-        <v>5200</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>565</v>
+        <v>591</v>
       </c>
       <c r="B71" s="1">
         <v>5200</v>
@@ -9910,7 +10449,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="B72" s="1">
         <v>5200</v>
@@ -9918,57 +10457,65 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>655</v>
+        <v>558</v>
       </c>
       <c r="B73" s="1">
-        <v>3640</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="B74" s="1">
-        <v>2600</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>406</v>
+        <v>648</v>
       </c>
       <c r="B75" s="1">
-        <v>5200</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>557</v>
+        <v>406</v>
       </c>
       <c r="B76" s="1">
-        <v>7800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>567</v>
+        <v>549</v>
       </c>
       <c r="B77" s="1">
-        <v>13000</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="B78" s="1">
-        <v>7800</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="B79" s="1">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>561</v>
+      </c>
+      <c r="B80" s="1">
         <v>2600</v>
       </c>
     </row>

--- a/clientes/files/TODITICO_CATÁLOGO.xlsx
+++ b/clientes/files/TODITICO_CATÁLOGO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\510 Con lo nuevo de Mexico\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\520 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D94514-2E7D-4928-BAC6-44C6F5237A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F8625B-C9B4-412E-B7F6-3EA038F90F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DAEWOO TICO" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="823">
   <si>
     <t>DESCRIPCION</t>
   </si>
@@ -808,9 +808,6 @@
     <t>FILTRO DE GASOLINA</t>
   </si>
   <si>
-    <t xml:space="preserve">FOCOS 60*55 </t>
-  </si>
-  <si>
     <t>FOCOS H4 LED</t>
   </si>
   <si>
@@ -869,12 +866,6 @@
   </si>
   <si>
     <t>LA H DE CAPOT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIMPIA CARBURADOR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIQUIDO DE FRENO </t>
   </si>
   <si>
     <t>LLANTAS R12</t>
@@ -3020,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3033,7 +3024,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B3" s="1">
         <v>6240</v>
@@ -3049,7 +3040,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B5" s="1">
         <v>10400</v>
@@ -3057,7 +3048,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B6" s="1">
         <v>3640</v>
@@ -3065,7 +3056,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B7" s="1">
         <v>4160</v>
@@ -3081,7 +3072,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B9" s="1">
         <v>46800</v>
@@ -3137,7 +3128,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="B16" s="1">
         <v>2600</v>
@@ -3161,15 +3152,15 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B19" s="1">
-        <v>4160</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B20" s="1">
         <v>2600</v>
@@ -3201,7 +3192,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B24" s="1">
         <v>26000</v>
@@ -3281,7 +3272,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B34" s="1">
         <v>36400</v>
@@ -3289,7 +3280,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B35" s="1">
         <v>7800</v>
@@ -3297,7 +3288,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B36" s="1">
         <v>15600</v>
@@ -3305,7 +3296,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B37" s="1">
         <v>41600</v>
@@ -3321,7 +3312,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="B39" s="1">
         <v>52000</v>
@@ -3329,7 +3320,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B40" s="1">
         <v>57200</v>
@@ -3337,7 +3328,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B41" s="1">
         <v>62400</v>
@@ -3353,7 +3344,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B43" s="1">
         <v>26000</v>
@@ -3361,7 +3352,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B44" s="1">
         <v>6240</v>
@@ -3369,7 +3360,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B45" s="1">
         <v>23400</v>
@@ -3377,7 +3368,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="B46" s="1">
         <v>20800</v>
@@ -3417,7 +3408,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B51" s="1">
         <v>520</v>
@@ -3433,7 +3424,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B53" s="1">
         <v>520</v>
@@ -3441,7 +3432,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B54" s="1">
         <v>520</v>
@@ -3449,10 +3440,10 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="4" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B55" s="1">
-        <v>2600</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -3481,7 +3472,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B59" s="1">
         <v>5200</v>
@@ -3489,7 +3480,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B60" s="1">
         <v>5200</v>
@@ -3609,7 +3600,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B75" s="1">
         <v>5200</v>
@@ -3689,7 +3680,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B85" s="1">
         <v>7800</v>
@@ -3705,7 +3696,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B87" s="1">
         <v>7800</v>
@@ -3713,7 +3704,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B88" s="1">
         <v>7800</v>
@@ -3721,7 +3712,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B89" s="1">
         <v>15600</v>
@@ -3785,7 +3776,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B97" s="1">
         <v>7800</v>
@@ -3793,7 +3784,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B98" s="1">
         <v>7800</v>
@@ -3801,7 +3792,7 @@
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="4" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B99" s="1">
         <v>36400</v>
@@ -3833,7 +3824,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B103" s="1">
         <v>13000</v>
@@ -3849,7 +3840,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B105" s="1">
         <v>23400</v>
@@ -3857,7 +3848,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B106" s="1">
         <v>130000</v>
@@ -3865,7 +3856,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B107" s="1">
         <v>13000</v>
@@ -3889,7 +3880,7 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B110" s="1">
         <v>23400</v>
@@ -3897,7 +3888,7 @@
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B111" s="1">
         <v>26000</v>
@@ -3905,7 +3896,7 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B112" s="1">
         <v>15600</v>
@@ -3913,7 +3904,7 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B113" s="1">
         <v>104</v>
@@ -3929,7 +3920,7 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="B115" s="1">
         <v>10400</v>
@@ -3945,7 +3936,7 @@
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="B117" s="1">
         <v>1040</v>
@@ -3961,7 +3952,7 @@
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B119" s="1">
         <v>3640</v>
@@ -4017,7 +4008,7 @@
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B126" s="1">
         <v>52000</v>
@@ -4025,7 +4016,7 @@
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B127" s="1">
         <v>52000</v>
@@ -4033,7 +4024,7 @@
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B128" s="1">
         <v>52000</v>
@@ -4049,7 +4040,7 @@
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B130" s="1">
         <v>223600</v>
@@ -4065,7 +4056,7 @@
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B132" s="1">
         <v>3640</v>
@@ -4073,7 +4064,7 @@
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B133" s="1">
         <v>10400</v>
@@ -4081,7 +4072,7 @@
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B134" s="1">
         <v>15600</v>
@@ -4121,7 +4112,7 @@
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B139" s="1">
         <v>130000</v>
@@ -4137,7 +4128,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="B141" s="1">
         <v>104</v>
@@ -4153,10 +4144,10 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B143" s="1">
-        <v>5200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -4185,7 +4176,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B147" s="1">
         <v>6240</v>
@@ -4233,7 +4224,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B153" s="1">
         <v>15600</v>
@@ -4241,7 +4232,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B154" s="1">
         <v>46800</v>
@@ -4249,7 +4240,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B155" s="1">
         <v>26000</v>
@@ -4257,15 +4248,15 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>259</v>
+        <v>404</v>
       </c>
       <c r="B156" s="1">
-        <v>4160</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B157" s="1">
         <v>15600</v>
@@ -4273,7 +4264,7 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B158" s="1">
         <v>10400</v>
@@ -4281,7 +4272,7 @@
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B159" s="1">
         <v>62400</v>
@@ -4289,7 +4280,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B160" s="1">
         <v>2600</v>
@@ -4297,7 +4288,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B161" s="1">
         <v>18200</v>
@@ -4305,7 +4296,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="B162" s="1">
         <v>1560</v>
@@ -4313,7 +4304,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B163" s="1">
         <v>1560</v>
@@ -4321,7 +4312,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B164" s="1">
         <v>104</v>
@@ -4329,7 +4320,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B165" s="1">
         <v>104</v>
@@ -4337,15 +4328,15 @@
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B166" s="1">
-        <v>5200</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B167" s="1">
         <v>2600</v>
@@ -4353,7 +4344,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B168" s="1">
         <v>52000</v>
@@ -4361,7 +4352,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B169" s="1">
         <v>2080</v>
@@ -4369,7 +4360,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="B170" s="1">
         <v>4160</v>
@@ -4377,7 +4368,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B171" s="1">
         <v>31200</v>
@@ -4385,7 +4376,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B172" s="1">
         <v>15600</v>
@@ -4393,7 +4384,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B173" s="1">
         <v>52000</v>
@@ -4401,7 +4392,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B174" s="1">
         <v>15600</v>
@@ -4409,7 +4400,7 @@
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B175" s="1">
         <v>3640</v>
@@ -4417,7 +4408,7 @@
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B176" s="1">
         <v>7800</v>
@@ -4425,7 +4416,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B177" s="1">
         <v>15600</v>
@@ -4433,7 +4424,7 @@
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B178" s="1">
         <v>4160</v>
@@ -4441,7 +4432,7 @@
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B179" s="1">
         <v>4160</v>
@@ -4449,7 +4440,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B180" s="1">
         <v>4160</v>
@@ -4457,7 +4448,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B181" s="1">
         <v>3640</v>
@@ -4465,7 +4456,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B182" s="1">
         <v>2600</v>
@@ -4473,7 +4464,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B183" s="1">
         <v>7800</v>
@@ -4481,7 +4472,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B184" s="1">
         <v>3640</v>
@@ -4489,7 +4480,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B185" s="1">
         <v>3640</v>
@@ -4497,7 +4488,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B186" s="1">
         <v>2600</v>
@@ -4505,7 +4496,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B187" s="1">
         <v>10400</v>
@@ -4513,7 +4504,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B188" s="1">
         <v>1040</v>
@@ -4521,7 +4512,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B189" s="1">
         <v>10400</v>
@@ -4529,7 +4520,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B190" s="1">
         <v>26000</v>
@@ -4537,7 +4528,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B191" s="1">
         <v>20800</v>
@@ -4545,7 +4536,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B192" s="1">
         <v>78000</v>
@@ -4553,7 +4544,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B193" s="1">
         <v>46800</v>
@@ -4561,7 +4552,7 @@
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="B194" s="1">
         <v>1560</v>
@@ -4569,47 +4560,47 @@
     </row>
     <row r="195" spans="1:2">
       <c r="A195" t="s">
-        <v>280</v>
+        <v>391</v>
       </c>
       <c r="B195" s="1">
-        <v>6240</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" t="s">
-        <v>281</v>
+        <v>396</v>
       </c>
       <c r="B196" s="1">
-        <v>7800</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B197" s="1">
-        <v>208000</v>
+        <v>166400</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B198" s="1">
-        <v>286000</v>
+        <v>270400</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="B199" s="1">
-        <v>291200</v>
+        <v>275600</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B200" s="1">
         <v>3120</v>
@@ -4617,7 +4608,7 @@
     </row>
     <row r="201" spans="1:2">
       <c r="A201" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="B201" s="1">
         <v>6240</v>
@@ -4625,7 +4616,7 @@
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="B202" s="1">
         <v>4160</v>
@@ -4633,7 +4624,7 @@
     </row>
     <row r="203" spans="1:2">
       <c r="A203" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B203" s="1">
         <v>10400</v>
@@ -4641,7 +4632,7 @@
     </row>
     <row r="204" spans="1:2">
       <c r="A204" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B204" s="1">
         <v>7800</v>
@@ -4649,7 +4640,7 @@
     </row>
     <row r="205" spans="1:2">
       <c r="A205" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B205" s="1">
         <v>2600</v>
@@ -4657,7 +4648,7 @@
     </row>
     <row r="206" spans="1:2">
       <c r="A206" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B206" s="1">
         <v>7800</v>
@@ -4665,7 +4656,7 @@
     </row>
     <row r="207" spans="1:2">
       <c r="A207" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B207" s="1">
         <v>36400</v>
@@ -4673,7 +4664,7 @@
     </row>
     <row r="208" spans="1:2">
       <c r="A208" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B208" s="1">
         <v>4160</v>
@@ -4681,7 +4672,7 @@
     </row>
     <row r="209" spans="1:2">
       <c r="A209" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B209" s="1">
         <v>5200</v>
@@ -4689,7 +4680,7 @@
     </row>
     <row r="210" spans="1:2">
       <c r="A210" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B210" s="1">
         <v>10400</v>
@@ -4697,7 +4688,7 @@
     </row>
     <row r="211" spans="1:2">
       <c r="A211" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B211" s="1">
         <v>4160</v>
@@ -4705,7 +4696,7 @@
     </row>
     <row r="212" spans="1:2">
       <c r="A212" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B212" s="1">
         <v>4160</v>
@@ -4713,7 +4704,7 @@
     </row>
     <row r="213" spans="1:2">
       <c r="A213" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B213" s="1">
         <v>4160</v>
@@ -4721,15 +4712,15 @@
     </row>
     <row r="214" spans="1:2">
       <c r="A214" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B214" s="1">
-        <v>6240</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B215" s="1">
         <v>26000</v>
@@ -4737,7 +4728,7 @@
     </row>
     <row r="216" spans="1:2">
       <c r="A216" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="B216" s="1">
         <v>2600</v>
@@ -4745,7 +4736,7 @@
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B217" s="1">
         <v>2600</v>
@@ -4753,7 +4744,7 @@
     </row>
     <row r="218" spans="1:2">
       <c r="A218" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B218" s="1">
         <v>15600</v>
@@ -4761,7 +4752,7 @@
     </row>
     <row r="219" spans="1:2">
       <c r="A219" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B219" s="1">
         <v>2600</v>
@@ -4769,7 +4760,7 @@
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B220" s="1">
         <v>145600</v>
@@ -4777,7 +4768,7 @@
     </row>
     <row r="221" spans="1:2">
       <c r="A221" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B221" s="1">
         <v>78000</v>
@@ -4785,7 +4776,7 @@
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B222" s="1">
         <v>33800</v>
@@ -4793,7 +4784,7 @@
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B223" s="1">
         <v>41600</v>
@@ -4801,7 +4792,7 @@
     </row>
     <row r="224" spans="1:2">
       <c r="A224" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B224" s="1">
         <v>15600</v>
@@ -4809,7 +4800,7 @@
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B225" s="1">
         <v>78000</v>
@@ -4817,7 +4808,7 @@
     </row>
     <row r="226" spans="1:2">
       <c r="A226" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B226" s="1">
         <v>78000</v>
@@ -4825,39 +4816,39 @@
     </row>
     <row r="227" spans="1:2">
       <c r="A227" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B227" s="1">
-        <v>31200</v>
+        <v>28600</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B228" s="1">
-        <v>33800</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="B229" s="1">
-        <v>36400</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="B230" s="1">
-        <v>36400</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B231" s="1">
         <v>3640</v>
@@ -4865,7 +4856,7 @@
     </row>
     <row r="232" spans="1:2">
       <c r="A232" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B232" s="1">
         <v>5200</v>
@@ -4873,7 +4864,7 @@
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B233" s="1">
         <v>31200</v>
@@ -4881,7 +4872,7 @@
     </row>
     <row r="234" spans="1:2">
       <c r="A234" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B234" s="1">
         <v>5200</v>
@@ -4889,7 +4880,7 @@
     </row>
     <row r="235" spans="1:2">
       <c r="A235" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B235" s="1">
         <v>10400</v>
@@ -4897,7 +4888,7 @@
     </row>
     <row r="236" spans="1:2">
       <c r="A236" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B236" s="1">
         <v>52000</v>
@@ -4905,7 +4896,7 @@
     </row>
     <row r="237" spans="1:2">
       <c r="A237" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B237" s="1">
         <v>62400</v>
@@ -4913,7 +4904,7 @@
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B238" s="1">
         <v>156000</v>
@@ -4921,7 +4912,7 @@
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="B239" s="1">
         <v>156000</v>
@@ -4929,7 +4920,7 @@
     </row>
     <row r="240" spans="1:2">
       <c r="A240" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B240" s="1">
         <v>83200</v>
@@ -4937,15 +4928,15 @@
     </row>
     <row r="241" spans="1:2">
       <c r="A241" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="B241" s="1">
-        <v>130000</v>
+        <v>114400</v>
       </c>
     </row>
     <row r="242" spans="1:2">
       <c r="A242" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B242" s="1">
         <v>57200</v>
@@ -4953,7 +4944,7 @@
     </row>
     <row r="243" spans="1:2">
       <c r="A243" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B243" s="1">
         <v>83200</v>
@@ -4961,7 +4952,7 @@
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B244" s="1">
         <v>15600</v>
@@ -4969,7 +4960,7 @@
     </row>
     <row r="245" spans="1:2">
       <c r="A245" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B245" s="1">
         <v>15600</v>
@@ -4977,7 +4968,7 @@
     </row>
     <row r="246" spans="1:2">
       <c r="A246" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B246" s="1">
         <v>88400</v>
@@ -4985,7 +4976,7 @@
     </row>
     <row r="247" spans="1:2">
       <c r="A247" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B247" s="1">
         <v>36400</v>
@@ -4993,7 +4984,7 @@
     </row>
     <row r="248" spans="1:2">
       <c r="A248" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B248" s="1">
         <v>104000</v>
@@ -5001,7 +4992,7 @@
     </row>
     <row r="249" spans="1:2">
       <c r="A249" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B249" s="1">
         <v>46800</v>
@@ -5009,7 +5000,7 @@
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B250" s="1">
         <v>10400</v>
@@ -5017,7 +5008,7 @@
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B251" s="1">
         <v>36400</v>
@@ -5025,7 +5016,7 @@
     </row>
     <row r="252" spans="1:2">
       <c r="A252" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B252" s="1">
         <v>13000</v>
@@ -5033,7 +5024,7 @@
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B253" s="1">
         <v>5200</v>
@@ -5041,7 +5032,7 @@
     </row>
     <row r="254" spans="1:2">
       <c r="A254" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B254" s="1">
         <v>10400</v>
@@ -5049,7 +5040,7 @@
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="B255" s="1">
         <v>6240</v>
@@ -5057,7 +5048,7 @@
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="B256" s="1">
         <v>6240</v>
@@ -5065,7 +5056,7 @@
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B257" s="1">
         <v>10400</v>
@@ -5073,7 +5064,7 @@
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B258" s="1">
         <v>10400</v>
@@ -5081,7 +5072,7 @@
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B259" s="1">
         <v>13000</v>
@@ -5089,7 +5080,7 @@
     </row>
     <row r="260" spans="1:2">
       <c r="A260" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B260" s="1">
         <v>31200</v>
@@ -5097,7 +5088,7 @@
     </row>
     <row r="261" spans="1:2">
       <c r="A261" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B261" s="1">
         <v>20800</v>
@@ -5105,7 +5096,7 @@
     </row>
     <row r="262" spans="1:2">
       <c r="A262" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B262" s="1">
         <v>15600</v>
@@ -5113,7 +5104,7 @@
     </row>
     <row r="263" spans="1:2">
       <c r="A263" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B263" s="1">
         <v>10400</v>
@@ -5121,7 +5112,7 @@
     </row>
     <row r="264" spans="1:2">
       <c r="A264" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B264" s="1">
         <v>104</v>
@@ -5129,7 +5120,7 @@
     </row>
     <row r="265" spans="1:2">
       <c r="A265" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B265" s="1">
         <v>78000</v>
@@ -5137,7 +5128,7 @@
     </row>
     <row r="266" spans="1:2">
       <c r="A266" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B266" s="1">
         <v>156000</v>
@@ -5145,7 +5136,7 @@
     </row>
     <row r="267" spans="1:2">
       <c r="A267" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B267" s="1">
         <v>10400</v>
@@ -5153,7 +5144,7 @@
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B268" s="1">
         <v>10400</v>
@@ -5161,7 +5152,7 @@
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B269" s="1">
         <v>7800</v>
@@ -5169,7 +5160,7 @@
     </row>
     <row r="270" spans="1:2">
       <c r="A270" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B270" s="1">
         <v>15600</v>
@@ -5177,7 +5168,7 @@
     </row>
     <row r="271" spans="1:2">
       <c r="A271" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B271" s="1">
         <v>7800</v>
@@ -5185,7 +5176,7 @@
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B272" s="1">
         <v>15600</v>
@@ -5193,7 +5184,7 @@
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B273" s="1">
         <v>20800</v>
@@ -5201,7 +5192,7 @@
     </row>
     <row r="274" spans="1:2">
       <c r="A274" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B274" s="1">
         <v>52000</v>
@@ -5209,7 +5200,7 @@
     </row>
     <row r="275" spans="1:2">
       <c r="A275" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B275" s="1">
         <v>36400</v>
@@ -5217,7 +5208,7 @@
     </row>
     <row r="276" spans="1:2">
       <c r="A276" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B276" s="1">
         <v>5200</v>
@@ -5225,7 +5216,7 @@
     </row>
     <row r="277" spans="1:2">
       <c r="A277" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B277" s="1">
         <v>67600</v>
@@ -5233,7 +5224,7 @@
     </row>
     <row r="278" spans="1:2">
       <c r="A278" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B278" s="1">
         <v>104000</v>
@@ -5241,7 +5232,7 @@
     </row>
     <row r="279" spans="1:2">
       <c r="A279" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B279" s="1">
         <v>13000</v>
@@ -5249,7 +5240,7 @@
     </row>
     <row r="280" spans="1:2">
       <c r="A280" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B280" s="1">
         <v>7800</v>
@@ -5257,7 +5248,7 @@
     </row>
     <row r="281" spans="1:2">
       <c r="A281" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B281" s="1">
         <v>52000</v>
@@ -5265,7 +5256,7 @@
     </row>
     <row r="282" spans="1:2">
       <c r="A282" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B282" s="1">
         <v>31200</v>
@@ -5273,7 +5264,7 @@
     </row>
     <row r="283" spans="1:2">
       <c r="A283" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B283" s="1">
         <v>49400</v>
@@ -5281,7 +5272,7 @@
     </row>
     <row r="284" spans="1:2">
       <c r="A284" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="B284" s="1">
         <v>2600</v>
@@ -5289,7 +5280,7 @@
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B285" s="1">
         <v>2600</v>
@@ -5297,7 +5288,7 @@
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B286" s="1">
         <v>4160</v>
@@ -5305,7 +5296,7 @@
     </row>
     <row r="287" spans="1:2">
       <c r="A287" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B287" s="1">
         <v>3640</v>
@@ -5313,7 +5304,7 @@
     </row>
     <row r="288" spans="1:2">
       <c r="A288" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B288" s="1">
         <v>10400</v>
@@ -5321,7 +5312,7 @@
     </row>
     <row r="289" spans="1:2">
       <c r="A289" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B289" s="1">
         <v>4160</v>
@@ -5329,7 +5320,7 @@
     </row>
     <row r="290" spans="1:2">
       <c r="A290" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B290" s="1">
         <v>5200</v>
@@ -5337,7 +5328,7 @@
     </row>
     <row r="291" spans="1:2">
       <c r="A291" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B291" s="1">
         <v>5200</v>
@@ -5345,7 +5336,7 @@
     </row>
     <row r="292" spans="1:2">
       <c r="A292" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B292" s="1">
         <v>5200</v>
@@ -5353,7 +5344,7 @@
     </row>
     <row r="293" spans="1:2">
       <c r="A293" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B293" s="1">
         <v>7800</v>
@@ -5361,7 +5352,7 @@
     </row>
     <row r="294" spans="1:2">
       <c r="A294" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B294" s="1">
         <v>7800</v>
@@ -5369,7 +5360,7 @@
     </row>
     <row r="295" spans="1:2">
       <c r="A295" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B295" s="1">
         <v>6240</v>
@@ -5377,7 +5368,7 @@
     </row>
     <row r="296" spans="1:2">
       <c r="A296" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B296" s="1">
         <v>7800</v>
@@ -5385,7 +5376,7 @@
     </row>
     <row r="297" spans="1:2">
       <c r="A297" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B297" s="1">
         <v>3120</v>
@@ -5393,7 +5384,7 @@
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="B298" s="1">
         <v>5200</v>
@@ -5401,7 +5392,7 @@
     </row>
     <row r="299" spans="1:2">
       <c r="A299" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B299" s="1">
         <v>78000</v>
@@ -5409,7 +5400,7 @@
     </row>
     <row r="300" spans="1:2">
       <c r="A300" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B300" s="1">
         <v>93600</v>
@@ -5417,7 +5408,7 @@
     </row>
     <row r="301" spans="1:2">
       <c r="A301" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B301" s="1">
         <v>46800</v>
@@ -5425,7 +5416,7 @@
     </row>
     <row r="302" spans="1:2">
       <c r="A302" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B302" s="1">
         <v>15600</v>
@@ -5433,7 +5424,7 @@
     </row>
     <row r="303" spans="1:2">
       <c r="A303" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B303" s="1">
         <v>10400</v>
@@ -5441,7 +5432,7 @@
     </row>
     <row r="304" spans="1:2">
       <c r="A304" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B304" s="1">
         <v>2080</v>
@@ -5449,7 +5440,7 @@
     </row>
     <row r="305" spans="1:2">
       <c r="A305" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="B305" s="1">
         <v>1040</v>
@@ -5457,7 +5448,7 @@
     </row>
     <row r="306" spans="1:2">
       <c r="A306" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="B306" s="1">
         <v>62400</v>
@@ -5465,7 +5456,7 @@
     </row>
     <row r="307" spans="1:2">
       <c r="A307" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B307" s="1">
         <v>39000</v>
@@ -5473,7 +5464,7 @@
     </row>
     <row r="308" spans="1:2">
       <c r="A308" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B308" s="1">
         <v>13000</v>
@@ -5481,7 +5472,7 @@
     </row>
     <row r="309" spans="1:2">
       <c r="A309" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B309" s="1">
         <v>31200</v>
@@ -5489,7 +5480,7 @@
     </row>
     <row r="310" spans="1:2">
       <c r="A310" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="B310" s="1">
         <v>5200</v>
@@ -5497,7 +5488,7 @@
     </row>
     <row r="311" spans="1:2">
       <c r="A311" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B311" s="1">
         <v>6240</v>
@@ -5505,7 +5496,7 @@
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B312" s="1">
         <v>130000</v>
@@ -5513,7 +5504,7 @@
     </row>
     <row r="313" spans="1:2">
       <c r="A313" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B313" s="1">
         <v>286000</v>
@@ -5521,7 +5512,7 @@
     </row>
     <row r="314" spans="1:2">
       <c r="A314" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B314" s="1">
         <v>13000</v>
@@ -5529,7 +5520,7 @@
     </row>
     <row r="315" spans="1:2">
       <c r="A315" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B315" s="1">
         <v>5200</v>
@@ -5537,7 +5528,7 @@
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B316" s="1">
         <v>10400</v>
@@ -5545,7 +5536,7 @@
     </row>
     <row r="317" spans="1:2">
       <c r="A317" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B317" s="1">
         <v>4160</v>
@@ -5553,7 +5544,7 @@
     </row>
     <row r="318" spans="1:2">
       <c r="A318" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B318" s="1">
         <v>4160</v>
@@ -5561,7 +5552,7 @@
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B319" s="1">
         <v>2080</v>
@@ -5569,7 +5560,7 @@
     </row>
     <row r="320" spans="1:2">
       <c r="A320" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B320" s="1">
         <v>7800</v>
@@ -5577,15 +5568,15 @@
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B321" s="1">
-        <v>5200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B322" s="1">
         <v>3640</v>
@@ -5593,7 +5584,7 @@
     </row>
     <row r="323" spans="1:2">
       <c r="A323" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B323" s="1">
         <v>23400</v>
@@ -5601,7 +5592,7 @@
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B324" s="1">
         <v>2080</v>
@@ -5609,7 +5600,7 @@
     </row>
     <row r="325" spans="1:2">
       <c r="A325" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B325" s="1">
         <v>2600</v>
@@ -5617,7 +5608,7 @@
     </row>
     <row r="326" spans="1:2">
       <c r="A326" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B326" s="1">
         <v>2600</v>
@@ -5625,7 +5616,7 @@
     </row>
     <row r="327" spans="1:2">
       <c r="A327" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B327" s="1">
         <v>2600</v>
@@ -5633,7 +5624,7 @@
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B328" s="1">
         <v>10400</v>
@@ -5641,23 +5632,23 @@
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B329" s="1">
-        <v>5200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="330" spans="1:2">
       <c r="A330" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B330" s="1">
-        <v>7800</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="B331" s="1">
         <v>6240</v>
@@ -5665,7 +5656,7 @@
     </row>
     <row r="332" spans="1:2">
       <c r="A332" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B332" s="1">
         <v>7800</v>
@@ -5673,23 +5664,23 @@
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B333" s="1">
-        <v>13000</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B334" s="1">
-        <v>7800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B335" s="1">
         <v>2600</v>
@@ -5697,7 +5688,7 @@
     </row>
     <row r="336" spans="1:2">
       <c r="A336" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B336" s="1">
         <v>3640</v>
@@ -5705,7 +5696,7 @@
     </row>
     <row r="337" spans="1:2">
       <c r="A337" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B337" s="1">
         <v>3120</v>
@@ -5713,7 +5704,7 @@
     </row>
     <row r="338" spans="1:2">
       <c r="A338" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B338" s="1">
         <v>1040</v>
@@ -5721,7 +5712,7 @@
     </row>
     <row r="339" spans="1:2">
       <c r="A339" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B339" s="1">
         <v>2600</v>
@@ -5729,7 +5720,7 @@
     </row>
     <row r="340" spans="1:2">
       <c r="A340" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B340" s="1">
         <v>1560</v>
@@ -5737,7 +5728,7 @@
     </row>
     <row r="341" spans="1:2">
       <c r="A341" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B341" s="1">
         <v>2080</v>
@@ -5745,7 +5736,7 @@
     </row>
     <row r="342" spans="1:2">
       <c r="A342" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B342" s="1">
         <v>1560</v>
@@ -5753,7 +5744,7 @@
     </row>
     <row r="343" spans="1:2">
       <c r="A343" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B343" s="1">
         <v>3640</v>
@@ -5761,7 +5752,7 @@
     </row>
     <row r="344" spans="1:2">
       <c r="A344" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="B344" s="1">
         <v>1560</v>
@@ -5769,7 +5760,7 @@
     </row>
     <row r="345" spans="1:2">
       <c r="A345" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B345" s="1">
         <v>1040</v>
@@ -5777,7 +5768,7 @@
     </row>
     <row r="346" spans="1:2">
       <c r="A346" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B346" s="1">
         <v>93600</v>
@@ -5785,7 +5776,7 @@
     </row>
     <row r="347" spans="1:2">
       <c r="A347" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B347" s="1">
         <v>5200</v>
@@ -5793,7 +5784,7 @@
     </row>
     <row r="348" spans="1:2">
       <c r="A348" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B348" s="1">
         <v>10400</v>
@@ -5801,7 +5792,7 @@
     </row>
     <row r="349" spans="1:2">
       <c r="A349" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="B349" s="1">
         <v>15600</v>
@@ -5809,7 +5800,7 @@
     </row>
     <row r="350" spans="1:2">
       <c r="A350" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B350" s="1">
         <v>15600</v>
@@ -5817,7 +5808,7 @@
     </row>
     <row r="351" spans="1:2">
       <c r="A351" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B351" s="1">
         <v>10400</v>
@@ -5825,7 +5816,7 @@
     </row>
     <row r="352" spans="1:2">
       <c r="A352" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B352" s="1">
         <v>23400</v>
@@ -5833,7 +5824,7 @@
     </row>
     <row r="353" spans="1:2">
       <c r="A353" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B353" s="1">
         <v>7800</v>
@@ -5841,7 +5832,7 @@
     </row>
     <row r="354" spans="1:2">
       <c r="A354" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B354" s="1">
         <v>1560</v>
@@ -5849,7 +5840,7 @@
     </row>
     <row r="355" spans="1:2">
       <c r="A355" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B355" s="1">
         <v>31200</v>
@@ -5857,7 +5848,7 @@
     </row>
     <row r="356" spans="1:2">
       <c r="A356" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B356" s="1">
         <v>7800</v>
@@ -5865,7 +5856,7 @@
     </row>
     <row r="357" spans="1:2">
       <c r="A357" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B357" s="1">
         <v>7800</v>
@@ -5873,7 +5864,7 @@
     </row>
     <row r="358" spans="1:2">
       <c r="A358" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="B358" s="1">
         <v>104000</v>
@@ -5881,7 +5872,7 @@
     </row>
     <row r="359" spans="1:2">
       <c r="A359" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B359" s="1">
         <v>18200</v>
@@ -5889,7 +5880,7 @@
     </row>
     <row r="360" spans="1:2">
       <c r="A360" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B360" s="1">
         <v>5200</v>
@@ -5897,7 +5888,7 @@
     </row>
     <row r="361" spans="1:2">
       <c r="A361" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B361" s="1">
         <v>2080</v>
@@ -5905,7 +5896,7 @@
     </row>
     <row r="362" spans="1:2">
       <c r="A362" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B362" s="1">
         <v>6240</v>
@@ -5930,12 +5921,12 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="5" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B2" s="1">
         <v>72800</v>
@@ -5951,7 +5942,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="7" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="B4" s="1">
         <v>18200</v>
@@ -5959,7 +5950,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="7" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B5" s="1">
         <v>93600</v>
@@ -5975,7 +5966,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="8" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B7" s="1">
         <v>62400</v>
@@ -5983,15 +5974,15 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="5" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B8" s="1">
-        <v>4160</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="B9" s="1">
         <v>67600</v>
@@ -6007,7 +5998,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="5" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="B11" s="1">
         <v>41600</v>
@@ -6031,7 +6022,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="9" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B14" s="1">
         <v>41600</v>
@@ -6047,7 +6038,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="11" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="B16" s="1">
         <v>52000</v>
@@ -6055,7 +6046,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B17" s="1">
         <v>57200</v>
@@ -6063,7 +6054,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="5" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B18" s="1">
         <v>62400</v>
@@ -6087,7 +6078,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B21" s="1">
         <v>31200</v>
@@ -6103,7 +6094,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="5" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B23" s="1">
         <v>36400</v>
@@ -6111,7 +6102,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="5" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B24" s="1">
         <v>41600</v>
@@ -6119,7 +6110,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="5" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B25" s="1">
         <v>520</v>
@@ -6127,7 +6118,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="5" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B26" s="1">
         <v>520</v>
@@ -6135,7 +6126,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="5" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B27" s="1">
         <v>520</v>
@@ -6143,7 +6134,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="5" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B28" s="1">
         <v>7800</v>
@@ -6151,7 +6142,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="5" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B29" s="1">
         <v>10400</v>
@@ -6159,7 +6150,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="5" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B30" s="1">
         <v>20800</v>
@@ -6167,7 +6158,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="12" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B31" s="1">
         <v>20800</v>
@@ -6175,7 +6166,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="5" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="B32" s="1">
         <v>7800</v>
@@ -6191,7 +6182,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="5" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B34" s="1">
         <v>7800</v>
@@ -6215,7 +6206,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="7" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B37" s="1">
         <v>3640</v>
@@ -6231,7 +6222,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="11" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B39" s="1">
         <v>7800</v>
@@ -6239,7 +6230,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="5" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B40" s="1">
         <v>15600</v>
@@ -6247,7 +6238,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="5" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="B41" s="1">
         <v>10400</v>
@@ -6255,7 +6246,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="9" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B42" s="1">
         <v>13000</v>
@@ -6263,7 +6254,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="5" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B43" s="1">
         <v>26000</v>
@@ -6271,7 +6262,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="7" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B44" s="1">
         <v>31200</v>
@@ -6279,7 +6270,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B45" s="1">
         <v>26000</v>
@@ -6287,7 +6278,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="7" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B46" s="1">
         <v>36400</v>
@@ -6295,7 +6286,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="14" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="B47" s="1">
         <v>182000</v>
@@ -6303,7 +6294,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="7" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B48" s="1">
         <v>7800</v>
@@ -6311,7 +6302,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="13" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="B49" s="1">
         <v>67600</v>
@@ -6319,7 +6310,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="15" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B50" s="1">
         <v>10400</v>
@@ -6327,7 +6318,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="B51" s="1">
         <v>26000</v>
@@ -6343,7 +6334,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="5" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="B53" s="1">
         <v>72800</v>
@@ -6351,7 +6342,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="6" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B54" s="1">
         <v>36400</v>
@@ -6359,7 +6350,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="16" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B55" s="1">
         <v>7800</v>
@@ -6375,7 +6366,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="16" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B57" s="1">
         <v>104000</v>
@@ -6383,7 +6374,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="17" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="B58" s="1">
         <v>41600</v>
@@ -6399,7 +6390,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="5" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B60" s="1">
         <v>52000</v>
@@ -6415,7 +6406,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="10" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="B62" s="1">
         <v>130000</v>
@@ -6423,7 +6414,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="5" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="B63" s="1">
         <v>114400</v>
@@ -6463,7 +6454,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="5" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="B68" s="1">
         <v>10400</v>
@@ -6471,7 +6462,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="19" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B69" s="1">
         <v>7800</v>
@@ -6479,7 +6470,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="5" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B70" s="1">
         <v>20800</v>
@@ -6487,15 +6478,15 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="5" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B71" s="1">
-        <v>5200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="9" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B72" s="1">
         <v>31200</v>
@@ -6503,7 +6494,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="5" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B73" s="1">
         <v>28600</v>
@@ -6511,7 +6502,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="5" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="B74" s="1">
         <v>36400</v>
@@ -6519,7 +6510,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="11" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="B75" s="1">
         <v>36400</v>
@@ -6527,7 +6518,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="20" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B76" s="1">
         <v>5200</v>
@@ -6551,7 +6542,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="5" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B79" s="1">
         <v>7800</v>
@@ -6559,7 +6550,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="13" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B80" s="1">
         <v>18200</v>
@@ -6567,7 +6558,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="5" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="B81" s="1">
         <v>2080</v>
@@ -6575,15 +6566,15 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="5" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B82" s="1">
-        <v>5200</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="5" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B83" s="1">
         <v>52000</v>
@@ -6591,7 +6582,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="10" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="B84" s="1">
         <v>4160</v>
@@ -6623,7 +6614,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="17" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="B88" s="1">
         <v>15600</v>
@@ -6631,7 +6622,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="17" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B89" s="1">
         <v>36400</v>
@@ -6647,15 +6638,15 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="5" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="B91" s="1">
-        <v>291200</v>
+        <v>275600</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="5" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="B92" s="1">
         <v>10400</v>
@@ -6679,7 +6670,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="5" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B95" s="1">
         <v>5200</v>
@@ -6687,7 +6678,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="10" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B96" s="1">
         <v>7800</v>
@@ -6703,15 +6694,15 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="5" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B98" s="1">
-        <v>6240</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="22" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="B99" s="1">
         <v>23400</v>
@@ -6719,7 +6710,7 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="B100" s="1">
         <v>18200</v>
@@ -6727,7 +6718,7 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="B101" s="1">
         <v>20800</v>
@@ -6735,7 +6726,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="5" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="B102" s="1">
         <v>18200</v>
@@ -6751,7 +6742,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="5" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B104" s="1">
         <v>7800</v>
@@ -6759,7 +6750,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="B105" s="1">
         <v>23400</v>
@@ -6767,39 +6758,39 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B106" s="1">
-        <v>36400</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B107" s="1">
-        <v>36400</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="B108" s="1">
-        <v>36400</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="B109" s="1">
-        <v>36400</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B110" s="1">
         <v>6240</v>
@@ -6815,7 +6806,7 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="B112" s="1">
         <v>182000</v>
@@ -6831,7 +6822,7 @@
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="B114" s="1">
         <v>26000</v>
@@ -6839,10 +6830,10 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="B115" s="1">
-        <v>130000</v>
+        <v>114400</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -6855,7 +6846,7 @@
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B117" s="1">
         <v>20800</v>
@@ -6863,7 +6854,7 @@
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="B118" s="1">
         <v>62400</v>
@@ -6879,7 +6870,7 @@
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B120" s="1">
         <v>10400</v>
@@ -6887,7 +6878,7 @@
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B121" s="1">
         <v>7800</v>
@@ -6895,7 +6886,7 @@
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="B122" s="1">
         <v>7800</v>
@@ -6903,7 +6894,7 @@
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="B123" s="1">
         <v>7800</v>
@@ -6911,7 +6902,7 @@
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="B124" s="1">
         <v>7800</v>
@@ -6919,7 +6910,7 @@
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B125" s="1">
         <v>39000</v>
@@ -6935,7 +6926,7 @@
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="B127" s="1">
         <v>78000</v>
@@ -6943,7 +6934,7 @@
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B128" s="1">
         <v>78000</v>
@@ -6951,7 +6942,7 @@
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="B129" s="1">
         <v>67600</v>
@@ -6959,7 +6950,7 @@
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="B130" s="1">
         <v>93600</v>
@@ -6967,7 +6958,7 @@
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="B131" s="1">
         <v>52000</v>
@@ -6975,7 +6966,7 @@
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="B132" s="1">
         <v>46800</v>
@@ -7007,7 +6998,7 @@
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="B136" s="1">
         <v>39000</v>
@@ -7023,7 +7014,7 @@
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="B138" s="1">
         <v>1560</v>
@@ -7031,7 +7022,7 @@
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B139" s="1">
         <v>7800</v>
@@ -7039,7 +7030,7 @@
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B140" s="1">
         <v>20800</v>
@@ -7047,7 +7038,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B141" s="1">
         <v>20800</v>
@@ -7055,7 +7046,7 @@
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B142" s="1">
         <v>36400</v>
@@ -7063,7 +7054,7 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B143" s="1">
         <v>10400</v>
@@ -7071,7 +7062,7 @@
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B144" s="1">
         <v>20800</v>
@@ -7079,7 +7070,7 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="B145" s="1">
         <v>5200</v>
@@ -7095,7 +7086,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="B147" s="1">
         <v>5200</v>
@@ -7103,7 +7094,7 @@
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="B148" s="1">
         <v>5200</v>
@@ -7111,7 +7102,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B149" s="1">
         <v>2600</v>
@@ -7119,23 +7110,23 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B150" s="1">
-        <v>5200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B151" s="1">
-        <v>5200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B152" s="1">
         <v>15600</v>
@@ -7143,23 +7134,23 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B153" s="1">
-        <v>5200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B154" s="1">
-        <v>7800</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B155" s="1">
         <v>7800</v>
@@ -7167,23 +7158,23 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B156" s="1">
-        <v>13000</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B157" s="1">
-        <v>7800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="B158" s="1">
         <v>7800</v>
@@ -7191,7 +7182,7 @@
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B159" s="1">
         <v>5200</v>
@@ -7199,7 +7190,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B160" s="1">
         <v>5200</v>
@@ -7207,7 +7198,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="B161" s="1">
         <v>6240</v>
@@ -7215,7 +7206,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="B162" s="1">
         <v>52000</v>
@@ -7231,7 +7222,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B164" s="1">
         <v>5200</v>
@@ -7256,7 +7247,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -7269,15 +7260,15 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="17" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B3" s="1">
-        <v>3120</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="26" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="B4" s="1">
         <v>13000</v>
@@ -7293,7 +7284,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="25" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B6" s="1">
         <v>104000</v>
@@ -7325,7 +7316,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B10" s="1">
         <v>93600</v>
@@ -7349,15 +7340,15 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="17" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B13" s="1">
-        <v>4160</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="17" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="B14" s="1">
         <v>41600</v>
@@ -7381,7 +7372,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="17" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="B17" s="1">
         <v>20800</v>
@@ -7389,7 +7380,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="17" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="B18" s="1">
         <v>5200</v>
@@ -7397,7 +7388,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="27" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B19" s="1">
         <v>41600</v>
@@ -7413,7 +7404,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="17" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="B21" s="1">
         <v>52000</v>
@@ -7421,7 +7412,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B22" s="1">
         <v>57200</v>
@@ -7429,7 +7420,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="17" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B23" s="1">
         <v>62400</v>
@@ -7477,7 +7468,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="17" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="B29" s="1">
         <v>15600</v>
@@ -7493,7 +7484,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="17" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B31" s="1">
         <v>31200</v>
@@ -7525,7 +7516,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="17" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B35" s="1">
         <v>520</v>
@@ -7533,7 +7524,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="17" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B36" s="1">
         <v>520</v>
@@ -7541,7 +7532,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="17" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B37" s="1">
         <v>520</v>
@@ -7549,7 +7540,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="28" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B38" s="1">
         <v>62400</v>
@@ -7557,7 +7548,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="17" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="B39" s="1">
         <v>62400</v>
@@ -7565,7 +7556,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="17" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="B40" s="1">
         <v>52000</v>
@@ -7573,7 +7564,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="17" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="B41" s="1">
         <v>52000</v>
@@ -7581,7 +7572,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="26" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B42" s="1">
         <v>5200</v>
@@ -7637,7 +7628,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="28" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B49" s="1">
         <v>3640</v>
@@ -7645,7 +7636,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="17" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B50" s="1">
         <v>3640</v>
@@ -7661,7 +7652,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="17" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B52" s="1">
         <v>20800</v>
@@ -7669,7 +7660,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="17" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B53" s="1">
         <v>41600</v>
@@ -7677,7 +7668,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="27" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B54" s="1">
         <v>46800</v>
@@ -7693,7 +7684,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="17" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B56" s="1">
         <v>15600</v>
@@ -7701,7 +7692,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="17" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B57" s="1">
         <v>52000</v>
@@ -7709,7 +7700,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="17" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B58" s="1">
         <v>39000</v>
@@ -7725,7 +7716,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="17" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B60" s="1">
         <v>7800</v>
@@ -7757,7 +7748,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="17" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B64" s="1">
         <v>15600</v>
@@ -7765,7 +7756,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="17" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="B65" s="1">
         <v>26000</v>
@@ -7781,7 +7772,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="17" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="B67" s="1">
         <v>83200</v>
@@ -7805,7 +7796,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="17" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="B70" s="1">
         <v>83200</v>
@@ -7869,7 +7860,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="17" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B78" s="1">
         <v>52000</v>
@@ -7957,7 +7948,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="17" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B89" s="1">
         <v>130000</v>
@@ -8005,7 +7996,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="17" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B95" s="1">
         <v>36400</v>
@@ -8013,7 +8004,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="17" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B96" s="1">
         <v>36400</v>
@@ -8021,7 +8012,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="17" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B97" s="1">
         <v>31200</v>
@@ -8029,7 +8020,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="17" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B98" s="1">
         <v>36400</v>
@@ -8045,7 +8036,7 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="17" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B100" s="1">
         <v>72800</v>
@@ -8053,7 +8044,7 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="17" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B101" s="1">
         <v>72800</v>
@@ -8061,7 +8052,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="31" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="B102" s="1">
         <v>93600</v>
@@ -8069,7 +8060,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="B103" s="1">
         <v>4160</v>
@@ -8077,7 +8068,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="17" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B104" s="1">
         <v>13000</v>
@@ -8085,7 +8076,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="17" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B105" s="1">
         <v>26000</v>
@@ -8093,7 +8084,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="17" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B106" s="1">
         <v>13000</v>
@@ -8101,15 +8092,15 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="17" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B107" s="1">
-        <v>5200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="17" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B108" s="1">
         <v>31200</v>
@@ -8149,7 +8140,7 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B113" s="1">
         <v>5200</v>
@@ -8157,7 +8148,7 @@
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B114" s="1">
         <v>7800</v>
@@ -8165,7 +8156,7 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="17" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B115" s="1">
         <v>7800</v>
@@ -8197,7 +8188,7 @@
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="17" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B119" s="1">
         <v>7800</v>
@@ -8205,7 +8196,7 @@
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="17" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B120" s="1">
         <v>10400</v>
@@ -8213,7 +8204,7 @@
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="B121" s="1">
         <v>6240</v>
@@ -8221,7 +8212,7 @@
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="17" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="B122" s="1">
         <v>18200</v>
@@ -8229,7 +8220,7 @@
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="17" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B123" s="1">
         <v>18200</v>
@@ -8237,15 +8228,15 @@
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="17" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B124" s="1">
-        <v>5200</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="17" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="B125" s="1">
         <v>4160</v>
@@ -8285,7 +8276,7 @@
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="17" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="B130" s="1">
         <v>5200</v>
@@ -8293,7 +8284,7 @@
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="17" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B131" s="1">
         <v>5200</v>
@@ -8301,7 +8292,7 @@
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="17" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B132" s="1">
         <v>72800</v>
@@ -8309,7 +8300,7 @@
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="28" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B133" s="1">
         <v>31200</v>
@@ -8317,7 +8308,7 @@
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="17" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B134" s="1">
         <v>31200</v>
@@ -8325,31 +8316,31 @@
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="33" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="B135" s="1">
-        <v>291200</v>
+        <v>275600</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="17" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B136" s="1">
-        <v>301600</v>
+        <v>286000</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="17" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="B137" s="1">
-        <v>312000</v>
+        <v>296400</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="17" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B138" s="1">
         <v>10400</v>
@@ -8357,7 +8348,7 @@
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="17" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B139" s="1">
         <v>7800</v>
@@ -8365,7 +8356,7 @@
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B140" s="1">
         <v>7800</v>
@@ -8373,7 +8364,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="17" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B141" s="1">
         <v>13000</v>
@@ -8389,7 +8380,7 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="17" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B143" s="1">
         <v>7800</v>
@@ -8405,7 +8396,7 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="17" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B145" s="1">
         <v>5200</v>
@@ -8437,15 +8428,15 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="17" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B149" s="1">
-        <v>6240</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="17" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="B150" s="1">
         <v>23400</v>
@@ -8453,7 +8444,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="B151" s="1">
         <v>18200</v>
@@ -8477,7 +8468,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="17" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B154" s="1">
         <v>39000</v>
@@ -8485,7 +8476,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="17" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B155" s="1">
         <v>39000</v>
@@ -8509,7 +8500,7 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="17" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B158" s="1">
         <v>72800</v>
@@ -8525,31 +8516,31 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="17" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="B160" s="1">
-        <v>36400</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="17" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="B161" s="1">
-        <v>41600</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="17" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="B162" s="1">
-        <v>36400</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="17" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B163" s="1">
         <v>41600</v>
@@ -8557,7 +8548,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="17" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B164" s="1">
         <v>780</v>
@@ -8589,7 +8580,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="17" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B168" s="1">
         <v>182000</v>
@@ -8597,7 +8588,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="17" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="B169" s="1">
         <v>187200</v>
@@ -8605,7 +8596,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="17" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B170" s="1">
         <v>192400</v>
@@ -8613,7 +8604,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="17" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B171" s="1">
         <v>182000</v>
@@ -8621,7 +8612,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="17" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B172" s="1">
         <v>182000</v>
@@ -8629,7 +8620,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="17" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B173" s="1">
         <v>182000</v>
@@ -8637,10 +8628,10 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="17" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="B174" s="1">
-        <v>130000</v>
+        <v>114400</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -8653,7 +8644,7 @@
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="17" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B176" s="1">
         <v>93600</v>
@@ -8661,7 +8652,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="17" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B177" s="1">
         <v>104000</v>
@@ -8685,7 +8676,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="34" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="B180" s="1">
         <v>20800</v>
@@ -8693,7 +8684,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B181" s="1">
         <v>20800</v>
@@ -8701,7 +8692,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="B182" s="1">
         <v>36400</v>
@@ -8709,7 +8700,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="17" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="B183" s="1">
         <v>62400</v>
@@ -8717,7 +8708,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="17" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="B184" s="1">
         <v>31200</v>
@@ -8733,7 +8724,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="17" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="B186" s="1">
         <v>46800</v>
@@ -8741,7 +8732,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="17" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B187" s="1">
         <v>10400</v>
@@ -8749,7 +8740,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B188" s="1">
         <v>15600</v>
@@ -8765,7 +8756,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B190" s="1">
         <v>18200</v>
@@ -8773,7 +8764,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B191" s="1">
         <v>7800</v>
@@ -8797,7 +8788,7 @@
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B194" s="1">
         <v>39000</v>
@@ -8813,7 +8804,7 @@
     </row>
     <row r="196" spans="1:2">
       <c r="A196" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B196" s="1">
         <v>78000</v>
@@ -8821,7 +8812,7 @@
     </row>
     <row r="197" spans="1:2">
       <c r="A197" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B197" s="1">
         <v>88400</v>
@@ -8853,7 +8844,7 @@
     </row>
     <row r="201" spans="1:2">
       <c r="A201" s="4" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B201" s="1">
         <v>72800</v>
@@ -8861,7 +8852,7 @@
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B202" s="1">
         <v>93600</v>
@@ -8925,7 +8916,7 @@
     </row>
     <row r="210" spans="1:2">
       <c r="A210" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B210" s="1">
         <v>93600</v>
@@ -9053,7 +9044,7 @@
     </row>
     <row r="226" spans="1:2">
       <c r="A226" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B226" s="1">
         <v>15600</v>
@@ -9069,7 +9060,7 @@
     </row>
     <row r="228" spans="1:2">
       <c r="A228" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B228" s="1">
         <v>20800</v>
@@ -9085,7 +9076,7 @@
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B230" s="1">
         <v>20800</v>
@@ -9109,7 +9100,7 @@
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B233" s="1">
         <v>18200</v>
@@ -9133,7 +9124,7 @@
     </row>
     <row r="236" spans="1:2">
       <c r="A236" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B236" s="1">
         <v>36400</v>
@@ -9141,7 +9132,7 @@
     </row>
     <row r="237" spans="1:2">
       <c r="A237" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B237" s="1">
         <v>36400</v>
@@ -9149,7 +9140,7 @@
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="B238" s="1">
         <v>7800</v>
@@ -9157,7 +9148,7 @@
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="B239" s="1">
         <v>5200</v>
@@ -9165,18 +9156,18 @@
     </row>
     <row r="240" spans="1:2">
       <c r="A240" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B240" s="1">
-        <v>5200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="241" spans="1:2">
       <c r="A241" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B241" s="1">
-        <v>5200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -9189,23 +9180,23 @@
     </row>
     <row r="243" spans="1:2">
       <c r="A243" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B243" s="1">
-        <v>5200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B244" s="1">
-        <v>7800</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="245" spans="1:2">
       <c r="A245" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B245" s="1">
         <v>10400</v>
@@ -9213,7 +9204,7 @@
     </row>
     <row r="246" spans="1:2">
       <c r="A246" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B246" s="1">
         <v>15600</v>
@@ -9221,23 +9212,23 @@
     </row>
     <row r="247" spans="1:2">
       <c r="A247" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B247" s="1">
-        <v>13000</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="248" spans="1:2">
       <c r="A248" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B248" s="1">
-        <v>7800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="249" spans="1:2">
       <c r="A249" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B249" s="1">
         <v>7800</v>
@@ -9245,7 +9236,7 @@
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B250" s="1">
         <v>7800</v>
@@ -9253,7 +9244,7 @@
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="B251" s="1">
         <v>10400</v>
@@ -9261,15 +9252,15 @@
     </row>
     <row r="252" spans="1:2">
       <c r="A252" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B252" s="1">
-        <v>2600</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="B253" s="1">
         <v>119600</v>
@@ -9277,7 +9268,7 @@
     </row>
     <row r="254" spans="1:2">
       <c r="A254" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="B254" s="1">
         <v>10400</v>
@@ -9285,7 +9276,7 @@
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="B255" s="1">
         <v>7800</v>
@@ -9293,7 +9284,7 @@
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B256" s="1">
         <v>5200</v>
@@ -9301,7 +9292,7 @@
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B257" s="1">
         <v>52000</v>
@@ -9350,12 +9341,12 @@
         <v>0</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="35" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B2" s="1">
         <v>93600</v>
@@ -9363,7 +9354,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="36" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="B3" s="1">
         <v>70200</v>
@@ -9371,7 +9362,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="36" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="B4" s="1">
         <v>46800</v>
@@ -9379,15 +9370,15 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="36" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B5" s="1">
-        <v>4160</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="36" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="B6" s="1">
         <v>31200</v>
@@ -9395,7 +9386,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="36" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B7" s="1">
         <v>57200</v>
@@ -9403,7 +9394,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="36" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B8" s="1">
         <v>62400</v>
@@ -9411,7 +9402,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="36" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B9" s="1">
         <v>13000</v>
@@ -9419,7 +9410,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="36" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B10" s="1">
         <v>18200</v>
@@ -9427,7 +9418,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="36" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B11" s="1">
         <v>52000</v>
@@ -9435,7 +9426,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="36" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B12" s="1">
         <v>46800</v>
@@ -9443,7 +9434,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="35" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="B13" s="1">
         <v>6240</v>
@@ -9451,7 +9442,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="36" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B14" s="1">
         <v>7800</v>
@@ -9459,7 +9450,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="36" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="B15" s="1">
         <v>26000</v>
@@ -9467,7 +9458,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="36" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B16" s="1">
         <v>20800</v>
@@ -9475,7 +9466,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="36" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B17" s="1">
         <v>18200</v>
@@ -9483,7 +9474,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="36" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B18" s="1">
         <v>52000</v>
@@ -9491,7 +9482,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="35" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B19" s="1">
         <v>26000</v>
@@ -9499,7 +9490,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="36" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="B20" s="1">
         <v>31200</v>
@@ -9507,7 +9498,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="36" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B21" s="1">
         <v>13000</v>
@@ -9515,15 +9506,15 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="36" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B22" s="1">
-        <v>5200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="36" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B23" s="1">
         <v>5200</v>
@@ -9531,7 +9522,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="36" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="B24" s="1">
         <v>7800</v>
@@ -9539,7 +9530,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="36" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B25" s="1">
         <v>5200</v>
@@ -9547,7 +9538,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="36" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B26" s="1">
         <v>18200</v>
@@ -9555,15 +9546,15 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="36" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B27" s="1">
-        <v>5200</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="B28">
         <v>4160</v>
@@ -9571,7 +9562,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B29">
         <v>7800</v>
@@ -9579,7 +9570,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B30">
         <v>13000</v>
@@ -9587,7 +9578,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B31">
         <v>10400</v>
@@ -9595,7 +9586,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B32">
         <v>5200</v>
@@ -9603,7 +9594,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="B33">
         <v>62400</v>
@@ -9611,7 +9602,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B34">
         <v>57200</v>
@@ -9619,31 +9610,31 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="B35">
-        <v>312000</v>
+        <v>296400</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B36">
-        <v>6240</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B37">
-        <v>46800</v>
+        <v>44200</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B38">
         <v>46800</v>
@@ -9651,7 +9642,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B39">
         <v>15600</v>
@@ -9659,7 +9650,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B40">
         <v>187200</v>
@@ -9667,7 +9658,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B41">
         <v>192400</v>
@@ -9675,15 +9666,15 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="B42">
-        <v>130000</v>
+        <v>114400</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="B43">
         <v>46800</v>
@@ -9691,7 +9682,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B44">
         <v>26000</v>
@@ -9699,7 +9690,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="B45">
         <v>2600</v>
@@ -9707,7 +9698,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="B46">
         <v>2600</v>
@@ -9715,7 +9706,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="B47">
         <v>7800</v>
@@ -9723,7 +9714,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B48">
         <v>23400</v>
@@ -9731,7 +9722,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="B49">
         <v>20800</v>
@@ -9739,7 +9730,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="B50">
         <v>10400</v>
@@ -9747,7 +9738,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="B51">
         <v>13000</v>
@@ -9755,15 +9746,15 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B52">
-        <v>5200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="B53">
         <v>2600</v>
@@ -9771,7 +9762,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="B54">
         <v>5200</v>
@@ -9779,7 +9770,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="B55">
         <v>2600</v>
@@ -9787,7 +9778,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B56">
         <v>36400</v>
@@ -9795,7 +9786,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B57">
         <v>15600</v>
@@ -9803,39 +9794,39 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B58">
-        <v>5200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B59">
-        <v>7800</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B60">
-        <v>13000</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B61">
-        <v>7800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B62">
         <v>5200</v>
@@ -9843,7 +9834,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B63">
         <v>5200</v>
@@ -9851,7 +9842,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B64">
         <v>52000</v>
@@ -9859,7 +9850,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B65">
         <v>15600</v>
@@ -9884,52 +9875,52 @@
         <v>0</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B2" s="1">
-        <v>4160</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B3" s="1">
-        <v>18200</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B4" s="1">
-        <v>4160</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B5" s="1">
-        <v>18200</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B6" s="1">
-        <v>20800</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B7" s="1">
         <v>18200</v>
@@ -9937,7 +9928,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B8" s="1">
         <v>20800</v>
@@ -9945,103 +9936,103 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="B9" s="1">
-        <v>4680</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B10" s="1">
-        <v>20800</v>
+        <v>16640</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B11" s="1">
-        <v>4160</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B12" s="1">
-        <v>4160</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="B13" s="1">
-        <v>4680</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="B14" s="1">
-        <v>3640</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B15" s="1">
-        <v>3120</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B16" s="1">
-        <v>6240</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B17" s="1">
-        <v>4160</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="B18" s="1">
-        <v>96200</v>
+        <v>91000</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="B19" s="1">
-        <v>109200</v>
+        <v>101400</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="B20" s="1">
-        <v>127400</v>
+        <v>114400</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B21" s="1">
         <v>41600</v>
@@ -10057,7 +10048,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="B23" s="1">
         <v>52000</v>
@@ -10065,7 +10056,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B24" s="1">
         <v>57200</v>
@@ -10073,7 +10064,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B25" s="1">
         <v>62400</v>
@@ -10081,31 +10072,31 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="B26" s="1">
-        <v>72800</v>
+        <v>70200</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B27" s="1">
-        <v>85800</v>
+        <v>83200</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B28" s="1">
-        <v>91000</v>
+        <v>88400</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B29" s="1">
         <v>520</v>
@@ -10113,7 +10104,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B30" s="1">
         <v>520</v>
@@ -10121,7 +10112,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B31" s="1">
         <v>520</v>
@@ -10129,15 +10120,15 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B32" s="1">
-        <v>2600</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B33" s="1">
         <v>7800</v>
@@ -10145,23 +10136,23 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B34" s="1">
-        <v>3640</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B35" s="1">
-        <v>5200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="B36" s="1">
         <v>2600</v>
@@ -10169,15 +10160,15 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B37" s="1">
-        <v>4160</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B38" s="1">
         <v>15600</v>
@@ -10185,23 +10176,23 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B39" s="1">
-        <v>2600</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B40" s="1">
-        <v>4160</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="B41" s="1">
         <v>4160</v>
@@ -10209,23 +10200,23 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B42" s="1">
-        <v>6240</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B43" s="1">
-        <v>5200</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B44" s="1">
         <v>7800</v>
@@ -10233,111 +10224,111 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="B45" s="1">
-        <v>3640</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B46" s="1">
-        <v>6240</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B47" s="1">
-        <v>6240</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B48" s="1">
-        <v>4160</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="B49" s="1">
-        <v>3120</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B50" s="1">
-        <v>6240</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B51" s="1">
-        <v>31200</v>
+        <v>28600</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B52" s="1">
-        <v>33800</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B53" s="1">
-        <v>36400</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B54" s="1">
-        <v>36400</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="B55" s="1">
-        <v>36400</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="B56" s="1">
-        <v>41600</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="B57" s="1">
-        <v>36400</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B58" s="1">
         <v>41600</v>
@@ -10345,15 +10336,15 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B59" s="1">
-        <v>46800</v>
+        <v>44200</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B60" s="1">
         <v>46800</v>
@@ -10361,111 +10352,111 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="B61" s="1">
-        <v>130000</v>
+        <v>114400</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="B62" s="1">
-        <v>6240</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B63" s="1">
-        <v>9360</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B64" s="1">
-        <v>10400</v>
+        <v>9360</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B65" s="1">
-        <v>7800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B66" s="1">
-        <v>6240</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B67" s="1">
-        <v>3640</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B68" s="1">
-        <v>6240</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B69" s="1">
-        <v>4160</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B70" s="1">
-        <v>6240</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B71" s="1">
-        <v>5200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B72" s="1">
-        <v>5200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B73" s="1">
-        <v>5200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="B74" s="1">
         <v>3640</v>
@@ -10473,7 +10464,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="B75" s="1">
         <v>2600</v>
@@ -10481,42 +10472,42 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B76" s="1">
-        <v>5200</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B77" s="1">
-        <v>7800</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B78" s="1">
-        <v>13000</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B79" s="1">
-        <v>7800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B80" s="1">
-        <v>2600</v>
+        <v>1560</v>
       </c>
     </row>
   </sheetData>

--- a/clientes/files/TODITICO_CATÁLOGO.xlsx
+++ b/clientes/files/TODITICO_CATÁLOGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\520 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F8625B-C9B4-412E-B7F6-3EA038F90F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABE7C5F-8EF7-4D87-BA04-F2ABEC06BC3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DAEWOO TICO" sheetId="1" r:id="rId1"/>
@@ -3019,7 +3019,7 @@
         <v>166</v>
       </c>
       <c r="B2" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3027,7 +3027,7 @@
         <v>421</v>
       </c>
       <c r="B3" s="1">
-        <v>6240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3035,7 +3035,7 @@
         <v>167</v>
       </c>
       <c r="B4" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3043,7 +3043,7 @@
         <v>459</v>
       </c>
       <c r="B5" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3051,7 +3051,7 @@
         <v>460</v>
       </c>
       <c r="B6" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3059,7 +3059,7 @@
         <v>593</v>
       </c>
       <c r="B7" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3067,7 +3067,7 @@
         <v>168</v>
       </c>
       <c r="B8" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3075,7 +3075,7 @@
         <v>461</v>
       </c>
       <c r="B9" s="1">
-        <v>46800</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3083,7 +3083,7 @@
         <v>169</v>
       </c>
       <c r="B10" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3091,7 +3091,7 @@
         <v>170</v>
       </c>
       <c r="B11" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3099,7 +3099,7 @@
         <v>171</v>
       </c>
       <c r="B12" s="1">
-        <v>83200</v>
+        <v>84800</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3107,7 +3107,7 @@
         <v>174</v>
       </c>
       <c r="B13" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3115,7 +3115,7 @@
         <v>172</v>
       </c>
       <c r="B14" s="1">
-        <v>78000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3123,7 +3123,7 @@
         <v>173</v>
       </c>
       <c r="B15" s="1">
-        <v>57200</v>
+        <v>58300</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3131,7 +3131,7 @@
         <v>666</v>
       </c>
       <c r="B16" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3139,7 +3139,7 @@
         <v>175</v>
       </c>
       <c r="B17" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3147,7 +3147,7 @@
         <v>176</v>
       </c>
       <c r="B18" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3155,7 +3155,7 @@
         <v>589</v>
       </c>
       <c r="B19" s="1">
-        <v>3120</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3163,7 +3163,7 @@
         <v>462</v>
       </c>
       <c r="B20" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3171,7 +3171,7 @@
         <v>177</v>
       </c>
       <c r="B21" s="1">
-        <v>1560</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3179,7 +3179,7 @@
         <v>178</v>
       </c>
       <c r="B22" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3187,7 +3187,7 @@
         <v>179</v>
       </c>
       <c r="B23" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3195,7 +3195,7 @@
         <v>550</v>
       </c>
       <c r="B24" s="1">
-        <v>26000</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3203,7 +3203,7 @@
         <v>180</v>
       </c>
       <c r="B25" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3211,7 +3211,7 @@
         <v>181</v>
       </c>
       <c r="B26" s="1">
-        <v>46800</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3219,7 +3219,7 @@
         <v>182</v>
       </c>
       <c r="B27" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3227,7 +3227,7 @@
         <v>183</v>
       </c>
       <c r="B28" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3235,7 +3235,7 @@
         <v>184</v>
       </c>
       <c r="B29" s="1">
-        <v>78000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3243,7 +3243,7 @@
         <v>185</v>
       </c>
       <c r="B30" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3251,7 +3251,7 @@
         <v>186</v>
       </c>
       <c r="B31" s="1">
-        <v>83200</v>
+        <v>84800</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3259,7 +3259,7 @@
         <v>187</v>
       </c>
       <c r="B32" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3267,7 +3267,7 @@
         <v>188</v>
       </c>
       <c r="B33" s="1">
-        <v>23400</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3275,7 +3275,7 @@
         <v>606</v>
       </c>
       <c r="B34" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3283,7 +3283,7 @@
         <v>569</v>
       </c>
       <c r="B35" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3291,7 +3291,7 @@
         <v>594</v>
       </c>
       <c r="B36" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3299,7 +3299,7 @@
         <v>430</v>
       </c>
       <c r="B37" s="1">
-        <v>41600</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3307,7 +3307,7 @@
         <v>163</v>
       </c>
       <c r="B38" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3315,7 +3315,7 @@
         <v>647</v>
       </c>
       <c r="B39" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3323,7 +3323,7 @@
         <v>581</v>
       </c>
       <c r="B40" s="1">
-        <v>57200</v>
+        <v>58300</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3331,7 +3331,7 @@
         <v>648</v>
       </c>
       <c r="B41" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3339,7 +3339,7 @@
         <v>189</v>
       </c>
       <c r="B42" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3347,7 +3347,7 @@
         <v>419</v>
       </c>
       <c r="B43" s="1">
-        <v>26000</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3355,7 +3355,7 @@
         <v>408</v>
       </c>
       <c r="B44" s="1">
-        <v>6240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3363,7 +3363,7 @@
         <v>729</v>
       </c>
       <c r="B45" s="1">
-        <v>23400</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3371,7 +3371,7 @@
         <v>730</v>
       </c>
       <c r="B46" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3379,7 +3379,7 @@
         <v>190</v>
       </c>
       <c r="B47" s="1">
-        <v>41600</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3387,7 +3387,7 @@
         <v>191</v>
       </c>
       <c r="B48" s="1">
-        <v>23400</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -3395,7 +3395,7 @@
         <v>192</v>
       </c>
       <c r="B49" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -3403,7 +3403,7 @@
         <v>193</v>
       </c>
       <c r="B50" s="1">
-        <v>23400</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -3411,7 +3411,7 @@
         <v>692</v>
       </c>
       <c r="B51" s="1">
-        <v>520</v>
+        <v>530</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -3419,7 +3419,7 @@
         <v>194</v>
       </c>
       <c r="B52" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -3427,7 +3427,7 @@
         <v>406</v>
       </c>
       <c r="B53" s="1">
-        <v>520</v>
+        <v>530</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -3435,7 +3435,7 @@
         <v>402</v>
       </c>
       <c r="B54" s="1">
-        <v>520</v>
+        <v>530</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -3443,7 +3443,7 @@
         <v>429</v>
       </c>
       <c r="B55" s="1">
-        <v>1560</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -3451,7 +3451,7 @@
         <v>195</v>
       </c>
       <c r="B56" s="1">
-        <v>46800</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -3459,7 +3459,7 @@
         <v>196</v>
       </c>
       <c r="B57" s="1">
-        <v>6240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -3467,7 +3467,7 @@
         <v>197</v>
       </c>
       <c r="B58" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -3475,7 +3475,7 @@
         <v>595</v>
       </c>
       <c r="B59" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -3483,7 +3483,7 @@
         <v>596</v>
       </c>
       <c r="B60" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -3491,7 +3491,7 @@
         <v>198</v>
       </c>
       <c r="B61" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -3499,7 +3499,7 @@
         <v>199</v>
       </c>
       <c r="B62" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -3507,7 +3507,7 @@
         <v>200</v>
       </c>
       <c r="B63" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -3515,7 +3515,7 @@
         <v>201</v>
       </c>
       <c r="B64" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -3523,7 +3523,7 @@
         <v>202</v>
       </c>
       <c r="B65" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -3531,7 +3531,7 @@
         <v>203</v>
       </c>
       <c r="B66" s="1">
-        <v>6240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -3539,7 +3539,7 @@
         <v>204</v>
       </c>
       <c r="B67" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -3547,7 +3547,7 @@
         <v>205</v>
       </c>
       <c r="B68" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -3555,7 +3555,7 @@
         <v>206</v>
       </c>
       <c r="B69" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -3563,7 +3563,7 @@
         <v>208</v>
       </c>
       <c r="B70" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -3571,7 +3571,7 @@
         <v>212</v>
       </c>
       <c r="B71" s="1">
-        <v>1040</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -3579,7 +3579,7 @@
         <v>209</v>
       </c>
       <c r="B72" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -3587,7 +3587,7 @@
         <v>210</v>
       </c>
       <c r="B73" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -3595,7 +3595,7 @@
         <v>211</v>
       </c>
       <c r="B74" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -3603,7 +3603,7 @@
         <v>476</v>
       </c>
       <c r="B75" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -3611,7 +3611,7 @@
         <v>207</v>
       </c>
       <c r="B76" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -3619,7 +3619,7 @@
         <v>213</v>
       </c>
       <c r="B77" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -3627,7 +3627,7 @@
         <v>214</v>
       </c>
       <c r="B78" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -3635,7 +3635,7 @@
         <v>215</v>
       </c>
       <c r="B79" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -3643,7 +3643,7 @@
         <v>216</v>
       </c>
       <c r="B80" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -3651,7 +3651,7 @@
         <v>217</v>
       </c>
       <c r="B81" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -3659,7 +3659,7 @@
         <v>218</v>
       </c>
       <c r="B82" s="1">
-        <v>23400</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -3667,7 +3667,7 @@
         <v>219</v>
       </c>
       <c r="B83" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -3675,7 +3675,7 @@
         <v>220</v>
       </c>
       <c r="B84" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -3683,7 +3683,7 @@
         <v>607</v>
       </c>
       <c r="B85" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -3691,7 +3691,7 @@
         <v>221</v>
       </c>
       <c r="B86" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -3699,7 +3699,7 @@
         <v>608</v>
       </c>
       <c r="B87" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -3707,7 +3707,7 @@
         <v>417</v>
       </c>
       <c r="B88" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -3715,7 +3715,7 @@
         <v>418</v>
       </c>
       <c r="B89" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -3723,7 +3723,7 @@
         <v>222</v>
       </c>
       <c r="B90" s="1">
-        <v>23400</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -3731,7 +3731,7 @@
         <v>223</v>
       </c>
       <c r="B91" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -3739,7 +3739,7 @@
         <v>224</v>
       </c>
       <c r="B92" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -3747,7 +3747,7 @@
         <v>225</v>
       </c>
       <c r="B93" s="1">
-        <v>182000</v>
+        <v>185500</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -3755,7 +3755,7 @@
         <v>226</v>
       </c>
       <c r="B94" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -3763,7 +3763,7 @@
         <v>227</v>
       </c>
       <c r="B95" s="1">
-        <v>156000</v>
+        <v>159000</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -3771,7 +3771,7 @@
         <v>228</v>
       </c>
       <c r="B96" s="1">
-        <v>26000</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -3779,7 +3779,7 @@
         <v>551</v>
       </c>
       <c r="B97" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -3787,7 +3787,7 @@
         <v>667</v>
       </c>
       <c r="B98" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -3795,7 +3795,7 @@
         <v>409</v>
       </c>
       <c r="B99" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -3803,7 +3803,7 @@
         <v>229</v>
       </c>
       <c r="B100" s="1">
-        <v>23400</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -3811,7 +3811,7 @@
         <v>230</v>
       </c>
       <c r="B101" s="1">
-        <v>41600</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -3819,7 +3819,7 @@
         <v>231</v>
       </c>
       <c r="B102" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -3827,7 +3827,7 @@
         <v>424</v>
       </c>
       <c r="B103" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -3835,7 +3835,7 @@
         <v>232</v>
       </c>
       <c r="B104" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -3843,7 +3843,7 @@
         <v>570</v>
       </c>
       <c r="B105" s="1">
-        <v>23400</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -3851,7 +3851,7 @@
         <v>483</v>
       </c>
       <c r="B106" s="1">
-        <v>130000</v>
+        <v>132500</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -3859,7 +3859,7 @@
         <v>587</v>
       </c>
       <c r="B107" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -3867,7 +3867,7 @@
         <v>233</v>
       </c>
       <c r="B108" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -3875,7 +3875,7 @@
         <v>234</v>
       </c>
       <c r="B109" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -3883,7 +3883,7 @@
         <v>731</v>
       </c>
       <c r="B110" s="1">
-        <v>23400</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -3891,7 +3891,7 @@
         <v>717</v>
       </c>
       <c r="B111" s="1">
-        <v>26000</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3899,7 +3899,7 @@
         <v>571</v>
       </c>
       <c r="B112" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3907,7 +3907,7 @@
         <v>590</v>
       </c>
       <c r="B113" s="1">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3915,7 +3915,7 @@
         <v>235</v>
       </c>
       <c r="B114" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3923,7 +3923,7 @@
         <v>732</v>
       </c>
       <c r="B115" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -3931,7 +3931,7 @@
         <v>236</v>
       </c>
       <c r="B116" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -3939,7 +3939,7 @@
         <v>733</v>
       </c>
       <c r="B117" s="1">
-        <v>1040</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3947,7 +3947,7 @@
         <v>237</v>
       </c>
       <c r="B118" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -3955,7 +3955,7 @@
         <v>410</v>
       </c>
       <c r="B119" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -3963,7 +3963,7 @@
         <v>238</v>
       </c>
       <c r="B120" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -3971,7 +3971,7 @@
         <v>239</v>
       </c>
       <c r="B121" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -3979,7 +3979,7 @@
         <v>240</v>
       </c>
       <c r="B122" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -3987,7 +3987,7 @@
         <v>241</v>
       </c>
       <c r="B123" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -3995,7 +3995,7 @@
         <v>242</v>
       </c>
       <c r="B124" s="1">
-        <v>78000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -4003,7 +4003,7 @@
         <v>243</v>
       </c>
       <c r="B125" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -4011,7 +4011,7 @@
         <v>668</v>
       </c>
       <c r="B126" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -4019,7 +4019,7 @@
         <v>669</v>
       </c>
       <c r="B127" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -4027,7 +4027,7 @@
         <v>431</v>
       </c>
       <c r="B128" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -4035,7 +4035,7 @@
         <v>244</v>
       </c>
       <c r="B129" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -4043,7 +4043,7 @@
         <v>597</v>
       </c>
       <c r="B130" s="1">
-        <v>223600</v>
+        <v>227900</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -4051,7 +4051,7 @@
         <v>245</v>
       </c>
       <c r="B131" s="1">
-        <v>93600</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -4059,7 +4059,7 @@
         <v>456</v>
       </c>
       <c r="B132" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -4067,7 +4067,7 @@
         <v>457</v>
       </c>
       <c r="B133" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -4075,7 +4075,7 @@
         <v>458</v>
       </c>
       <c r="B134" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -4083,7 +4083,7 @@
         <v>246</v>
       </c>
       <c r="B135" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -4091,7 +4091,7 @@
         <v>247</v>
       </c>
       <c r="B136" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -4099,7 +4099,7 @@
         <v>248</v>
       </c>
       <c r="B137" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -4107,7 +4107,7 @@
         <v>250</v>
       </c>
       <c r="B138" s="1">
-        <v>41600</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -4115,7 +4115,7 @@
         <v>420</v>
       </c>
       <c r="B139" s="1">
-        <v>130000</v>
+        <v>132500</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -4123,7 +4123,7 @@
         <v>14</v>
       </c>
       <c r="B140" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -4131,7 +4131,7 @@
         <v>602</v>
       </c>
       <c r="B141" s="1">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -4139,7 +4139,7 @@
         <v>249</v>
       </c>
       <c r="B142" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -4147,7 +4147,7 @@
         <v>552</v>
       </c>
       <c r="B143" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -4155,7 +4155,7 @@
         <v>251</v>
       </c>
       <c r="B144" s="1">
-        <v>26000</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -4163,7 +4163,7 @@
         <v>252</v>
       </c>
       <c r="B145" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -4171,7 +4171,7 @@
         <v>253</v>
       </c>
       <c r="B146" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -4179,7 +4179,7 @@
         <v>598</v>
       </c>
       <c r="B147" s="1">
-        <v>6240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -4187,7 +4187,7 @@
         <v>254</v>
       </c>
       <c r="B148" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -4195,7 +4195,7 @@
         <v>255</v>
       </c>
       <c r="B149" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -4203,7 +4203,7 @@
         <v>256</v>
       </c>
       <c r="B150" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -4211,7 +4211,7 @@
         <v>257</v>
       </c>
       <c r="B151" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -4219,7 +4219,7 @@
         <v>258</v>
       </c>
       <c r="B152" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -4227,7 +4227,7 @@
         <v>261</v>
       </c>
       <c r="B153" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -4235,7 +4235,7 @@
         <v>262</v>
       </c>
       <c r="B154" s="1">
-        <v>46800</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -4243,7 +4243,7 @@
         <v>263</v>
       </c>
       <c r="B155" s="1">
-        <v>26000</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -4251,7 +4251,7 @@
         <v>404</v>
       </c>
       <c r="B156" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -4259,7 +4259,7 @@
         <v>259</v>
       </c>
       <c r="B157" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -4267,7 +4267,7 @@
         <v>463</v>
       </c>
       <c r="B158" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -4275,7 +4275,7 @@
         <v>260</v>
       </c>
       <c r="B159" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -4283,7 +4283,7 @@
         <v>264</v>
       </c>
       <c r="B160" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -4291,7 +4291,7 @@
         <v>689</v>
       </c>
       <c r="B161" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -4299,7 +4299,7 @@
         <v>641</v>
       </c>
       <c r="B162" s="1">
-        <v>1560</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -4307,7 +4307,7 @@
         <v>642</v>
       </c>
       <c r="B163" s="1">
-        <v>1560</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -4315,7 +4315,7 @@
         <v>603</v>
       </c>
       <c r="B164" s="1">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -4323,7 +4323,7 @@
         <v>604</v>
       </c>
       <c r="B165" s="1">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -4331,7 +4331,7 @@
         <v>484</v>
       </c>
       <c r="B166" s="1">
-        <v>3120</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -4339,7 +4339,7 @@
         <v>265</v>
       </c>
       <c r="B167" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -4347,7 +4347,7 @@
         <v>609</v>
       </c>
       <c r="B168" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -4355,7 +4355,7 @@
         <v>734</v>
       </c>
       <c r="B169" s="1">
-        <v>2080</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -4363,7 +4363,7 @@
         <v>735</v>
       </c>
       <c r="B170" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -4371,7 +4371,7 @@
         <v>266</v>
       </c>
       <c r="B171" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -4379,7 +4379,7 @@
         <v>267</v>
       </c>
       <c r="B172" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -4387,7 +4387,7 @@
         <v>268</v>
       </c>
       <c r="B173" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -4395,7 +4395,7 @@
         <v>269</v>
       </c>
       <c r="B174" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4403,7 +4403,7 @@
         <v>270</v>
       </c>
       <c r="B175" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4411,7 +4411,7 @@
         <v>271</v>
       </c>
       <c r="B176" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4419,7 +4419,7 @@
         <v>272</v>
       </c>
       <c r="B177" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4427,7 +4427,7 @@
         <v>273</v>
       </c>
       <c r="B178" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4435,7 +4435,7 @@
         <v>422</v>
       </c>
       <c r="B179" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4443,7 +4443,7 @@
         <v>423</v>
       </c>
       <c r="B180" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4451,7 +4451,7 @@
         <v>610</v>
       </c>
       <c r="B181" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4459,7 +4459,7 @@
         <v>611</v>
       </c>
       <c r="B182" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4467,7 +4467,7 @@
         <v>612</v>
       </c>
       <c r="B183" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4475,7 +4475,7 @@
         <v>613</v>
       </c>
       <c r="B184" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4483,7 +4483,7 @@
         <v>614</v>
       </c>
       <c r="B185" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4491,7 +4491,7 @@
         <v>615</v>
       </c>
       <c r="B186" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4499,7 +4499,7 @@
         <v>274</v>
       </c>
       <c r="B187" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4507,7 +4507,7 @@
         <v>276</v>
       </c>
       <c r="B188" s="1">
-        <v>1040</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4515,7 +4515,7 @@
         <v>275</v>
       </c>
       <c r="B189" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4523,7 +4523,7 @@
         <v>616</v>
       </c>
       <c r="B190" s="1">
-        <v>26000</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4531,7 +4531,7 @@
         <v>277</v>
       </c>
       <c r="B191" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4539,7 +4539,7 @@
         <v>464</v>
       </c>
       <c r="B192" s="1">
-        <v>78000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4547,7 +4547,7 @@
         <v>278</v>
       </c>
       <c r="B193" s="1">
-        <v>46800</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4555,7 +4555,7 @@
         <v>736</v>
       </c>
       <c r="B194" s="1">
-        <v>1560</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4563,7 +4563,7 @@
         <v>391</v>
       </c>
       <c r="B195" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4571,7 +4571,7 @@
         <v>396</v>
       </c>
       <c r="B196" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4579,7 +4579,7 @@
         <v>466</v>
       </c>
       <c r="B197" s="1">
-        <v>166400</v>
+        <v>169600</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4587,7 +4587,7 @@
         <v>279</v>
       </c>
       <c r="B198" s="1">
-        <v>270400</v>
+        <v>275600</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4595,7 +4595,7 @@
         <v>649</v>
       </c>
       <c r="B199" s="1">
-        <v>275600</v>
+        <v>280900</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4603,7 +4603,7 @@
         <v>280</v>
       </c>
       <c r="B200" s="1">
-        <v>3120</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4611,7 +4611,7 @@
         <v>696</v>
       </c>
       <c r="B201" s="1">
-        <v>6240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4619,7 +4619,7 @@
         <v>737</v>
       </c>
       <c r="B202" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4627,7 +4627,7 @@
         <v>411</v>
       </c>
       <c r="B203" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4635,7 +4635,7 @@
         <v>281</v>
       </c>
       <c r="B204" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4643,7 +4643,7 @@
         <v>412</v>
       </c>
       <c r="B205" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4651,7 +4651,7 @@
         <v>282</v>
       </c>
       <c r="B206" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4659,7 +4659,7 @@
         <v>283</v>
       </c>
       <c r="B207" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4667,7 +4667,7 @@
         <v>284</v>
       </c>
       <c r="B208" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4675,7 +4675,7 @@
         <v>285</v>
       </c>
       <c r="B209" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4683,7 +4683,7 @@
         <v>286</v>
       </c>
       <c r="B210" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4691,7 +4691,7 @@
         <v>287</v>
       </c>
       <c r="B211" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4699,7 +4699,7 @@
         <v>288</v>
       </c>
       <c r="B212" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4707,7 +4707,7 @@
         <v>289</v>
       </c>
       <c r="B213" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4715,7 +4715,7 @@
         <v>553</v>
       </c>
       <c r="B214" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4723,7 +4723,7 @@
         <v>290</v>
       </c>
       <c r="B215" s="1">
-        <v>26000</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4731,7 +4731,7 @@
         <v>738</v>
       </c>
       <c r="B216" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4739,7 +4739,7 @@
         <v>739</v>
       </c>
       <c r="B217" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4747,7 +4747,7 @@
         <v>291</v>
       </c>
       <c r="B218" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4755,7 +4755,7 @@
         <v>292</v>
       </c>
       <c r="B219" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4763,7 +4763,7 @@
         <v>293</v>
       </c>
       <c r="B220" s="1">
-        <v>145600</v>
+        <v>148400</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4771,7 +4771,7 @@
         <v>294</v>
       </c>
       <c r="B221" s="1">
-        <v>78000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4779,7 +4779,7 @@
         <v>572</v>
       </c>
       <c r="B222" s="1">
-        <v>33800</v>
+        <v>34450</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4787,7 +4787,7 @@
         <v>670</v>
       </c>
       <c r="B223" s="1">
-        <v>41600</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4795,7 +4795,7 @@
         <v>295</v>
       </c>
       <c r="B224" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4803,7 +4803,7 @@
         <v>671</v>
       </c>
       <c r="B225" s="1">
-        <v>78000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4811,7 +4811,7 @@
         <v>296</v>
       </c>
       <c r="B226" s="1">
-        <v>78000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4819,7 +4819,7 @@
         <v>718</v>
       </c>
       <c r="B227" s="1">
-        <v>28600</v>
+        <v>29150</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4827,7 +4827,7 @@
         <v>719</v>
       </c>
       <c r="B228" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4835,7 +4835,7 @@
         <v>720</v>
       </c>
       <c r="B229" s="1">
-        <v>33800</v>
+        <v>34450</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4843,7 +4843,7 @@
         <v>721</v>
       </c>
       <c r="B230" s="1">
-        <v>33800</v>
+        <v>34450</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4851,7 +4851,7 @@
         <v>617</v>
       </c>
       <c r="B231" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4859,7 +4859,7 @@
         <v>297</v>
       </c>
       <c r="B232" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4867,7 +4867,7 @@
         <v>573</v>
       </c>
       <c r="B233" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4875,7 +4875,7 @@
         <v>298</v>
       </c>
       <c r="B234" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4883,7 +4883,7 @@
         <v>299</v>
       </c>
       <c r="B235" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4891,7 +4891,7 @@
         <v>300</v>
       </c>
       <c r="B236" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4899,7 +4899,7 @@
         <v>301</v>
       </c>
       <c r="B237" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4907,7 +4907,7 @@
         <v>302</v>
       </c>
       <c r="B238" s="1">
-        <v>156000</v>
+        <v>159000</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4915,7 +4915,7 @@
         <v>672</v>
       </c>
       <c r="B239" s="1">
-        <v>156000</v>
+        <v>159000</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4923,7 +4923,7 @@
         <v>303</v>
       </c>
       <c r="B240" s="1">
-        <v>83200</v>
+        <v>84800</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4931,7 +4931,7 @@
         <v>740</v>
       </c>
       <c r="B241" s="1">
-        <v>114400</v>
+        <v>116600</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4939,7 +4939,7 @@
         <v>304</v>
       </c>
       <c r="B242" s="1">
-        <v>57200</v>
+        <v>58300</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4947,7 +4947,7 @@
         <v>305</v>
       </c>
       <c r="B243" s="1">
-        <v>83200</v>
+        <v>84800</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4955,7 +4955,7 @@
         <v>306</v>
       </c>
       <c r="B244" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4963,7 +4963,7 @@
         <v>618</v>
       </c>
       <c r="B245" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4971,7 +4971,7 @@
         <v>307</v>
       </c>
       <c r="B246" s="1">
-        <v>88400</v>
+        <v>90100</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4979,7 +4979,7 @@
         <v>308</v>
       </c>
       <c r="B247" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -4987,7 +4987,7 @@
         <v>309</v>
       </c>
       <c r="B248" s="1">
-        <v>104000</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -4995,7 +4995,7 @@
         <v>310</v>
       </c>
       <c r="B249" s="1">
-        <v>46800</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -5003,7 +5003,7 @@
         <v>690</v>
       </c>
       <c r="B250" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -5011,7 +5011,7 @@
         <v>311</v>
       </c>
       <c r="B251" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -5019,7 +5019,7 @@
         <v>312</v>
       </c>
       <c r="B252" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -5027,7 +5027,7 @@
         <v>313</v>
       </c>
       <c r="B253" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -5035,7 +5035,7 @@
         <v>467</v>
       </c>
       <c r="B254" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -5043,7 +5043,7 @@
         <v>741</v>
       </c>
       <c r="B255" s="1">
-        <v>6240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -5051,7 +5051,7 @@
         <v>742</v>
       </c>
       <c r="B256" s="1">
-        <v>6240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -5059,7 +5059,7 @@
         <v>468</v>
       </c>
       <c r="B257" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -5067,7 +5067,7 @@
         <v>314</v>
       </c>
       <c r="B258" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -5075,7 +5075,7 @@
         <v>315</v>
       </c>
       <c r="B259" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -5083,7 +5083,7 @@
         <v>316</v>
       </c>
       <c r="B260" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -5091,7 +5091,7 @@
         <v>414</v>
       </c>
       <c r="B261" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -5099,7 +5099,7 @@
         <v>317</v>
       </c>
       <c r="B262" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -5107,7 +5107,7 @@
         <v>318</v>
       </c>
       <c r="B263" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -5115,7 +5115,7 @@
         <v>605</v>
       </c>
       <c r="B264" s="1">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -5123,7 +5123,7 @@
         <v>319</v>
       </c>
       <c r="B265" s="1">
-        <v>78000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -5131,7 +5131,7 @@
         <v>320</v>
       </c>
       <c r="B266" s="1">
-        <v>156000</v>
+        <v>159000</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -5139,7 +5139,7 @@
         <v>321</v>
       </c>
       <c r="B267" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -5147,7 +5147,7 @@
         <v>322</v>
       </c>
       <c r="B268" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -5155,7 +5155,7 @@
         <v>323</v>
       </c>
       <c r="B269" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -5163,7 +5163,7 @@
         <v>324</v>
       </c>
       <c r="B270" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -5171,7 +5171,7 @@
         <v>325</v>
       </c>
       <c r="B271" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -5179,7 +5179,7 @@
         <v>326</v>
       </c>
       <c r="B272" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -5187,7 +5187,7 @@
         <v>327</v>
       </c>
       <c r="B273" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -5195,7 +5195,7 @@
         <v>328</v>
       </c>
       <c r="B274" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -5203,7 +5203,7 @@
         <v>329</v>
       </c>
       <c r="B275" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -5211,7 +5211,7 @@
         <v>330</v>
       </c>
       <c r="B276" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -5219,7 +5219,7 @@
         <v>331</v>
       </c>
       <c r="B277" s="1">
-        <v>67600</v>
+        <v>68900</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -5227,7 +5227,7 @@
         <v>332</v>
       </c>
       <c r="B278" s="1">
-        <v>104000</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -5235,7 +5235,7 @@
         <v>333</v>
       </c>
       <c r="B279" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -5243,7 +5243,7 @@
         <v>334</v>
       </c>
       <c r="B280" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -5251,7 +5251,7 @@
         <v>574</v>
       </c>
       <c r="B281" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -5259,7 +5259,7 @@
         <v>599</v>
       </c>
       <c r="B282" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -5267,7 +5267,7 @@
         <v>600</v>
       </c>
       <c r="B283" s="1">
-        <v>49400</v>
+        <v>50350</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -5275,7 +5275,7 @@
         <v>743</v>
       </c>
       <c r="B284" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -5283,7 +5283,7 @@
         <v>619</v>
       </c>
       <c r="B285" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -5291,7 +5291,7 @@
         <v>335</v>
       </c>
       <c r="B286" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -5299,7 +5299,7 @@
         <v>620</v>
       </c>
       <c r="B287" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -5307,7 +5307,7 @@
         <v>336</v>
       </c>
       <c r="B288" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -5315,7 +5315,7 @@
         <v>337</v>
       </c>
       <c r="B289" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -5323,7 +5323,7 @@
         <v>338</v>
       </c>
       <c r="B290" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5331,7 +5331,7 @@
         <v>339</v>
       </c>
       <c r="B291" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5339,7 +5339,7 @@
         <v>340</v>
       </c>
       <c r="B292" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5347,7 +5347,7 @@
         <v>341</v>
       </c>
       <c r="B293" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5355,7 +5355,7 @@
         <v>342</v>
       </c>
       <c r="B294" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5363,7 +5363,7 @@
         <v>343</v>
       </c>
       <c r="B295" s="1">
-        <v>6240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5371,7 +5371,7 @@
         <v>415</v>
       </c>
       <c r="B296" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5379,7 +5379,7 @@
         <v>416</v>
       </c>
       <c r="B297" s="1">
-        <v>3120</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5387,7 +5387,7 @@
         <v>601</v>
       </c>
       <c r="B298" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5395,7 +5395,7 @@
         <v>344</v>
       </c>
       <c r="B299" s="1">
-        <v>78000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5403,7 +5403,7 @@
         <v>345</v>
       </c>
       <c r="B300" s="1">
-        <v>93600</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5411,7 +5411,7 @@
         <v>346</v>
       </c>
       <c r="B301" s="1">
-        <v>46800</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5419,7 +5419,7 @@
         <v>347</v>
       </c>
       <c r="B302" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5427,7 +5427,7 @@
         <v>348</v>
       </c>
       <c r="B303" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5435,7 +5435,7 @@
         <v>349</v>
       </c>
       <c r="B304" s="1">
-        <v>2080</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5443,7 +5443,7 @@
         <v>744</v>
       </c>
       <c r="B305" s="1">
-        <v>1040</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5451,7 +5451,7 @@
         <v>673</v>
       </c>
       <c r="B306" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5459,7 +5459,7 @@
         <v>350</v>
       </c>
       <c r="B307" s="1">
-        <v>39000</v>
+        <v>39750</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5467,7 +5467,7 @@
         <v>351</v>
       </c>
       <c r="B308" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5475,7 +5475,7 @@
         <v>352</v>
       </c>
       <c r="B309" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5483,7 +5483,7 @@
         <v>575</v>
       </c>
       <c r="B310" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5491,7 +5491,7 @@
         <v>353</v>
       </c>
       <c r="B311" s="1">
-        <v>6240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5499,7 +5499,7 @@
         <v>354</v>
       </c>
       <c r="B312" s="1">
-        <v>130000</v>
+        <v>132500</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5507,7 +5507,7 @@
         <v>407</v>
       </c>
       <c r="B313" s="1">
-        <v>286000</v>
+        <v>291500</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5515,7 +5515,7 @@
         <v>355</v>
       </c>
       <c r="B314" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5523,7 +5523,7 @@
         <v>356</v>
       </c>
       <c r="B315" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5531,7 +5531,7 @@
         <v>576</v>
       </c>
       <c r="B316" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5539,7 +5539,7 @@
         <v>357</v>
       </c>
       <c r="B317" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5547,7 +5547,7 @@
         <v>358</v>
       </c>
       <c r="B318" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5555,7 +5555,7 @@
         <v>651</v>
       </c>
       <c r="B319" s="1">
-        <v>2080</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5563,7 +5563,7 @@
         <v>577</v>
       </c>
       <c r="B320" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5571,7 +5571,7 @@
         <v>588</v>
       </c>
       <c r="B321" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5579,7 +5579,7 @@
         <v>359</v>
       </c>
       <c r="B322" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5587,7 +5587,7 @@
         <v>360</v>
       </c>
       <c r="B323" s="1">
-        <v>23400</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5595,7 +5595,7 @@
         <v>361</v>
       </c>
       <c r="B324" s="1">
-        <v>2080</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5603,7 +5603,7 @@
         <v>362</v>
       </c>
       <c r="B325" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5611,7 +5611,7 @@
         <v>363</v>
       </c>
       <c r="B326" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5619,7 +5619,7 @@
         <v>364</v>
       </c>
       <c r="B327" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5627,7 +5627,7 @@
         <v>365</v>
       </c>
       <c r="B328" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5635,7 +5635,7 @@
         <v>403</v>
       </c>
       <c r="B329" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5643,7 +5643,7 @@
         <v>546</v>
       </c>
       <c r="B330" s="1">
-        <v>6240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5651,7 +5651,7 @@
         <v>822</v>
       </c>
       <c r="B331" s="1">
-        <v>6240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5659,7 +5659,7 @@
         <v>366</v>
       </c>
       <c r="B332" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5667,7 +5667,7 @@
         <v>556</v>
       </c>
       <c r="B333" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5675,7 +5675,7 @@
         <v>557</v>
       </c>
       <c r="B334" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5683,7 +5683,7 @@
         <v>367</v>
       </c>
       <c r="B335" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5691,7 +5691,7 @@
         <v>368</v>
       </c>
       <c r="B336" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5699,7 +5699,7 @@
         <v>369</v>
       </c>
       <c r="B337" s="1">
-        <v>3120</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5707,7 +5707,7 @@
         <v>370</v>
       </c>
       <c r="B338" s="1">
-        <v>1040</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5715,7 +5715,7 @@
         <v>371</v>
       </c>
       <c r="B339" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5723,7 +5723,7 @@
         <v>372</v>
       </c>
       <c r="B340" s="1">
-        <v>1560</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5731,7 +5731,7 @@
         <v>373</v>
       </c>
       <c r="B341" s="1">
-        <v>2080</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5739,7 +5739,7 @@
         <v>413</v>
       </c>
       <c r="B342" s="1">
-        <v>1560</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5747,7 +5747,7 @@
         <v>465</v>
       </c>
       <c r="B343" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5755,7 +5755,7 @@
         <v>621</v>
       </c>
       <c r="B344" s="1">
-        <v>1560</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5763,7 +5763,7 @@
         <v>374</v>
       </c>
       <c r="B345" s="1">
-        <v>1040</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5771,7 +5771,7 @@
         <v>485</v>
       </c>
       <c r="B346" s="1">
-        <v>93600</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5779,7 +5779,7 @@
         <v>469</v>
       </c>
       <c r="B347" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5787,7 +5787,7 @@
         <v>375</v>
       </c>
       <c r="B348" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5795,7 +5795,7 @@
         <v>674</v>
       </c>
       <c r="B349" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5803,7 +5803,7 @@
         <v>675</v>
       </c>
       <c r="B350" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5811,7 +5811,7 @@
         <v>376</v>
       </c>
       <c r="B351" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5819,7 +5819,7 @@
         <v>377</v>
       </c>
       <c r="B352" s="1">
-        <v>23400</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5827,7 +5827,7 @@
         <v>378</v>
       </c>
       <c r="B353" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5835,7 +5835,7 @@
         <v>622</v>
       </c>
       <c r="B354" s="1">
-        <v>1560</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5843,7 +5843,7 @@
         <v>379</v>
       </c>
       <c r="B355" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5851,7 +5851,7 @@
         <v>470</v>
       </c>
       <c r="B356" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5859,7 +5859,7 @@
         <v>471</v>
       </c>
       <c r="B357" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5867,7 +5867,7 @@
         <v>676</v>
       </c>
       <c r="B358" s="1">
-        <v>104000</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5875,7 +5875,7 @@
         <v>380</v>
       </c>
       <c r="B359" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5883,7 +5883,7 @@
         <v>381</v>
       </c>
       <c r="B360" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5891,7 +5891,7 @@
         <v>454</v>
       </c>
       <c r="B361" s="1">
-        <v>2080</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5899,7 +5899,7 @@
         <v>382</v>
       </c>
       <c r="B362" s="1">
-        <v>6240</v>
+        <v>6360</v>
       </c>
     </row>
   </sheetData>
@@ -5929,7 +5929,7 @@
         <v>486</v>
       </c>
       <c r="B2" s="1">
-        <v>72800</v>
+        <v>74200</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5937,7 +5937,7 @@
         <v>123</v>
       </c>
       <c r="B3" s="1">
-        <v>104000</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5945,7 +5945,7 @@
         <v>757</v>
       </c>
       <c r="B4" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -5953,7 +5953,7 @@
         <v>578</v>
       </c>
       <c r="B5" s="1">
-        <v>93600</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -5961,7 +5961,7 @@
         <v>164</v>
       </c>
       <c r="B6" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -5969,7 +5969,7 @@
         <v>579</v>
       </c>
       <c r="B7" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -5977,7 +5977,7 @@
         <v>589</v>
       </c>
       <c r="B8" s="1">
-        <v>3120</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -5985,7 +5985,7 @@
         <v>758</v>
       </c>
       <c r="B9" s="1">
-        <v>67600</v>
+        <v>68900</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -5993,7 +5993,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -6001,7 +6001,7 @@
         <v>759</v>
       </c>
       <c r="B11" s="1">
-        <v>41600</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -6009,7 +6009,7 @@
         <v>124</v>
       </c>
       <c r="B12" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6017,7 +6017,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6025,7 +6025,7 @@
         <v>430</v>
       </c>
       <c r="B14" s="1">
-        <v>41600</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -6033,7 +6033,7 @@
         <v>163</v>
       </c>
       <c r="B15" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -6041,7 +6041,7 @@
         <v>647</v>
       </c>
       <c r="B16" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6049,7 +6049,7 @@
         <v>581</v>
       </c>
       <c r="B17" s="1">
-        <v>57200</v>
+        <v>58300</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6057,7 +6057,7 @@
         <v>648</v>
       </c>
       <c r="B18" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6065,7 +6065,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6073,7 +6073,7 @@
         <v>125</v>
       </c>
       <c r="B20" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6081,7 +6081,7 @@
         <v>478</v>
       </c>
       <c r="B21" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6089,7 +6089,7 @@
         <v>36</v>
       </c>
       <c r="B22" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6097,7 +6097,7 @@
         <v>487</v>
       </c>
       <c r="B23" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6105,7 +6105,7 @@
         <v>488</v>
       </c>
       <c r="B24" s="1">
-        <v>41600</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6113,7 +6113,7 @@
         <v>692</v>
       </c>
       <c r="B25" s="1">
-        <v>520</v>
+        <v>530</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6121,7 +6121,7 @@
         <v>406</v>
       </c>
       <c r="B26" s="1">
-        <v>520</v>
+        <v>530</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6129,7 +6129,7 @@
         <v>402</v>
       </c>
       <c r="B27" s="1">
-        <v>520</v>
+        <v>530</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6137,7 +6137,7 @@
         <v>439</v>
       </c>
       <c r="B28" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6145,7 +6145,7 @@
         <v>760</v>
       </c>
       <c r="B29" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6153,7 +6153,7 @@
         <v>489</v>
       </c>
       <c r="B30" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6161,7 +6161,7 @@
         <v>490</v>
       </c>
       <c r="B31" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6169,7 +6169,7 @@
         <v>761</v>
       </c>
       <c r="B32" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -6177,7 +6177,7 @@
         <v>12</v>
       </c>
       <c r="B33" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -6185,7 +6185,7 @@
         <v>762</v>
       </c>
       <c r="B34" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -6193,7 +6193,7 @@
         <v>1</v>
       </c>
       <c r="B35" s="1">
-        <v>1300</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -6201,7 +6201,7 @@
         <v>7</v>
       </c>
       <c r="B36" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6209,7 +6209,7 @@
         <v>434</v>
       </c>
       <c r="B37" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -6217,7 +6217,7 @@
         <v>2</v>
       </c>
       <c r="B38" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -6225,7 +6225,7 @@
         <v>491</v>
       </c>
       <c r="B39" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6233,7 +6233,7 @@
         <v>479</v>
       </c>
       <c r="B40" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -6241,7 +6241,7 @@
         <v>763</v>
       </c>
       <c r="B41" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6249,7 +6249,7 @@
         <v>438</v>
       </c>
       <c r="B42" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6257,7 +6257,7 @@
         <v>440</v>
       </c>
       <c r="B43" s="1">
-        <v>26000</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -6265,7 +6265,7 @@
         <v>492</v>
       </c>
       <c r="B44" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -6273,7 +6273,7 @@
         <v>493</v>
       </c>
       <c r="B45" s="1">
-        <v>26000</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -6281,7 +6281,7 @@
         <v>494</v>
       </c>
       <c r="B46" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6289,7 +6289,7 @@
         <v>764</v>
       </c>
       <c r="B47" s="1">
-        <v>182000</v>
+        <v>185500</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -6297,7 +6297,7 @@
         <v>551</v>
       </c>
       <c r="B48" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -6305,7 +6305,7 @@
         <v>765</v>
       </c>
       <c r="B49" s="1">
-        <v>67600</v>
+        <v>68900</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -6313,7 +6313,7 @@
         <v>751</v>
       </c>
       <c r="B50" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -6321,7 +6321,7 @@
         <v>722</v>
       </c>
       <c r="B51" s="1">
-        <v>26000</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -6329,7 +6329,7 @@
         <v>29</v>
       </c>
       <c r="B52" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -6337,7 +6337,7 @@
         <v>766</v>
       </c>
       <c r="B53" s="1">
-        <v>72800</v>
+        <v>74200</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -6345,7 +6345,7 @@
         <v>495</v>
       </c>
       <c r="B54" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -6353,7 +6353,7 @@
         <v>436</v>
       </c>
       <c r="B55" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -6361,7 +6361,7 @@
         <v>126</v>
       </c>
       <c r="B56" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -6369,7 +6369,7 @@
         <v>496</v>
       </c>
       <c r="B57" s="1">
-        <v>104000</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -6377,7 +6377,7 @@
         <v>767</v>
       </c>
       <c r="B58" s="1">
-        <v>41600</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -6385,7 +6385,7 @@
         <v>30</v>
       </c>
       <c r="B59" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -6393,7 +6393,7 @@
         <v>427</v>
       </c>
       <c r="B60" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -6401,7 +6401,7 @@
         <v>8</v>
       </c>
       <c r="B61" s="1">
-        <v>78000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -6409,7 +6409,7 @@
         <v>768</v>
       </c>
       <c r="B62" s="1">
-        <v>130000</v>
+        <v>132500</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -6417,7 +6417,7 @@
         <v>769</v>
       </c>
       <c r="B63" s="1">
-        <v>114400</v>
+        <v>116600</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -6425,7 +6425,7 @@
         <v>127</v>
       </c>
       <c r="B64" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -6433,7 +6433,7 @@
         <v>13</v>
       </c>
       <c r="B65" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -6441,7 +6441,7 @@
         <v>116</v>
       </c>
       <c r="B66" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -6449,7 +6449,7 @@
         <v>14</v>
       </c>
       <c r="B67" s="1">
-        <v>67600</v>
+        <v>68900</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -6457,7 +6457,7 @@
         <v>770</v>
       </c>
       <c r="B68" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -6465,7 +6465,7 @@
         <v>771</v>
       </c>
       <c r="B69" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -6473,7 +6473,7 @@
         <v>426</v>
       </c>
       <c r="B70" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -6481,7 +6481,7 @@
         <v>552</v>
       </c>
       <c r="B71" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -6489,7 +6489,7 @@
         <v>497</v>
       </c>
       <c r="B72" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -6497,7 +6497,7 @@
         <v>498</v>
       </c>
       <c r="B73" s="1">
-        <v>28600</v>
+        <v>29150</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -6505,7 +6505,7 @@
         <v>772</v>
       </c>
       <c r="B74" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -6513,7 +6513,7 @@
         <v>773</v>
       </c>
       <c r="B75" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -6521,7 +6521,7 @@
         <v>586</v>
       </c>
       <c r="B76" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -6529,7 +6529,7 @@
         <v>15</v>
       </c>
       <c r="B77" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -6537,7 +6537,7 @@
         <v>16</v>
       </c>
       <c r="B78" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -6545,7 +6545,7 @@
         <v>580</v>
       </c>
       <c r="B79" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -6553,7 +6553,7 @@
         <v>688</v>
       </c>
       <c r="B80" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -6561,7 +6561,7 @@
         <v>774</v>
       </c>
       <c r="B81" s="1">
-        <v>2080</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -6569,7 +6569,7 @@
         <v>484</v>
       </c>
       <c r="B82" s="1">
-        <v>3120</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -6577,7 +6577,7 @@
         <v>775</v>
       </c>
       <c r="B83" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -6585,7 +6585,7 @@
         <v>735</v>
       </c>
       <c r="B84" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -6593,7 +6593,7 @@
         <v>3</v>
       </c>
       <c r="B85" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -6601,7 +6601,7 @@
         <v>17</v>
       </c>
       <c r="B86" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -6609,7 +6609,7 @@
         <v>128</v>
       </c>
       <c r="B87" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -6617,7 +6617,7 @@
         <v>715</v>
       </c>
       <c r="B88" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -6625,7 +6625,7 @@
         <v>499</v>
       </c>
       <c r="B89" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -6633,7 +6633,7 @@
         <v>9</v>
       </c>
       <c r="B90" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -6641,7 +6641,7 @@
         <v>623</v>
       </c>
       <c r="B91" s="1">
-        <v>275600</v>
+        <v>280900</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -6649,7 +6649,7 @@
         <v>776</v>
       </c>
       <c r="B92" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -6657,7 +6657,7 @@
         <v>18</v>
       </c>
       <c r="B93" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -6665,7 +6665,7 @@
         <v>19</v>
       </c>
       <c r="B94" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -6673,7 +6673,7 @@
         <v>500</v>
       </c>
       <c r="B95" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -6681,7 +6681,7 @@
         <v>501</v>
       </c>
       <c r="B96" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -6689,7 +6689,7 @@
         <v>25</v>
       </c>
       <c r="B97" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -6697,7 +6697,7 @@
         <v>553</v>
       </c>
       <c r="B98" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -6705,7 +6705,7 @@
         <v>777</v>
       </c>
       <c r="B99" s="1">
-        <v>23400</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -6713,7 +6713,7 @@
         <v>778</v>
       </c>
       <c r="B100" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -6721,7 +6721,7 @@
         <v>779</v>
       </c>
       <c r="B101" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -6729,7 +6729,7 @@
         <v>780</v>
       </c>
       <c r="B102" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -6737,7 +6737,7 @@
         <v>129</v>
       </c>
       <c r="B103" s="1">
-        <v>104000</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -6745,7 +6745,7 @@
         <v>502</v>
       </c>
       <c r="B104" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -6753,7 +6753,7 @@
         <v>781</v>
       </c>
       <c r="B105" s="1">
-        <v>23400</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -6761,7 +6761,7 @@
         <v>752</v>
       </c>
       <c r="B106" s="1">
-        <v>33800</v>
+        <v>34450</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -6769,7 +6769,7 @@
         <v>723</v>
       </c>
       <c r="B107" s="1">
-        <v>33800</v>
+        <v>34450</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -6777,7 +6777,7 @@
         <v>720</v>
       </c>
       <c r="B108" s="1">
-        <v>33800</v>
+        <v>34450</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -6785,7 +6785,7 @@
         <v>721</v>
       </c>
       <c r="B109" s="1">
-        <v>33800</v>
+        <v>34450</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -6793,7 +6793,7 @@
         <v>503</v>
       </c>
       <c r="B110" s="1">
-        <v>6240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -6801,7 +6801,7 @@
         <v>100</v>
       </c>
       <c r="B111" s="1">
-        <v>93600</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -6809,7 +6809,7 @@
         <v>654</v>
       </c>
       <c r="B112" s="1">
-        <v>182000</v>
+        <v>185500</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -6817,7 +6817,7 @@
         <v>24</v>
       </c>
       <c r="B113" s="1">
-        <v>93600</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -6825,7 +6825,7 @@
         <v>782</v>
       </c>
       <c r="B114" s="1">
-        <v>26000</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -6833,7 +6833,7 @@
         <v>740</v>
       </c>
       <c r="B115" s="1">
-        <v>114400</v>
+        <v>116600</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -6841,7 +6841,7 @@
         <v>20</v>
       </c>
       <c r="B116" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -6849,7 +6849,7 @@
         <v>433</v>
       </c>
       <c r="B117" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -6857,7 +6857,7 @@
         <v>783</v>
       </c>
       <c r="B118" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -6865,7 +6865,7 @@
         <v>115</v>
       </c>
       <c r="B119" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -6873,7 +6873,7 @@
         <v>504</v>
       </c>
       <c r="B120" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -6881,7 +6881,7 @@
         <v>505</v>
       </c>
       <c r="B121" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -6889,7 +6889,7 @@
         <v>784</v>
       </c>
       <c r="B122" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -6897,7 +6897,7 @@
         <v>716</v>
       </c>
       <c r="B123" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -6905,7 +6905,7 @@
         <v>785</v>
       </c>
       <c r="B124" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -6913,7 +6913,7 @@
         <v>506</v>
       </c>
       <c r="B125" s="1">
-        <v>39000</v>
+        <v>39750</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -6921,7 +6921,7 @@
         <v>21</v>
       </c>
       <c r="B126" s="1">
-        <v>26000</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -6929,7 +6929,7 @@
         <v>756</v>
       </c>
       <c r="B127" s="1">
-        <v>78000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -6937,7 +6937,7 @@
         <v>480</v>
       </c>
       <c r="B128" s="1">
-        <v>78000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -6945,7 +6945,7 @@
         <v>786</v>
       </c>
       <c r="B129" s="1">
-        <v>67600</v>
+        <v>68900</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -6953,7 +6953,7 @@
         <v>787</v>
       </c>
       <c r="B130" s="1">
-        <v>93600</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -6961,7 +6961,7 @@
         <v>788</v>
       </c>
       <c r="B131" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -6969,7 +6969,7 @@
         <v>789</v>
       </c>
       <c r="B132" s="1">
-        <v>46800</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -6977,7 +6977,7 @@
         <v>73</v>
       </c>
       <c r="B133" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -6985,7 +6985,7 @@
         <v>74</v>
       </c>
       <c r="B134" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -6993,7 +6993,7 @@
         <v>162</v>
       </c>
       <c r="B135" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -7001,7 +7001,7 @@
         <v>790</v>
       </c>
       <c r="B136" s="1">
-        <v>39000</v>
+        <v>39750</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -7009,7 +7009,7 @@
         <v>130</v>
       </c>
       <c r="B137" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -7017,7 +7017,7 @@
         <v>791</v>
       </c>
       <c r="B138" s="1">
-        <v>1560</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -7025,7 +7025,7 @@
         <v>709</v>
       </c>
       <c r="B139" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -7033,7 +7033,7 @@
         <v>432</v>
       </c>
       <c r="B140" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -7041,7 +7041,7 @@
         <v>507</v>
       </c>
       <c r="B141" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -7049,7 +7049,7 @@
         <v>508</v>
       </c>
       <c r="B142" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -7057,7 +7057,7 @@
         <v>437</v>
       </c>
       <c r="B143" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -7065,7 +7065,7 @@
         <v>509</v>
       </c>
       <c r="B144" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -7073,7 +7073,7 @@
         <v>792</v>
       </c>
       <c r="B145" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -7081,7 +7081,7 @@
         <v>4</v>
       </c>
       <c r="B146" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -7089,7 +7089,7 @@
         <v>793</v>
       </c>
       <c r="B147" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -7097,7 +7097,7 @@
         <v>650</v>
       </c>
       <c r="B148" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -7105,7 +7105,7 @@
         <v>651</v>
       </c>
       <c r="B149" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -7113,7 +7113,7 @@
         <v>588</v>
       </c>
       <c r="B150" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -7121,7 +7121,7 @@
         <v>554</v>
       </c>
       <c r="B151" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -7129,7 +7129,7 @@
         <v>510</v>
       </c>
       <c r="B152" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -7137,7 +7137,7 @@
         <v>403</v>
       </c>
       <c r="B153" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -7145,7 +7145,7 @@
         <v>546</v>
       </c>
       <c r="B154" s="1">
-        <v>6240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -7153,7 +7153,7 @@
         <v>441</v>
       </c>
       <c r="B155" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -7161,7 +7161,7 @@
         <v>556</v>
       </c>
       <c r="B156" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -7169,7 +7169,7 @@
         <v>557</v>
       </c>
       <c r="B157" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -7177,7 +7177,7 @@
         <v>794</v>
       </c>
       <c r="B158" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -7185,7 +7185,7 @@
         <v>435</v>
       </c>
       <c r="B159" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -7193,7 +7193,7 @@
         <v>795</v>
       </c>
       <c r="B160" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -7201,7 +7201,7 @@
         <v>796</v>
       </c>
       <c r="B161" s="1">
-        <v>6240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -7209,7 +7209,7 @@
         <v>624</v>
       </c>
       <c r="B162" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -7217,7 +7217,7 @@
         <v>10</v>
       </c>
       <c r="B163" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -7225,7 +7225,7 @@
         <v>797</v>
       </c>
       <c r="B164" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
   </sheetData>
@@ -7255,7 +7255,7 @@
         <v>28</v>
       </c>
       <c r="B2" s="1">
-        <v>72800</v>
+        <v>74200</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -7263,7 +7263,7 @@
         <v>745</v>
       </c>
       <c r="B3" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7271,7 +7271,7 @@
         <v>746</v>
       </c>
       <c r="B4" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -7279,7 +7279,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1">
-        <v>72800</v>
+        <v>74200</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -7287,7 +7287,7 @@
         <v>747</v>
       </c>
       <c r="B6" s="1">
-        <v>104000</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -7295,7 +7295,7 @@
         <v>122</v>
       </c>
       <c r="B7" s="1">
-        <v>104000</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -7303,7 +7303,7 @@
         <v>131</v>
       </c>
       <c r="B8" s="1">
-        <v>130000</v>
+        <v>132500</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -7311,7 +7311,7 @@
         <v>26</v>
       </c>
       <c r="B9" s="1">
-        <v>83200</v>
+        <v>84800</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -7319,7 +7319,7 @@
         <v>567</v>
       </c>
       <c r="B10" s="1">
-        <v>93600</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -7327,7 +7327,7 @@
         <v>82</v>
       </c>
       <c r="B11" s="1">
-        <v>93600</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -7335,7 +7335,7 @@
         <v>165</v>
       </c>
       <c r="B12" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -7343,7 +7343,7 @@
         <v>589</v>
       </c>
       <c r="B13" s="1">
-        <v>3120</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -7351,7 +7351,7 @@
         <v>798</v>
       </c>
       <c r="B14" s="1">
-        <v>41600</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -7359,7 +7359,7 @@
         <v>132</v>
       </c>
       <c r="B15" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -7367,7 +7367,7 @@
         <v>133</v>
       </c>
       <c r="B16" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -7375,7 +7375,7 @@
         <v>753</v>
       </c>
       <c r="B17" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -7383,7 +7383,7 @@
         <v>625</v>
       </c>
       <c r="B18" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -7391,7 +7391,7 @@
         <v>430</v>
       </c>
       <c r="B19" s="1">
-        <v>41600</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -7399,7 +7399,7 @@
         <v>163</v>
       </c>
       <c r="B20" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -7407,7 +7407,7 @@
         <v>647</v>
       </c>
       <c r="B21" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -7415,7 +7415,7 @@
         <v>581</v>
       </c>
       <c r="B22" s="1">
-        <v>57200</v>
+        <v>58300</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -7423,7 +7423,7 @@
         <v>648</v>
       </c>
       <c r="B23" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -7431,7 +7431,7 @@
         <v>83</v>
       </c>
       <c r="B24" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -7439,7 +7439,7 @@
         <v>31</v>
       </c>
       <c r="B25" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -7447,7 +7447,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -7455,7 +7455,7 @@
         <v>121</v>
       </c>
       <c r="B27" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -7463,7 +7463,7 @@
         <v>134</v>
       </c>
       <c r="B28" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -7471,7 +7471,7 @@
         <v>698</v>
       </c>
       <c r="B29" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -7479,7 +7479,7 @@
         <v>37</v>
       </c>
       <c r="B30" s="1">
-        <v>41600</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -7487,7 +7487,7 @@
         <v>477</v>
       </c>
       <c r="B31" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -7495,7 +7495,7 @@
         <v>38</v>
       </c>
       <c r="B32" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -7503,7 +7503,7 @@
         <v>158</v>
       </c>
       <c r="B33" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -7511,7 +7511,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>23400</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -7519,7 +7519,7 @@
         <v>692</v>
       </c>
       <c r="B35" s="1">
-        <v>520</v>
+        <v>530</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -7527,7 +7527,7 @@
         <v>406</v>
       </c>
       <c r="B36" s="1">
-        <v>520</v>
+        <v>530</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -7535,7 +7535,7 @@
         <v>402</v>
       </c>
       <c r="B37" s="1">
-        <v>520</v>
+        <v>530</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -7543,7 +7543,7 @@
         <v>626</v>
       </c>
       <c r="B38" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -7551,7 +7551,7 @@
         <v>627</v>
       </c>
       <c r="B39" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -7559,7 +7559,7 @@
         <v>628</v>
       </c>
       <c r="B40" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -7567,7 +7567,7 @@
         <v>629</v>
       </c>
       <c r="B41" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -7575,7 +7575,7 @@
         <v>511</v>
       </c>
       <c r="B42" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -7583,7 +7583,7 @@
         <v>85</v>
       </c>
       <c r="B43" s="1">
-        <v>41600</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -7591,7 +7591,7 @@
         <v>84</v>
       </c>
       <c r="B44" s="1">
-        <v>41600</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -7599,7 +7599,7 @@
         <v>86</v>
       </c>
       <c r="B45" s="1">
-        <v>41600</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -7607,7 +7607,7 @@
         <v>135</v>
       </c>
       <c r="B46" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -7615,7 +7615,7 @@
         <v>136</v>
       </c>
       <c r="B47" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -7623,7 +7623,7 @@
         <v>87</v>
       </c>
       <c r="B48" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -7631,7 +7631,7 @@
         <v>444</v>
       </c>
       <c r="B49" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -7639,7 +7639,7 @@
         <v>512</v>
       </c>
       <c r="B50" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -7647,7 +7647,7 @@
         <v>137</v>
       </c>
       <c r="B51" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -7655,7 +7655,7 @@
         <v>513</v>
       </c>
       <c r="B52" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -7663,7 +7663,7 @@
         <v>451</v>
       </c>
       <c r="B53" s="1">
-        <v>41600</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -7671,7 +7671,7 @@
         <v>452</v>
       </c>
       <c r="B54" s="1">
-        <v>46800</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -7679,7 +7679,7 @@
         <v>138</v>
       </c>
       <c r="B55" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -7687,7 +7687,7 @@
         <v>699</v>
       </c>
       <c r="B56" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -7695,7 +7695,7 @@
         <v>583</v>
       </c>
       <c r="B57" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -7703,7 +7703,7 @@
         <v>584</v>
       </c>
       <c r="B58" s="1">
-        <v>39000</v>
+        <v>39750</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -7711,7 +7711,7 @@
         <v>139</v>
       </c>
       <c r="B59" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -7719,7 +7719,7 @@
         <v>551</v>
       </c>
       <c r="B60" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -7727,7 +7727,7 @@
         <v>140</v>
       </c>
       <c r="B61" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -7735,7 +7735,7 @@
         <v>89</v>
       </c>
       <c r="B62" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -7743,7 +7743,7 @@
         <v>88</v>
       </c>
       <c r="B63" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -7751,7 +7751,7 @@
         <v>559</v>
       </c>
       <c r="B64" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -7759,7 +7759,7 @@
         <v>722</v>
       </c>
       <c r="B65" s="1">
-        <v>26000</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -7767,7 +7767,7 @@
         <v>118</v>
       </c>
       <c r="B66" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -7775,7 +7775,7 @@
         <v>799</v>
       </c>
       <c r="B67" s="1">
-        <v>83200</v>
+        <v>84800</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -7783,7 +7783,7 @@
         <v>39</v>
       </c>
       <c r="B68" s="1">
-        <v>83200</v>
+        <v>84800</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -7791,7 +7791,7 @@
         <v>40</v>
       </c>
       <c r="B69" s="1">
-        <v>83200</v>
+        <v>84800</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -7799,7 +7799,7 @@
         <v>800</v>
       </c>
       <c r="B70" s="1">
-        <v>83200</v>
+        <v>84800</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -7807,7 +7807,7 @@
         <v>120</v>
       </c>
       <c r="B71" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -7815,7 +7815,7 @@
         <v>41</v>
       </c>
       <c r="B72" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -7823,7 +7823,7 @@
         <v>42</v>
       </c>
       <c r="B73" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -7831,7 +7831,7 @@
         <v>43</v>
       </c>
       <c r="B74" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -7839,7 +7839,7 @@
         <v>44</v>
       </c>
       <c r="B75" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -7847,7 +7847,7 @@
         <v>45</v>
       </c>
       <c r="B76" s="1">
-        <v>78000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -7855,7 +7855,7 @@
         <v>46</v>
       </c>
       <c r="B77" s="1">
-        <v>104000</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -7863,7 +7863,7 @@
         <v>687</v>
       </c>
       <c r="B78" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -7871,7 +7871,7 @@
         <v>90</v>
       </c>
       <c r="B79" s="1">
-        <v>26000</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -7879,7 +7879,7 @@
         <v>32</v>
       </c>
       <c r="B80" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -7887,7 +7887,7 @@
         <v>27</v>
       </c>
       <c r="B81" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -7895,7 +7895,7 @@
         <v>33</v>
       </c>
       <c r="B82" s="1">
-        <v>83200</v>
+        <v>84800</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -7903,7 +7903,7 @@
         <v>141</v>
       </c>
       <c r="B83" s="1">
-        <v>83200</v>
+        <v>84800</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -7911,7 +7911,7 @@
         <v>49</v>
       </c>
       <c r="B84" s="1">
-        <v>130000</v>
+        <v>132500</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -7919,7 +7919,7 @@
         <v>48</v>
       </c>
       <c r="B85" s="1">
-        <v>130000</v>
+        <v>132500</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -7927,7 +7927,7 @@
         <v>47</v>
       </c>
       <c r="B86" s="1">
-        <v>119600</v>
+        <v>121900</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -7935,7 +7935,7 @@
         <v>50</v>
       </c>
       <c r="B87" s="1">
-        <v>130000</v>
+        <v>132500</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -7943,7 +7943,7 @@
         <v>51</v>
       </c>
       <c r="B88" s="1">
-        <v>130000</v>
+        <v>132500</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -7951,7 +7951,7 @@
         <v>474</v>
       </c>
       <c r="B89" s="1">
-        <v>130000</v>
+        <v>132500</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -7959,7 +7959,7 @@
         <v>55</v>
       </c>
       <c r="B90" s="1">
-        <v>78000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -7967,7 +7967,7 @@
         <v>52</v>
       </c>
       <c r="B91" s="1">
-        <v>104000</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -7975,7 +7975,7 @@
         <v>53</v>
       </c>
       <c r="B92" s="1">
-        <v>114400</v>
+        <v>116600</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -7983,7 +7983,7 @@
         <v>54</v>
       </c>
       <c r="B93" s="1">
-        <v>114400</v>
+        <v>116600</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -7991,7 +7991,7 @@
         <v>56</v>
       </c>
       <c r="B94" s="1">
-        <v>114400</v>
+        <v>116600</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -7999,7 +7999,7 @@
         <v>475</v>
       </c>
       <c r="B95" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -8007,7 +8007,7 @@
         <v>514</v>
       </c>
       <c r="B96" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -8015,7 +8015,7 @@
         <v>700</v>
       </c>
       <c r="B97" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -8023,7 +8023,7 @@
         <v>701</v>
       </c>
       <c r="B98" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -8031,7 +8031,7 @@
         <v>142</v>
       </c>
       <c r="B99" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -8039,7 +8039,7 @@
         <v>801</v>
       </c>
       <c r="B100" s="1">
-        <v>72800</v>
+        <v>74200</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -8047,7 +8047,7 @@
         <v>544</v>
       </c>
       <c r="B101" s="1">
-        <v>72800</v>
+        <v>74200</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -8055,7 +8055,7 @@
         <v>802</v>
       </c>
       <c r="B102" s="1">
-        <v>93600</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -8063,7 +8063,7 @@
         <v>643</v>
       </c>
       <c r="B103" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -8071,7 +8071,7 @@
         <v>515</v>
       </c>
       <c r="B104" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -8079,7 +8079,7 @@
         <v>428</v>
       </c>
       <c r="B105" s="1">
-        <v>26000</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -8087,7 +8087,7 @@
         <v>693</v>
       </c>
       <c r="B106" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -8095,7 +8095,7 @@
         <v>552</v>
       </c>
       <c r="B107" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -8103,7 +8103,7 @@
         <v>702</v>
       </c>
       <c r="B108" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -8111,7 +8111,7 @@
         <v>93</v>
       </c>
       <c r="B109" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -8119,7 +8119,7 @@
         <v>92</v>
       </c>
       <c r="B110" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -8127,7 +8127,7 @@
         <v>91</v>
       </c>
       <c r="B111" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -8135,7 +8135,7 @@
         <v>94</v>
       </c>
       <c r="B112" s="1">
-        <v>78000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -8143,7 +8143,7 @@
         <v>585</v>
       </c>
       <c r="B113" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -8151,7 +8151,7 @@
         <v>646</v>
       </c>
       <c r="B114" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -8159,7 +8159,7 @@
         <v>560</v>
       </c>
       <c r="B115" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -8167,7 +8167,7 @@
         <v>57</v>
       </c>
       <c r="B116" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -8175,7 +8175,7 @@
         <v>58</v>
       </c>
       <c r="B117" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -8183,7 +8183,7 @@
         <v>59</v>
       </c>
       <c r="B118" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -8191,7 +8191,7 @@
         <v>561</v>
       </c>
       <c r="B119" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -8199,7 +8199,7 @@
         <v>562</v>
       </c>
       <c r="B120" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -8207,7 +8207,7 @@
         <v>677</v>
       </c>
       <c r="B121" s="1">
-        <v>6240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -8215,7 +8215,7 @@
         <v>685</v>
       </c>
       <c r="B122" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -8223,7 +8223,7 @@
         <v>686</v>
       </c>
       <c r="B123" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -8231,7 +8231,7 @@
         <v>484</v>
       </c>
       <c r="B124" s="1">
-        <v>3120</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -8239,7 +8239,7 @@
         <v>735</v>
       </c>
       <c r="B125" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -8247,7 +8247,7 @@
         <v>60</v>
       </c>
       <c r="B126" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -8255,7 +8255,7 @@
         <v>61</v>
       </c>
       <c r="B127" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -8263,7 +8263,7 @@
         <v>157</v>
       </c>
       <c r="B128" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -8271,7 +8271,7 @@
         <v>62</v>
       </c>
       <c r="B129" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -8279,7 +8279,7 @@
         <v>754</v>
       </c>
       <c r="B130" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -8287,7 +8287,7 @@
         <v>694</v>
       </c>
       <c r="B131" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -8295,7 +8295,7 @@
         <v>563</v>
       </c>
       <c r="B132" s="1">
-        <v>72800</v>
+        <v>74200</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -8303,7 +8303,7 @@
         <v>697</v>
       </c>
       <c r="B133" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -8311,7 +8311,7 @@
         <v>455</v>
       </c>
       <c r="B134" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -8319,7 +8319,7 @@
         <v>623</v>
       </c>
       <c r="B135" s="1">
-        <v>275600</v>
+        <v>280900</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -8327,7 +8327,7 @@
         <v>630</v>
       </c>
       <c r="B136" s="1">
-        <v>286000</v>
+        <v>291500</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -8335,7 +8335,7 @@
         <v>631</v>
       </c>
       <c r="B137" s="1">
-        <v>296400</v>
+        <v>302100</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -8343,7 +8343,7 @@
         <v>449</v>
       </c>
       <c r="B138" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -8351,7 +8351,7 @@
         <v>448</v>
       </c>
       <c r="B139" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -8359,7 +8359,7 @@
         <v>450</v>
       </c>
       <c r="B140" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -8367,7 +8367,7 @@
         <v>447</v>
       </c>
       <c r="B141" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -8375,7 +8375,7 @@
         <v>143</v>
       </c>
       <c r="B142" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -8383,7 +8383,7 @@
         <v>446</v>
       </c>
       <c r="B143" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -8391,7 +8391,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -8399,7 +8399,7 @@
         <v>591</v>
       </c>
       <c r="B145" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -8407,7 +8407,7 @@
         <v>96</v>
       </c>
       <c r="B146" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -8415,7 +8415,7 @@
         <v>95</v>
       </c>
       <c r="B147" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -8423,7 +8423,7 @@
         <v>97</v>
       </c>
       <c r="B148" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -8431,7 +8431,7 @@
         <v>553</v>
       </c>
       <c r="B149" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -8439,7 +8439,7 @@
         <v>803</v>
       </c>
       <c r="B150" s="1">
-        <v>23400</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -8447,7 +8447,7 @@
         <v>804</v>
       </c>
       <c r="B151" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -8455,7 +8455,7 @@
         <v>145</v>
       </c>
       <c r="B152" s="1">
-        <v>130000</v>
+        <v>132500</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -8463,7 +8463,7 @@
         <v>119</v>
       </c>
       <c r="B153" s="1">
-        <v>104000</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -8471,7 +8471,7 @@
         <v>703</v>
       </c>
       <c r="B154" s="1">
-        <v>39000</v>
+        <v>39750</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -8479,7 +8479,7 @@
         <v>704</v>
       </c>
       <c r="B155" s="1">
-        <v>39000</v>
+        <v>39750</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -8487,7 +8487,7 @@
         <v>98</v>
       </c>
       <c r="B156" s="1">
-        <v>78000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -8495,7 +8495,7 @@
         <v>63</v>
       </c>
       <c r="B157" s="1">
-        <v>78000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -8503,7 +8503,7 @@
         <v>472</v>
       </c>
       <c r="B158" s="1">
-        <v>72800</v>
+        <v>74200</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -8511,7 +8511,7 @@
         <v>99</v>
       </c>
       <c r="B159" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -8519,7 +8519,7 @@
         <v>720</v>
       </c>
       <c r="B160" s="1">
-        <v>33800</v>
+        <v>34450</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -8527,7 +8527,7 @@
         <v>724</v>
       </c>
       <c r="B161" s="1">
-        <v>39000</v>
+        <v>39750</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -8535,7 +8535,7 @@
         <v>721</v>
       </c>
       <c r="B162" s="1">
-        <v>33800</v>
+        <v>34450</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -8543,7 +8543,7 @@
         <v>725</v>
       </c>
       <c r="B163" s="1">
-        <v>41600</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -8551,7 +8551,7 @@
         <v>695</v>
       </c>
       <c r="B164" s="1">
-        <v>780</v>
+        <v>795</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -8559,7 +8559,7 @@
         <v>101</v>
       </c>
       <c r="B165" s="1">
-        <v>104000</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -8567,7 +8567,7 @@
         <v>102</v>
       </c>
       <c r="B166" s="1">
-        <v>119600</v>
+        <v>121900</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -8575,7 +8575,7 @@
         <v>103</v>
       </c>
       <c r="B167" s="1">
-        <v>182000</v>
+        <v>185500</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -8583,7 +8583,7 @@
         <v>632</v>
       </c>
       <c r="B168" s="1">
-        <v>182000</v>
+        <v>185500</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -8591,7 +8591,7 @@
         <v>633</v>
       </c>
       <c r="B169" s="1">
-        <v>187200</v>
+        <v>190800</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -8599,7 +8599,7 @@
         <v>678</v>
       </c>
       <c r="B170" s="1">
-        <v>192400</v>
+        <v>196100</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -8607,7 +8607,7 @@
         <v>679</v>
       </c>
       <c r="B171" s="1">
-        <v>182000</v>
+        <v>185500</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -8615,7 +8615,7 @@
         <v>680</v>
       </c>
       <c r="B172" s="1">
-        <v>182000</v>
+        <v>185500</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -8623,7 +8623,7 @@
         <v>681</v>
       </c>
       <c r="B173" s="1">
-        <v>182000</v>
+        <v>185500</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -8631,7 +8631,7 @@
         <v>740</v>
       </c>
       <c r="B174" s="1">
-        <v>114400</v>
+        <v>116600</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -8639,7 +8639,7 @@
         <v>23</v>
       </c>
       <c r="B175" s="1">
-        <v>93600</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -8647,7 +8647,7 @@
         <v>442</v>
       </c>
       <c r="B176" s="1">
-        <v>93600</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -8655,7 +8655,7 @@
         <v>564</v>
       </c>
       <c r="B177" s="1">
-        <v>104000</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -8663,7 +8663,7 @@
         <v>146</v>
       </c>
       <c r="B178" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -8671,7 +8671,7 @@
         <v>147</v>
       </c>
       <c r="B179" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -8679,7 +8679,7 @@
         <v>755</v>
       </c>
       <c r="B180" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -8687,7 +8687,7 @@
         <v>705</v>
       </c>
       <c r="B181" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -8695,7 +8695,7 @@
         <v>652</v>
       </c>
       <c r="B182" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -8703,7 +8703,7 @@
         <v>805</v>
       </c>
       <c r="B183" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -8711,7 +8711,7 @@
         <v>748</v>
       </c>
       <c r="B184" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -8719,7 +8719,7 @@
         <v>148</v>
       </c>
       <c r="B185" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -8727,7 +8727,7 @@
         <v>706</v>
       </c>
       <c r="B186" s="1">
-        <v>46800</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -8735,7 +8735,7 @@
         <v>516</v>
       </c>
       <c r="B187" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -8743,7 +8743,7 @@
         <v>749</v>
       </c>
       <c r="B188" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -8751,7 +8751,7 @@
         <v>149</v>
       </c>
       <c r="B189" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -8759,7 +8759,7 @@
         <v>565</v>
       </c>
       <c r="B190" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -8767,7 +8767,7 @@
         <v>707</v>
       </c>
       <c r="B191" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -8775,7 +8775,7 @@
         <v>150</v>
       </c>
       <c r="B192" s="1">
-        <v>23400</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -8783,7 +8783,7 @@
         <v>104</v>
       </c>
       <c r="B193" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -8791,7 +8791,7 @@
         <v>517</v>
       </c>
       <c r="B194" s="1">
-        <v>39000</v>
+        <v>39750</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -8799,7 +8799,7 @@
         <v>151</v>
       </c>
       <c r="B195" s="1">
-        <v>23400</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -8807,7 +8807,7 @@
         <v>481</v>
       </c>
       <c r="B196" s="1">
-        <v>78000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -8815,7 +8815,7 @@
         <v>708</v>
       </c>
       <c r="B197" s="1">
-        <v>88400</v>
+        <v>90100</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -8823,7 +8823,7 @@
         <v>64</v>
       </c>
       <c r="B198" s="1">
-        <v>83200</v>
+        <v>84800</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -8831,7 +8831,7 @@
         <v>152</v>
       </c>
       <c r="B199" s="1">
-        <v>78000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -8839,7 +8839,7 @@
         <v>65</v>
       </c>
       <c r="B200" s="1">
-        <v>104000</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -8847,7 +8847,7 @@
         <v>545</v>
       </c>
       <c r="B201" s="1">
-        <v>72800</v>
+        <v>74200</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -8855,7 +8855,7 @@
         <v>547</v>
       </c>
       <c r="B202" s="1">
-        <v>93600</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -8863,7 +8863,7 @@
         <v>66</v>
       </c>
       <c r="B203" s="1">
-        <v>67600</v>
+        <v>68900</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -8871,7 +8871,7 @@
         <v>67</v>
       </c>
       <c r="B204" s="1">
-        <v>41600</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -8879,7 +8879,7 @@
         <v>68</v>
       </c>
       <c r="B205" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -8887,7 +8887,7 @@
         <v>69</v>
       </c>
       <c r="B206" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -8895,7 +8895,7 @@
         <v>70</v>
       </c>
       <c r="B207" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -8903,7 +8903,7 @@
         <v>71</v>
       </c>
       <c r="B208" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -8911,7 +8911,7 @@
         <v>72</v>
       </c>
       <c r="B209" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -8919,7 +8919,7 @@
         <v>473</v>
       </c>
       <c r="B210" s="1">
-        <v>93600</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -8927,7 +8927,7 @@
         <v>160</v>
       </c>
       <c r="B211" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -8935,7 +8935,7 @@
         <v>161</v>
       </c>
       <c r="B212" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -8943,7 +8943,7 @@
         <v>75</v>
       </c>
       <c r="B213" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -8951,7 +8951,7 @@
         <v>159</v>
       </c>
       <c r="B214" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -8959,7 +8959,7 @@
         <v>107</v>
       </c>
       <c r="B215" s="1">
-        <v>130000</v>
+        <v>132500</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -8967,7 +8967,7 @@
         <v>108</v>
       </c>
       <c r="B216" s="1">
-        <v>104000</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -8975,7 +8975,7 @@
         <v>110</v>
       </c>
       <c r="B217" s="1">
-        <v>104000</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -8983,7 +8983,7 @@
         <v>105</v>
       </c>
       <c r="B218" s="1">
-        <v>78000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -8991,7 +8991,7 @@
         <v>106</v>
       </c>
       <c r="B219" s="1">
-        <v>78000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -8999,7 +8999,7 @@
         <v>109</v>
       </c>
       <c r="B220" s="1">
-        <v>93600</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -9007,7 +9007,7 @@
         <v>111</v>
       </c>
       <c r="B221" s="1">
-        <v>93600</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -9015,7 +9015,7 @@
         <v>153</v>
       </c>
       <c r="B222" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -9023,7 +9023,7 @@
         <v>154</v>
       </c>
       <c r="B223" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -9031,7 +9031,7 @@
         <v>76</v>
       </c>
       <c r="B224" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -9039,7 +9039,7 @@
         <v>77</v>
       </c>
       <c r="B225" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -9047,7 +9047,7 @@
         <v>714</v>
       </c>
       <c r="B226" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -9055,7 +9055,7 @@
         <v>78</v>
       </c>
       <c r="B227" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -9063,7 +9063,7 @@
         <v>443</v>
       </c>
       <c r="B228" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -9071,7 +9071,7 @@
         <v>79</v>
       </c>
       <c r="B229" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -9079,7 +9079,7 @@
         <v>518</v>
       </c>
       <c r="B230" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -9087,7 +9087,7 @@
         <v>80</v>
       </c>
       <c r="B231" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -9095,7 +9095,7 @@
         <v>81</v>
       </c>
       <c r="B232" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -9103,7 +9103,7 @@
         <v>519</v>
       </c>
       <c r="B233" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -9111,7 +9111,7 @@
         <v>113</v>
       </c>
       <c r="B234" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -9119,7 +9119,7 @@
         <v>114</v>
       </c>
       <c r="B235" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -9127,7 +9127,7 @@
         <v>453</v>
       </c>
       <c r="B236" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -9135,7 +9135,7 @@
         <v>710</v>
       </c>
       <c r="B237" s="1">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -9143,7 +9143,7 @@
         <v>750</v>
       </c>
       <c r="B238" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -9151,7 +9151,7 @@
         <v>650</v>
       </c>
       <c r="B239" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -9159,7 +9159,7 @@
         <v>588</v>
       </c>
       <c r="B240" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -9167,7 +9167,7 @@
         <v>555</v>
       </c>
       <c r="B241" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -9175,7 +9175,7 @@
         <v>117</v>
       </c>
       <c r="B242" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -9183,7 +9183,7 @@
         <v>403</v>
       </c>
       <c r="B243" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -9191,7 +9191,7 @@
         <v>546</v>
       </c>
       <c r="B244" s="1">
-        <v>6240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -9199,7 +9199,7 @@
         <v>568</v>
       </c>
       <c r="B245" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -9207,7 +9207,7 @@
         <v>566</v>
       </c>
       <c r="B246" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -9215,7 +9215,7 @@
         <v>556</v>
       </c>
       <c r="B247" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -9223,7 +9223,7 @@
         <v>557</v>
       </c>
       <c r="B248" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -9231,7 +9231,7 @@
         <v>634</v>
       </c>
       <c r="B249" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -9239,7 +9239,7 @@
         <v>711</v>
       </c>
       <c r="B250" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -9247,7 +9247,7 @@
         <v>712</v>
       </c>
       <c r="B251" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -9255,7 +9255,7 @@
         <v>558</v>
       </c>
       <c r="B252" s="1">
-        <v>1560</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -9263,7 +9263,7 @@
         <v>635</v>
       </c>
       <c r="B253" s="1">
-        <v>119600</v>
+        <v>121900</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -9271,7 +9271,7 @@
         <v>713</v>
       </c>
       <c r="B254" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -9279,7 +9279,7 @@
         <v>794</v>
       </c>
       <c r="B255" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -9287,7 +9287,7 @@
         <v>445</v>
       </c>
       <c r="B256" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -9295,7 +9295,7 @@
         <v>682</v>
       </c>
       <c r="B257" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -9303,7 +9303,7 @@
         <v>112</v>
       </c>
       <c r="B258" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -9311,7 +9311,7 @@
         <v>155</v>
       </c>
       <c r="B259" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -9319,7 +9319,7 @@
         <v>156</v>
       </c>
       <c r="B260" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
   </sheetData>
@@ -9349,7 +9349,7 @@
         <v>592</v>
       </c>
       <c r="B2" s="1">
-        <v>93600</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9357,7 +9357,7 @@
         <v>806</v>
       </c>
       <c r="B3" s="1">
-        <v>70200</v>
+        <v>71550</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9365,7 +9365,7 @@
         <v>807</v>
       </c>
       <c r="B4" s="1">
-        <v>46800</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9373,7 +9373,7 @@
         <v>589</v>
       </c>
       <c r="B5" s="1">
-        <v>3120</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -9381,7 +9381,7 @@
         <v>808</v>
       </c>
       <c r="B6" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -9389,7 +9389,7 @@
         <v>581</v>
       </c>
       <c r="B7" s="1">
-        <v>57200</v>
+        <v>58300</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -9397,7 +9397,7 @@
         <v>648</v>
       </c>
       <c r="B8" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -9405,7 +9405,7 @@
         <v>520</v>
       </c>
       <c r="B9" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -9413,7 +9413,7 @@
         <v>521</v>
       </c>
       <c r="B10" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -9421,7 +9421,7 @@
         <v>522</v>
       </c>
       <c r="B11" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -9429,7 +9429,7 @@
         <v>523</v>
       </c>
       <c r="B12" s="1">
-        <v>46800</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -9437,7 +9437,7 @@
         <v>809</v>
       </c>
       <c r="B13" s="1">
-        <v>6240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -9445,7 +9445,7 @@
         <v>551</v>
       </c>
       <c r="B14" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -9453,7 +9453,7 @@
         <v>722</v>
       </c>
       <c r="B15" s="1">
-        <v>26000</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -9461,7 +9461,7 @@
         <v>524</v>
       </c>
       <c r="B16" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -9469,7 +9469,7 @@
         <v>525</v>
       </c>
       <c r="B17" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -9477,7 +9477,7 @@
         <v>691</v>
       </c>
       <c r="B18" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -9485,7 +9485,7 @@
         <v>526</v>
       </c>
       <c r="B19" s="1">
-        <v>26000</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -9493,7 +9493,7 @@
         <v>810</v>
       </c>
       <c r="B20" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -9501,7 +9501,7 @@
         <v>527</v>
       </c>
       <c r="B21" s="1">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -9509,7 +9509,7 @@
         <v>552</v>
       </c>
       <c r="B22" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -9517,7 +9517,7 @@
         <v>528</v>
       </c>
       <c r="B23" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -9525,7 +9525,7 @@
         <v>821</v>
       </c>
       <c r="B24" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -9533,7 +9533,7 @@
         <v>529</v>
       </c>
       <c r="B25" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -9541,7 +9541,7 @@
         <v>684</v>
       </c>
       <c r="B26" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -9549,7 +9549,7 @@
         <v>484</v>
       </c>
       <c r="B27" s="1">
-        <v>3120</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -9557,7 +9557,7 @@
         <v>735</v>
       </c>
       <c r="B28">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -9565,7 +9565,7 @@
         <v>530</v>
       </c>
       <c r="B29">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -9573,7 +9573,7 @@
         <v>531</v>
       </c>
       <c r="B30">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -9581,7 +9581,7 @@
         <v>532</v>
       </c>
       <c r="B31">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -9589,7 +9589,7 @@
         <v>533</v>
       </c>
       <c r="B32">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -9597,7 +9597,7 @@
         <v>534</v>
       </c>
       <c r="B33">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -9605,7 +9605,7 @@
         <v>535</v>
       </c>
       <c r="B34">
-        <v>57200</v>
+        <v>58300</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -9613,7 +9613,7 @@
         <v>631</v>
       </c>
       <c r="B35">
-        <v>296400</v>
+        <v>302100</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -9621,7 +9621,7 @@
         <v>553</v>
       </c>
       <c r="B36">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -9629,7 +9629,7 @@
         <v>726</v>
       </c>
       <c r="B37">
-        <v>44200</v>
+        <v>45050</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -9637,7 +9637,7 @@
         <v>727</v>
       </c>
       <c r="B38">
-        <v>46800</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -9645,7 +9645,7 @@
         <v>536</v>
       </c>
       <c r="B39">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -9653,7 +9653,7 @@
         <v>683</v>
       </c>
       <c r="B40">
-        <v>187200</v>
+        <v>190800</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -9661,7 +9661,7 @@
         <v>636</v>
       </c>
       <c r="B41">
-        <v>192400</v>
+        <v>196100</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -9669,7 +9669,7 @@
         <v>740</v>
       </c>
       <c r="B42">
-        <v>114400</v>
+        <v>116600</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -9677,7 +9677,7 @@
         <v>537</v>
       </c>
       <c r="B43">
-        <v>46800</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -9685,7 +9685,7 @@
         <v>538</v>
       </c>
       <c r="B44">
-        <v>26000</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -9693,7 +9693,7 @@
         <v>811</v>
       </c>
       <c r="B45">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -9701,7 +9701,7 @@
         <v>812</v>
       </c>
       <c r="B46">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -9709,7 +9709,7 @@
         <v>813</v>
       </c>
       <c r="B47">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -9717,7 +9717,7 @@
         <v>539</v>
       </c>
       <c r="B48">
-        <v>23400</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -9725,7 +9725,7 @@
         <v>814</v>
       </c>
       <c r="B49">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -9733,7 +9733,7 @@
         <v>815</v>
       </c>
       <c r="B50">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -9741,7 +9741,7 @@
         <v>816</v>
       </c>
       <c r="B51">
-        <v>13000</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -9749,7 +9749,7 @@
         <v>588</v>
       </c>
       <c r="B52">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -9757,7 +9757,7 @@
         <v>817</v>
       </c>
       <c r="B53">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -9765,7 +9765,7 @@
         <v>818</v>
       </c>
       <c r="B54">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -9773,7 +9773,7 @@
         <v>819</v>
       </c>
       <c r="B55">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -9781,7 +9781,7 @@
         <v>548</v>
       </c>
       <c r="B56">
-        <v>36400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -9789,7 +9789,7 @@
         <v>549</v>
       </c>
       <c r="B57">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -9797,7 +9797,7 @@
         <v>403</v>
       </c>
       <c r="B58">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -9805,7 +9805,7 @@
         <v>546</v>
       </c>
       <c r="B59">
-        <v>6240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -9813,7 +9813,7 @@
         <v>556</v>
       </c>
       <c r="B60">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -9821,7 +9821,7 @@
         <v>557</v>
       </c>
       <c r="B61">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -9829,7 +9829,7 @@
         <v>540</v>
       </c>
       <c r="B62">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -9837,7 +9837,7 @@
         <v>541</v>
       </c>
       <c r="B63">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -9845,7 +9845,7 @@
         <v>637</v>
       </c>
       <c r="B64">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -9853,7 +9853,7 @@
         <v>542</v>
       </c>
       <c r="B65">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
   </sheetData>
@@ -9883,7 +9883,7 @@
         <v>383</v>
       </c>
       <c r="B2" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9891,7 +9891,7 @@
         <v>384</v>
       </c>
       <c r="B3" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9899,7 +9899,7 @@
         <v>385</v>
       </c>
       <c r="B4" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9907,7 +9907,7 @@
         <v>386</v>
       </c>
       <c r="B5" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -9915,7 +9915,7 @@
         <v>640</v>
       </c>
       <c r="B6" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -9923,7 +9923,7 @@
         <v>387</v>
       </c>
       <c r="B7" s="1">
-        <v>18200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -9931,7 +9931,7 @@
         <v>660</v>
       </c>
       <c r="B8" s="1">
-        <v>20800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -9939,7 +9939,7 @@
         <v>662</v>
       </c>
       <c r="B9" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -9947,7 +9947,7 @@
         <v>661</v>
       </c>
       <c r="B10" s="1">
-        <v>16640</v>
+        <v>16960</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -9955,7 +9955,7 @@
         <v>388</v>
       </c>
       <c r="B11" s="1">
-        <v>3120</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -9963,7 +9963,7 @@
         <v>405</v>
       </c>
       <c r="B12" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -9971,7 +9971,7 @@
         <v>659</v>
       </c>
       <c r="B13" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -9979,7 +9979,7 @@
         <v>665</v>
       </c>
       <c r="B14" s="1">
-        <v>3120</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -9987,7 +9987,7 @@
         <v>745</v>
       </c>
       <c r="B15" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -9995,7 +9995,7 @@
         <v>389</v>
       </c>
       <c r="B16" s="1">
-        <v>4680</v>
+        <v>4770</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -10003,7 +10003,7 @@
         <v>589</v>
       </c>
       <c r="B17" s="1">
-        <v>3120</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -10011,7 +10011,7 @@
         <v>663</v>
       </c>
       <c r="B18" s="1">
-        <v>91000</v>
+        <v>92750</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -10019,7 +10019,7 @@
         <v>655</v>
       </c>
       <c r="B19" s="1">
-        <v>101400</v>
+        <v>103350</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -10027,7 +10027,7 @@
         <v>656</v>
       </c>
       <c r="B20" s="1">
-        <v>114400</v>
+        <v>116600</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -10035,7 +10035,7 @@
         <v>430</v>
       </c>
       <c r="B21" s="1">
-        <v>41600</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -10043,7 +10043,7 @@
         <v>163</v>
       </c>
       <c r="B22" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -10051,7 +10051,7 @@
         <v>647</v>
       </c>
       <c r="B23" s="1">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -10059,7 +10059,7 @@
         <v>581</v>
       </c>
       <c r="B24" s="1">
-        <v>57200</v>
+        <v>58300</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -10067,7 +10067,7 @@
         <v>648</v>
       </c>
       <c r="B25" s="1">
-        <v>62400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -10075,7 +10075,7 @@
         <v>657</v>
       </c>
       <c r="B26" s="1">
-        <v>70200</v>
+        <v>71550</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -10083,7 +10083,7 @@
         <v>658</v>
       </c>
       <c r="B27" s="1">
-        <v>83200</v>
+        <v>84800</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -10091,7 +10091,7 @@
         <v>664</v>
       </c>
       <c r="B28" s="1">
-        <v>88400</v>
+        <v>90100</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -10099,7 +10099,7 @@
         <v>692</v>
       </c>
       <c r="B29" s="1">
-        <v>520</v>
+        <v>530</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -10107,7 +10107,7 @@
         <v>406</v>
       </c>
       <c r="B30" s="1">
-        <v>520</v>
+        <v>530</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -10115,7 +10115,7 @@
         <v>402</v>
       </c>
       <c r="B31" s="1">
-        <v>520</v>
+        <v>530</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -10123,7 +10123,7 @@
         <v>429</v>
       </c>
       <c r="B32" s="1">
-        <v>1560</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -10131,7 +10131,7 @@
         <v>551</v>
       </c>
       <c r="B33" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -10139,7 +10139,7 @@
         <v>390</v>
       </c>
       <c r="B34" s="1">
-        <v>3120</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -10147,7 +10147,7 @@
         <v>552</v>
       </c>
       <c r="B35" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -10155,7 +10155,7 @@
         <v>820</v>
       </c>
       <c r="B36" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -10163,7 +10163,7 @@
         <v>404</v>
       </c>
       <c r="B37" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -10171,7 +10171,7 @@
         <v>259</v>
       </c>
       <c r="B38" s="1">
-        <v>15600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -10179,7 +10179,7 @@
         <v>425</v>
       </c>
       <c r="B39" s="1">
-        <v>2080</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -10187,7 +10187,7 @@
         <v>484</v>
       </c>
       <c r="B40" s="1">
-        <v>3120</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -10195,7 +10195,7 @@
         <v>735</v>
       </c>
       <c r="B41" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -10203,7 +10203,7 @@
         <v>391</v>
       </c>
       <c r="B42" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -10211,7 +10211,7 @@
         <v>392</v>
       </c>
       <c r="B43" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -10219,7 +10219,7 @@
         <v>393</v>
       </c>
       <c r="B44" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -10227,7 +10227,7 @@
         <v>638</v>
       </c>
       <c r="B45" s="1">
-        <v>3120</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -10235,7 +10235,7 @@
         <v>394</v>
       </c>
       <c r="B46" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -10243,7 +10243,7 @@
         <v>395</v>
       </c>
       <c r="B47" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -10251,7 +10251,7 @@
         <v>396</v>
       </c>
       <c r="B48" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -10259,7 +10259,7 @@
         <v>728</v>
       </c>
       <c r="B49" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -10267,7 +10267,7 @@
         <v>553</v>
       </c>
       <c r="B50" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -10275,7 +10275,7 @@
         <v>718</v>
       </c>
       <c r="B51" s="1">
-        <v>28600</v>
+        <v>29150</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -10283,7 +10283,7 @@
         <v>719</v>
       </c>
       <c r="B52" s="1">
-        <v>31200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -10291,7 +10291,7 @@
         <v>752</v>
       </c>
       <c r="B53" s="1">
-        <v>33800</v>
+        <v>34450</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -10299,7 +10299,7 @@
         <v>723</v>
       </c>
       <c r="B54" s="1">
-        <v>33800</v>
+        <v>34450</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -10307,7 +10307,7 @@
         <v>720</v>
       </c>
       <c r="B55" s="1">
-        <v>33800</v>
+        <v>34450</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -10315,7 +10315,7 @@
         <v>724</v>
       </c>
       <c r="B56" s="1">
-        <v>39000</v>
+        <v>39750</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -10323,7 +10323,7 @@
         <v>721</v>
       </c>
       <c r="B57" s="1">
-        <v>33800</v>
+        <v>34450</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -10331,7 +10331,7 @@
         <v>725</v>
       </c>
       <c r="B58" s="1">
-        <v>41600</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -10339,7 +10339,7 @@
         <v>726</v>
       </c>
       <c r="B59" s="1">
-        <v>44200</v>
+        <v>45050</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -10347,7 +10347,7 @@
         <v>727</v>
       </c>
       <c r="B60" s="1">
-        <v>46800</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -10355,7 +10355,7 @@
         <v>740</v>
       </c>
       <c r="B61" s="1">
-        <v>114400</v>
+        <v>116600</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -10363,7 +10363,7 @@
         <v>639</v>
       </c>
       <c r="B62" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -10371,7 +10371,7 @@
         <v>543</v>
       </c>
       <c r="B63" s="1">
-        <v>7800</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -10379,7 +10379,7 @@
         <v>397</v>
       </c>
       <c r="B64" s="1">
-        <v>9360</v>
+        <v>9540</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -10387,7 +10387,7 @@
         <v>653</v>
       </c>
       <c r="B65" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -10395,7 +10395,7 @@
         <v>398</v>
       </c>
       <c r="B66" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -10403,7 +10403,7 @@
         <v>399</v>
       </c>
       <c r="B67" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -10411,7 +10411,7 @@
         <v>400</v>
       </c>
       <c r="B68" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -10419,7 +10419,7 @@
         <v>582</v>
       </c>
       <c r="B69" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -10427,7 +10427,7 @@
         <v>401</v>
       </c>
       <c r="B70" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -10435,7 +10435,7 @@
         <v>588</v>
       </c>
       <c r="B71" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -10443,7 +10443,7 @@
         <v>554</v>
       </c>
       <c r="B72" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -10451,7 +10451,7 @@
         <v>555</v>
       </c>
       <c r="B73" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -10459,7 +10459,7 @@
         <v>644</v>
       </c>
       <c r="B74" s="1">
-        <v>3640</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -10467,7 +10467,7 @@
         <v>645</v>
       </c>
       <c r="B75" s="1">
-        <v>2600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -10475,7 +10475,7 @@
         <v>403</v>
       </c>
       <c r="B76" s="1">
-        <v>4160</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -10483,7 +10483,7 @@
         <v>546</v>
       </c>
       <c r="B77" s="1">
-        <v>6240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -10491,7 +10491,7 @@
         <v>556</v>
       </c>
       <c r="B78" s="1">
-        <v>10400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -10499,7 +10499,7 @@
         <v>557</v>
       </c>
       <c r="B79" s="1">
-        <v>5200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -10507,7 +10507,7 @@
         <v>558</v>
       </c>
       <c r="B80" s="1">
-        <v>1560</v>
+        <v>1590</v>
       </c>
     </row>
   </sheetData>

--- a/clientes/files/TODITICO_CATÁLOGO.xlsx
+++ b/clientes/files/TODITICO_CATÁLOGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Catálogos Proformas\Este\520 Actual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABE7C5F-8EF7-4D87-BA04-F2ABEC06BC3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61676FA7-720D-459B-A177-3A3C3403536E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="671" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="824">
   <si>
     <t>DESCRIPCION</t>
   </si>
@@ -2498,6 +2498,9 @@
   </si>
   <si>
     <t>TERMOSTATO</t>
+  </si>
+  <si>
+    <t>BATERÍA 35 AH</t>
   </si>
 </sst>
 </file>
@@ -2999,7 +3002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B362"/>
+  <dimension ref="A1:B363"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="83.85546875" customWidth="1"/>
@@ -3296,23 +3299,23 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>430</v>
+        <v>823</v>
       </c>
       <c r="B37" s="1">
-        <v>42400</v>
+        <v>45050</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>163</v>
+        <v>430</v>
       </c>
       <c r="B38" s="1">
-        <v>53000</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>647</v>
+        <v>163</v>
       </c>
       <c r="B39" s="1">
         <v>53000</v>
@@ -3320,119 +3323,119 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>581</v>
+        <v>647</v>
       </c>
       <c r="B40" s="1">
-        <v>58300</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>648</v>
+        <v>581</v>
       </c>
       <c r="B41" s="1">
-        <v>63600</v>
+        <v>58300</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>189</v>
+        <v>648</v>
       </c>
       <c r="B42" s="1">
-        <v>13250</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>419</v>
+        <v>189</v>
       </c>
       <c r="B43" s="1">
-        <v>26500</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="B44" s="1">
-        <v>6360</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>729</v>
+        <v>408</v>
       </c>
       <c r="B45" s="1">
-        <v>23850</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B46" s="1">
-        <v>21200</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>190</v>
+        <v>730</v>
       </c>
       <c r="B47" s="1">
-        <v>42400</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B48" s="1">
-        <v>23850</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B49" s="1">
-        <v>31800</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B50" s="1">
-        <v>23850</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>692</v>
+        <v>193</v>
       </c>
       <c r="B51" s="1">
-        <v>530</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>194</v>
+        <v>692</v>
       </c>
       <c r="B52" s="1">
-        <v>7950</v>
+        <v>530</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>406</v>
+        <v>194</v>
       </c>
       <c r="B53" s="1">
-        <v>530</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="4" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B54" s="1">
         <v>530</v>
@@ -3440,39 +3443,39 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="4" t="s">
-        <v>429</v>
+        <v>402</v>
       </c>
       <c r="B55" s="1">
-        <v>1590</v>
+        <v>530</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>195</v>
+        <v>429</v>
       </c>
       <c r="B56" s="1">
-        <v>47700</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B57" s="1">
-        <v>6360</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B58" s="1">
-        <v>5300</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>595</v>
+        <v>197</v>
       </c>
       <c r="B59" s="1">
         <v>5300</v>
@@ -3480,7 +3483,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B60" s="1">
         <v>5300</v>
@@ -3488,31 +3491,31 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>198</v>
+        <v>596</v>
       </c>
       <c r="B61" s="1">
-        <v>31800</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B62" s="1">
-        <v>21200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B63" s="1">
-        <v>7950</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B64" s="1">
         <v>7950</v>
@@ -3520,79 +3523,79 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B65" s="1">
-        <v>10600</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B66" s="1">
-        <v>6360</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B67" s="1">
-        <v>4240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B68" s="1">
-        <v>2650</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B69" s="1">
-        <v>4240</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B70" s="1">
-        <v>2650</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B71" s="1">
-        <v>1060</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B72" s="1">
-        <v>7950</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B73" s="1">
-        <v>5300</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B74" s="1">
         <v>5300</v>
@@ -3600,7 +3603,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>476</v>
+        <v>211</v>
       </c>
       <c r="B75" s="1">
         <v>5300</v>
@@ -3608,71 +3611,71 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>207</v>
+        <v>476</v>
       </c>
       <c r="B76" s="1">
-        <v>3710</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B77" s="1">
-        <v>5300</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B78" s="1">
-        <v>7950</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B79" s="1">
-        <v>10600</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B80" s="1">
-        <v>13250</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B81" s="1">
-        <v>10600</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B82" s="1">
-        <v>23850</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B83" s="1">
-        <v>13250</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B84" s="1">
         <v>13250</v>
@@ -3680,31 +3683,31 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>607</v>
+        <v>220</v>
       </c>
       <c r="B85" s="1">
-        <v>7950</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>221</v>
+        <v>607</v>
       </c>
       <c r="B86" s="1">
-        <v>4240</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>608</v>
+        <v>221</v>
       </c>
       <c r="B87" s="1">
-        <v>7950</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>417</v>
+        <v>608</v>
       </c>
       <c r="B88" s="1">
         <v>7950</v>
@@ -3712,79 +3715,79 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B89" s="1">
-        <v>15900</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>222</v>
+        <v>418</v>
       </c>
       <c r="B90" s="1">
-        <v>23850</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B91" s="1">
-        <v>37100</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B92" s="1">
-        <v>53000</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B93" s="1">
-        <v>185500</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B94" s="1">
-        <v>4240</v>
+        <v>185500</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B95" s="1">
-        <v>159000</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B96" s="1">
-        <v>26500</v>
+        <v>159000</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>551</v>
+        <v>228</v>
       </c>
       <c r="B97" s="1">
-        <v>7950</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>667</v>
+        <v>551</v>
       </c>
       <c r="B98" s="1">
         <v>7950</v>
@@ -3792,231 +3795,231 @@
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="4" t="s">
-        <v>409</v>
+        <v>667</v>
       </c>
       <c r="B99" s="1">
-        <v>37100</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>229</v>
+        <v>409</v>
       </c>
       <c r="B100" s="1">
-        <v>23850</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B101" s="1">
-        <v>42400</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B102" s="1">
-        <v>10600</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>424</v>
+        <v>231</v>
       </c>
       <c r="B103" s="1">
-        <v>13250</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="4" t="s">
-        <v>232</v>
+        <v>424</v>
       </c>
       <c r="B104" s="1">
-        <v>10600</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>570</v>
+        <v>232</v>
       </c>
       <c r="B105" s="1">
-        <v>23850</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>483</v>
+        <v>570</v>
       </c>
       <c r="B106" s="1">
-        <v>132500</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>587</v>
+        <v>483</v>
       </c>
       <c r="B107" s="1">
-        <v>13250</v>
+        <v>132500</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>233</v>
+        <v>587</v>
       </c>
       <c r="B108" s="1">
-        <v>18550</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B109" s="1">
-        <v>37100</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>731</v>
+        <v>234</v>
       </c>
       <c r="B110" s="1">
-        <v>23850</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>717</v>
+        <v>731</v>
       </c>
       <c r="B111" s="1">
-        <v>26500</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>571</v>
+        <v>717</v>
       </c>
       <c r="B112" s="1">
-        <v>15900</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>590</v>
+        <v>571</v>
       </c>
       <c r="B113" s="1">
-        <v>106</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>235</v>
+        <v>590</v>
       </c>
       <c r="B114" s="1">
-        <v>53000</v>
+        <v>106</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>732</v>
+        <v>235</v>
       </c>
       <c r="B115" s="1">
-        <v>10600</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>236</v>
+        <v>732</v>
       </c>
       <c r="B116" s="1">
-        <v>15900</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>733</v>
+        <v>236</v>
       </c>
       <c r="B117" s="1">
-        <v>1060</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>237</v>
+        <v>733</v>
       </c>
       <c r="B118" s="1">
-        <v>31800</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>410</v>
+        <v>237</v>
       </c>
       <c r="B119" s="1">
-        <v>3710</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>238</v>
+        <v>410</v>
       </c>
       <c r="B120" s="1">
-        <v>10600</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B121" s="1">
-        <v>7950</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B122" s="1">
-        <v>10600</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B123" s="1">
-        <v>31800</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B124" s="1">
-        <v>79500</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B125" s="1">
-        <v>21200</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>668</v>
+        <v>243</v>
       </c>
       <c r="B126" s="1">
-        <v>53000</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B127" s="1">
         <v>53000</v>
@@ -4024,7 +4027,7 @@
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>431</v>
+        <v>669</v>
       </c>
       <c r="B128" s="1">
         <v>53000</v>
@@ -4032,279 +4035,279 @@
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>244</v>
+        <v>431</v>
       </c>
       <c r="B129" s="1">
-        <v>13250</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>597</v>
+        <v>244</v>
       </c>
       <c r="B130" s="1">
-        <v>227900</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>245</v>
+        <v>597</v>
       </c>
       <c r="B131" s="1">
-        <v>95400</v>
+        <v>227900</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>456</v>
+        <v>245</v>
       </c>
       <c r="B132" s="1">
-        <v>3710</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B133" s="1">
-        <v>10600</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B134" s="1">
-        <v>15900</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>246</v>
+        <v>458</v>
       </c>
       <c r="B135" s="1">
-        <v>31800</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B136" s="1">
-        <v>63600</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B137" s="1">
-        <v>10600</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B138" s="1">
-        <v>42400</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>420</v>
+        <v>250</v>
       </c>
       <c r="B139" s="1">
-        <v>132500</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>14</v>
+        <v>420</v>
       </c>
       <c r="B140" s="1">
-        <v>63600</v>
+        <v>132500</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>602</v>
+        <v>14</v>
       </c>
       <c r="B141" s="1">
-        <v>106</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>249</v>
+        <v>602</v>
       </c>
       <c r="B142" s="1">
-        <v>7950</v>
+        <v>106</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>552</v>
+        <v>249</v>
       </c>
       <c r="B143" s="1">
-        <v>4240</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>251</v>
+        <v>552</v>
       </c>
       <c r="B144" s="1">
-        <v>26500</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B145" s="1">
-        <v>31800</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B146" s="1">
-        <v>53000</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>598</v>
+        <v>253</v>
       </c>
       <c r="B147" s="1">
-        <v>6360</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>254</v>
+        <v>598</v>
       </c>
       <c r="B148" s="1">
-        <v>21200</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B149" s="1">
-        <v>37100</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B150" s="1">
-        <v>4240</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B151" s="1">
-        <v>5300</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B152" s="1">
-        <v>4240</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B153" s="1">
-        <v>15900</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B154" s="1">
-        <v>47700</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B155" s="1">
-        <v>26500</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>404</v>
+        <v>263</v>
       </c>
       <c r="B156" s="1">
-        <v>2650</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>259</v>
+        <v>404</v>
       </c>
       <c r="B157" s="1">
-        <v>15900</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>463</v>
+        <v>259</v>
       </c>
       <c r="B158" s="1">
-        <v>10600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>260</v>
+        <v>463</v>
       </c>
       <c r="B159" s="1">
-        <v>63600</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B160" s="1">
-        <v>2650</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>689</v>
+        <v>264</v>
       </c>
       <c r="B161" s="1">
-        <v>18550</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>641</v>
+        <v>689</v>
       </c>
       <c r="B162" s="1">
-        <v>1590</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B163" s="1">
         <v>1590</v>
@@ -4312,15 +4315,15 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>603</v>
+        <v>642</v>
       </c>
       <c r="B164" s="1">
-        <v>106</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B165" s="1">
         <v>106</v>
@@ -4328,111 +4331,111 @@
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>484</v>
+        <v>604</v>
       </c>
       <c r="B166" s="1">
-        <v>3180</v>
+        <v>106</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>265</v>
+        <v>484</v>
       </c>
       <c r="B167" s="1">
-        <v>2650</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>609</v>
+        <v>265</v>
       </c>
       <c r="B168" s="1">
-        <v>53000</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>734</v>
+        <v>609</v>
       </c>
       <c r="B169" s="1">
-        <v>2120</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B170" s="1">
-        <v>4240</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>266</v>
+        <v>735</v>
       </c>
       <c r="B171" s="1">
-        <v>31800</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B172" s="1">
-        <v>15900</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B173" s="1">
-        <v>53000</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B174" s="1">
-        <v>15900</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B175" s="1">
-        <v>3710</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B176" s="1">
-        <v>7950</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B177" s="1">
-        <v>15900</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B178" s="1">
-        <v>4240</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>422</v>
+        <v>273</v>
       </c>
       <c r="B179" s="1">
         <v>4240</v>
@@ -4440,7 +4443,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B180" s="1">
         <v>4240</v>
@@ -4448,39 +4451,39 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>610</v>
+        <v>423</v>
       </c>
       <c r="B181" s="1">
-        <v>3710</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B182" s="1">
-        <v>2650</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B183" s="1">
-        <v>7950</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B184" s="1">
-        <v>3710</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B185" s="1">
         <v>3710</v>
@@ -4488,215 +4491,215 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B186" s="1">
-        <v>2650</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" t="s">
-        <v>274</v>
+        <v>615</v>
       </c>
       <c r="B187" s="1">
-        <v>10600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B188" s="1">
-        <v>1060</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B189" s="1">
-        <v>10600</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
-        <v>616</v>
+        <v>275</v>
       </c>
       <c r="B190" s="1">
-        <v>26500</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" t="s">
-        <v>277</v>
+        <v>616</v>
       </c>
       <c r="B191" s="1">
-        <v>21200</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" t="s">
-        <v>464</v>
+        <v>277</v>
       </c>
       <c r="B192" s="1">
-        <v>79500</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" t="s">
-        <v>278</v>
+        <v>464</v>
       </c>
       <c r="B193" s="1">
-        <v>47700</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
-        <v>736</v>
+        <v>278</v>
       </c>
       <c r="B194" s="1">
-        <v>1590</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" t="s">
-        <v>391</v>
+        <v>736</v>
       </c>
       <c r="B195" s="1">
-        <v>4240</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B196" s="1">
-        <v>3710</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" t="s">
-        <v>466</v>
+        <v>396</v>
       </c>
       <c r="B197" s="1">
-        <v>169600</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" t="s">
-        <v>279</v>
+        <v>466</v>
       </c>
       <c r="B198" s="1">
-        <v>275600</v>
+        <v>169600</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" t="s">
-        <v>649</v>
+        <v>279</v>
       </c>
       <c r="B199" s="1">
-        <v>280900</v>
+        <v>275600</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" t="s">
-        <v>280</v>
+        <v>649</v>
       </c>
       <c r="B200" s="1">
-        <v>3180</v>
+        <v>280900</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" t="s">
-        <v>696</v>
+        <v>280</v>
       </c>
       <c r="B201" s="1">
-        <v>6360</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
-        <v>737</v>
+        <v>696</v>
       </c>
       <c r="B202" s="1">
-        <v>4240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" t="s">
-        <v>411</v>
+        <v>737</v>
       </c>
       <c r="B203" s="1">
-        <v>10600</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" t="s">
-        <v>281</v>
+        <v>411</v>
       </c>
       <c r="B204" s="1">
-        <v>7950</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" t="s">
-        <v>412</v>
+        <v>281</v>
       </c>
       <c r="B205" s="1">
-        <v>2650</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="206" spans="1:2">
       <c r="A206" t="s">
-        <v>282</v>
+        <v>412</v>
       </c>
       <c r="B206" s="1">
-        <v>7950</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B207" s="1">
-        <v>37100</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B208" s="1">
-        <v>4240</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B209" s="1">
-        <v>5300</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="210" spans="1:2">
       <c r="A210" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B210" s="1">
-        <v>10600</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B211" s="1">
-        <v>4240</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B212" s="1">
         <v>4240</v>
@@ -4704,7 +4707,7 @@
     </row>
     <row r="213" spans="1:2">
       <c r="A213" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B213" s="1">
         <v>4240</v>
@@ -4712,7 +4715,7 @@
     </row>
     <row r="214" spans="1:2">
       <c r="A214" t="s">
-        <v>553</v>
+        <v>289</v>
       </c>
       <c r="B214" s="1">
         <v>4240</v>
@@ -4720,23 +4723,23 @@
     </row>
     <row r="215" spans="1:2">
       <c r="A215" t="s">
-        <v>290</v>
+        <v>553</v>
       </c>
       <c r="B215" s="1">
-        <v>26500</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="216" spans="1:2">
       <c r="A216" t="s">
-        <v>738</v>
+        <v>290</v>
       </c>
       <c r="B216" s="1">
-        <v>2650</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B217" s="1">
         <v>2650</v>
@@ -4744,71 +4747,71 @@
     </row>
     <row r="218" spans="1:2">
       <c r="A218" t="s">
-        <v>291</v>
+        <v>739</v>
       </c>
       <c r="B218" s="1">
-        <v>15900</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="219" spans="1:2">
       <c r="A219" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B219" s="1">
-        <v>2650</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B220" s="1">
-        <v>148400</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="221" spans="1:2">
       <c r="A221" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B221" s="1">
-        <v>79500</v>
+        <v>148400</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>572</v>
+        <v>294</v>
       </c>
       <c r="B222" s="1">
-        <v>34450</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>670</v>
+        <v>572</v>
       </c>
       <c r="B223" s="1">
-        <v>42400</v>
+        <v>34450</v>
       </c>
     </row>
     <row r="224" spans="1:2">
       <c r="A224" t="s">
-        <v>295</v>
+        <v>670</v>
       </c>
       <c r="B224" s="1">
-        <v>15900</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>671</v>
+        <v>295</v>
       </c>
       <c r="B225" s="1">
-        <v>79500</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="226" spans="1:2">
       <c r="A226" t="s">
-        <v>296</v>
+        <v>671</v>
       </c>
       <c r="B226" s="1">
         <v>79500</v>
@@ -4816,31 +4819,31 @@
     </row>
     <row r="227" spans="1:2">
       <c r="A227" t="s">
-        <v>718</v>
+        <v>296</v>
       </c>
       <c r="B227" s="1">
-        <v>29150</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B228" s="1">
-        <v>31800</v>
+        <v>29150</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B229" s="1">
-        <v>34450</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B230" s="1">
         <v>34450</v>
@@ -4848,71 +4851,71 @@
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>617</v>
+        <v>721</v>
       </c>
       <c r="B231" s="1">
-        <v>3710</v>
+        <v>34450</v>
       </c>
     </row>
     <row r="232" spans="1:2">
       <c r="A232" t="s">
-        <v>297</v>
+        <v>617</v>
       </c>
       <c r="B232" s="1">
-        <v>5300</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>573</v>
+        <v>297</v>
       </c>
       <c r="B233" s="1">
-        <v>31800</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="234" spans="1:2">
       <c r="A234" t="s">
-        <v>298</v>
+        <v>573</v>
       </c>
       <c r="B234" s="1">
-        <v>5300</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B235" s="1">
-        <v>10600</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="236" spans="1:2">
       <c r="A236" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B236" s="1">
-        <v>53000</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="237" spans="1:2">
       <c r="A237" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B237" s="1">
-        <v>63600</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B238" s="1">
-        <v>159000</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
-        <v>672</v>
+        <v>302</v>
       </c>
       <c r="B239" s="1">
         <v>159000</v>
@@ -4920,47 +4923,47 @@
     </row>
     <row r="240" spans="1:2">
       <c r="A240" t="s">
-        <v>303</v>
+        <v>672</v>
       </c>
       <c r="B240" s="1">
-        <v>84800</v>
+        <v>159000</v>
       </c>
     </row>
     <row r="241" spans="1:2">
       <c r="A241" t="s">
-        <v>740</v>
+        <v>303</v>
       </c>
       <c r="B241" s="1">
-        <v>116600</v>
+        <v>84800</v>
       </c>
     </row>
     <row r="242" spans="1:2">
       <c r="A242" t="s">
-        <v>304</v>
+        <v>740</v>
       </c>
       <c r="B242" s="1">
-        <v>58300</v>
+        <v>116600</v>
       </c>
     </row>
     <row r="243" spans="1:2">
       <c r="A243" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B243" s="1">
-        <v>84800</v>
+        <v>58300</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B244" s="1">
-        <v>15900</v>
+        <v>84800</v>
       </c>
     </row>
     <row r="245" spans="1:2">
       <c r="A245" t="s">
-        <v>618</v>
+        <v>306</v>
       </c>
       <c r="B245" s="1">
         <v>15900</v>
@@ -4968,87 +4971,87 @@
     </row>
     <row r="246" spans="1:2">
       <c r="A246" t="s">
-        <v>307</v>
+        <v>618</v>
       </c>
       <c r="B246" s="1">
-        <v>90100</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="247" spans="1:2">
       <c r="A247" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B247" s="1">
-        <v>37100</v>
+        <v>90100</v>
       </c>
     </row>
     <row r="248" spans="1:2">
       <c r="A248" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B248" s="1">
-        <v>106000</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="249" spans="1:2">
       <c r="A249" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B249" s="1">
-        <v>47700</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
-        <v>690</v>
+        <v>310</v>
       </c>
       <c r="B250" s="1">
-        <v>10600</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>311</v>
+        <v>690</v>
       </c>
       <c r="B251" s="1">
-        <v>37100</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="252" spans="1:2">
       <c r="A252" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B252" s="1">
-        <v>13250</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B253" s="1">
-        <v>5300</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="254" spans="1:2">
       <c r="A254" t="s">
-        <v>467</v>
+        <v>313</v>
       </c>
       <c r="B254" s="1">
-        <v>10600</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>741</v>
+        <v>467</v>
       </c>
       <c r="B255" s="1">
-        <v>6360</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B256" s="1">
         <v>6360</v>
@@ -5056,15 +5059,15 @@
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>468</v>
+        <v>742</v>
       </c>
       <c r="B257" s="1">
-        <v>10600</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
-        <v>314</v>
+        <v>468</v>
       </c>
       <c r="B258" s="1">
         <v>10600</v>
@@ -5072,79 +5075,79 @@
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B259" s="1">
-        <v>13250</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="260" spans="1:2">
       <c r="A260" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B260" s="1">
-        <v>31800</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="261" spans="1:2">
       <c r="A261" t="s">
-        <v>414</v>
+        <v>316</v>
       </c>
       <c r="B261" s="1">
-        <v>21200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="262" spans="1:2">
       <c r="A262" t="s">
-        <v>317</v>
+        <v>414</v>
       </c>
       <c r="B262" s="1">
-        <v>15900</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="263" spans="1:2">
       <c r="A263" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B263" s="1">
-        <v>10600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="264" spans="1:2">
       <c r="A264" t="s">
-        <v>605</v>
+        <v>318</v>
       </c>
       <c r="B264" s="1">
-        <v>106</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="265" spans="1:2">
       <c r="A265" t="s">
-        <v>319</v>
+        <v>605</v>
       </c>
       <c r="B265" s="1">
-        <v>79500</v>
+        <v>106</v>
       </c>
     </row>
     <row r="266" spans="1:2">
       <c r="A266" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B266" s="1">
-        <v>159000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="267" spans="1:2">
       <c r="A267" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B267" s="1">
-        <v>10600</v>
+        <v>159000</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B268" s="1">
         <v>10600</v>
@@ -5152,135 +5155,135 @@
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B269" s="1">
-        <v>7950</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="270" spans="1:2">
       <c r="A270" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B270" s="1">
-        <v>15900</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="271" spans="1:2">
       <c r="A271" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B271" s="1">
-        <v>7950</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B272" s="1">
-        <v>15900</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B273" s="1">
-        <v>21200</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="274" spans="1:2">
       <c r="A274" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B274" s="1">
-        <v>53000</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B275" s="1">
-        <v>37100</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="276" spans="1:2">
       <c r="A276" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B276" s="1">
-        <v>5300</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="277" spans="1:2">
       <c r="A277" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B277" s="1">
-        <v>68900</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="278" spans="1:2">
       <c r="A278" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B278" s="1">
-        <v>106000</v>
+        <v>68900</v>
       </c>
     </row>
     <row r="279" spans="1:2">
       <c r="A279" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B279" s="1">
-        <v>13250</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="280" spans="1:2">
       <c r="A280" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B280" s="1">
-        <v>7950</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="281" spans="1:2">
       <c r="A281" t="s">
-        <v>574</v>
+        <v>334</v>
       </c>
       <c r="B281" s="1">
-        <v>53000</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="282" spans="1:2">
       <c r="A282" t="s">
-        <v>599</v>
+        <v>574</v>
       </c>
       <c r="B282" s="1">
-        <v>31800</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="283" spans="1:2">
       <c r="A283" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B283" s="1">
-        <v>50350</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="284" spans="1:2">
       <c r="A284" t="s">
-        <v>743</v>
+        <v>600</v>
       </c>
       <c r="B284" s="1">
-        <v>2650</v>
+        <v>50350</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>619</v>
+        <v>743</v>
       </c>
       <c r="B285" s="1">
         <v>2650</v>
@@ -5288,47 +5291,47 @@
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>335</v>
+        <v>619</v>
       </c>
       <c r="B286" s="1">
-        <v>4240</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="287" spans="1:2">
       <c r="A287" t="s">
-        <v>620</v>
+        <v>335</v>
       </c>
       <c r="B287" s="1">
-        <v>3710</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" t="s">
-        <v>336</v>
+        <v>620</v>
       </c>
       <c r="B288" s="1">
-        <v>10600</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B289" s="1">
-        <v>4240</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="290" spans="1:2">
       <c r="A290" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B290" s="1">
-        <v>5300</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="291" spans="1:2">
       <c r="A291" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B291" s="1">
         <v>5300</v>
@@ -5336,7 +5339,7 @@
     </row>
     <row r="292" spans="1:2">
       <c r="A292" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B292" s="1">
         <v>5300</v>
@@ -5344,15 +5347,15 @@
     </row>
     <row r="293" spans="1:2">
       <c r="A293" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B293" s="1">
-        <v>7950</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="294" spans="1:2">
       <c r="A294" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B294" s="1">
         <v>7950</v>
@@ -5360,191 +5363,191 @@
     </row>
     <row r="295" spans="1:2">
       <c r="A295" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B295" s="1">
-        <v>6360</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="296" spans="1:2">
       <c r="A296" t="s">
-        <v>415</v>
+        <v>343</v>
       </c>
       <c r="B296" s="1">
-        <v>7950</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="297" spans="1:2">
       <c r="A297" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B297" s="1">
-        <v>3180</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>601</v>
+        <v>416</v>
       </c>
       <c r="B298" s="1">
-        <v>5300</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" t="s">
-        <v>344</v>
+        <v>601</v>
       </c>
       <c r="B299" s="1">
-        <v>79500</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="300" spans="1:2">
       <c r="A300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B300" s="1">
-        <v>95400</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="301" spans="1:2">
       <c r="A301" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B301" s="1">
-        <v>47700</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="302" spans="1:2">
       <c r="A302" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B302" s="1">
-        <v>15900</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="303" spans="1:2">
       <c r="A303" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B303" s="1">
-        <v>10600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="304" spans="1:2">
       <c r="A304" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B304" s="1">
-        <v>2120</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="305" spans="1:2">
       <c r="A305" t="s">
-        <v>744</v>
+        <v>349</v>
       </c>
       <c r="B305" s="1">
-        <v>1060</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="306" spans="1:2">
       <c r="A306" t="s">
-        <v>673</v>
+        <v>744</v>
       </c>
       <c r="B306" s="1">
-        <v>63600</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="307" spans="1:2">
       <c r="A307" t="s">
-        <v>350</v>
+        <v>673</v>
       </c>
       <c r="B307" s="1">
-        <v>39750</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="308" spans="1:2">
       <c r="A308" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B308" s="1">
-        <v>13250</v>
+        <v>39750</v>
       </c>
     </row>
     <row r="309" spans="1:2">
       <c r="A309" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B309" s="1">
-        <v>31800</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="310" spans="1:2">
       <c r="A310" t="s">
-        <v>575</v>
+        <v>352</v>
       </c>
       <c r="B310" s="1">
-        <v>5300</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="311" spans="1:2">
       <c r="A311" t="s">
-        <v>353</v>
+        <v>575</v>
       </c>
       <c r="B311" s="1">
-        <v>6360</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B312" s="1">
-        <v>132500</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="313" spans="1:2">
       <c r="A313" t="s">
-        <v>407</v>
+        <v>354</v>
       </c>
       <c r="B313" s="1">
-        <v>291500</v>
+        <v>132500</v>
       </c>
     </row>
     <row r="314" spans="1:2">
       <c r="A314" t="s">
-        <v>355</v>
+        <v>407</v>
       </c>
       <c r="B314" s="1">
-        <v>13250</v>
+        <v>291500</v>
       </c>
     </row>
     <row r="315" spans="1:2">
       <c r="A315" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B315" s="1">
-        <v>5300</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
-        <v>576</v>
+        <v>356</v>
       </c>
       <c r="B316" s="1">
-        <v>10600</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="317" spans="1:2">
       <c r="A317" t="s">
-        <v>357</v>
+        <v>576</v>
       </c>
       <c r="B317" s="1">
-        <v>4240</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="318" spans="1:2">
       <c r="A318" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B318" s="1">
         <v>4240</v>
@@ -5552,63 +5555,63 @@
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>651</v>
+        <v>358</v>
       </c>
       <c r="B319" s="1">
-        <v>2120</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="320" spans="1:2">
       <c r="A320" t="s">
-        <v>577</v>
+        <v>651</v>
       </c>
       <c r="B320" s="1">
-        <v>7950</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="B321" s="1">
-        <v>4240</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>359</v>
+        <v>588</v>
       </c>
       <c r="B322" s="1">
-        <v>3710</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="323" spans="1:2">
       <c r="A323" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B323" s="1">
-        <v>23850</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B324" s="1">
-        <v>2120</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="325" spans="1:2">
       <c r="A325" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B325" s="1">
-        <v>2650</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="326" spans="1:2">
       <c r="A326" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B326" s="1">
         <v>2650</v>
@@ -5616,7 +5619,7 @@
     </row>
     <row r="327" spans="1:2">
       <c r="A327" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B327" s="1">
         <v>2650</v>
@@ -5624,31 +5627,31 @@
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B328" s="1">
-        <v>10600</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>403</v>
+        <v>365</v>
       </c>
       <c r="B329" s="1">
-        <v>4240</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="330" spans="1:2">
       <c r="A330" t="s">
-        <v>546</v>
+        <v>403</v>
       </c>
       <c r="B330" s="1">
-        <v>6360</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
-        <v>822</v>
+        <v>546</v>
       </c>
       <c r="B331" s="1">
         <v>6360</v>
@@ -5656,151 +5659,151 @@
     </row>
     <row r="332" spans="1:2">
       <c r="A332" t="s">
-        <v>366</v>
+        <v>822</v>
       </c>
       <c r="B332" s="1">
-        <v>7950</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>556</v>
+        <v>366</v>
       </c>
       <c r="B333" s="1">
-        <v>10600</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B334" s="1">
-        <v>5300</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
-        <v>367</v>
+        <v>557</v>
       </c>
       <c r="B335" s="1">
-        <v>2650</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="336" spans="1:2">
       <c r="A336" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B336" s="1">
-        <v>3710</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="337" spans="1:2">
       <c r="A337" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B337" s="1">
-        <v>3180</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="338" spans="1:2">
       <c r="A338" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B338" s="1">
-        <v>1060</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="339" spans="1:2">
       <c r="A339" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B339" s="1">
-        <v>2650</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="A340" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B340" s="1">
-        <v>1590</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="341" spans="1:2">
       <c r="A341" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B341" s="1">
-        <v>2120</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="342" spans="1:2">
       <c r="A342" t="s">
-        <v>413</v>
+        <v>373</v>
       </c>
       <c r="B342" s="1">
-        <v>1590</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="A343" t="s">
-        <v>465</v>
+        <v>413</v>
       </c>
       <c r="B343" s="1">
-        <v>3710</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="344" spans="1:2">
       <c r="A344" t="s">
-        <v>621</v>
+        <v>465</v>
       </c>
       <c r="B344" s="1">
-        <v>1590</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="345" spans="1:2">
       <c r="A345" t="s">
-        <v>374</v>
+        <v>621</v>
       </c>
       <c r="B345" s="1">
-        <v>1060</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="346" spans="1:2">
       <c r="A346" t="s">
-        <v>485</v>
+        <v>374</v>
       </c>
       <c r="B346" s="1">
-        <v>95400</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="347" spans="1:2">
       <c r="A347" t="s">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="B347" s="1">
-        <v>5300</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="348" spans="1:2">
       <c r="A348" t="s">
-        <v>375</v>
+        <v>469</v>
       </c>
       <c r="B348" s="1">
-        <v>10600</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="349" spans="1:2">
       <c r="A349" t="s">
-        <v>674</v>
+        <v>375</v>
       </c>
       <c r="B349" s="1">
-        <v>15900</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="350" spans="1:2">
       <c r="A350" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B350" s="1">
         <v>15900</v>
@@ -5808,55 +5811,55 @@
     </row>
     <row r="351" spans="1:2">
       <c r="A351" t="s">
-        <v>376</v>
+        <v>675</v>
       </c>
       <c r="B351" s="1">
-        <v>10600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="352" spans="1:2">
       <c r="A352" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B352" s="1">
-        <v>23850</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="353" spans="1:2">
       <c r="A353" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B353" s="1">
-        <v>7950</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="354" spans="1:2">
       <c r="A354" t="s">
-        <v>622</v>
+        <v>378</v>
       </c>
       <c r="B354" s="1">
-        <v>1590</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="355" spans="1:2">
       <c r="A355" t="s">
-        <v>379</v>
+        <v>622</v>
       </c>
       <c r="B355" s="1">
-        <v>31800</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="356" spans="1:2">
       <c r="A356" t="s">
-        <v>470</v>
+        <v>379</v>
       </c>
       <c r="B356" s="1">
-        <v>7950</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="357" spans="1:2">
       <c r="A357" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B357" s="1">
         <v>7950</v>
@@ -5864,41 +5867,49 @@
     </row>
     <row r="358" spans="1:2">
       <c r="A358" t="s">
-        <v>676</v>
+        <v>471</v>
       </c>
       <c r="B358" s="1">
-        <v>106000</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="359" spans="1:2">
       <c r="A359" t="s">
-        <v>380</v>
+        <v>676</v>
       </c>
       <c r="B359" s="1">
-        <v>18550</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="360" spans="1:2">
       <c r="A360" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B360" s="1">
-        <v>5300</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="361" spans="1:2">
       <c r="A361" t="s">
-        <v>454</v>
+        <v>381</v>
       </c>
       <c r="B361" s="1">
-        <v>2120</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="362" spans="1:2">
       <c r="A362" t="s">
+        <v>454</v>
+      </c>
+      <c r="B362" s="1">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" t="s">
         <v>382</v>
       </c>
-      <c r="B362" s="1">
+      <c r="B363" s="1">
         <v>6360</v>
       </c>
     </row>
@@ -5909,7 +5920,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B164"/>
+  <dimension ref="A1:B165"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="64.5703125" bestFit="1" customWidth="1"/>
@@ -6022,23 +6033,23 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="9" t="s">
-        <v>430</v>
+        <v>823</v>
       </c>
       <c r="B14" s="1">
-        <v>42400</v>
+        <v>45050</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>163</v>
+        <v>430</v>
       </c>
       <c r="B15" s="1">
-        <v>53000</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="11" t="s">
-        <v>647</v>
+        <v>163</v>
       </c>
       <c r="B16" s="1">
         <v>53000</v>
@@ -6046,39 +6057,39 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
-        <v>581</v>
+        <v>647</v>
       </c>
       <c r="B17" s="1">
-        <v>58300</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="5" t="s">
-        <v>648</v>
+        <v>581</v>
       </c>
       <c r="B18" s="1">
-        <v>63600</v>
+        <v>58300</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="5" t="s">
-        <v>6</v>
+        <v>648</v>
       </c>
       <c r="B19" s="1">
-        <v>13250</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="5" t="s">
-        <v>125</v>
+        <v>6</v>
       </c>
       <c r="B20" s="1">
-        <v>31800</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>478</v>
+        <v>125</v>
       </c>
       <c r="B21" s="1">
         <v>31800</v>
@@ -6086,39 +6097,39 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="5" t="s">
-        <v>36</v>
+        <v>478</v>
       </c>
       <c r="B22" s="1">
-        <v>53000</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="5" t="s">
-        <v>487</v>
+        <v>36</v>
       </c>
       <c r="B23" s="1">
-        <v>37100</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="5" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B24" s="1">
-        <v>42400</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="5" t="s">
-        <v>692</v>
+        <v>488</v>
       </c>
       <c r="B25" s="1">
-        <v>530</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="5" t="s">
-        <v>406</v>
+        <v>692</v>
       </c>
       <c r="B26" s="1">
         <v>530</v>
@@ -6126,7 +6137,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="5" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B27" s="1">
         <v>530</v>
@@ -6134,31 +6145,31 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="5" t="s">
-        <v>439</v>
+        <v>402</v>
       </c>
       <c r="B28" s="1">
-        <v>7950</v>
+        <v>530</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="5" t="s">
-        <v>760</v>
+        <v>439</v>
       </c>
       <c r="B29" s="1">
-        <v>10600</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="5" t="s">
-        <v>489</v>
+        <v>760</v>
       </c>
       <c r="B30" s="1">
-        <v>21200</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="12" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B31" s="1">
         <v>21200</v>
@@ -6166,231 +6177,231 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="5" t="s">
-        <v>761</v>
+        <v>490</v>
       </c>
       <c r="B32" s="1">
-        <v>7950</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="5" t="s">
-        <v>12</v>
+        <v>761</v>
       </c>
       <c r="B33" s="1">
-        <v>5300</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="5" t="s">
-        <v>762</v>
+        <v>12</v>
       </c>
       <c r="B34" s="1">
-        <v>7950</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="5" t="s">
-        <v>1</v>
+        <v>762</v>
       </c>
       <c r="B35" s="1">
-        <v>1325</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="5" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B36" s="1">
-        <v>5300</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="7" t="s">
-        <v>434</v>
+        <v>7</v>
       </c>
       <c r="B37" s="1">
-        <v>3710</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="13" t="s">
-        <v>2</v>
+        <v>434</v>
       </c>
       <c r="B38" s="1">
-        <v>13250</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="11" t="s">
-        <v>491</v>
+        <v>2</v>
       </c>
       <c r="B39" s="1">
-        <v>7950</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="5" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="B40" s="1">
-        <v>15900</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="5" t="s">
-        <v>763</v>
+        <v>479</v>
       </c>
       <c r="B41" s="1">
-        <v>10600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="9" t="s">
-        <v>438</v>
+        <v>763</v>
       </c>
       <c r="B42" s="1">
-        <v>13250</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="5" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B43" s="1">
-        <v>26500</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="7" t="s">
-        <v>492</v>
+        <v>440</v>
       </c>
       <c r="B44" s="1">
-        <v>31800</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B45" s="1">
-        <v>26500</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="7" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B46" s="1">
-        <v>37100</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="14" t="s">
-        <v>764</v>
+        <v>494</v>
       </c>
       <c r="B47" s="1">
-        <v>185500</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="7" t="s">
-        <v>551</v>
+        <v>764</v>
       </c>
       <c r="B48" s="1">
-        <v>7950</v>
+        <v>185500</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="13" t="s">
-        <v>765</v>
+        <v>551</v>
       </c>
       <c r="B49" s="1">
-        <v>68900</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="15" t="s">
-        <v>751</v>
+        <v>765</v>
       </c>
       <c r="B50" s="1">
-        <v>10600</v>
+        <v>68900</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>722</v>
+        <v>751</v>
       </c>
       <c r="B51" s="1">
-        <v>26500</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="5" t="s">
-        <v>29</v>
+        <v>722</v>
       </c>
       <c r="B52" s="1">
-        <v>18550</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="5" t="s">
-        <v>766</v>
+        <v>29</v>
       </c>
       <c r="B53" s="1">
-        <v>74200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="6" t="s">
-        <v>495</v>
+        <v>766</v>
       </c>
       <c r="B54" s="1">
-        <v>37100</v>
+        <v>74200</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="16" t="s">
-        <v>436</v>
+        <v>495</v>
       </c>
       <c r="B55" s="1">
-        <v>7950</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="10" t="s">
-        <v>126</v>
+        <v>436</v>
       </c>
       <c r="B56" s="1">
-        <v>15900</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="16" t="s">
-        <v>496</v>
+        <v>126</v>
       </c>
       <c r="B57" s="1">
-        <v>106000</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="17" t="s">
-        <v>767</v>
+        <v>496</v>
       </c>
       <c r="B58" s="1">
-        <v>42400</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="5" t="s">
-        <v>30</v>
+        <v>767</v>
       </c>
       <c r="B59" s="1">
-        <v>53000</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="5" t="s">
-        <v>427</v>
+        <v>30</v>
       </c>
       <c r="B60" s="1">
         <v>53000</v>
@@ -6398,119 +6409,119 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="10" t="s">
-        <v>8</v>
+        <v>427</v>
       </c>
       <c r="B61" s="1">
-        <v>79500</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="10" t="s">
-        <v>768</v>
+        <v>8</v>
       </c>
       <c r="B62" s="1">
-        <v>132500</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="5" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B63" s="1">
-        <v>116600</v>
+        <v>132500</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="18" t="s">
-        <v>127</v>
+        <v>769</v>
       </c>
       <c r="B64" s="1">
-        <v>63600</v>
+        <v>116600</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="10" t="s">
-        <v>13</v>
+        <v>127</v>
       </c>
       <c r="B65" s="1">
-        <v>31800</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="10" t="s">
-        <v>116</v>
+        <v>13</v>
       </c>
       <c r="B66" s="1">
-        <v>37100</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="5" t="s">
-        <v>14</v>
+        <v>116</v>
       </c>
       <c r="B67" s="1">
-        <v>68900</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="5" t="s">
-        <v>770</v>
+        <v>14</v>
       </c>
       <c r="B68" s="1">
-        <v>10600</v>
+        <v>68900</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="19" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B69" s="1">
-        <v>7950</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="5" t="s">
-        <v>426</v>
+        <v>771</v>
       </c>
       <c r="B70" s="1">
-        <v>21200</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="5" t="s">
-        <v>552</v>
+        <v>426</v>
       </c>
       <c r="B71" s="1">
-        <v>4240</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="9" t="s">
-        <v>497</v>
+        <v>552</v>
       </c>
       <c r="B72" s="1">
-        <v>31800</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="5" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B73" s="1">
-        <v>29150</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="5" t="s">
-        <v>772</v>
+        <v>498</v>
       </c>
       <c r="B74" s="1">
-        <v>37100</v>
+        <v>29150</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="11" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B75" s="1">
         <v>37100</v>
@@ -6518,15 +6529,15 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="20" t="s">
-        <v>586</v>
+        <v>773</v>
       </c>
       <c r="B76" s="1">
-        <v>5300</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="10" t="s">
-        <v>15</v>
+        <v>586</v>
       </c>
       <c r="B77" s="1">
         <v>5300</v>
@@ -6534,239 +6545,239 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B78" s="1">
-        <v>15900</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="5" t="s">
-        <v>580</v>
+        <v>16</v>
       </c>
       <c r="B79" s="1">
-        <v>7950</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="13" t="s">
-        <v>688</v>
+        <v>580</v>
       </c>
       <c r="B80" s="1">
-        <v>18550</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="5" t="s">
-        <v>774</v>
+        <v>688</v>
       </c>
       <c r="B81" s="1">
-        <v>2120</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="5" t="s">
-        <v>484</v>
+        <v>774</v>
       </c>
       <c r="B82" s="1">
-        <v>3180</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="5" t="s">
-        <v>775</v>
+        <v>484</v>
       </c>
       <c r="B83" s="1">
-        <v>53000</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="10" t="s">
-        <v>735</v>
+        <v>775</v>
       </c>
       <c r="B84" s="1">
-        <v>4240</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>3</v>
+        <v>735</v>
       </c>
       <c r="B85" s="1">
-        <v>63600</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="11" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B86" s="1">
-        <v>5300</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="17" t="s">
-        <v>128</v>
+        <v>17</v>
       </c>
       <c r="B87" s="1">
-        <v>10600</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="17" t="s">
-        <v>715</v>
+        <v>128</v>
       </c>
       <c r="B88" s="1">
-        <v>15900</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="17" t="s">
-        <v>499</v>
+        <v>715</v>
       </c>
       <c r="B89" s="1">
-        <v>37100</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="21" t="s">
-        <v>9</v>
+        <v>499</v>
       </c>
       <c r="B90" s="1">
-        <v>31800</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="5" t="s">
-        <v>623</v>
+        <v>9</v>
       </c>
       <c r="B91" s="1">
-        <v>280900</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="5" t="s">
-        <v>776</v>
+        <v>623</v>
       </c>
       <c r="B92" s="1">
-        <v>10600</v>
+        <v>275600</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="5" t="s">
-        <v>18</v>
+        <v>776</v>
       </c>
       <c r="B93" s="1">
-        <v>13250</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B94" s="1">
-        <v>7950</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="5" t="s">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="B95" s="1">
-        <v>5300</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="10" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B96" s="1">
-        <v>7950</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="5" t="s">
-        <v>25</v>
+        <v>501</v>
       </c>
       <c r="B97" s="1">
-        <v>5300</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="5" t="s">
-        <v>553</v>
+        <v>25</v>
       </c>
       <c r="B98" s="1">
-        <v>4240</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="22" t="s">
-        <v>777</v>
+        <v>553</v>
       </c>
       <c r="B99" s="1">
-        <v>23850</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B100" s="1">
-        <v>18550</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B101" s="1">
-        <v>21200</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="5" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B102" s="1">
-        <v>18550</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="5" t="s">
-        <v>129</v>
+        <v>780</v>
       </c>
       <c r="B103" s="1">
-        <v>106000</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="5" t="s">
-        <v>502</v>
+        <v>129</v>
       </c>
       <c r="B104" s="1">
-        <v>7950</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>781</v>
+        <v>502</v>
       </c>
       <c r="B105" s="1">
-        <v>23850</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>752</v>
+        <v>781</v>
       </c>
       <c r="B106" s="1">
-        <v>34450</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>723</v>
+        <v>752</v>
       </c>
       <c r="B107" s="1">
         <v>34450</v>
@@ -6774,7 +6785,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B108" s="1">
         <v>34450</v>
@@ -6782,7 +6793,7 @@
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B109" s="1">
         <v>34450</v>
@@ -6790,103 +6801,103 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>503</v>
+        <v>721</v>
       </c>
       <c r="B110" s="1">
-        <v>6360</v>
+        <v>34450</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="4" t="s">
-        <v>100</v>
+        <v>503</v>
       </c>
       <c r="B111" s="1">
-        <v>95400</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>654</v>
+        <v>100</v>
       </c>
       <c r="B112" s="1">
-        <v>185500</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>24</v>
+        <v>654</v>
       </c>
       <c r="B113" s="1">
-        <v>95400</v>
+        <v>185500</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>782</v>
+        <v>24</v>
       </c>
       <c r="B114" s="1">
-        <v>26500</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>740</v>
+        <v>782</v>
       </c>
       <c r="B115" s="1">
-        <v>116600</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>20</v>
+        <v>740</v>
       </c>
       <c r="B116" s="1">
-        <v>31800</v>
+        <v>116600</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>433</v>
+        <v>20</v>
       </c>
       <c r="B117" s="1">
-        <v>21200</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>783</v>
+        <v>433</v>
       </c>
       <c r="B118" s="1">
-        <v>63600</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>115</v>
+        <v>783</v>
       </c>
       <c r="B119" s="1">
-        <v>37100</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>504</v>
+        <v>115</v>
       </c>
       <c r="B120" s="1">
-        <v>10600</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B121" s="1">
-        <v>7950</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>784</v>
+        <v>505</v>
       </c>
       <c r="B122" s="1">
         <v>7950</v>
@@ -6894,7 +6905,7 @@
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>716</v>
+        <v>784</v>
       </c>
       <c r="B123" s="1">
         <v>7950</v>
@@ -6902,7 +6913,7 @@
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>785</v>
+        <v>716</v>
       </c>
       <c r="B124" s="1">
         <v>7950</v>
@@ -6910,31 +6921,31 @@
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>506</v>
+        <v>785</v>
       </c>
       <c r="B125" s="1">
-        <v>39750</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>21</v>
+        <v>506</v>
       </c>
       <c r="B126" s="1">
-        <v>26500</v>
+        <v>39750</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>756</v>
+        <v>21</v>
       </c>
       <c r="B127" s="1">
-        <v>79500</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>480</v>
+        <v>756</v>
       </c>
       <c r="B128" s="1">
         <v>79500</v>
@@ -6942,103 +6953,103 @@
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>786</v>
+        <v>480</v>
       </c>
       <c r="B129" s="1">
-        <v>68900</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B130" s="1">
-        <v>95400</v>
+        <v>68900</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B131" s="1">
-        <v>53000</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B132" s="1">
-        <v>47700</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>73</v>
+        <v>789</v>
       </c>
       <c r="B133" s="1">
-        <v>2650</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B134" s="1">
-        <v>5300</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>162</v>
+        <v>74</v>
       </c>
       <c r="B135" s="1">
-        <v>2650</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>790</v>
+        <v>162</v>
       </c>
       <c r="B136" s="1">
-        <v>39750</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>130</v>
+        <v>790</v>
       </c>
       <c r="B137" s="1">
-        <v>18550</v>
+        <v>39750</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>791</v>
+        <v>130</v>
       </c>
       <c r="B138" s="1">
-        <v>1590</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>709</v>
+        <v>791</v>
       </c>
       <c r="B139" s="1">
-        <v>7950</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>432</v>
+        <v>709</v>
       </c>
       <c r="B140" s="1">
-        <v>21200</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>507</v>
+        <v>432</v>
       </c>
       <c r="B141" s="1">
         <v>21200</v>
@@ -7046,55 +7057,55 @@
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B142" s="1">
-        <v>37100</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>437</v>
+        <v>508</v>
       </c>
       <c r="B143" s="1">
-        <v>10600</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>509</v>
+        <v>437</v>
       </c>
       <c r="B144" s="1">
-        <v>21200</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>792</v>
+        <v>509</v>
       </c>
       <c r="B145" s="1">
-        <v>5300</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>4</v>
+        <v>792</v>
       </c>
       <c r="B146" s="1">
-        <v>7950</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>793</v>
+        <v>4</v>
       </c>
       <c r="B147" s="1">
-        <v>5300</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>650</v>
+        <v>793</v>
       </c>
       <c r="B148" s="1">
         <v>5300</v>
@@ -7102,23 +7113,23 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B149" s="1">
-        <v>2650</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>588</v>
+        <v>651</v>
       </c>
       <c r="B150" s="1">
-        <v>4240</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>554</v>
+        <v>588</v>
       </c>
       <c r="B151" s="1">
         <v>4240</v>
@@ -7126,71 +7137,71 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>510</v>
+        <v>554</v>
       </c>
       <c r="B152" s="1">
-        <v>15900</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>403</v>
+        <v>510</v>
       </c>
       <c r="B153" s="1">
-        <v>4240</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>546</v>
+        <v>403</v>
       </c>
       <c r="B154" s="1">
-        <v>6360</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>441</v>
+        <v>546</v>
       </c>
       <c r="B155" s="1">
-        <v>7950</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>556</v>
+        <v>441</v>
       </c>
       <c r="B156" s="1">
-        <v>10600</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B157" s="1">
-        <v>5300</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>794</v>
+        <v>557</v>
       </c>
       <c r="B158" s="1">
-        <v>7950</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>435</v>
+        <v>794</v>
       </c>
       <c r="B159" s="1">
-        <v>5300</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>795</v>
+        <v>435</v>
       </c>
       <c r="B160" s="1">
         <v>5300</v>
@@ -7198,33 +7209,41 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B161" s="1">
-        <v>6360</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>624</v>
+        <v>796</v>
       </c>
       <c r="B162" s="1">
-        <v>53000</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>10</v>
+        <v>624</v>
       </c>
       <c r="B163" s="1">
-        <v>18550</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
+        <v>10</v>
+      </c>
+      <c r="B164" s="1">
+        <v>18550</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" t="s">
         <v>797</v>
       </c>
-      <c r="B164" s="1">
+      <c r="B165" s="1">
         <v>5300</v>
       </c>
     </row>
@@ -7235,7 +7254,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B260"/>
+  <dimension ref="A1:B261"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="83.85546875" bestFit="1" customWidth="1"/>
@@ -7388,23 +7407,23 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="27" t="s">
-        <v>430</v>
+        <v>823</v>
       </c>
       <c r="B19" s="1">
-        <v>42400</v>
+        <v>45050</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="17" t="s">
-        <v>163</v>
+        <v>430</v>
       </c>
       <c r="B20" s="1">
-        <v>53000</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="17" t="s">
-        <v>647</v>
+        <v>163</v>
       </c>
       <c r="B21" s="1">
         <v>53000</v>
@@ -7412,39 +7431,39 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>581</v>
+        <v>647</v>
       </c>
       <c r="B22" s="1">
-        <v>58300</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="17" t="s">
-        <v>648</v>
+        <v>581</v>
       </c>
       <c r="B23" s="1">
-        <v>63600</v>
+        <v>58300</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>83</v>
+        <v>648</v>
       </c>
       <c r="B24" s="1">
-        <v>13250</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="26" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="B25" s="1">
-        <v>21200</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="17" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B26" s="1">
         <v>21200</v>
@@ -7452,15 +7471,15 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="17" t="s">
-        <v>121</v>
+        <v>22</v>
       </c>
       <c r="B27" s="1">
-        <v>31800</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="B28" s="1">
         <v>31800</v>
@@ -7468,31 +7487,31 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="17" t="s">
-        <v>698</v>
+        <v>134</v>
       </c>
       <c r="B29" s="1">
-        <v>15900</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="17" t="s">
-        <v>37</v>
+        <v>698</v>
       </c>
       <c r="B30" s="1">
-        <v>42400</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="17" t="s">
-        <v>477</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1">
-        <v>31800</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="17" t="s">
-        <v>38</v>
+        <v>477</v>
       </c>
       <c r="B32" s="1">
         <v>31800</v>
@@ -7500,31 +7519,31 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="17" t="s">
-        <v>158</v>
+        <v>38</v>
       </c>
       <c r="B33" s="1">
-        <v>53000</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="17" t="s">
-        <v>34</v>
+        <v>158</v>
       </c>
       <c r="B34" s="1">
-        <v>23850</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="17" t="s">
-        <v>692</v>
+        <v>34</v>
       </c>
       <c r="B35" s="1">
-        <v>530</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="17" t="s">
-        <v>406</v>
+        <v>692</v>
       </c>
       <c r="B36" s="1">
         <v>530</v>
@@ -7532,7 +7551,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="17" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B37" s="1">
         <v>530</v>
@@ -7540,15 +7559,15 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="28" t="s">
-        <v>626</v>
+        <v>402</v>
       </c>
       <c r="B38" s="1">
-        <v>63600</v>
+        <v>530</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="17" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B39" s="1">
         <v>63600</v>
@@ -7556,15 +7575,15 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="17" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B40" s="1">
-        <v>53000</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="17" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B41" s="1">
         <v>53000</v>
@@ -7572,23 +7591,23 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="26" t="s">
-        <v>511</v>
+        <v>629</v>
       </c>
       <c r="B42" s="1">
-        <v>5300</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="17" t="s">
-        <v>85</v>
+        <v>511</v>
       </c>
       <c r="B43" s="1">
-        <v>42400</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B44" s="1">
         <v>42400</v>
@@ -7596,7 +7615,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B45" s="1">
         <v>42400</v>
@@ -7604,15 +7623,15 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="25" t="s">
-        <v>135</v>
+        <v>86</v>
       </c>
       <c r="B46" s="1">
-        <v>5300</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B47" s="1">
         <v>5300</v>
@@ -7620,23 +7639,23 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="17" t="s">
-        <v>87</v>
+        <v>136</v>
       </c>
       <c r="B48" s="1">
-        <v>2650</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="28" t="s">
-        <v>444</v>
+        <v>87</v>
       </c>
       <c r="B49" s="1">
-        <v>3710</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="17" t="s">
-        <v>512</v>
+        <v>444</v>
       </c>
       <c r="B50" s="1">
         <v>3710</v>
@@ -7644,143 +7663,143 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="17" t="s">
-        <v>137</v>
+        <v>512</v>
       </c>
       <c r="B51" s="1">
-        <v>15900</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="17" t="s">
-        <v>513</v>
+        <v>137</v>
       </c>
       <c r="B52" s="1">
-        <v>21200</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="17" t="s">
-        <v>451</v>
+        <v>513</v>
       </c>
       <c r="B53" s="1">
-        <v>42400</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="27" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B54" s="1">
-        <v>47700</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="17" t="s">
-        <v>138</v>
+        <v>452</v>
       </c>
       <c r="B55" s="1">
-        <v>13250</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="17" t="s">
-        <v>699</v>
+        <v>138</v>
       </c>
       <c r="B56" s="1">
-        <v>15900</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="17" t="s">
-        <v>583</v>
+        <v>699</v>
       </c>
       <c r="B57" s="1">
-        <v>53000</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="17" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B58" s="1">
-        <v>39750</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="17" t="s">
-        <v>139</v>
+        <v>584</v>
       </c>
       <c r="B59" s="1">
-        <v>21200</v>
+        <v>39750</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="17" t="s">
-        <v>551</v>
+        <v>139</v>
       </c>
       <c r="B60" s="1">
-        <v>7950</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="17" t="s">
-        <v>140</v>
+        <v>551</v>
       </c>
       <c r="B61" s="1">
-        <v>13250</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="17" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="B62" s="1">
-        <v>15900</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B63" s="1">
-        <v>31800</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="17" t="s">
-        <v>559</v>
+        <v>88</v>
       </c>
       <c r="B64" s="1">
-        <v>15900</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="17" t="s">
-        <v>722</v>
+        <v>559</v>
       </c>
       <c r="B65" s="1">
-        <v>26500</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="17" t="s">
-        <v>118</v>
+        <v>722</v>
       </c>
       <c r="B66" s="1">
-        <v>18550</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="17" t="s">
-        <v>799</v>
+        <v>118</v>
       </c>
       <c r="B67" s="1">
-        <v>84800</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="17" t="s">
-        <v>39</v>
+        <v>799</v>
       </c>
       <c r="B68" s="1">
         <v>84800</v>
@@ -7788,7 +7807,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B69" s="1">
         <v>84800</v>
@@ -7796,7 +7815,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="17" t="s">
-        <v>800</v>
+        <v>40</v>
       </c>
       <c r="B70" s="1">
         <v>84800</v>
@@ -7804,39 +7823,39 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>120</v>
+        <v>800</v>
       </c>
       <c r="B71" s="1">
-        <v>15900</v>
+        <v>84800</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>41</v>
+        <v>120</v>
       </c>
       <c r="B72" s="1">
-        <v>7950</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B73" s="1">
-        <v>10600</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B74" s="1">
-        <v>21200</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B75" s="1">
         <v>21200</v>
@@ -7844,47 +7863,47 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B76" s="1">
-        <v>79500</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B77" s="1">
-        <v>106000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="17" t="s">
-        <v>687</v>
+        <v>46</v>
       </c>
       <c r="B78" s="1">
-        <v>53000</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="29" t="s">
-        <v>90</v>
+        <v>687</v>
       </c>
       <c r="B79" s="1">
-        <v>26500</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="17" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="B80" s="1">
-        <v>53000</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="17" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B81" s="1">
         <v>53000</v>
@@ -7892,15 +7911,15 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="17" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B82" s="1">
-        <v>84800</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="17" t="s">
-        <v>141</v>
+        <v>33</v>
       </c>
       <c r="B83" s="1">
         <v>84800</v>
@@ -7908,15 +7927,15 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="17" t="s">
-        <v>49</v>
+        <v>141</v>
       </c>
       <c r="B84" s="1">
-        <v>132500</v>
+        <v>84800</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B85" s="1">
         <v>132500</v>
@@ -7924,23 +7943,23 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B86" s="1">
-        <v>121900</v>
+        <v>132500</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="17" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B87" s="1">
-        <v>132500</v>
+        <v>121900</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B88" s="1">
         <v>132500</v>
@@ -7948,7 +7967,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="17" t="s">
-        <v>474</v>
+        <v>51</v>
       </c>
       <c r="B89" s="1">
         <v>132500</v>
@@ -7956,31 +7975,31 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="17" t="s">
-        <v>55</v>
+        <v>474</v>
       </c>
       <c r="B90" s="1">
-        <v>79500</v>
+        <v>132500</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="17" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B91" s="1">
-        <v>106000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B92" s="1">
-        <v>116600</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B93" s="1">
         <v>116600</v>
@@ -7988,7 +8007,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B94" s="1">
         <v>116600</v>
@@ -7996,15 +8015,15 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="17" t="s">
-        <v>475</v>
+        <v>56</v>
       </c>
       <c r="B95" s="1">
-        <v>37100</v>
+        <v>116600</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="17" t="s">
-        <v>514</v>
+        <v>475</v>
       </c>
       <c r="B96" s="1">
         <v>37100</v>
@@ -8012,23 +8031,23 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="17" t="s">
-        <v>700</v>
+        <v>514</v>
       </c>
       <c r="B97" s="1">
-        <v>31800</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="17" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B98" s="1">
-        <v>37100</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="30" t="s">
-        <v>142</v>
+        <v>701</v>
       </c>
       <c r="B99" s="1">
         <v>37100</v>
@@ -8036,15 +8055,15 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="17" t="s">
-        <v>801</v>
+        <v>142</v>
       </c>
       <c r="B100" s="1">
-        <v>74200</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="17" t="s">
-        <v>544</v>
+        <v>801</v>
       </c>
       <c r="B101" s="1">
         <v>74200</v>
@@ -8052,63 +8071,63 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="31" t="s">
-        <v>802</v>
+        <v>544</v>
       </c>
       <c r="B102" s="1">
-        <v>95400</v>
+        <v>74200</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>643</v>
+        <v>802</v>
       </c>
       <c r="B103" s="1">
-        <v>4240</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="17" t="s">
-        <v>515</v>
+        <v>643</v>
       </c>
       <c r="B104" s="1">
-        <v>13250</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="17" t="s">
-        <v>428</v>
+        <v>515</v>
       </c>
       <c r="B105" s="1">
-        <v>26500</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="17" t="s">
-        <v>693</v>
+        <v>428</v>
       </c>
       <c r="B106" s="1">
-        <v>13250</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="17" t="s">
-        <v>552</v>
+        <v>693</v>
       </c>
       <c r="B107" s="1">
-        <v>4240</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="17" t="s">
-        <v>702</v>
+        <v>552</v>
       </c>
       <c r="B108" s="1">
-        <v>31800</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="17" t="s">
-        <v>93</v>
+        <v>702</v>
       </c>
       <c r="B109" s="1">
         <v>31800</v>
@@ -8116,7 +8135,7 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B110" s="1">
         <v>31800</v>
@@ -8124,39 +8143,39 @@
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B111" s="1">
-        <v>63600</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B112" s="1">
-        <v>79500</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>585</v>
+        <v>94</v>
       </c>
       <c r="B113" s="1">
-        <v>5300</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>646</v>
+        <v>585</v>
       </c>
       <c r="B114" s="1">
-        <v>7950</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="17" t="s">
-        <v>560</v>
+        <v>646</v>
       </c>
       <c r="B115" s="1">
         <v>7950</v>
@@ -8164,15 +8183,15 @@
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="17" t="s">
-        <v>57</v>
+        <v>560</v>
       </c>
       <c r="B116" s="1">
-        <v>5300</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B117" s="1">
         <v>5300</v>
@@ -8180,15 +8199,15 @@
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="27" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B118" s="1">
-        <v>7950</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="17" t="s">
-        <v>561</v>
+        <v>59</v>
       </c>
       <c r="B119" s="1">
         <v>7950</v>
@@ -8196,31 +8215,31 @@
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="17" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B120" s="1">
-        <v>10600</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>677</v>
+        <v>562</v>
       </c>
       <c r="B121" s="1">
-        <v>6360</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="17" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="B122" s="1">
-        <v>18550</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="17" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B123" s="1">
         <v>18550</v>
@@ -8228,31 +8247,31 @@
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="17" t="s">
-        <v>484</v>
+        <v>686</v>
       </c>
       <c r="B124" s="1">
-        <v>3180</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="17" t="s">
-        <v>735</v>
+        <v>484</v>
       </c>
       <c r="B125" s="1">
-        <v>4240</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="17" t="s">
-        <v>60</v>
+        <v>735</v>
       </c>
       <c r="B126" s="1">
-        <v>13250</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B127" s="1">
         <v>13250</v>
@@ -8260,15 +8279,15 @@
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="17" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="B128" s="1">
-        <v>10600</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="17" t="s">
-        <v>62</v>
+        <v>157</v>
       </c>
       <c r="B129" s="1">
         <v>10600</v>
@@ -8276,15 +8295,15 @@
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="17" t="s">
-        <v>754</v>
+        <v>62</v>
       </c>
       <c r="B130" s="1">
-        <v>5300</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="17" t="s">
-        <v>694</v>
+        <v>754</v>
       </c>
       <c r="B131" s="1">
         <v>5300</v>
@@ -8292,23 +8311,23 @@
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="17" t="s">
-        <v>563</v>
+        <v>694</v>
       </c>
       <c r="B132" s="1">
-        <v>74200</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="28" t="s">
-        <v>697</v>
+        <v>563</v>
       </c>
       <c r="B133" s="1">
-        <v>31800</v>
+        <v>74200</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="17" t="s">
-        <v>455</v>
+        <v>697</v>
       </c>
       <c r="B134" s="1">
         <v>31800</v>
@@ -8316,47 +8335,47 @@
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="33" t="s">
-        <v>623</v>
+        <v>455</v>
       </c>
       <c r="B135" s="1">
-        <v>280900</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="17" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="B136" s="1">
-        <v>291500</v>
+        <v>275600</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="17" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B137" s="1">
-        <v>302100</v>
+        <v>291500</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="17" t="s">
-        <v>449</v>
+        <v>631</v>
       </c>
       <c r="B138" s="1">
-        <v>10600</v>
+        <v>302100</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="17" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B139" s="1">
-        <v>7950</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B140" s="1">
         <v>7950</v>
@@ -8364,31 +8383,31 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="17" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B141" s="1">
-        <v>13250</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="17" t="s">
-        <v>143</v>
+        <v>447</v>
       </c>
       <c r="B142" s="1">
-        <v>5300</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="17" t="s">
-        <v>446</v>
+        <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>7950</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="17" t="s">
-        <v>144</v>
+        <v>446</v>
       </c>
       <c r="B144" s="1">
         <v>7950</v>
@@ -8396,23 +8415,23 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="17" t="s">
-        <v>591</v>
+        <v>144</v>
       </c>
       <c r="B145" s="1">
-        <v>5300</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="17" t="s">
-        <v>96</v>
+        <v>591</v>
       </c>
       <c r="B146" s="1">
-        <v>7950</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B147" s="1">
         <v>7950</v>
@@ -8420,7 +8439,7 @@
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B148" s="1">
         <v>7950</v>
@@ -8428,55 +8447,55 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="17" t="s">
-        <v>553</v>
+        <v>97</v>
       </c>
       <c r="B149" s="1">
-        <v>4240</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="17" t="s">
-        <v>803</v>
+        <v>553</v>
       </c>
       <c r="B150" s="1">
-        <v>23850</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B151" s="1">
-        <v>18550</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="17" t="s">
-        <v>145</v>
+        <v>804</v>
       </c>
       <c r="B152" s="1">
-        <v>132500</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="B153" s="1">
-        <v>106000</v>
+        <v>132500</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="17" t="s">
-        <v>703</v>
+        <v>119</v>
       </c>
       <c r="B154" s="1">
-        <v>39750</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="17" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B155" s="1">
         <v>39750</v>
@@ -8484,15 +8503,15 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="17" t="s">
-        <v>98</v>
+        <v>704</v>
       </c>
       <c r="B156" s="1">
-        <v>79500</v>
+        <v>39750</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="17" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="B157" s="1">
         <v>79500</v>
@@ -8500,87 +8519,87 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="17" t="s">
-        <v>472</v>
+        <v>63</v>
       </c>
       <c r="B158" s="1">
-        <v>74200</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="17" t="s">
-        <v>99</v>
+        <v>472</v>
       </c>
       <c r="B159" s="1">
-        <v>63600</v>
+        <v>74200</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="17" t="s">
-        <v>720</v>
+        <v>99</v>
       </c>
       <c r="B160" s="1">
-        <v>34450</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="17" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B161" s="1">
-        <v>39750</v>
+        <v>34450</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="17" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B162" s="1">
-        <v>34450</v>
+        <v>39750</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="17" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="B163" s="1">
-        <v>42400</v>
+        <v>34450</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="17" t="s">
-        <v>695</v>
+        <v>725</v>
       </c>
       <c r="B164" s="1">
-        <v>795</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="30" t="s">
-        <v>101</v>
+        <v>695</v>
       </c>
       <c r="B165" s="1">
-        <v>106000</v>
+        <v>795</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B166" s="1">
-        <v>121900</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B167" s="1">
-        <v>185500</v>
+        <v>121900</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="17" t="s">
-        <v>632</v>
+        <v>103</v>
       </c>
       <c r="B168" s="1">
         <v>185500</v>
@@ -8588,31 +8607,31 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="17" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B169" s="1">
-        <v>190800</v>
+        <v>185500</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="17" t="s">
-        <v>678</v>
+        <v>633</v>
       </c>
       <c r="B170" s="1">
-        <v>196100</v>
+        <v>190800</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="17" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B171" s="1">
-        <v>185500</v>
+        <v>196100</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="17" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B172" s="1">
         <v>185500</v>
@@ -8620,7 +8639,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B173" s="1">
         <v>185500</v>
@@ -8628,23 +8647,23 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="17" t="s">
-        <v>740</v>
+        <v>681</v>
       </c>
       <c r="B174" s="1">
-        <v>116600</v>
+        <v>185500</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="17" t="s">
-        <v>23</v>
+        <v>740</v>
       </c>
       <c r="B175" s="1">
-        <v>95400</v>
+        <v>116600</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="17" t="s">
-        <v>442</v>
+        <v>23</v>
       </c>
       <c r="B176" s="1">
         <v>95400</v>
@@ -8652,23 +8671,23 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="17" t="s">
-        <v>564</v>
+        <v>442</v>
       </c>
       <c r="B177" s="1">
-        <v>106000</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="17" t="s">
-        <v>146</v>
+        <v>564</v>
       </c>
       <c r="B178" s="1">
-        <v>21200</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B179" s="1">
         <v>21200</v>
@@ -8676,7 +8695,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="34" t="s">
-        <v>755</v>
+        <v>147</v>
       </c>
       <c r="B180" s="1">
         <v>21200</v>
@@ -8684,7 +8703,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>705</v>
+        <v>755</v>
       </c>
       <c r="B181" s="1">
         <v>21200</v>
@@ -8692,199 +8711,199 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>652</v>
+        <v>705</v>
       </c>
       <c r="B182" s="1">
-        <v>37100</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="17" t="s">
-        <v>805</v>
+        <v>652</v>
       </c>
       <c r="B183" s="1">
-        <v>63600</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="17" t="s">
-        <v>748</v>
+        <v>805</v>
       </c>
       <c r="B184" s="1">
-        <v>31800</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="17" t="s">
-        <v>148</v>
+        <v>748</v>
       </c>
       <c r="B185" s="1">
-        <v>37100</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="17" t="s">
-        <v>706</v>
+        <v>148</v>
       </c>
       <c r="B186" s="1">
-        <v>47700</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="17" t="s">
-        <v>516</v>
+        <v>706</v>
       </c>
       <c r="B187" s="1">
-        <v>10600</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" t="s">
-        <v>749</v>
+        <v>516</v>
       </c>
       <c r="B188" s="1">
-        <v>15900</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" t="s">
-        <v>149</v>
+        <v>749</v>
       </c>
       <c r="B189" s="1">
-        <v>31800</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
-        <v>565</v>
+        <v>149</v>
       </c>
       <c r="B190" s="1">
-        <v>18550</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" t="s">
-        <v>707</v>
+        <v>565</v>
       </c>
       <c r="B191" s="1">
-        <v>7950</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" t="s">
-        <v>150</v>
+        <v>707</v>
       </c>
       <c r="B192" s="1">
-        <v>23850</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="B193" s="1">
-        <v>13250</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
-        <v>517</v>
+        <v>104</v>
       </c>
       <c r="B194" s="1">
-        <v>39750</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" t="s">
-        <v>151</v>
+        <v>517</v>
       </c>
       <c r="B195" s="1">
-        <v>23850</v>
+        <v>39750</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" t="s">
-        <v>481</v>
+        <v>151</v>
       </c>
       <c r="B196" s="1">
-        <v>79500</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" t="s">
-        <v>708</v>
+        <v>481</v>
       </c>
       <c r="B197" s="1">
-        <v>90100</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" t="s">
-        <v>64</v>
+        <v>708</v>
       </c>
       <c r="B198" s="1">
-        <v>84800</v>
+        <v>90100</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" t="s">
-        <v>152</v>
+        <v>64</v>
       </c>
       <c r="B199" s="1">
-        <v>79500</v>
+        <v>84800</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" t="s">
-        <v>65</v>
+        <v>152</v>
       </c>
       <c r="B200" s="1">
-        <v>106000</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" s="4" t="s">
-        <v>545</v>
+        <v>65</v>
       </c>
       <c r="B201" s="1">
-        <v>74200</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B202" s="1">
-        <v>95400</v>
+        <v>74200</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" t="s">
-        <v>66</v>
+        <v>547</v>
       </c>
       <c r="B203" s="1">
-        <v>68900</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B204" s="1">
-        <v>42400</v>
+        <v>68900</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B205" s="1">
-        <v>53000</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="206" spans="1:2">
       <c r="A206" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B206" s="1">
         <v>53000</v>
@@ -8892,87 +8911,87 @@
     </row>
     <row r="207" spans="1:2">
       <c r="A207" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B207" s="1">
-        <v>63600</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B208" s="1">
-        <v>53000</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B209" s="1">
-        <v>63600</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="210" spans="1:2">
       <c r="A210" t="s">
-        <v>473</v>
+        <v>72</v>
       </c>
       <c r="B210" s="1">
-        <v>95400</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" t="s">
-        <v>160</v>
+        <v>473</v>
       </c>
       <c r="B211" s="1">
-        <v>2650</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B212" s="1">
-        <v>5300</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="213" spans="1:2">
       <c r="A213" t="s">
-        <v>75</v>
+        <v>161</v>
       </c>
       <c r="B213" s="1">
-        <v>4240</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214" t="s">
-        <v>159</v>
+        <v>75</v>
       </c>
       <c r="B214" s="1">
-        <v>2650</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" t="s">
-        <v>107</v>
+        <v>159</v>
       </c>
       <c r="B215" s="1">
-        <v>132500</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="216" spans="1:2">
       <c r="A216" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B216" s="1">
-        <v>106000</v>
+        <v>132500</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B217" s="1">
         <v>106000</v>
@@ -8980,15 +8999,15 @@
     </row>
     <row r="218" spans="1:2">
       <c r="A218" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B218" s="1">
-        <v>79500</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="219" spans="1:2">
       <c r="A219" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B219" s="1">
         <v>79500</v>
@@ -8996,15 +9015,15 @@
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B220" s="1">
-        <v>95400</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="221" spans="1:2">
       <c r="A221" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B221" s="1">
         <v>95400</v>
@@ -9012,15 +9031,15 @@
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="B222" s="1">
-        <v>18550</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B223" s="1">
         <v>18550</v>
@@ -9028,31 +9047,31 @@
     </row>
     <row r="224" spans="1:2">
       <c r="A224" t="s">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="B224" s="1">
-        <v>15900</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B225" s="1">
-        <v>21200</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="226" spans="1:2">
       <c r="A226" t="s">
-        <v>714</v>
+        <v>77</v>
       </c>
       <c r="B226" s="1">
-        <v>15900</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227" t="s">
-        <v>78</v>
+        <v>714</v>
       </c>
       <c r="B227" s="1">
         <v>15900</v>
@@ -9060,15 +9079,15 @@
     </row>
     <row r="228" spans="1:2">
       <c r="A228" t="s">
-        <v>443</v>
+        <v>78</v>
       </c>
       <c r="B228" s="1">
-        <v>21200</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229" t="s">
-        <v>79</v>
+        <v>443</v>
       </c>
       <c r="B229" s="1">
         <v>21200</v>
@@ -9076,7 +9095,7 @@
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>518</v>
+        <v>79</v>
       </c>
       <c r="B230" s="1">
         <v>21200</v>
@@ -9084,7 +9103,7 @@
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>80</v>
+        <v>518</v>
       </c>
       <c r="B231" s="1">
         <v>21200</v>
@@ -9092,7 +9111,7 @@
     </row>
     <row r="232" spans="1:2">
       <c r="A232" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B232" s="1">
         <v>21200</v>
@@ -9100,23 +9119,23 @@
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>519</v>
+        <v>81</v>
       </c>
       <c r="B233" s="1">
-        <v>18550</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="234" spans="1:2">
       <c r="A234" t="s">
-        <v>113</v>
+        <v>519</v>
       </c>
       <c r="B234" s="1">
-        <v>10600</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B235" s="1">
         <v>10600</v>
@@ -9124,15 +9143,15 @@
     </row>
     <row r="236" spans="1:2">
       <c r="A236" t="s">
-        <v>453</v>
+        <v>114</v>
       </c>
       <c r="B236" s="1">
-        <v>37100</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="237" spans="1:2">
       <c r="A237" t="s">
-        <v>710</v>
+        <v>453</v>
       </c>
       <c r="B237" s="1">
         <v>37100</v>
@@ -9140,31 +9159,31 @@
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
-        <v>750</v>
+        <v>710</v>
       </c>
       <c r="B238" s="1">
-        <v>7950</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="B239" s="1">
-        <v>5300</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" t="s">
-        <v>588</v>
+        <v>650</v>
       </c>
       <c r="B240" s="1">
-        <v>4240</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="241" spans="1:2">
       <c r="A241" t="s">
-        <v>555</v>
+        <v>588</v>
       </c>
       <c r="B241" s="1">
         <v>4240</v>
@@ -9172,71 +9191,71 @@
     </row>
     <row r="242" spans="1:2">
       <c r="A242" t="s">
-        <v>117</v>
+        <v>555</v>
       </c>
       <c r="B242" s="1">
-        <v>15900</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="243" spans="1:2">
       <c r="A243" t="s">
-        <v>403</v>
+        <v>117</v>
       </c>
       <c r="B243" s="1">
-        <v>4240</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>546</v>
+        <v>403</v>
       </c>
       <c r="B244" s="1">
-        <v>6360</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="245" spans="1:2">
       <c r="A245" t="s">
-        <v>568</v>
+        <v>546</v>
       </c>
       <c r="B245" s="1">
-        <v>10600</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="246" spans="1:2">
       <c r="A246" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B246" s="1">
-        <v>15900</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="247" spans="1:2">
       <c r="A247" t="s">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="B247" s="1">
-        <v>10600</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="248" spans="1:2">
       <c r="A248" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B248" s="1">
-        <v>5300</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="249" spans="1:2">
       <c r="A249" t="s">
-        <v>634</v>
+        <v>557</v>
       </c>
       <c r="B249" s="1">
-        <v>7950</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
-        <v>711</v>
+        <v>634</v>
       </c>
       <c r="B250" s="1">
         <v>7950</v>
@@ -9244,81 +9263,89 @@
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B251" s="1">
-        <v>10600</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="252" spans="1:2">
       <c r="A252" t="s">
-        <v>558</v>
+        <v>712</v>
       </c>
       <c r="B252" s="1">
-        <v>1590</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>635</v>
+        <v>558</v>
       </c>
       <c r="B253" s="1">
-        <v>121900</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="254" spans="1:2">
       <c r="A254" t="s">
-        <v>713</v>
+        <v>635</v>
       </c>
       <c r="B254" s="1">
-        <v>10600</v>
+        <v>121900</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>794</v>
+        <v>713</v>
       </c>
       <c r="B255" s="1">
-        <v>7950</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>445</v>
+        <v>794</v>
       </c>
       <c r="B256" s="1">
-        <v>5300</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>682</v>
+        <v>445</v>
       </c>
       <c r="B257" s="1">
-        <v>53000</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
-        <v>112</v>
+        <v>682</v>
       </c>
       <c r="B258" s="1">
-        <v>31800</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
-        <v>155</v>
+        <v>112</v>
       </c>
       <c r="B259" s="1">
-        <v>18550</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="260" spans="1:2">
       <c r="A260" t="s">
+        <v>155</v>
+      </c>
+      <c r="B260" s="1">
+        <v>18550</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" t="s">
         <v>156</v>
       </c>
-      <c r="B260" s="1">
+      <c r="B261" s="1">
         <v>21200</v>
       </c>
     </row>
@@ -9613,7 +9640,7 @@
         <v>631</v>
       </c>
       <c r="B35">
-        <v>302100</v>
+        <v>291500</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -9863,7 +9890,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="58.140625" customWidth="1"/>
@@ -10008,47 +10035,47 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>663</v>
+        <v>823</v>
       </c>
       <c r="B18" s="1">
-        <v>92750</v>
+        <v>45050</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="B19" s="1">
-        <v>103350</v>
+        <v>92750</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B20" s="1">
-        <v>116600</v>
+        <v>103350</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>430</v>
+        <v>656</v>
       </c>
       <c r="B21" s="1">
-        <v>42400</v>
+        <v>116600</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>163</v>
+        <v>430</v>
       </c>
       <c r="B22" s="1">
-        <v>53000</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>647</v>
+        <v>163</v>
       </c>
       <c r="B23" s="1">
         <v>53000</v>
@@ -10056,55 +10083,55 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>581</v>
+        <v>647</v>
       </c>
       <c r="B24" s="1">
-        <v>58300</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>648</v>
+        <v>581</v>
       </c>
       <c r="B25" s="1">
-        <v>63600</v>
+        <v>58300</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="B26" s="1">
-        <v>71550</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B27" s="1">
-        <v>84800</v>
+        <v>71550</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="B28" s="1">
-        <v>90100</v>
+        <v>84800</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>692</v>
+        <v>664</v>
       </c>
       <c r="B29" s="1">
-        <v>530</v>
+        <v>90100</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>406</v>
+        <v>692</v>
       </c>
       <c r="B30" s="1">
         <v>530</v>
@@ -10112,7 +10139,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B31" s="1">
         <v>530</v>
@@ -10120,47 +10147,47 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>429</v>
+        <v>402</v>
       </c>
       <c r="B32" s="1">
-        <v>1590</v>
+        <v>530</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>551</v>
+        <v>429</v>
       </c>
       <c r="B33" s="1">
-        <v>7950</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>390</v>
+        <v>551</v>
       </c>
       <c r="B34" s="1">
-        <v>3180</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>552</v>
+        <v>390</v>
       </c>
       <c r="B35" s="1">
-        <v>4240</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>820</v>
+        <v>552</v>
       </c>
       <c r="B36" s="1">
-        <v>2650</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>404</v>
+        <v>820</v>
       </c>
       <c r="B37" s="1">
         <v>2650</v>
@@ -10168,39 +10195,39 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>259</v>
+        <v>404</v>
       </c>
       <c r="B38" s="1">
-        <v>15900</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>425</v>
+        <v>259</v>
       </c>
       <c r="B39" s="1">
-        <v>2120</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>484</v>
+        <v>425</v>
       </c>
       <c r="B40" s="1">
-        <v>3180</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>735</v>
+        <v>484</v>
       </c>
       <c r="B41" s="1">
-        <v>4240</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>391</v>
+        <v>735</v>
       </c>
       <c r="B42" s="1">
         <v>4240</v>
@@ -10208,95 +10235,95 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B43" s="1">
-        <v>3710</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B44" s="1">
-        <v>7950</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>638</v>
+        <v>393</v>
       </c>
       <c r="B45" s="1">
-        <v>3180</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>394</v>
+        <v>638</v>
       </c>
       <c r="B46" s="1">
-        <v>5300</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B47" s="1">
-        <v>4240</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B48" s="1">
-        <v>3710</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>728</v>
+        <v>396</v>
       </c>
       <c r="B49" s="1">
-        <v>2650</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>553</v>
+        <v>728</v>
       </c>
       <c r="B50" s="1">
-        <v>4240</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>718</v>
+        <v>553</v>
       </c>
       <c r="B51" s="1">
-        <v>29150</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B52" s="1">
-        <v>31800</v>
+        <v>29150</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>752</v>
+        <v>719</v>
       </c>
       <c r="B53" s="1">
-        <v>34450</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>723</v>
+        <v>752</v>
       </c>
       <c r="B54" s="1">
         <v>34450</v>
@@ -10304,7 +10331,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B55" s="1">
         <v>34450</v>
@@ -10312,87 +10339,87 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B56" s="1">
-        <v>39750</v>
+        <v>34450</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B57" s="1">
-        <v>34450</v>
+        <v>39750</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="B58" s="1">
-        <v>42400</v>
+        <v>34450</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B59" s="1">
-        <v>45050</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B60" s="1">
-        <v>47700</v>
+        <v>45050</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="B61" s="1">
-        <v>116600</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>639</v>
+        <v>740</v>
       </c>
       <c r="B62" s="1">
-        <v>5300</v>
+        <v>116600</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>543</v>
+        <v>639</v>
       </c>
       <c r="B63" s="1">
-        <v>7950</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>397</v>
+        <v>543</v>
       </c>
       <c r="B64" s="1">
-        <v>9540</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>653</v>
+        <v>397</v>
       </c>
       <c r="B65" s="1">
-        <v>5300</v>
+        <v>9540</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>398</v>
+        <v>653</v>
       </c>
       <c r="B66" s="1">
         <v>5300</v>
@@ -10400,23 +10427,23 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B67" s="1">
-        <v>2650</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B68" s="1">
-        <v>3710</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>582</v>
+        <v>400</v>
       </c>
       <c r="B69" s="1">
         <v>3710</v>
@@ -10424,23 +10451,23 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>401</v>
+        <v>582</v>
       </c>
       <c r="B70" s="1">
-        <v>5300</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>588</v>
+        <v>401</v>
       </c>
       <c r="B71" s="1">
-        <v>4240</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>554</v>
+        <v>588</v>
       </c>
       <c r="B72" s="1">
         <v>4240</v>
@@ -10448,7 +10475,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B73" s="1">
         <v>4240</v>
@@ -10456,57 +10483,65 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>644</v>
+        <v>555</v>
       </c>
       <c r="B74" s="1">
-        <v>3710</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B75" s="1">
-        <v>2650</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>403</v>
+        <v>645</v>
       </c>
       <c r="B76" s="1">
-        <v>4240</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>546</v>
+        <v>403</v>
       </c>
       <c r="B77" s="1">
-        <v>6360</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="B78" s="1">
-        <v>10600</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B79" s="1">
-        <v>5300</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
+        <v>557</v>
+      </c>
+      <c r="B80" s="1">
+        <v>5300</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
         <v>558</v>
       </c>
-      <c r="B80" s="1">
+      <c r="B81" s="1">
         <v>1590</v>
       </c>
     </row>
